--- a/output/2024-10-08.xlsx
+++ b/output/2024-10-08.xlsx
@@ -625,34 +625,34 @@
         <v>1</v>
       </c>
       <c r="E14" t="n">
-        <v>3.66</v>
+        <v>3.64</v>
       </c>
       <c r="F14" t="n">
-        <v>9.68</v>
+        <v>9.31</v>
       </c>
       <c r="G14" t="n">
-        <v>35.6</v>
+        <v>29.4</v>
       </c>
       <c r="H14" t="n">
         <v>100</v>
       </c>
       <c r="I14" t="n">
-        <v>18</v>
+        <v>23</v>
       </c>
       <c r="J14" t="n">
-        <v>-18.56</v>
+        <v>100.9</v>
       </c>
       <c r="K14" t="n">
-        <v>-195.7</v>
+        <v>-54.23</v>
       </c>
       <c r="L14" t="n">
-        <v>196.58</v>
+        <v>114.55</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>07:32:33</t>
+          <t>07:33:19</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -667,34 +667,34 @@
         <v>2</v>
       </c>
       <c r="E15" t="n">
-        <v>4.07</v>
+        <v>4.11</v>
       </c>
       <c r="F15" t="n">
-        <v>9.42</v>
+        <v>9.07</v>
       </c>
       <c r="G15" t="n">
-        <v>35.1</v>
+        <v>29.9</v>
       </c>
       <c r="H15" t="n">
         <v>100</v>
       </c>
       <c r="I15" t="n">
-        <v>16</v>
+        <v>23</v>
       </c>
       <c r="J15" t="n">
-        <v>107.36</v>
+        <v>-79.68000000000001</v>
       </c>
       <c r="K15" t="n">
-        <v>-36.8</v>
+        <v>108.5</v>
       </c>
       <c r="L15" t="n">
-        <v>113.49</v>
+        <v>134.62</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>07:34:53</t>
+          <t>07:35:17</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -709,34 +709,34 @@
         <v>3</v>
       </c>
       <c r="E16" t="n">
-        <v>3.91</v>
+        <v>3.18</v>
       </c>
       <c r="F16" t="n">
-        <v>9.44</v>
+        <v>9.210000000000001</v>
       </c>
       <c r="G16" t="n">
-        <v>50.4</v>
+        <v>54.6</v>
       </c>
       <c r="H16" t="n">
-        <v>98.09999999999999</v>
+        <v>93.2</v>
       </c>
       <c r="I16" t="n">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="J16" t="n">
-        <v>116.11</v>
+        <v>-110.69</v>
       </c>
       <c r="K16" t="n">
-        <v>-120.73</v>
+        <v>261.22</v>
       </c>
       <c r="L16" t="n">
-        <v>167.51</v>
+        <v>283.71</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>07:39:32</t>
+          <t>07:38:44</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -751,34 +751,34 @@
         <v>1</v>
       </c>
       <c r="E17" t="n">
-        <v>3.76</v>
+        <v>3.26</v>
       </c>
       <c r="F17" t="n">
-        <v>9.289999999999999</v>
+        <v>9.869999999999999</v>
       </c>
       <c r="G17" t="n">
-        <v>41.4</v>
+        <v>50.4</v>
       </c>
       <c r="H17" t="n">
         <v>100</v>
       </c>
       <c r="I17" t="n">
-        <v>17</v>
+        <v>25</v>
       </c>
       <c r="J17" t="n">
-        <v>-230.74</v>
+        <v>-117.67</v>
       </c>
       <c r="K17" t="n">
-        <v>142.85</v>
+        <v>118.07</v>
       </c>
       <c r="L17" t="n">
-        <v>271.38</v>
+        <v>166.69</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>07:41:23</t>
+          <t>07:40:27</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -796,31 +796,31 @@
         <v>3.58</v>
       </c>
       <c r="F18" t="n">
-        <v>8.91</v>
+        <v>9.970000000000001</v>
       </c>
       <c r="G18" t="n">
-        <v>40</v>
+        <v>43.6</v>
       </c>
       <c r="H18" t="n">
         <v>100</v>
       </c>
       <c r="I18" t="n">
-        <v>16</v>
+        <v>23</v>
       </c>
       <c r="J18" t="n">
-        <v>-81.26000000000001</v>
+        <v>-94.64</v>
       </c>
       <c r="K18" t="n">
-        <v>-122.8</v>
+        <v>-118.78</v>
       </c>
       <c r="L18" t="n">
-        <v>147.25</v>
+        <v>151.87</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>07:43:40</t>
+          <t>07:42:21</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -835,34 +835,34 @@
         <v>3</v>
       </c>
       <c r="E19" t="n">
-        <v>3.11</v>
+        <v>4.14</v>
       </c>
       <c r="F19" t="n">
-        <v>9.35</v>
+        <v>9.51</v>
       </c>
       <c r="G19" t="n">
-        <v>40.8</v>
+        <v>48.2</v>
       </c>
       <c r="H19" t="n">
-        <v>99</v>
+        <v>95.90000000000001</v>
       </c>
       <c r="I19" t="n">
-        <v>16</v>
+        <v>19</v>
       </c>
       <c r="J19" t="n">
-        <v>-114.08</v>
+        <v>242.16</v>
       </c>
       <c r="K19" t="n">
-        <v>34.02</v>
+        <v>24.91</v>
       </c>
       <c r="L19" t="n">
-        <v>119.04</v>
+        <v>243.44</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>07:49:06</t>
+          <t>07:45:40</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -877,34 +877,34 @@
         <v>1</v>
       </c>
       <c r="E20" t="n">
-        <v>3.44</v>
+        <v>3.42</v>
       </c>
       <c r="F20" t="n">
-        <v>9.98</v>
+        <v>8.66</v>
       </c>
       <c r="G20" t="n">
-        <v>43.2</v>
+        <v>26</v>
       </c>
       <c r="H20" t="n">
-        <v>100</v>
+        <v>97.5</v>
       </c>
       <c r="I20" t="n">
-        <v>16</v>
+        <v>22</v>
       </c>
       <c r="J20" t="n">
-        <v>238.72</v>
+        <v>145.74</v>
       </c>
       <c r="K20" t="n">
-        <v>-179.2</v>
+        <v>527.6</v>
       </c>
       <c r="L20" t="n">
-        <v>298.49</v>
+        <v>547.36</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>07:51:56</t>
+          <t>07:48:17</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -919,34 +919,34 @@
         <v>2</v>
       </c>
       <c r="E21" t="n">
-        <v>3.36</v>
+        <v>2.98</v>
       </c>
       <c r="F21" t="n">
-        <v>9.06</v>
+        <v>9.640000000000001</v>
       </c>
       <c r="G21" t="n">
-        <v>28.9</v>
+        <v>37.8</v>
       </c>
       <c r="H21" t="n">
-        <v>98.3</v>
+        <v>100</v>
       </c>
       <c r="I21" t="n">
-        <v>16</v>
+        <v>25</v>
       </c>
       <c r="J21" t="n">
-        <v>117.93</v>
+        <v>510.63</v>
       </c>
       <c r="K21" t="n">
-        <v>-229.24</v>
+        <v>38.99</v>
       </c>
       <c r="L21" t="n">
-        <v>257.79</v>
+        <v>512.11</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>07:53:55</t>
+          <t>07:50:23</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -961,34 +961,34 @@
         <v>3</v>
       </c>
       <c r="E22" t="n">
-        <v>3.39</v>
+        <v>3.72</v>
       </c>
       <c r="F22" t="n">
-        <v>8.74</v>
+        <v>8.94</v>
       </c>
       <c r="G22" t="n">
-        <v>54.1</v>
+        <v>51.7</v>
       </c>
       <c r="H22" t="n">
-        <v>100</v>
+        <v>98.3</v>
       </c>
       <c r="I22" t="n">
         <v>19</v>
       </c>
       <c r="J22" t="n">
-        <v>251.17</v>
+        <v>-22.81</v>
       </c>
       <c r="K22" t="n">
-        <v>30.34</v>
+        <v>254</v>
       </c>
       <c r="L22" t="n">
-        <v>253</v>
+        <v>255.02</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>07:59:30</t>
+          <t>07:54:57</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -1003,34 +1003,34 @@
         <v>1</v>
       </c>
       <c r="E23" t="n">
-        <v>3.56</v>
+        <v>3.46</v>
       </c>
       <c r="F23" t="n">
-        <v>8.800000000000001</v>
+        <v>9.41</v>
       </c>
       <c r="G23" t="n">
-        <v>52.9</v>
+        <v>49.3</v>
       </c>
       <c r="H23" t="n">
         <v>100</v>
       </c>
       <c r="I23" t="n">
-        <v>17</v>
+        <v>22</v>
       </c>
       <c r="J23" t="n">
-        <v>-879.1799999999999</v>
+        <v>-403.28</v>
       </c>
       <c r="K23" t="n">
-        <v>-171.38</v>
+        <v>-393.6</v>
       </c>
       <c r="L23" t="n">
-        <v>895.73</v>
+        <v>563.52</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>08:01:18</t>
+          <t>07:57:08</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -1045,34 +1045,34 @@
         <v>2</v>
       </c>
       <c r="E24" t="n">
-        <v>3.21</v>
+        <v>3.61</v>
       </c>
       <c r="F24" t="n">
-        <v>8.470000000000001</v>
+        <v>9.699999999999999</v>
       </c>
       <c r="G24" t="n">
-        <v>39.8</v>
+        <v>41.2</v>
       </c>
       <c r="H24" t="n">
         <v>100</v>
       </c>
       <c r="I24" t="n">
-        <v>17</v>
+        <v>25</v>
       </c>
       <c r="J24" t="n">
-        <v>222.53</v>
+        <v>-0.34</v>
       </c>
       <c r="K24" t="n">
-        <v>517.25</v>
+        <v>158.63</v>
       </c>
       <c r="L24" t="n">
-        <v>563.09</v>
+        <v>158.63</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>08:02:39</t>
+          <t>07:58:23</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -1087,34 +1087,34 @@
         <v>3</v>
       </c>
       <c r="E25" t="n">
-        <v>3.66</v>
+        <v>3.59</v>
       </c>
       <c r="F25" t="n">
-        <v>9.390000000000001</v>
+        <v>9.73</v>
       </c>
       <c r="G25" t="n">
-        <v>53.8</v>
+        <v>51.4</v>
       </c>
       <c r="H25" t="n">
         <v>100</v>
       </c>
       <c r="I25" t="n">
-        <v>16</v>
+        <v>23</v>
       </c>
       <c r="J25" t="n">
-        <v>180.17</v>
+        <v>-269.08</v>
       </c>
       <c r="K25" t="n">
-        <v>118.32</v>
+        <v>159.92</v>
       </c>
       <c r="L25" t="n">
-        <v>215.54</v>
+        <v>313.01</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>08:06:53</t>
+          <t>08:02:21</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
@@ -1129,34 +1129,34 @@
         <v>1</v>
       </c>
       <c r="E26" t="n">
-        <v>3.72</v>
+        <v>4.05</v>
       </c>
       <c r="F26" t="n">
-        <v>9.18</v>
+        <v>9.57</v>
       </c>
       <c r="G26" t="n">
-        <v>46.5</v>
+        <v>63.7</v>
       </c>
       <c r="H26" t="n">
-        <v>100</v>
+        <v>90.2</v>
       </c>
       <c r="I26" t="n">
-        <v>16</v>
+        <v>23</v>
       </c>
       <c r="J26" t="n">
-        <v>-112.44</v>
+        <v>-722.11</v>
       </c>
       <c r="K26" t="n">
-        <v>-4.25</v>
+        <v>-68.72</v>
       </c>
       <c r="L26" t="n">
-        <v>112.52</v>
+        <v>725.37</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>08:08:41</t>
+          <t>08:04:36</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
@@ -1171,34 +1171,34 @@
         <v>2</v>
       </c>
       <c r="E27" t="n">
-        <v>3.84</v>
+        <v>3.93</v>
       </c>
       <c r="F27" t="n">
-        <v>9.720000000000001</v>
+        <v>9.98</v>
       </c>
       <c r="G27" t="n">
-        <v>56.3</v>
+        <v>43.7</v>
       </c>
       <c r="H27" t="n">
         <v>100</v>
       </c>
       <c r="I27" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="J27" t="n">
-        <v>151.7</v>
+        <v>24.83</v>
       </c>
       <c r="K27" t="n">
-        <v>99.33</v>
+        <v>442.88</v>
       </c>
       <c r="L27" t="n">
-        <v>181.32</v>
+        <v>443.58</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>08:10:53</t>
+          <t>08:06:39</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
@@ -1213,34 +1213,34 @@
         <v>3</v>
       </c>
       <c r="E28" t="n">
-        <v>3.08</v>
+        <v>4</v>
       </c>
       <c r="F28" t="n">
-        <v>8.74</v>
+        <v>9.41</v>
       </c>
       <c r="G28" t="n">
-        <v>37.3</v>
+        <v>39.9</v>
       </c>
       <c r="H28" t="n">
         <v>100</v>
       </c>
       <c r="I28" t="n">
-        <v>17</v>
+        <v>21</v>
       </c>
       <c r="J28" t="n">
-        <v>311.11</v>
+        <v>488.45</v>
       </c>
       <c r="K28" t="n">
-        <v>179.68</v>
+        <v>236.01</v>
       </c>
       <c r="L28" t="n">
-        <v>359.27</v>
+        <v>542.48</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>08:19:35</t>
+          <t>08:15:29</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
@@ -1255,34 +1255,34 @@
         <v>1</v>
       </c>
       <c r="E29" t="n">
-        <v>3.48</v>
+        <v>3.41</v>
       </c>
       <c r="F29" t="n">
-        <v>9.720000000000001</v>
+        <v>9.5</v>
       </c>
       <c r="G29" t="n">
-        <v>44.6</v>
+        <v>47.7</v>
       </c>
       <c r="H29" t="n">
-        <v>99.5</v>
+        <v>100</v>
       </c>
       <c r="I29" t="n">
-        <v>17</v>
+        <v>24</v>
       </c>
       <c r="J29" t="n">
-        <v>6.25</v>
+        <v>58.04</v>
       </c>
       <c r="K29" t="n">
-        <v>168.1</v>
+        <v>-173.05</v>
       </c>
       <c r="L29" t="n">
-        <v>168.22</v>
+        <v>182.52</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>08:21:39</t>
+          <t>08:16:28</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
@@ -1297,34 +1297,34 @@
         <v>2</v>
       </c>
       <c r="E30" t="n">
-        <v>3.38</v>
+        <v>3.98</v>
       </c>
       <c r="F30" t="n">
-        <v>9.869999999999999</v>
+        <v>8.710000000000001</v>
       </c>
       <c r="G30" t="n">
-        <v>47</v>
+        <v>47.6</v>
       </c>
       <c r="H30" t="n">
-        <v>97.3</v>
+        <v>98.59999999999999</v>
       </c>
       <c r="I30" t="n">
-        <v>16</v>
+        <v>20</v>
       </c>
       <c r="J30" t="n">
-        <v>57.88</v>
+        <v>-19.34</v>
       </c>
       <c r="K30" t="n">
-        <v>-3.2</v>
+        <v>221.99</v>
       </c>
       <c r="L30" t="n">
-        <v>57.97</v>
+        <v>222.83</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>08:23:13</t>
+          <t>08:18:12</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
@@ -1339,34 +1339,34 @@
         <v>3</v>
       </c>
       <c r="E31" t="n">
-        <v>3.79</v>
+        <v>3.69</v>
       </c>
       <c r="F31" t="n">
-        <v>8.949999999999999</v>
+        <v>9.48</v>
       </c>
       <c r="G31" t="n">
-        <v>29.9</v>
+        <v>42.3</v>
       </c>
       <c r="H31" t="n">
-        <v>96.59999999999999</v>
+        <v>90.90000000000001</v>
       </c>
       <c r="I31" t="n">
-        <v>16</v>
+        <v>24</v>
       </c>
       <c r="J31" t="n">
-        <v>103.3</v>
+        <v>31.89</v>
       </c>
       <c r="K31" t="n">
-        <v>-245.02</v>
+        <v>-84.14</v>
       </c>
       <c r="L31" t="n">
-        <v>265.91</v>
+        <v>89.98</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>08:27:32</t>
+          <t>08:22:38</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
@@ -1381,34 +1381,34 @@
         <v>1</v>
       </c>
       <c r="E32" t="n">
-        <v>3.79</v>
+        <v>3.68</v>
       </c>
       <c r="F32" t="n">
-        <v>9.789999999999999</v>
+        <v>9.1</v>
       </c>
       <c r="G32" t="n">
-        <v>48.5</v>
+        <v>43.2</v>
       </c>
       <c r="H32" t="n">
-        <v>100</v>
+        <v>92</v>
       </c>
       <c r="I32" t="n">
-        <v>16</v>
+        <v>20</v>
       </c>
       <c r="J32" t="n">
-        <v>-166.61</v>
+        <v>-382.18</v>
       </c>
       <c r="K32" t="n">
-        <v>140.43</v>
+        <v>57.57</v>
       </c>
       <c r="L32" t="n">
-        <v>217.9</v>
+        <v>386.49</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>08:28:37</t>
+          <t>08:24:47</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
@@ -1423,34 +1423,34 @@
         <v>2</v>
       </c>
       <c r="E33" t="n">
-        <v>3.92</v>
+        <v>4.42</v>
       </c>
       <c r="F33" t="n">
-        <v>8.93</v>
+        <v>9.24</v>
       </c>
       <c r="G33" t="n">
-        <v>49.9</v>
+        <v>48.1</v>
       </c>
       <c r="H33" t="n">
-        <v>94.8</v>
+        <v>100</v>
       </c>
       <c r="I33" t="n">
-        <v>16</v>
+        <v>20</v>
       </c>
       <c r="J33" t="n">
-        <v>-110.73</v>
+        <v>147.43</v>
       </c>
       <c r="K33" t="n">
-        <v>367.42</v>
+        <v>-398.07</v>
       </c>
       <c r="L33" t="n">
-        <v>383.74</v>
+        <v>424.49</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>08:29:37</t>
+          <t>08:25:45</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
@@ -1465,13 +1465,13 @@
         <v>3</v>
       </c>
       <c r="E34" t="n">
-        <v>4.41</v>
+        <v>4.04</v>
       </c>
       <c r="F34" t="n">
-        <v>8.890000000000001</v>
+        <v>9.970000000000001</v>
       </c>
       <c r="G34" t="n">
-        <v>41.7</v>
+        <v>39.9</v>
       </c>
       <c r="H34" t="n">
         <v>100</v>
@@ -1480,19 +1480,19 @@
         <v>19</v>
       </c>
       <c r="J34" t="n">
-        <v>163.43</v>
+        <v>-74.73999999999999</v>
       </c>
       <c r="K34" t="n">
-        <v>49.3</v>
+        <v>-80.39</v>
       </c>
       <c r="L34" t="n">
-        <v>170.71</v>
+        <v>109.76</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>08:34:27</t>
+          <t>08:30:54</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
@@ -1507,34 +1507,34 @@
         <v>1</v>
       </c>
       <c r="E35" t="n">
-        <v>3.89</v>
+        <v>3.77</v>
       </c>
       <c r="F35" t="n">
-        <v>9.779999999999999</v>
+        <v>10.02</v>
       </c>
       <c r="G35" t="n">
-        <v>32</v>
+        <v>48.6</v>
       </c>
       <c r="H35" t="n">
-        <v>98.40000000000001</v>
+        <v>100</v>
       </c>
       <c r="I35" t="n">
-        <v>16</v>
+        <v>22</v>
       </c>
       <c r="J35" t="n">
-        <v>105.11</v>
+        <v>19.54</v>
       </c>
       <c r="K35" t="n">
-        <v>77</v>
+        <v>289.57</v>
       </c>
       <c r="L35" t="n">
-        <v>130.3</v>
+        <v>290.23</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>08:36:57</t>
+          <t>08:32:23</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
@@ -1549,34 +1549,34 @@
         <v>2</v>
       </c>
       <c r="E36" t="n">
-        <v>4.04</v>
+        <v>3.89</v>
       </c>
       <c r="F36" t="n">
-        <v>9.27</v>
+        <v>9.23</v>
       </c>
       <c r="G36" t="n">
-        <v>50.7</v>
+        <v>44.8</v>
       </c>
       <c r="H36" t="n">
-        <v>99.7</v>
+        <v>100</v>
       </c>
       <c r="I36" t="n">
-        <v>16</v>
+        <v>22</v>
       </c>
       <c r="J36" t="n">
-        <v>278.84</v>
+        <v>144.18</v>
       </c>
       <c r="K36" t="n">
-        <v>-49.37</v>
+        <v>-225.51</v>
       </c>
       <c r="L36" t="n">
-        <v>283.18</v>
+        <v>267.66</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>08:39:03</t>
+          <t>08:34:30</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
@@ -1591,34 +1591,34 @@
         <v>3</v>
       </c>
       <c r="E37" t="n">
-        <v>3.42</v>
+        <v>3.73</v>
       </c>
       <c r="F37" t="n">
-        <v>9.48</v>
+        <v>8.960000000000001</v>
       </c>
       <c r="G37" t="n">
-        <v>43.2</v>
+        <v>33.8</v>
       </c>
       <c r="H37" t="n">
-        <v>91.5</v>
+        <v>97</v>
       </c>
       <c r="I37" t="n">
-        <v>17</v>
+        <v>25</v>
       </c>
       <c r="J37" t="n">
-        <v>239.68</v>
+        <v>-120.48</v>
       </c>
       <c r="K37" t="n">
-        <v>-126.85</v>
+        <v>92</v>
       </c>
       <c r="L37" t="n">
-        <v>271.18</v>
+        <v>151.59</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>08:42:56</t>
+          <t>08:38:04</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
@@ -1633,34 +1633,34 @@
         <v>1</v>
       </c>
       <c r="E38" t="n">
-        <v>4.04</v>
+        <v>3.8</v>
       </c>
       <c r="F38" t="n">
-        <v>9.869999999999999</v>
+        <v>8.640000000000001</v>
       </c>
       <c r="G38" t="n">
-        <v>46.3</v>
+        <v>50</v>
       </c>
       <c r="H38" t="n">
-        <v>92.59999999999999</v>
+        <v>100</v>
       </c>
       <c r="I38" t="n">
-        <v>17</v>
+        <v>20</v>
       </c>
       <c r="J38" t="n">
-        <v>604.21</v>
+        <v>264.91</v>
       </c>
       <c r="K38" t="n">
-        <v>202.37</v>
+        <v>120.62</v>
       </c>
       <c r="L38" t="n">
-        <v>637.2</v>
+        <v>291.08</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>08:44:13</t>
+          <t>08:39:59</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
@@ -1675,34 +1675,34 @@
         <v>2</v>
       </c>
       <c r="E39" t="n">
-        <v>4.44</v>
+        <v>4.16</v>
       </c>
       <c r="F39" t="n">
-        <v>9.800000000000001</v>
+        <v>9.41</v>
       </c>
       <c r="G39" t="n">
-        <v>52.2</v>
+        <v>45.4</v>
       </c>
       <c r="H39" t="n">
-        <v>97.5</v>
+        <v>98.8</v>
       </c>
       <c r="I39" t="n">
-        <v>16</v>
+        <v>23</v>
       </c>
       <c r="J39" t="n">
-        <v>187.63</v>
+        <v>-1.92</v>
       </c>
       <c r="K39" t="n">
-        <v>141.57</v>
+        <v>537.58</v>
       </c>
       <c r="L39" t="n">
-        <v>235.05</v>
+        <v>537.58</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>08:46:13</t>
+          <t>08:41:47</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
@@ -1717,34 +1717,34 @@
         <v>3</v>
       </c>
       <c r="E40" t="n">
-        <v>3.49</v>
+        <v>4.38</v>
       </c>
       <c r="F40" t="n">
-        <v>9.65</v>
+        <v>9.630000000000001</v>
       </c>
       <c r="G40" t="n">
-        <v>36.7</v>
+        <v>50.5</v>
       </c>
       <c r="H40" t="n">
         <v>100</v>
       </c>
       <c r="I40" t="n">
-        <v>18</v>
+        <v>23</v>
       </c>
       <c r="J40" t="n">
-        <v>281.18</v>
+        <v>143.64</v>
       </c>
       <c r="K40" t="n">
-        <v>-294.67</v>
+        <v>-560.17</v>
       </c>
       <c r="L40" t="n">
-        <v>407.3</v>
+        <v>578.29</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>08:52:04</t>
+          <t>08:47:17</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
@@ -1759,34 +1759,34 @@
         <v>1</v>
       </c>
       <c r="E41" t="n">
-        <v>4.3</v>
+        <v>3.89</v>
       </c>
       <c r="F41" t="n">
-        <v>9.48</v>
+        <v>9.529999999999999</v>
       </c>
       <c r="G41" t="n">
-        <v>31.2</v>
+        <v>45.4</v>
       </c>
       <c r="H41" t="n">
-        <v>100</v>
+        <v>95.5</v>
       </c>
       <c r="I41" t="n">
-        <v>17</v>
+        <v>21</v>
       </c>
       <c r="J41" t="n">
-        <v>-301.27</v>
+        <v>-357.17</v>
       </c>
       <c r="K41" t="n">
-        <v>244.62</v>
+        <v>-54.7</v>
       </c>
       <c r="L41" t="n">
-        <v>388.08</v>
+        <v>361.34</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>08:53:39</t>
+          <t>08:48:34</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
@@ -1801,34 +1801,34 @@
         <v>2</v>
       </c>
       <c r="E42" t="n">
-        <v>4.35</v>
+        <v>4.26</v>
       </c>
       <c r="F42" t="n">
-        <v>8.99</v>
+        <v>9.81</v>
       </c>
       <c r="G42" t="n">
-        <v>41.6</v>
+        <v>39.6</v>
       </c>
       <c r="H42" t="n">
-        <v>95.09999999999999</v>
+        <v>100</v>
       </c>
       <c r="I42" t="n">
-        <v>18</v>
+        <v>21</v>
       </c>
       <c r="J42" t="n">
-        <v>63.93</v>
+        <v>-362.22</v>
       </c>
       <c r="K42" t="n">
-        <v>417.94</v>
+        <v>96.95999999999999</v>
       </c>
       <c r="L42" t="n">
-        <v>422.8</v>
+        <v>374.98</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>08:55:01</t>
+          <t>08:51:10</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
@@ -1843,34 +1843,34 @@
         <v>3</v>
       </c>
       <c r="E43" t="n">
-        <v>3.2</v>
+        <v>3.84</v>
       </c>
       <c r="F43" t="n">
-        <v>9.32</v>
+        <v>10.11</v>
       </c>
       <c r="G43" t="n">
-        <v>32.4</v>
+        <v>48.1</v>
       </c>
       <c r="H43" t="n">
-        <v>97.09999999999999</v>
+        <v>94.5</v>
       </c>
       <c r="I43" t="n">
-        <v>16</v>
+        <v>24</v>
       </c>
       <c r="J43" t="n">
-        <v>131.64</v>
+        <v>-448.91</v>
       </c>
       <c r="K43" t="n">
-        <v>123.55</v>
+        <v>-66.47</v>
       </c>
       <c r="L43" t="n">
-        <v>180.54</v>
+        <v>453.8</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>09:05:06</t>
+          <t>08:58:16</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
@@ -1885,34 +1885,34 @@
         <v>1</v>
       </c>
       <c r="E44" t="n">
-        <v>4.38</v>
+        <v>3.94</v>
       </c>
       <c r="F44" t="n">
-        <v>9.619999999999999</v>
+        <v>9.029999999999999</v>
       </c>
       <c r="G44" t="n">
-        <v>50.5</v>
+        <v>41.3</v>
       </c>
       <c r="H44" t="n">
-        <v>99.8</v>
+        <v>100</v>
       </c>
       <c r="I44" t="n">
-        <v>19</v>
+        <v>25</v>
       </c>
       <c r="J44" t="n">
-        <v>-67.51000000000001</v>
+        <v>-167.18</v>
       </c>
       <c r="K44" t="n">
-        <v>-59.05</v>
+        <v>-118.12</v>
       </c>
       <c r="L44" t="n">
-        <v>89.69</v>
+        <v>204.7</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>09:06:20</t>
+          <t>08:59:56</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
@@ -1927,34 +1927,34 @@
         <v>2</v>
       </c>
       <c r="E45" t="n">
-        <v>3.56</v>
+        <v>3.61</v>
       </c>
       <c r="F45" t="n">
-        <v>9.949999999999999</v>
+        <v>8.9</v>
       </c>
       <c r="G45" t="n">
-        <v>35.3</v>
+        <v>37.8</v>
       </c>
       <c r="H45" t="n">
         <v>100</v>
       </c>
       <c r="I45" t="n">
-        <v>17</v>
+        <v>22</v>
       </c>
       <c r="J45" t="n">
-        <v>241.23</v>
+        <v>-35.66</v>
       </c>
       <c r="K45" t="n">
-        <v>61.02</v>
+        <v>49.4</v>
       </c>
       <c r="L45" t="n">
-        <v>248.83</v>
+        <v>60.93</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>09:07:47</t>
+          <t>09:01:11</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
@@ -1969,34 +1969,34 @@
         <v>3</v>
       </c>
       <c r="E46" t="n">
-        <v>3.55</v>
+        <v>3.45</v>
       </c>
       <c r="F46" t="n">
-        <v>9.66</v>
+        <v>9.869999999999999</v>
       </c>
       <c r="G46" t="n">
-        <v>29.9</v>
+        <v>38.9</v>
       </c>
       <c r="H46" t="n">
-        <v>100</v>
+        <v>96.40000000000001</v>
       </c>
       <c r="I46" t="n">
-        <v>16</v>
+        <v>25</v>
       </c>
       <c r="J46" t="n">
-        <v>-34.35</v>
+        <v>54.92</v>
       </c>
       <c r="K46" t="n">
-        <v>-78.72</v>
+        <v>54.93</v>
       </c>
       <c r="L46" t="n">
-        <v>85.89</v>
+        <v>77.68000000000001</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>09:12:22</t>
+          <t>09:05:12</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
@@ -2011,34 +2011,34 @@
         <v>1</v>
       </c>
       <c r="E47" t="n">
-        <v>4.47</v>
+        <v>3.73</v>
       </c>
       <c r="F47" t="n">
-        <v>9.42</v>
+        <v>10.15</v>
       </c>
       <c r="G47" t="n">
-        <v>46.7</v>
+        <v>52.6</v>
       </c>
       <c r="H47" t="n">
-        <v>97.7</v>
+        <v>100</v>
       </c>
       <c r="I47" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="J47" t="n">
-        <v>-436.33</v>
+        <v>-292.23</v>
       </c>
       <c r="K47" t="n">
-        <v>108.69</v>
+        <v>-4.68</v>
       </c>
       <c r="L47" t="n">
-        <v>449.67</v>
+        <v>292.26</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>09:13:51</t>
+          <t>09:07:51</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
@@ -2053,34 +2053,34 @@
         <v>2</v>
       </c>
       <c r="E48" t="n">
-        <v>4.68</v>
+        <v>4.23</v>
       </c>
       <c r="F48" t="n">
-        <v>9.15</v>
+        <v>9.539999999999999</v>
       </c>
       <c r="G48" t="n">
-        <v>50.7</v>
+        <v>37.6</v>
       </c>
       <c r="H48" t="n">
-        <v>99.7</v>
+        <v>96.3</v>
       </c>
       <c r="I48" t="n">
-        <v>16</v>
+        <v>25</v>
       </c>
       <c r="J48" t="n">
-        <v>-8.57</v>
+        <v>-150.92</v>
       </c>
       <c r="K48" t="n">
-        <v>188.4</v>
+        <v>44.88</v>
       </c>
       <c r="L48" t="n">
-        <v>188.6</v>
+        <v>157.45</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>09:16:22</t>
+          <t>09:09:08</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
@@ -2095,34 +2095,34 @@
         <v>3</v>
       </c>
       <c r="E49" t="n">
-        <v>3.75</v>
+        <v>3.65</v>
       </c>
       <c r="F49" t="n">
-        <v>8.68</v>
+        <v>9.68</v>
       </c>
       <c r="G49" t="n">
-        <v>46.1</v>
+        <v>37.7</v>
       </c>
       <c r="H49" t="n">
-        <v>97.7</v>
+        <v>99.40000000000001</v>
       </c>
       <c r="I49" t="n">
-        <v>18</v>
+        <v>23</v>
       </c>
       <c r="J49" t="n">
-        <v>15.91</v>
+        <v>-33.18</v>
       </c>
       <c r="K49" t="n">
-        <v>-223.2</v>
+        <v>300.29</v>
       </c>
       <c r="L49" t="n">
-        <v>223.77</v>
+        <v>302.12</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>09:20:32</t>
+          <t>09:13:34</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
@@ -2137,34 +2137,34 @@
         <v>1</v>
       </c>
       <c r="E50" t="n">
-        <v>4.01</v>
+        <v>4.13</v>
       </c>
       <c r="F50" t="n">
-        <v>9.279999999999999</v>
+        <v>9.369999999999999</v>
       </c>
       <c r="G50" t="n">
-        <v>45.3</v>
+        <v>34.7</v>
       </c>
       <c r="H50" t="n">
-        <v>99.3</v>
+        <v>97.7</v>
       </c>
       <c r="I50" t="n">
-        <v>18</v>
+        <v>25</v>
       </c>
       <c r="J50" t="n">
-        <v>-289.43</v>
+        <v>-456.41</v>
       </c>
       <c r="K50" t="n">
-        <v>47.44</v>
+        <v>-314.78</v>
       </c>
       <c r="L50" t="n">
-        <v>293.29</v>
+        <v>554.4400000000001</v>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>09:21:22</t>
+          <t>09:15:03</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
@@ -2179,10 +2179,10 @@
         <v>2</v>
       </c>
       <c r="E51" t="n">
-        <v>4.59</v>
+        <v>3.87</v>
       </c>
       <c r="F51" t="n">
-        <v>9.039999999999999</v>
+        <v>9.619999999999999</v>
       </c>
       <c r="G51" t="n">
         <v>43.1</v>
@@ -2191,22 +2191,22 @@
         <v>100</v>
       </c>
       <c r="I51" t="n">
-        <v>16</v>
+        <v>19</v>
       </c>
       <c r="J51" t="n">
-        <v>203.96</v>
+        <v>5.72</v>
       </c>
       <c r="K51" t="n">
-        <v>308.89</v>
+        <v>-278.4</v>
       </c>
       <c r="L51" t="n">
-        <v>370.15</v>
+        <v>278.46</v>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>09:23:46</t>
+          <t>09:16:38</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
@@ -2221,34 +2221,34 @@
         <v>3</v>
       </c>
       <c r="E52" t="n">
-        <v>4.01</v>
+        <v>4.7</v>
       </c>
       <c r="F52" t="n">
-        <v>9.23</v>
+        <v>9.51</v>
       </c>
       <c r="G52" t="n">
-        <v>62.1</v>
+        <v>43.8</v>
       </c>
       <c r="H52" t="n">
-        <v>92.40000000000001</v>
+        <v>99.40000000000001</v>
       </c>
       <c r="I52" t="n">
-        <v>16</v>
+        <v>22</v>
       </c>
       <c r="J52" t="n">
-        <v>-60.91</v>
+        <v>-200.92</v>
       </c>
       <c r="K52" t="n">
-        <v>-302.56</v>
+        <v>265.49</v>
       </c>
       <c r="L52" t="n">
-        <v>308.63</v>
+        <v>332.95</v>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>09:27:26</t>
+          <t>09:22:10</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
@@ -2263,34 +2263,34 @@
         <v>1</v>
       </c>
       <c r="E53" t="n">
-        <v>3.33</v>
+        <v>4.21</v>
       </c>
       <c r="F53" t="n">
-        <v>9.73</v>
+        <v>9.48</v>
       </c>
       <c r="G53" t="n">
-        <v>47.7</v>
+        <v>32.3</v>
       </c>
       <c r="H53" t="n">
-        <v>96.3</v>
+        <v>97.40000000000001</v>
       </c>
       <c r="I53" t="n">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="J53" t="n">
-        <v>-429.47</v>
+        <v>568.12</v>
       </c>
       <c r="K53" t="n">
-        <v>177.81</v>
+        <v>-361.71</v>
       </c>
       <c r="L53" t="n">
-        <v>464.82</v>
+        <v>673.5</v>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>09:29:53</t>
+          <t>09:24:22</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
@@ -2305,34 +2305,34 @@
         <v>2</v>
       </c>
       <c r="E54" t="n">
-        <v>4.19</v>
+        <v>4.3</v>
       </c>
       <c r="F54" t="n">
-        <v>9.279999999999999</v>
+        <v>9.220000000000001</v>
       </c>
       <c r="G54" t="n">
-        <v>40.8</v>
+        <v>41.4</v>
       </c>
       <c r="H54" t="n">
-        <v>100</v>
+        <v>90.40000000000001</v>
       </c>
       <c r="I54" t="n">
-        <v>18</v>
+        <v>23</v>
       </c>
       <c r="J54" t="n">
-        <v>-82.34</v>
+        <v>-298.94</v>
       </c>
       <c r="K54" t="n">
-        <v>361.54</v>
+        <v>266.23</v>
       </c>
       <c r="L54" t="n">
-        <v>370.8</v>
+        <v>400.31</v>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>09:31:44</t>
+          <t>09:26:29</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
@@ -2347,34 +2347,34 @@
         <v>3</v>
       </c>
       <c r="E55" t="n">
-        <v>4.43</v>
+        <v>4.04</v>
       </c>
       <c r="F55" t="n">
-        <v>9.44</v>
+        <v>9.76</v>
       </c>
       <c r="G55" t="n">
-        <v>30.3</v>
+        <v>42.7</v>
       </c>
       <c r="H55" t="n">
-        <v>98.3</v>
+        <v>100</v>
       </c>
       <c r="I55" t="n">
-        <v>16</v>
+        <v>23</v>
       </c>
       <c r="J55" t="n">
-        <v>56.45</v>
+        <v>-125.5</v>
       </c>
       <c r="K55" t="n">
-        <v>82.34</v>
+        <v>-424.41</v>
       </c>
       <c r="L55" t="n">
-        <v>99.83</v>
+        <v>442.57</v>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>09:36:43</t>
+          <t>09:30:06</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
@@ -2389,34 +2389,34 @@
         <v>1</v>
       </c>
       <c r="E56" t="n">
-        <v>4.23</v>
+        <v>3.74</v>
       </c>
       <c r="F56" t="n">
-        <v>9.75</v>
+        <v>9.73</v>
       </c>
       <c r="G56" t="n">
-        <v>42.7</v>
+        <v>30.2</v>
       </c>
       <c r="H56" t="n">
         <v>100</v>
       </c>
       <c r="I56" t="n">
-        <v>16</v>
+        <v>22</v>
       </c>
       <c r="J56" t="n">
-        <v>70.34</v>
+        <v>-366.93</v>
       </c>
       <c r="K56" t="n">
-        <v>192.24</v>
+        <v>120.27</v>
       </c>
       <c r="L56" t="n">
-        <v>204.7</v>
+        <v>386.14</v>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>09:39:00</t>
+          <t>09:32:37</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
@@ -2431,34 +2431,34 @@
         <v>2</v>
       </c>
       <c r="E57" t="n">
-        <v>4.36</v>
+        <v>4.85</v>
       </c>
       <c r="F57" t="n">
-        <v>8.92</v>
+        <v>9.970000000000001</v>
       </c>
       <c r="G57" t="n">
-        <v>60.3</v>
+        <v>51.5</v>
       </c>
       <c r="H57" t="n">
         <v>100</v>
       </c>
       <c r="I57" t="n">
-        <v>16</v>
+        <v>22</v>
       </c>
       <c r="J57" t="n">
-        <v>484.55</v>
+        <v>-19.24</v>
       </c>
       <c r="K57" t="n">
-        <v>808.22</v>
+        <v>-412.9</v>
       </c>
       <c r="L57" t="n">
-        <v>942.34</v>
+        <v>413.35</v>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>09:40:58</t>
+          <t>09:34:37</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
@@ -2473,34 +2473,34 @@
         <v>3</v>
       </c>
       <c r="E58" t="n">
-        <v>4.25</v>
+        <v>4.3</v>
       </c>
       <c r="F58" t="n">
-        <v>8.859999999999999</v>
+        <v>8.91</v>
       </c>
       <c r="G58" t="n">
-        <v>39.9</v>
+        <v>40.9</v>
       </c>
       <c r="H58" t="n">
-        <v>96.3</v>
+        <v>92.2</v>
       </c>
       <c r="I58" t="n">
         <v>19</v>
       </c>
       <c r="J58" t="n">
-        <v>687.96</v>
+        <v>-582.8</v>
       </c>
       <c r="K58" t="n">
-        <v>809.45</v>
+        <v>-615.03</v>
       </c>
       <c r="L58" t="n">
-        <v>1062.31</v>
+        <v>847.3</v>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>09:49:24</t>
+          <t>09:47:53</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
@@ -2515,34 +2515,34 @@
         <v>1</v>
       </c>
       <c r="E59" t="n">
-        <v>4.12</v>
+        <v>5.3</v>
       </c>
       <c r="F59" t="n">
-        <v>9.68</v>
+        <v>9.24</v>
       </c>
       <c r="G59" t="n">
-        <v>47.6</v>
+        <v>40.8</v>
       </c>
       <c r="H59" t="n">
         <v>100</v>
       </c>
       <c r="I59" t="n">
-        <v>16</v>
+        <v>22</v>
       </c>
       <c r="J59" t="n">
-        <v>-12.91</v>
+        <v>240.08</v>
       </c>
       <c r="K59" t="n">
-        <v>-34</v>
+        <v>-8.35</v>
       </c>
       <c r="L59" t="n">
-        <v>36.37</v>
+        <v>240.23</v>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>09:51:47</t>
+          <t>09:49:09</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
@@ -2557,34 +2557,34 @@
         <v>2</v>
       </c>
       <c r="E60" t="n">
-        <v>4.25</v>
+        <v>4.07</v>
       </c>
       <c r="F60" t="n">
-        <v>9.69</v>
+        <v>9.289999999999999</v>
       </c>
       <c r="G60" t="n">
-        <v>27.2</v>
+        <v>44.7</v>
       </c>
       <c r="H60" t="n">
-        <v>93.2</v>
+        <v>100</v>
       </c>
       <c r="I60" t="n">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="J60" t="n">
-        <v>-114.36</v>
+        <v>229.2</v>
       </c>
       <c r="K60" t="n">
-        <v>-119.58</v>
+        <v>204.64</v>
       </c>
       <c r="L60" t="n">
-        <v>165.46</v>
+        <v>307.26</v>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>09:53:11</t>
+          <t>09:50:06</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
@@ -2599,34 +2599,34 @@
         <v>3</v>
       </c>
       <c r="E61" t="n">
-        <v>4.48</v>
+        <v>4.01</v>
       </c>
       <c r="F61" t="n">
-        <v>9.720000000000001</v>
+        <v>8.68</v>
       </c>
       <c r="G61" t="n">
-        <v>46.6</v>
+        <v>44.7</v>
       </c>
       <c r="H61" t="n">
         <v>100</v>
       </c>
       <c r="I61" t="n">
-        <v>18</v>
+        <v>24</v>
       </c>
       <c r="J61" t="n">
-        <v>131.33</v>
+        <v>-64.31999999999999</v>
       </c>
       <c r="K61" t="n">
-        <v>-114.66</v>
+        <v>-39.22</v>
       </c>
       <c r="L61" t="n">
-        <v>174.34</v>
+        <v>75.33</v>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>09:56:57</t>
+          <t>09:54:33</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
@@ -2641,34 +2641,34 @@
         <v>1</v>
       </c>
       <c r="E62" t="n">
-        <v>4.26</v>
+        <v>3.72</v>
       </c>
       <c r="F62" t="n">
-        <v>9.210000000000001</v>
+        <v>9.23</v>
       </c>
       <c r="G62" t="n">
-        <v>39.1</v>
+        <v>43.7</v>
       </c>
       <c r="H62" t="n">
         <v>100</v>
       </c>
       <c r="I62" t="n">
-        <v>18</v>
+        <v>22</v>
       </c>
       <c r="J62" t="n">
-        <v>313.2</v>
+        <v>-207.92</v>
       </c>
       <c r="K62" t="n">
-        <v>145.69</v>
+        <v>-122.14</v>
       </c>
       <c r="L62" t="n">
-        <v>345.43</v>
+        <v>241.14</v>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>09:58:16</t>
+          <t>09:55:21</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
@@ -2683,34 +2683,34 @@
         <v>2</v>
       </c>
       <c r="E63" t="n">
-        <v>4.04</v>
+        <v>4.39</v>
       </c>
       <c r="F63" t="n">
-        <v>9.539999999999999</v>
+        <v>9.59</v>
       </c>
       <c r="G63" t="n">
-        <v>33.5</v>
+        <v>48.9</v>
       </c>
       <c r="H63" t="n">
-        <v>95.90000000000001</v>
+        <v>100</v>
       </c>
       <c r="I63" t="n">
-        <v>16</v>
+        <v>23</v>
       </c>
       <c r="J63" t="n">
-        <v>27.14</v>
+        <v>-146.4</v>
       </c>
       <c r="K63" t="n">
-        <v>-258.07</v>
+        <v>-48.8</v>
       </c>
       <c r="L63" t="n">
-        <v>259.5</v>
+        <v>154.32</v>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>09:59:37</t>
+          <t>09:57:43</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
@@ -2725,34 +2725,34 @@
         <v>3</v>
       </c>
       <c r="E64" t="n">
-        <v>4.17</v>
+        <v>4.16</v>
       </c>
       <c r="F64" t="n">
-        <v>8.609999999999999</v>
+        <v>9.720000000000001</v>
       </c>
       <c r="G64" t="n">
-        <v>47.6</v>
+        <v>36.7</v>
       </c>
       <c r="H64" t="n">
-        <v>98.5</v>
+        <v>100</v>
       </c>
       <c r="I64" t="n">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="J64" t="n">
-        <v>-38.46</v>
+        <v>-62.56</v>
       </c>
       <c r="K64" t="n">
-        <v>384.23</v>
+        <v>-237.66</v>
       </c>
       <c r="L64" t="n">
-        <v>386.15</v>
+        <v>245.75</v>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>10:04:33</t>
+          <t>10:02:48</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
@@ -2767,34 +2767,34 @@
         <v>1</v>
       </c>
       <c r="E65" t="n">
-        <v>3.78</v>
+        <v>3.95</v>
       </c>
       <c r="F65" t="n">
-        <v>8.98</v>
+        <v>9.210000000000001</v>
       </c>
       <c r="G65" t="n">
-        <v>39.4</v>
+        <v>48.2</v>
       </c>
       <c r="H65" t="n">
-        <v>100</v>
+        <v>96.7</v>
       </c>
       <c r="I65" t="n">
-        <v>16</v>
+        <v>20</v>
       </c>
       <c r="J65" t="n">
-        <v>124.14</v>
+        <v>411.17</v>
       </c>
       <c r="K65" t="n">
-        <v>-36.99</v>
+        <v>196.94</v>
       </c>
       <c r="L65" t="n">
-        <v>129.54</v>
+        <v>455.9</v>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>10:06:38</t>
+          <t>10:04:41</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
@@ -2809,34 +2809,34 @@
         <v>2</v>
       </c>
       <c r="E66" t="n">
-        <v>4.18</v>
+        <v>4.43</v>
       </c>
       <c r="F66" t="n">
-        <v>9.19</v>
+        <v>9.539999999999999</v>
       </c>
       <c r="G66" t="n">
-        <v>36.7</v>
+        <v>44.3</v>
       </c>
       <c r="H66" t="n">
-        <v>96.7</v>
+        <v>100</v>
       </c>
       <c r="I66" t="n">
-        <v>16</v>
+        <v>19</v>
       </c>
       <c r="J66" t="n">
-        <v>-18.39</v>
+        <v>-5.86</v>
       </c>
       <c r="K66" t="n">
-        <v>-255.28</v>
+        <v>-192.16</v>
       </c>
       <c r="L66" t="n">
-        <v>255.94</v>
+        <v>192.25</v>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>10:08:36</t>
+          <t>10:06:40</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
@@ -2851,34 +2851,34 @@
         <v>3</v>
       </c>
       <c r="E67" t="n">
-        <v>4.71</v>
+        <v>4.44</v>
       </c>
       <c r="F67" t="n">
-        <v>9.039999999999999</v>
+        <v>9.32</v>
       </c>
       <c r="G67" t="n">
-        <v>54.9</v>
+        <v>40.3</v>
       </c>
       <c r="H67" t="n">
-        <v>100</v>
+        <v>96.7</v>
       </c>
       <c r="I67" t="n">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="J67" t="n">
-        <v>77.48</v>
+        <v>940.62</v>
       </c>
       <c r="K67" t="n">
-        <v>191.33</v>
+        <v>-682.6799999999999</v>
       </c>
       <c r="L67" t="n">
-        <v>206.43</v>
+        <v>1162.24</v>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>10:13:02</t>
+          <t>10:11:18</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
@@ -2893,34 +2893,34 @@
         <v>1</v>
       </c>
       <c r="E68" t="n">
-        <v>4.44</v>
+        <v>4.33</v>
       </c>
       <c r="F68" t="n">
-        <v>10.13</v>
+        <v>9.460000000000001</v>
       </c>
       <c r="G68" t="n">
-        <v>35</v>
+        <v>48.4</v>
       </c>
       <c r="H68" t="n">
-        <v>100</v>
+        <v>99.3</v>
       </c>
       <c r="I68" t="n">
-        <v>19</v>
+        <v>22</v>
       </c>
       <c r="J68" t="n">
-        <v>-224.59</v>
+        <v>63.78</v>
       </c>
       <c r="K68" t="n">
-        <v>-72.18000000000001</v>
+        <v>284.06</v>
       </c>
       <c r="L68" t="n">
-        <v>235.91</v>
+        <v>291.14</v>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>10:14:47</t>
+          <t>10:12:33</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
@@ -2935,34 +2935,34 @@
         <v>2</v>
       </c>
       <c r="E69" t="n">
-        <v>4.18</v>
+        <v>4.71</v>
       </c>
       <c r="F69" t="n">
-        <v>9.69</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="G69" t="n">
-        <v>35.4</v>
+        <v>50.2</v>
       </c>
       <c r="H69" t="n">
         <v>100</v>
       </c>
       <c r="I69" t="n">
-        <v>18</v>
+        <v>23</v>
       </c>
       <c r="J69" t="n">
-        <v>103.92</v>
+        <v>124</v>
       </c>
       <c r="K69" t="n">
-        <v>-304.43</v>
+        <v>-708.33</v>
       </c>
       <c r="L69" t="n">
-        <v>321.68</v>
+        <v>719.1</v>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>10:16:36</t>
+          <t>10:14:49</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
@@ -2977,34 +2977,34 @@
         <v>3</v>
       </c>
       <c r="E70" t="n">
-        <v>4.26</v>
+        <v>4.03</v>
       </c>
       <c r="F70" t="n">
-        <v>8.33</v>
+        <v>9.42</v>
       </c>
       <c r="G70" t="n">
-        <v>34.3</v>
+        <v>35.5</v>
       </c>
       <c r="H70" t="n">
-        <v>100</v>
+        <v>97.59999999999999</v>
       </c>
       <c r="I70" t="n">
-        <v>17</v>
+        <v>23</v>
       </c>
       <c r="J70" t="n">
-        <v>-466.01</v>
+        <v>78.98999999999999</v>
       </c>
       <c r="K70" t="n">
-        <v>-316.37</v>
+        <v>-386.06</v>
       </c>
       <c r="L70" t="n">
-        <v>563.25</v>
+        <v>394.06</v>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>10:21:33</t>
+          <t>10:20:31</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
@@ -3022,31 +3022,31 @@
         <v>3.95</v>
       </c>
       <c r="F71" t="n">
-        <v>9.77</v>
+        <v>9.17</v>
       </c>
       <c r="G71" t="n">
-        <v>44.4</v>
+        <v>54.9</v>
       </c>
       <c r="H71" t="n">
         <v>100</v>
       </c>
       <c r="I71" t="n">
-        <v>16</v>
+        <v>21</v>
       </c>
       <c r="J71" t="n">
-        <v>-278.35</v>
+        <v>-150.25</v>
       </c>
       <c r="K71" t="n">
-        <v>257.67</v>
+        <v>-288.3</v>
       </c>
       <c r="L71" t="n">
-        <v>379.31</v>
+        <v>325.11</v>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>10:23:20</t>
+          <t>10:22:45</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
@@ -3061,34 +3061,34 @@
         <v>2</v>
       </c>
       <c r="E72" t="n">
-        <v>4.28</v>
+        <v>4.33</v>
       </c>
       <c r="F72" t="n">
-        <v>8.550000000000001</v>
+        <v>9.43</v>
       </c>
       <c r="G72" t="n">
-        <v>50.1</v>
+        <v>31.1</v>
       </c>
       <c r="H72" t="n">
-        <v>100</v>
+        <v>96.8</v>
       </c>
       <c r="I72" t="n">
-        <v>16</v>
+        <v>23</v>
       </c>
       <c r="J72" t="n">
-        <v>-437.6</v>
+        <v>388.56</v>
       </c>
       <c r="K72" t="n">
-        <v>-945.4</v>
+        <v>795.99</v>
       </c>
       <c r="L72" t="n">
-        <v>1041.76</v>
+        <v>885.77</v>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>10:24:44</t>
+          <t>10:23:50</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
@@ -3103,34 +3103,34 @@
         <v>3</v>
       </c>
       <c r="E73" t="n">
-        <v>5.41</v>
+        <v>4.07</v>
       </c>
       <c r="F73" t="n">
-        <v>9.220000000000001</v>
+        <v>9.6</v>
       </c>
       <c r="G73" t="n">
-        <v>24.1</v>
+        <v>57.3</v>
       </c>
       <c r="H73" t="n">
-        <v>96.8</v>
+        <v>100</v>
       </c>
       <c r="I73" t="n">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="J73" t="n">
-        <v>82.23</v>
+        <v>-269.76</v>
       </c>
       <c r="K73" t="n">
-        <v>51.51</v>
+        <v>-16.3</v>
       </c>
       <c r="L73" t="n">
-        <v>97.03</v>
+        <v>270.26</v>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>10:36:35</t>
+          <t>10:35:56</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
@@ -3145,34 +3145,34 @@
         <v>1</v>
       </c>
       <c r="E74" t="n">
-        <v>4.6</v>
+        <v>4.03</v>
       </c>
       <c r="F74" t="n">
-        <v>9.75</v>
+        <v>9.210000000000001</v>
       </c>
       <c r="G74" t="n">
-        <v>46.4</v>
+        <v>44.3</v>
       </c>
       <c r="H74" t="n">
         <v>100</v>
       </c>
       <c r="I74" t="n">
-        <v>16</v>
+        <v>21</v>
       </c>
       <c r="J74" t="n">
-        <v>-418.2</v>
+        <v>80.40000000000001</v>
       </c>
       <c r="K74" t="n">
-        <v>-38.13</v>
+        <v>-30.32</v>
       </c>
       <c r="L74" t="n">
-        <v>419.94</v>
+        <v>85.93000000000001</v>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>10:37:58</t>
+          <t>10:38:23</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
@@ -3187,34 +3187,34 @@
         <v>2</v>
       </c>
       <c r="E75" t="n">
-        <v>4.24</v>
+        <v>3.97</v>
       </c>
       <c r="F75" t="n">
-        <v>9.44</v>
+        <v>9.23</v>
       </c>
       <c r="G75" t="n">
-        <v>43.2</v>
+        <v>37.4</v>
       </c>
       <c r="H75" t="n">
-        <v>97.7</v>
+        <v>94.5</v>
       </c>
       <c r="I75" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="J75" t="n">
-        <v>-32.37</v>
+        <v>-107.47</v>
       </c>
       <c r="K75" t="n">
-        <v>6.53</v>
+        <v>367.17</v>
       </c>
       <c r="L75" t="n">
-        <v>33.02</v>
+        <v>382.57</v>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>10:39:52</t>
+          <t>10:40:41</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
@@ -3229,34 +3229,34 @@
         <v>3</v>
       </c>
       <c r="E76" t="n">
-        <v>3.92</v>
+        <v>3.94</v>
       </c>
       <c r="F76" t="n">
-        <v>8.82</v>
+        <v>9.640000000000001</v>
       </c>
       <c r="G76" t="n">
-        <v>39.2</v>
+        <v>38.8</v>
       </c>
       <c r="H76" t="n">
-        <v>98.5</v>
+        <v>99.3</v>
       </c>
       <c r="I76" t="n">
-        <v>16</v>
+        <v>22</v>
       </c>
       <c r="J76" t="n">
-        <v>111.17</v>
+        <v>-125.43</v>
       </c>
       <c r="K76" t="n">
-        <v>-26.55</v>
+        <v>288.22</v>
       </c>
       <c r="L76" t="n">
-        <v>114.3</v>
+        <v>314.33</v>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>10:43:33</t>
+          <t>10:46:10</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
@@ -3271,34 +3271,34 @@
         <v>1</v>
       </c>
       <c r="E77" t="n">
-        <v>4.23</v>
+        <v>3.67</v>
       </c>
       <c r="F77" t="n">
-        <v>9.24</v>
+        <v>10.46</v>
       </c>
       <c r="G77" t="n">
-        <v>37.8</v>
+        <v>40.9</v>
       </c>
       <c r="H77" t="n">
         <v>100</v>
       </c>
       <c r="I77" t="n">
-        <v>16</v>
+        <v>24</v>
       </c>
       <c r="J77" t="n">
-        <v>71.45999999999999</v>
+        <v>-374.79</v>
       </c>
       <c r="K77" t="n">
-        <v>-131.79</v>
+        <v>-227.58</v>
       </c>
       <c r="L77" t="n">
-        <v>149.92</v>
+        <v>438.48</v>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>10:45:46</t>
+          <t>10:47:01</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
@@ -3313,34 +3313,34 @@
         <v>2</v>
       </c>
       <c r="E78" t="n">
-        <v>4.38</v>
+        <v>4.41</v>
       </c>
       <c r="F78" t="n">
-        <v>9.52</v>
+        <v>8.92</v>
       </c>
       <c r="G78" t="n">
-        <v>50.8</v>
+        <v>40.5</v>
       </c>
       <c r="H78" t="n">
-        <v>95.09999999999999</v>
+        <v>100</v>
       </c>
       <c r="I78" t="n">
-        <v>16</v>
+        <v>24</v>
       </c>
       <c r="J78" t="n">
-        <v>428.36</v>
+        <v>171.79</v>
       </c>
       <c r="K78" t="n">
-        <v>119.26</v>
+        <v>-383.73</v>
       </c>
       <c r="L78" t="n">
-        <v>444.65</v>
+        <v>420.43</v>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>10:47:32</t>
+          <t>10:48:16</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
@@ -3355,34 +3355,34 @@
         <v>3</v>
       </c>
       <c r="E79" t="n">
-        <v>5.03</v>
+        <v>4.65</v>
       </c>
       <c r="F79" t="n">
-        <v>9.66</v>
+        <v>9.210000000000001</v>
       </c>
       <c r="G79" t="n">
-        <v>45.3</v>
+        <v>48.5</v>
       </c>
       <c r="H79" t="n">
-        <v>93.09999999999999</v>
+        <v>94.40000000000001</v>
       </c>
       <c r="I79" t="n">
-        <v>17</v>
+        <v>24</v>
       </c>
       <c r="J79" t="n">
-        <v>150.7</v>
+        <v>398.11</v>
       </c>
       <c r="K79" t="n">
-        <v>85.17</v>
+        <v>-172.64</v>
       </c>
       <c r="L79" t="n">
-        <v>173.1</v>
+        <v>433.93</v>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>10:53:23</t>
+          <t>10:53:25</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
@@ -3397,34 +3397,34 @@
         <v>1</v>
       </c>
       <c r="E80" t="n">
-        <v>3.81</v>
+        <v>3.91</v>
       </c>
       <c r="F80" t="n">
-        <v>9.550000000000001</v>
+        <v>9.25</v>
       </c>
       <c r="G80" t="n">
-        <v>50</v>
+        <v>56</v>
       </c>
       <c r="H80" t="n">
-        <v>96.8</v>
+        <v>99.7</v>
       </c>
       <c r="I80" t="n">
-        <v>16</v>
+        <v>25</v>
       </c>
       <c r="J80" t="n">
-        <v>500.55</v>
+        <v>124.78</v>
       </c>
       <c r="K80" t="n">
-        <v>127.24</v>
+        <v>76.17</v>
       </c>
       <c r="L80" t="n">
-        <v>516.47</v>
+        <v>146.19</v>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>10:55:16</t>
+          <t>10:54:01</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
@@ -3439,34 +3439,34 @@
         <v>2</v>
       </c>
       <c r="E81" t="n">
-        <v>4.59</v>
+        <v>4.42</v>
       </c>
       <c r="F81" t="n">
-        <v>9.92</v>
+        <v>9.26</v>
       </c>
       <c r="G81" t="n">
-        <v>42.6</v>
+        <v>50.8</v>
       </c>
       <c r="H81" t="n">
-        <v>100</v>
+        <v>98.3</v>
       </c>
       <c r="I81" t="n">
-        <v>16</v>
+        <v>23</v>
       </c>
       <c r="J81" t="n">
-        <v>-248.51</v>
+        <v>216.63</v>
       </c>
       <c r="K81" t="n">
-        <v>-418.15</v>
+        <v>409.84</v>
       </c>
       <c r="L81" t="n">
-        <v>486.42</v>
+        <v>463.57</v>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>10:56:35</t>
+          <t>10:56:27</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
@@ -3481,34 +3481,34 @@
         <v>3</v>
       </c>
       <c r="E82" t="n">
-        <v>4.66</v>
+        <v>4.15</v>
       </c>
       <c r="F82" t="n">
-        <v>8.85</v>
+        <v>9.619999999999999</v>
       </c>
       <c r="G82" t="n">
-        <v>58.6</v>
+        <v>38.5</v>
       </c>
       <c r="H82" t="n">
-        <v>100</v>
+        <v>97.09999999999999</v>
       </c>
       <c r="I82" t="n">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="J82" t="n">
-        <v>-25.12</v>
+        <v>42.09</v>
       </c>
       <c r="K82" t="n">
-        <v>594.97</v>
+        <v>279.2</v>
       </c>
       <c r="L82" t="n">
-        <v>595.5</v>
+        <v>282.35</v>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>11:01:54</t>
+          <t>11:02:02</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
@@ -3523,34 +3523,34 @@
         <v>1</v>
       </c>
       <c r="E83" t="n">
-        <v>4.34</v>
+        <v>4.44</v>
       </c>
       <c r="F83" t="n">
-        <v>9.039999999999999</v>
+        <v>9.59</v>
       </c>
       <c r="G83" t="n">
-        <v>54.7</v>
+        <v>39.7</v>
       </c>
       <c r="H83" t="n">
-        <v>100</v>
+        <v>96.59999999999999</v>
       </c>
       <c r="I83" t="n">
-        <v>16</v>
+        <v>21</v>
       </c>
       <c r="J83" t="n">
-        <v>79.59999999999999</v>
+        <v>138.15</v>
       </c>
       <c r="K83" t="n">
-        <v>52.88</v>
+        <v>-321.13</v>
       </c>
       <c r="L83" t="n">
-        <v>95.56</v>
+        <v>349.58</v>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>11:04:00</t>
+          <t>11:04:17</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
@@ -3565,34 +3565,34 @@
         <v>2</v>
       </c>
       <c r="E84" t="n">
-        <v>4.93</v>
+        <v>4.71</v>
       </c>
       <c r="F84" t="n">
-        <v>9.380000000000001</v>
+        <v>9.75</v>
       </c>
       <c r="G84" t="n">
-        <v>36</v>
+        <v>58.6</v>
       </c>
       <c r="H84" t="n">
-        <v>96.90000000000001</v>
+        <v>100</v>
       </c>
       <c r="I84" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="J84" t="n">
-        <v>-155.81</v>
+        <v>314.18</v>
       </c>
       <c r="K84" t="n">
-        <v>245.87</v>
+        <v>114.94</v>
       </c>
       <c r="L84" t="n">
-        <v>291.09</v>
+        <v>334.54</v>
       </c>
     </row>
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>11:05:49</t>
+          <t>11:05:20</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
@@ -3607,34 +3607,34 @@
         <v>3</v>
       </c>
       <c r="E85" t="n">
-        <v>4.15</v>
+        <v>4.63</v>
       </c>
       <c r="F85" t="n">
-        <v>8.91</v>
+        <v>9.390000000000001</v>
       </c>
       <c r="G85" t="n">
-        <v>39.4</v>
+        <v>50.7</v>
       </c>
       <c r="H85" t="n">
-        <v>99.90000000000001</v>
+        <v>100</v>
       </c>
       <c r="I85" t="n">
         <v>19</v>
       </c>
       <c r="J85" t="n">
-        <v>90.05</v>
+        <v>401.8</v>
       </c>
       <c r="K85" t="n">
-        <v>-86.13</v>
+        <v>375.96</v>
       </c>
       <c r="L85" t="n">
-        <v>124.61</v>
+        <v>550.26</v>
       </c>
     </row>
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>11:10:15</t>
+          <t>11:10:09</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
@@ -3649,34 +3649,34 @@
         <v>1</v>
       </c>
       <c r="E86" t="n">
-        <v>4.01</v>
+        <v>4.61</v>
       </c>
       <c r="F86" t="n">
-        <v>9.49</v>
+        <v>9.58</v>
       </c>
       <c r="G86" t="n">
-        <v>28.3</v>
+        <v>38.8</v>
       </c>
       <c r="H86" t="n">
-        <v>100</v>
+        <v>96.7</v>
       </c>
       <c r="I86" t="n">
-        <v>16</v>
+        <v>20</v>
       </c>
       <c r="J86" t="n">
-        <v>787.92</v>
+        <v>491.58</v>
       </c>
       <c r="K86" t="n">
-        <v>-107.38</v>
+        <v>-290.21</v>
       </c>
       <c r="L86" t="n">
-        <v>795.21</v>
+        <v>570.86</v>
       </c>
     </row>
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>11:12:43</t>
+          <t>11:11:44</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
@@ -3691,34 +3691,34 @@
         <v>2</v>
       </c>
       <c r="E87" t="n">
-        <v>4.32</v>
+        <v>4.34</v>
       </c>
       <c r="F87" t="n">
-        <v>10.18</v>
+        <v>9.44</v>
       </c>
       <c r="G87" t="n">
-        <v>48.2</v>
+        <v>55</v>
       </c>
       <c r="H87" t="n">
-        <v>96.3</v>
+        <v>100</v>
       </c>
       <c r="I87" t="n">
-        <v>17</v>
+        <v>25</v>
       </c>
       <c r="J87" t="n">
-        <v>-728.53</v>
+        <v>9.720000000000001</v>
       </c>
       <c r="K87" t="n">
-        <v>378.56</v>
+        <v>136.93</v>
       </c>
       <c r="L87" t="n">
-        <v>821.02</v>
+        <v>137.27</v>
       </c>
     </row>
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>11:13:54</t>
+          <t>11:12:36</t>
         </is>
       </c>
       <c r="B88" t="inlineStr">
@@ -3733,28 +3733,28 @@
         <v>3</v>
       </c>
       <c r="E88" t="n">
-        <v>4.88</v>
+        <v>4.09</v>
       </c>
       <c r="F88" t="n">
-        <v>9.699999999999999</v>
+        <v>8.93</v>
       </c>
       <c r="G88" t="n">
-        <v>54.9</v>
+        <v>31.7</v>
       </c>
       <c r="H88" t="n">
-        <v>98.8</v>
+        <v>95.2</v>
       </c>
       <c r="I88" t="n">
-        <v>18</v>
+        <v>25</v>
       </c>
       <c r="J88" t="n">
-        <v>678.21</v>
+        <v>-318.06</v>
       </c>
       <c r="K88" t="n">
-        <v>220.24</v>
+        <v>-165.64</v>
       </c>
       <c r="L88" t="n">
-        <v>713.0700000000001</v>
+        <v>358.61</v>
       </c>
     </row>
   </sheetData>

--- a/output/2024-10-08.xlsx
+++ b/output/2024-10-08.xlsx
@@ -640,13 +640,13 @@
         <v>23</v>
       </c>
       <c r="J14" t="n">
-        <v>100.9</v>
+        <v>130.43</v>
       </c>
       <c r="K14" t="n">
-        <v>-54.23</v>
+        <v>-70.11</v>
       </c>
       <c r="L14" t="n">
-        <v>114.55</v>
+        <v>148.08</v>
       </c>
     </row>
     <row r="15">
@@ -682,13 +682,13 @@
         <v>23</v>
       </c>
       <c r="J15" t="n">
-        <v>-79.68000000000001</v>
+        <v>-105.32</v>
       </c>
       <c r="K15" t="n">
-        <v>108.5</v>
+        <v>143.41</v>
       </c>
       <c r="L15" t="n">
-        <v>134.62</v>
+        <v>177.93</v>
       </c>
     </row>
     <row r="16">
@@ -724,13 +724,13 @@
         <v>20</v>
       </c>
       <c r="J16" t="n">
-        <v>-110.69</v>
+        <v>-101.87</v>
       </c>
       <c r="K16" t="n">
-        <v>261.22</v>
+        <v>240.4</v>
       </c>
       <c r="L16" t="n">
-        <v>283.71</v>
+        <v>261.09</v>
       </c>
     </row>
     <row r="17">
@@ -766,13 +766,13 @@
         <v>25</v>
       </c>
       <c r="J17" t="n">
-        <v>-117.67</v>
+        <v>-120.45</v>
       </c>
       <c r="K17" t="n">
-        <v>118.07</v>
+        <v>120.86</v>
       </c>
       <c r="L17" t="n">
-        <v>166.69</v>
+        <v>170.63</v>
       </c>
     </row>
     <row r="18">
@@ -808,13 +808,13 @@
         <v>23</v>
       </c>
       <c r="J18" t="n">
-        <v>-94.64</v>
+        <v>-116.91</v>
       </c>
       <c r="K18" t="n">
-        <v>-118.78</v>
+        <v>-146.73</v>
       </c>
       <c r="L18" t="n">
-        <v>151.87</v>
+        <v>187.61</v>
       </c>
     </row>
     <row r="19">
@@ -850,13 +850,13 @@
         <v>19</v>
       </c>
       <c r="J19" t="n">
-        <v>242.16</v>
+        <v>312.55</v>
       </c>
       <c r="K19" t="n">
-        <v>24.91</v>
+        <v>32.15</v>
       </c>
       <c r="L19" t="n">
-        <v>243.44</v>
+        <v>314.2</v>
       </c>
     </row>
     <row r="20">
@@ -892,13 +892,13 @@
         <v>22</v>
       </c>
       <c r="J20" t="n">
-        <v>145.74</v>
+        <v>144.89</v>
       </c>
       <c r="K20" t="n">
-        <v>527.6</v>
+        <v>524.54</v>
       </c>
       <c r="L20" t="n">
-        <v>547.36</v>
+        <v>544.1799999999999</v>
       </c>
     </row>
     <row r="21">
@@ -934,13 +934,13 @@
         <v>25</v>
       </c>
       <c r="J21" t="n">
-        <v>510.63</v>
+        <v>436.27</v>
       </c>
       <c r="K21" t="n">
-        <v>38.99</v>
+        <v>33.31</v>
       </c>
       <c r="L21" t="n">
-        <v>512.11</v>
+        <v>437.54</v>
       </c>
     </row>
     <row r="22">
@@ -976,13 +976,13 @@
         <v>19</v>
       </c>
       <c r="J22" t="n">
-        <v>-22.81</v>
+        <v>-33.01</v>
       </c>
       <c r="K22" t="n">
-        <v>254</v>
+        <v>367.58</v>
       </c>
       <c r="L22" t="n">
-        <v>255.02</v>
+        <v>369.06</v>
       </c>
     </row>
     <row r="23">
@@ -1018,13 +1018,13 @@
         <v>22</v>
       </c>
       <c r="J23" t="n">
-        <v>-403.28</v>
+        <v>-460.51</v>
       </c>
       <c r="K23" t="n">
-        <v>-393.6</v>
+        <v>-449.45</v>
       </c>
       <c r="L23" t="n">
-        <v>563.52</v>
+        <v>643.49</v>
       </c>
     </row>
     <row r="24">
@@ -1060,13 +1060,13 @@
         <v>25</v>
       </c>
       <c r="J24" t="n">
-        <v>-0.34</v>
+        <v>-0.61</v>
       </c>
       <c r="K24" t="n">
-        <v>158.63</v>
+        <v>287.12</v>
       </c>
       <c r="L24" t="n">
-        <v>158.63</v>
+        <v>287.12</v>
       </c>
     </row>
     <row r="25">
@@ -1102,13 +1102,13 @@
         <v>23</v>
       </c>
       <c r="J25" t="n">
-        <v>-269.08</v>
+        <v>-373.88</v>
       </c>
       <c r="K25" t="n">
-        <v>159.92</v>
+        <v>222.21</v>
       </c>
       <c r="L25" t="n">
-        <v>313.01</v>
+        <v>434.93</v>
       </c>
     </row>
     <row r="26">
@@ -1144,13 +1144,13 @@
         <v>23</v>
       </c>
       <c r="J26" t="n">
-        <v>-722.11</v>
+        <v>-910.47</v>
       </c>
       <c r="K26" t="n">
-        <v>-68.72</v>
+        <v>-86.64</v>
       </c>
       <c r="L26" t="n">
-        <v>725.37</v>
+        <v>914.58</v>
       </c>
     </row>
     <row r="27">
@@ -1186,13 +1186,13 @@
         <v>20</v>
       </c>
       <c r="J27" t="n">
-        <v>24.83</v>
+        <v>40.45</v>
       </c>
       <c r="K27" t="n">
-        <v>442.88</v>
+        <v>721.5</v>
       </c>
       <c r="L27" t="n">
-        <v>443.58</v>
+        <v>722.64</v>
       </c>
     </row>
     <row r="28">
@@ -1228,13 +1228,13 @@
         <v>21</v>
       </c>
       <c r="J28" t="n">
-        <v>488.45</v>
+        <v>718.48</v>
       </c>
       <c r="K28" t="n">
-        <v>236.01</v>
+        <v>347.15</v>
       </c>
       <c r="L28" t="n">
-        <v>542.48</v>
+        <v>797.95</v>
       </c>
     </row>
     <row r="29">
@@ -1270,13 +1270,13 @@
         <v>24</v>
       </c>
       <c r="J29" t="n">
-        <v>58.04</v>
+        <v>59.56</v>
       </c>
       <c r="K29" t="n">
-        <v>-173.05</v>
+        <v>-177.57</v>
       </c>
       <c r="L29" t="n">
-        <v>182.52</v>
+        <v>187.29</v>
       </c>
     </row>
     <row r="30">
@@ -1312,13 +1312,13 @@
         <v>20</v>
       </c>
       <c r="J30" t="n">
-        <v>-19.34</v>
+        <v>-22.39</v>
       </c>
       <c r="K30" t="n">
-        <v>221.99</v>
+        <v>257.02</v>
       </c>
       <c r="L30" t="n">
-        <v>222.83</v>
+        <v>257.99</v>
       </c>
     </row>
     <row r="31">
@@ -1354,13 +1354,13 @@
         <v>24</v>
       </c>
       <c r="J31" t="n">
-        <v>31.89</v>
+        <v>45.47</v>
       </c>
       <c r="K31" t="n">
-        <v>-84.14</v>
+        <v>-119.98</v>
       </c>
       <c r="L31" t="n">
-        <v>89.98</v>
+        <v>128.31</v>
       </c>
     </row>
     <row r="32">
@@ -1396,13 +1396,13 @@
         <v>20</v>
       </c>
       <c r="J32" t="n">
-        <v>-382.18</v>
+        <v>-384.76</v>
       </c>
       <c r="K32" t="n">
-        <v>57.57</v>
+        <v>57.96</v>
       </c>
       <c r="L32" t="n">
-        <v>386.49</v>
+        <v>389.1</v>
       </c>
     </row>
     <row r="33">
@@ -1438,13 +1438,13 @@
         <v>20</v>
       </c>
       <c r="J33" t="n">
-        <v>147.43</v>
+        <v>162.59</v>
       </c>
       <c r="K33" t="n">
-        <v>-398.07</v>
+        <v>-439.02</v>
       </c>
       <c r="L33" t="n">
-        <v>424.49</v>
+        <v>468.16</v>
       </c>
     </row>
     <row r="34">
@@ -1480,13 +1480,13 @@
         <v>19</v>
       </c>
       <c r="J34" t="n">
-        <v>-74.73999999999999</v>
+        <v>-137.57</v>
       </c>
       <c r="K34" t="n">
-        <v>-80.39</v>
+        <v>-147.97</v>
       </c>
       <c r="L34" t="n">
-        <v>109.76</v>
+        <v>202.04</v>
       </c>
     </row>
     <row r="35">
@@ -1522,13 +1522,13 @@
         <v>22</v>
       </c>
       <c r="J35" t="n">
-        <v>19.54</v>
+        <v>24.85</v>
       </c>
       <c r="K35" t="n">
-        <v>289.57</v>
+        <v>368.31</v>
       </c>
       <c r="L35" t="n">
-        <v>290.23</v>
+        <v>369.15</v>
       </c>
     </row>
     <row r="36">
@@ -1564,13 +1564,13 @@
         <v>22</v>
       </c>
       <c r="J36" t="n">
-        <v>144.18</v>
+        <v>192.86</v>
       </c>
       <c r="K36" t="n">
-        <v>-225.51</v>
+        <v>-301.65</v>
       </c>
       <c r="L36" t="n">
-        <v>267.66</v>
+        <v>358.03</v>
       </c>
     </row>
     <row r="37">
@@ -1606,13 +1606,13 @@
         <v>25</v>
       </c>
       <c r="J37" t="n">
-        <v>-120.48</v>
+        <v>-183.5</v>
       </c>
       <c r="K37" t="n">
-        <v>92</v>
+        <v>140.12</v>
       </c>
       <c r="L37" t="n">
-        <v>151.59</v>
+        <v>230.88</v>
       </c>
     </row>
     <row r="38">
@@ -1648,13 +1648,13 @@
         <v>20</v>
       </c>
       <c r="J38" t="n">
-        <v>264.91</v>
+        <v>435.53</v>
       </c>
       <c r="K38" t="n">
-        <v>120.62</v>
+        <v>198.31</v>
       </c>
       <c r="L38" t="n">
-        <v>291.08</v>
+        <v>478.55</v>
       </c>
     </row>
     <row r="39">
@@ -1690,13 +1690,13 @@
         <v>23</v>
       </c>
       <c r="J39" t="n">
-        <v>-1.92</v>
+        <v>-2.41</v>
       </c>
       <c r="K39" t="n">
-        <v>537.58</v>
+        <v>674.85</v>
       </c>
       <c r="L39" t="n">
-        <v>537.58</v>
+        <v>674.85</v>
       </c>
     </row>
     <row r="40">
@@ -1732,13 +1732,13 @@
         <v>23</v>
       </c>
       <c r="J40" t="n">
-        <v>143.64</v>
+        <v>181.58</v>
       </c>
       <c r="K40" t="n">
-        <v>-560.17</v>
+        <v>-708.15</v>
       </c>
       <c r="L40" t="n">
-        <v>578.29</v>
+        <v>731.0599999999999</v>
       </c>
     </row>
     <row r="41">
@@ -1774,13 +1774,13 @@
         <v>21</v>
       </c>
       <c r="J41" t="n">
-        <v>-357.17</v>
+        <v>-664.4299999999999</v>
       </c>
       <c r="K41" t="n">
-        <v>-54.7</v>
+        <v>-101.76</v>
       </c>
       <c r="L41" t="n">
-        <v>361.34</v>
+        <v>672.17</v>
       </c>
     </row>
     <row r="42">
@@ -1816,13 +1816,13 @@
         <v>21</v>
       </c>
       <c r="J42" t="n">
-        <v>-362.22</v>
+        <v>-647.58</v>
       </c>
       <c r="K42" t="n">
-        <v>96.95999999999999</v>
+        <v>173.35</v>
       </c>
       <c r="L42" t="n">
-        <v>374.98</v>
+        <v>670.38</v>
       </c>
     </row>
     <row r="43">
@@ -1858,13 +1858,13 @@
         <v>24</v>
       </c>
       <c r="J43" t="n">
-        <v>-448.91</v>
+        <v>-631.63</v>
       </c>
       <c r="K43" t="n">
-        <v>-66.47</v>
+        <v>-93.53</v>
       </c>
       <c r="L43" t="n">
-        <v>453.8</v>
+        <v>638.52</v>
       </c>
     </row>
     <row r="44">
@@ -1900,13 +1900,13 @@
         <v>25</v>
       </c>
       <c r="J44" t="n">
-        <v>-167.18</v>
+        <v>-169.58</v>
       </c>
       <c r="K44" t="n">
-        <v>-118.12</v>
+        <v>-119.81</v>
       </c>
       <c r="L44" t="n">
-        <v>204.7</v>
+        <v>207.63</v>
       </c>
     </row>
     <row r="45">
@@ -1942,13 +1942,13 @@
         <v>22</v>
       </c>
       <c r="J45" t="n">
-        <v>-35.66</v>
+        <v>-67.3</v>
       </c>
       <c r="K45" t="n">
-        <v>49.4</v>
+        <v>93.23</v>
       </c>
       <c r="L45" t="n">
-        <v>60.93</v>
+        <v>114.98</v>
       </c>
     </row>
     <row r="46">
@@ -1984,13 +1984,13 @@
         <v>25</v>
       </c>
       <c r="J46" t="n">
-        <v>54.92</v>
+        <v>76.66</v>
       </c>
       <c r="K46" t="n">
-        <v>54.93</v>
+        <v>76.67</v>
       </c>
       <c r="L46" t="n">
-        <v>77.68000000000001</v>
+        <v>108.42</v>
       </c>
     </row>
     <row r="47">
@@ -2026,13 +2026,13 @@
         <v>19</v>
       </c>
       <c r="J47" t="n">
-        <v>-292.23</v>
+        <v>-329.01</v>
       </c>
       <c r="K47" t="n">
-        <v>-4.68</v>
+        <v>-5.27</v>
       </c>
       <c r="L47" t="n">
-        <v>292.26</v>
+        <v>329.05</v>
       </c>
     </row>
     <row r="48">
@@ -2068,13 +2068,13 @@
         <v>25</v>
       </c>
       <c r="J48" t="n">
-        <v>-150.92</v>
+        <v>-196.11</v>
       </c>
       <c r="K48" t="n">
-        <v>44.88</v>
+        <v>58.32</v>
       </c>
       <c r="L48" t="n">
-        <v>157.45</v>
+        <v>204.6</v>
       </c>
     </row>
     <row r="49">
@@ -2110,13 +2110,13 @@
         <v>23</v>
       </c>
       <c r="J49" t="n">
-        <v>-33.18</v>
+        <v>-32.67</v>
       </c>
       <c r="K49" t="n">
-        <v>300.29</v>
+        <v>295.68</v>
       </c>
       <c r="L49" t="n">
-        <v>302.12</v>
+        <v>297.48</v>
       </c>
     </row>
     <row r="50">
@@ -2152,13 +2152,13 @@
         <v>25</v>
       </c>
       <c r="J50" t="n">
-        <v>-456.41</v>
+        <v>-453.29</v>
       </c>
       <c r="K50" t="n">
-        <v>-314.78</v>
+        <v>-312.63</v>
       </c>
       <c r="L50" t="n">
-        <v>554.4400000000001</v>
+        <v>550.64</v>
       </c>
     </row>
     <row r="51">
@@ -2194,13 +2194,13 @@
         <v>19</v>
       </c>
       <c r="J51" t="n">
-        <v>5.72</v>
+        <v>8.19</v>
       </c>
       <c r="K51" t="n">
-        <v>-278.4</v>
+        <v>-398.42</v>
       </c>
       <c r="L51" t="n">
-        <v>278.46</v>
+        <v>398.5</v>
       </c>
     </row>
     <row r="52">
@@ -2236,13 +2236,13 @@
         <v>22</v>
       </c>
       <c r="J52" t="n">
-        <v>-200.92</v>
+        <v>-275.05</v>
       </c>
       <c r="K52" t="n">
-        <v>265.49</v>
+        <v>363.44</v>
       </c>
       <c r="L52" t="n">
-        <v>332.95</v>
+        <v>455.78</v>
       </c>
     </row>
     <row r="53">
@@ -2278,13 +2278,13 @@
         <v>21</v>
       </c>
       <c r="J53" t="n">
-        <v>568.12</v>
+        <v>710.7</v>
       </c>
       <c r="K53" t="n">
-        <v>-361.71</v>
+        <v>-452.49</v>
       </c>
       <c r="L53" t="n">
-        <v>673.5</v>
+        <v>842.52</v>
       </c>
     </row>
     <row r="54">
@@ -2320,13 +2320,13 @@
         <v>23</v>
       </c>
       <c r="J54" t="n">
-        <v>-298.94</v>
+        <v>-425.29</v>
       </c>
       <c r="K54" t="n">
-        <v>266.23</v>
+        <v>378.76</v>
       </c>
       <c r="L54" t="n">
-        <v>400.31</v>
+        <v>569.5</v>
       </c>
     </row>
     <row r="55">
@@ -2362,13 +2362,13 @@
         <v>23</v>
       </c>
       <c r="J55" t="n">
-        <v>-125.5</v>
+        <v>-165.25</v>
       </c>
       <c r="K55" t="n">
-        <v>-424.41</v>
+        <v>-558.8099999999999</v>
       </c>
       <c r="L55" t="n">
-        <v>442.57</v>
+        <v>582.73</v>
       </c>
     </row>
     <row r="56">
@@ -2404,13 +2404,13 @@
         <v>22</v>
       </c>
       <c r="J56" t="n">
-        <v>-366.93</v>
+        <v>-583.54</v>
       </c>
       <c r="K56" t="n">
-        <v>120.27</v>
+        <v>191.27</v>
       </c>
       <c r="L56" t="n">
-        <v>386.14</v>
+        <v>614.08</v>
       </c>
     </row>
     <row r="57">
@@ -2446,13 +2446,13 @@
         <v>22</v>
       </c>
       <c r="J57" t="n">
-        <v>-19.24</v>
+        <v>-34.86</v>
       </c>
       <c r="K57" t="n">
-        <v>-412.9</v>
+        <v>-748.02</v>
       </c>
       <c r="L57" t="n">
-        <v>413.35</v>
+        <v>748.83</v>
       </c>
     </row>
     <row r="58">
@@ -2488,13 +2488,13 @@
         <v>19</v>
       </c>
       <c r="J58" t="n">
-        <v>-582.8</v>
+        <v>-803.79</v>
       </c>
       <c r="K58" t="n">
-        <v>-615.03</v>
+        <v>-848.24</v>
       </c>
       <c r="L58" t="n">
-        <v>847.3</v>
+        <v>1168.58</v>
       </c>
     </row>
     <row r="59">
@@ -2530,13 +2530,13 @@
         <v>22</v>
       </c>
       <c r="J59" t="n">
-        <v>240.08</v>
+        <v>307.63</v>
       </c>
       <c r="K59" t="n">
-        <v>-8.35</v>
+        <v>-10.7</v>
       </c>
       <c r="L59" t="n">
-        <v>240.23</v>
+        <v>307.82</v>
       </c>
     </row>
     <row r="60">
@@ -2572,13 +2572,13 @@
         <v>20</v>
       </c>
       <c r="J60" t="n">
-        <v>229.2</v>
+        <v>243.2</v>
       </c>
       <c r="K60" t="n">
-        <v>204.64</v>
+        <v>217.14</v>
       </c>
       <c r="L60" t="n">
-        <v>307.26</v>
+        <v>326.03</v>
       </c>
     </row>
     <row r="61">
@@ -2614,13 +2614,13 @@
         <v>24</v>
       </c>
       <c r="J61" t="n">
-        <v>-64.31999999999999</v>
+        <v>-108.71</v>
       </c>
       <c r="K61" t="n">
-        <v>-39.22</v>
+        <v>-66.29000000000001</v>
       </c>
       <c r="L61" t="n">
-        <v>75.33</v>
+        <v>127.33</v>
       </c>
     </row>
     <row r="62">
@@ -2656,13 +2656,13 @@
         <v>22</v>
       </c>
       <c r="J62" t="n">
-        <v>-207.92</v>
+        <v>-229.03</v>
       </c>
       <c r="K62" t="n">
-        <v>-122.14</v>
+        <v>-134.54</v>
       </c>
       <c r="L62" t="n">
-        <v>241.14</v>
+        <v>265.63</v>
       </c>
     </row>
     <row r="63">
@@ -2698,13 +2698,13 @@
         <v>23</v>
       </c>
       <c r="J63" t="n">
-        <v>-146.4</v>
+        <v>-212.38</v>
       </c>
       <c r="K63" t="n">
-        <v>-48.8</v>
+        <v>-70.8</v>
       </c>
       <c r="L63" t="n">
-        <v>154.32</v>
+        <v>223.87</v>
       </c>
     </row>
     <row r="64">
@@ -2740,13 +2740,13 @@
         <v>19</v>
       </c>
       <c r="J64" t="n">
-        <v>-62.56</v>
+        <v>-80.73999999999999</v>
       </c>
       <c r="K64" t="n">
-        <v>-237.66</v>
+        <v>-306.74</v>
       </c>
       <c r="L64" t="n">
-        <v>245.75</v>
+        <v>317.18</v>
       </c>
     </row>
     <row r="65">
@@ -2782,13 +2782,13 @@
         <v>20</v>
       </c>
       <c r="J65" t="n">
-        <v>411.17</v>
+        <v>486.61</v>
       </c>
       <c r="K65" t="n">
-        <v>196.94</v>
+        <v>233.08</v>
       </c>
       <c r="L65" t="n">
-        <v>455.9</v>
+        <v>539.55</v>
       </c>
     </row>
     <row r="66">
@@ -2824,13 +2824,13 @@
         <v>19</v>
       </c>
       <c r="J66" t="n">
-        <v>-5.86</v>
+        <v>-10.84</v>
       </c>
       <c r="K66" t="n">
-        <v>-192.16</v>
+        <v>-355.67</v>
       </c>
       <c r="L66" t="n">
-        <v>192.25</v>
+        <v>355.84</v>
       </c>
     </row>
     <row r="67">
@@ -2866,13 +2866,13 @@
         <v>19</v>
       </c>
       <c r="J67" t="n">
-        <v>940.62</v>
+        <v>977.78</v>
       </c>
       <c r="K67" t="n">
-        <v>-682.6799999999999</v>
+        <v>-709.64</v>
       </c>
       <c r="L67" t="n">
-        <v>1162.24</v>
+        <v>1208.16</v>
       </c>
     </row>
     <row r="68">
@@ -2908,13 +2908,13 @@
         <v>22</v>
       </c>
       <c r="J68" t="n">
-        <v>63.78</v>
+        <v>108.02</v>
       </c>
       <c r="K68" t="n">
-        <v>284.06</v>
+        <v>481.12</v>
       </c>
       <c r="L68" t="n">
-        <v>291.14</v>
+        <v>493.09</v>
       </c>
     </row>
     <row r="69">
@@ -2950,13 +2950,13 @@
         <v>23</v>
       </c>
       <c r="J69" t="n">
-        <v>124</v>
+        <v>152.17</v>
       </c>
       <c r="K69" t="n">
-        <v>-708.33</v>
+        <v>-869.25</v>
       </c>
       <c r="L69" t="n">
-        <v>719.1</v>
+        <v>882.47</v>
       </c>
     </row>
     <row r="70">
@@ -2992,13 +2992,13 @@
         <v>23</v>
       </c>
       <c r="J70" t="n">
-        <v>78.98999999999999</v>
+        <v>108.25</v>
       </c>
       <c r="K70" t="n">
-        <v>-386.06</v>
+        <v>-529.11</v>
       </c>
       <c r="L70" t="n">
-        <v>394.06</v>
+        <v>540.0700000000001</v>
       </c>
     </row>
     <row r="71">
@@ -3034,13 +3034,13 @@
         <v>21</v>
       </c>
       <c r="J71" t="n">
-        <v>-150.25</v>
+        <v>-275.58</v>
       </c>
       <c r="K71" t="n">
-        <v>-288.3</v>
+        <v>-528.78</v>
       </c>
       <c r="L71" t="n">
-        <v>325.11</v>
+        <v>596.28</v>
       </c>
     </row>
     <row r="72">
@@ -3076,13 +3076,13 @@
         <v>23</v>
       </c>
       <c r="J72" t="n">
-        <v>388.56</v>
+        <v>475.87</v>
       </c>
       <c r="K72" t="n">
-        <v>795.99</v>
+        <v>974.84</v>
       </c>
       <c r="L72" t="n">
-        <v>885.77</v>
+        <v>1084.79</v>
       </c>
     </row>
     <row r="73">
@@ -3118,13 +3118,13 @@
         <v>20</v>
       </c>
       <c r="J73" t="n">
-        <v>-269.76</v>
+        <v>-573.85</v>
       </c>
       <c r="K73" t="n">
-        <v>-16.3</v>
+        <v>-34.67</v>
       </c>
       <c r="L73" t="n">
-        <v>270.26</v>
+        <v>574.9</v>
       </c>
     </row>
     <row r="74">
@@ -3160,13 +3160,13 @@
         <v>21</v>
       </c>
       <c r="J74" t="n">
-        <v>80.40000000000001</v>
+        <v>142.06</v>
       </c>
       <c r="K74" t="n">
-        <v>-30.32</v>
+        <v>-53.57</v>
       </c>
       <c r="L74" t="n">
-        <v>85.93000000000001</v>
+        <v>151.83</v>
       </c>
     </row>
     <row r="75">
@@ -3202,13 +3202,13 @@
         <v>20</v>
       </c>
       <c r="J75" t="n">
-        <v>-107.47</v>
+        <v>-106.28</v>
       </c>
       <c r="K75" t="n">
-        <v>367.17</v>
+        <v>363.09</v>
       </c>
       <c r="L75" t="n">
-        <v>382.57</v>
+        <v>378.33</v>
       </c>
     </row>
     <row r="76">
@@ -3244,13 +3244,13 @@
         <v>22</v>
       </c>
       <c r="J76" t="n">
-        <v>-125.43</v>
+        <v>-123.13</v>
       </c>
       <c r="K76" t="n">
-        <v>288.22</v>
+        <v>282.94</v>
       </c>
       <c r="L76" t="n">
-        <v>314.33</v>
+        <v>308.57</v>
       </c>
     </row>
     <row r="77">
@@ -3286,13 +3286,13 @@
         <v>24</v>
       </c>
       <c r="J77" t="n">
-        <v>-374.79</v>
+        <v>-328.34</v>
       </c>
       <c r="K77" t="n">
-        <v>-227.58</v>
+        <v>-199.38</v>
       </c>
       <c r="L77" t="n">
-        <v>438.48</v>
+        <v>384.13</v>
       </c>
     </row>
     <row r="78">
@@ -3328,13 +3328,13 @@
         <v>24</v>
       </c>
       <c r="J78" t="n">
-        <v>171.79</v>
+        <v>169.8</v>
       </c>
       <c r="K78" t="n">
-        <v>-383.73</v>
+        <v>-379.29</v>
       </c>
       <c r="L78" t="n">
-        <v>420.43</v>
+        <v>415.57</v>
       </c>
     </row>
     <row r="79">
@@ -3370,13 +3370,13 @@
         <v>24</v>
       </c>
       <c r="J79" t="n">
-        <v>398.11</v>
+        <v>399.62</v>
       </c>
       <c r="K79" t="n">
-        <v>-172.64</v>
+        <v>-173.3</v>
       </c>
       <c r="L79" t="n">
-        <v>433.93</v>
+        <v>435.58</v>
       </c>
     </row>
     <row r="80">
@@ -3412,13 +3412,13 @@
         <v>25</v>
       </c>
       <c r="J80" t="n">
-        <v>124.78</v>
+        <v>200.8</v>
       </c>
       <c r="K80" t="n">
-        <v>76.17</v>
+        <v>122.57</v>
       </c>
       <c r="L80" t="n">
-        <v>146.19</v>
+        <v>235.25</v>
       </c>
     </row>
     <row r="81">
@@ -3454,13 +3454,13 @@
         <v>23</v>
       </c>
       <c r="J81" t="n">
-        <v>216.63</v>
+        <v>248.94</v>
       </c>
       <c r="K81" t="n">
-        <v>409.84</v>
+        <v>470.97</v>
       </c>
       <c r="L81" t="n">
-        <v>463.57</v>
+        <v>532.72</v>
       </c>
     </row>
     <row r="82">
@@ -3496,13 +3496,13 @@
         <v>20</v>
       </c>
       <c r="J82" t="n">
-        <v>42.09</v>
+        <v>60.9</v>
       </c>
       <c r="K82" t="n">
-        <v>279.2</v>
+        <v>403.97</v>
       </c>
       <c r="L82" t="n">
-        <v>282.35</v>
+        <v>408.54</v>
       </c>
     </row>
     <row r="83">
@@ -3538,13 +3538,13 @@
         <v>21</v>
       </c>
       <c r="J83" t="n">
-        <v>138.15</v>
+        <v>227.05</v>
       </c>
       <c r="K83" t="n">
-        <v>-321.13</v>
+        <v>-527.78</v>
       </c>
       <c r="L83" t="n">
-        <v>349.58</v>
+        <v>574.55</v>
       </c>
     </row>
     <row r="84">
@@ -3580,13 +3580,13 @@
         <v>19</v>
       </c>
       <c r="J84" t="n">
-        <v>314.18</v>
+        <v>580</v>
       </c>
       <c r="K84" t="n">
-        <v>114.94</v>
+        <v>212.18</v>
       </c>
       <c r="L84" t="n">
-        <v>334.54</v>
+        <v>617.59</v>
       </c>
     </row>
     <row r="85">
@@ -3622,13 +3622,13 @@
         <v>19</v>
       </c>
       <c r="J85" t="n">
-        <v>401.8</v>
+        <v>596.22</v>
       </c>
       <c r="K85" t="n">
-        <v>375.96</v>
+        <v>557.87</v>
       </c>
       <c r="L85" t="n">
-        <v>550.26</v>
+        <v>816.51</v>
       </c>
     </row>
     <row r="86">
@@ -3664,13 +3664,13 @@
         <v>20</v>
       </c>
       <c r="J86" t="n">
-        <v>491.58</v>
+        <v>792.34</v>
       </c>
       <c r="K86" t="n">
-        <v>-290.21</v>
+        <v>-467.76</v>
       </c>
       <c r="L86" t="n">
-        <v>570.86</v>
+        <v>920.11</v>
       </c>
     </row>
     <row r="87">
@@ -3706,13 +3706,13 @@
         <v>25</v>
       </c>
       <c r="J87" t="n">
-        <v>9.720000000000001</v>
+        <v>27.67</v>
       </c>
       <c r="K87" t="n">
-        <v>136.93</v>
+        <v>389.72</v>
       </c>
       <c r="L87" t="n">
-        <v>137.27</v>
+        <v>390.7</v>
       </c>
     </row>
     <row r="88">
@@ -3748,13 +3748,13 @@
         <v>25</v>
       </c>
       <c r="J88" t="n">
-        <v>-318.06</v>
+        <v>-495.19</v>
       </c>
       <c r="K88" t="n">
-        <v>-165.64</v>
+        <v>-257.88</v>
       </c>
       <c r="L88" t="n">
-        <v>358.61</v>
+        <v>558.3099999999999</v>
       </c>
     </row>
   </sheetData>

--- a/output/2024-10-08.xlsx
+++ b/output/2024-10-08.xlsx
@@ -640,13 +640,13 @@
         <v>23</v>
       </c>
       <c r="J14" t="n">
-        <v>130.43</v>
+        <v>98.16</v>
       </c>
       <c r="K14" t="n">
-        <v>-70.11</v>
+        <v>-52.76</v>
       </c>
       <c r="L14" t="n">
-        <v>148.08</v>
+        <v>111.44</v>
       </c>
     </row>
     <row r="15">
@@ -682,13 +682,13 @@
         <v>23</v>
       </c>
       <c r="J15" t="n">
-        <v>-105.32</v>
+        <v>-77.31</v>
       </c>
       <c r="K15" t="n">
-        <v>143.41</v>
+        <v>105.27</v>
       </c>
       <c r="L15" t="n">
-        <v>177.93</v>
+        <v>130.61</v>
       </c>
     </row>
     <row r="16">
@@ -724,13 +724,13 @@
         <v>20</v>
       </c>
       <c r="J16" t="n">
-        <v>-101.87</v>
+        <v>-72.43000000000001</v>
       </c>
       <c r="K16" t="n">
-        <v>240.4</v>
+        <v>170.93</v>
       </c>
       <c r="L16" t="n">
-        <v>261.09</v>
+        <v>185.65</v>
       </c>
     </row>
     <row r="17">
@@ -766,13 +766,13 @@
         <v>25</v>
       </c>
       <c r="J17" t="n">
-        <v>-120.45</v>
+        <v>-95.28</v>
       </c>
       <c r="K17" t="n">
-        <v>120.86</v>
+        <v>95.59999999999999</v>
       </c>
       <c r="L17" t="n">
-        <v>170.63</v>
+        <v>134.97</v>
       </c>
     </row>
     <row r="18">
@@ -808,13 +808,13 @@
         <v>23</v>
       </c>
       <c r="J18" t="n">
-        <v>-116.91</v>
+        <v>-84.15000000000001</v>
       </c>
       <c r="K18" t="n">
-        <v>-146.73</v>
+        <v>-105.62</v>
       </c>
       <c r="L18" t="n">
-        <v>187.61</v>
+        <v>135.04</v>
       </c>
     </row>
     <row r="19">
@@ -850,13 +850,13 @@
         <v>19</v>
       </c>
       <c r="J19" t="n">
-        <v>312.55</v>
+        <v>193.96</v>
       </c>
       <c r="K19" t="n">
-        <v>32.15</v>
+        <v>19.95</v>
       </c>
       <c r="L19" t="n">
-        <v>314.2</v>
+        <v>194.99</v>
       </c>
     </row>
     <row r="20">
@@ -892,13 +892,13 @@
         <v>22</v>
       </c>
       <c r="J20" t="n">
-        <v>144.89</v>
+        <v>88.67</v>
       </c>
       <c r="K20" t="n">
-        <v>524.54</v>
+        <v>320.99</v>
       </c>
       <c r="L20" t="n">
-        <v>544.1799999999999</v>
+        <v>333.01</v>
       </c>
     </row>
     <row r="21">
@@ -934,13 +934,13 @@
         <v>25</v>
       </c>
       <c r="J21" t="n">
-        <v>436.27</v>
+        <v>304.73</v>
       </c>
       <c r="K21" t="n">
-        <v>33.31</v>
+        <v>23.27</v>
       </c>
       <c r="L21" t="n">
-        <v>437.54</v>
+        <v>305.62</v>
       </c>
     </row>
     <row r="22">
@@ -976,13 +976,13 @@
         <v>19</v>
       </c>
       <c r="J22" t="n">
-        <v>-33.01</v>
+        <v>-18.27</v>
       </c>
       <c r="K22" t="n">
-        <v>367.58</v>
+        <v>203.48</v>
       </c>
       <c r="L22" t="n">
-        <v>369.06</v>
+        <v>204.3</v>
       </c>
     </row>
     <row r="23">
@@ -1018,13 +1018,13 @@
         <v>22</v>
       </c>
       <c r="J23" t="n">
-        <v>-460.51</v>
+        <v>-248.87</v>
       </c>
       <c r="K23" t="n">
-        <v>-449.45</v>
+        <v>-242.9</v>
       </c>
       <c r="L23" t="n">
-        <v>643.49</v>
+        <v>347.76</v>
       </c>
     </row>
     <row r="24">
@@ -1060,13 +1060,13 @@
         <v>25</v>
       </c>
       <c r="J24" t="n">
-        <v>-0.61</v>
+        <v>-0.36</v>
       </c>
       <c r="K24" t="n">
-        <v>287.12</v>
+        <v>170.39</v>
       </c>
       <c r="L24" t="n">
-        <v>287.12</v>
+        <v>170.39</v>
       </c>
     </row>
     <row r="25">
@@ -1102,13 +1102,13 @@
         <v>23</v>
       </c>
       <c r="J25" t="n">
-        <v>-373.88</v>
+        <v>-207.08</v>
       </c>
       <c r="K25" t="n">
-        <v>222.21</v>
+        <v>123.07</v>
       </c>
       <c r="L25" t="n">
-        <v>434.93</v>
+        <v>240.9</v>
       </c>
     </row>
     <row r="26">
@@ -1144,13 +1144,13 @@
         <v>23</v>
       </c>
       <c r="J26" t="n">
-        <v>-910.47</v>
+        <v>-455.12</v>
       </c>
       <c r="K26" t="n">
-        <v>-86.64</v>
+        <v>-43.31</v>
       </c>
       <c r="L26" t="n">
-        <v>914.58</v>
+        <v>457.17</v>
       </c>
     </row>
     <row r="27">
@@ -1186,13 +1186,13 @@
         <v>20</v>
       </c>
       <c r="J27" t="n">
-        <v>40.45</v>
+        <v>18.55</v>
       </c>
       <c r="K27" t="n">
-        <v>721.5</v>
+        <v>330.9</v>
       </c>
       <c r="L27" t="n">
-        <v>722.64</v>
+        <v>331.42</v>
       </c>
     </row>
     <row r="28">
@@ -1228,13 +1228,13 @@
         <v>21</v>
       </c>
       <c r="J28" t="n">
-        <v>718.48</v>
+        <v>338.17</v>
       </c>
       <c r="K28" t="n">
-        <v>347.15</v>
+        <v>163.4</v>
       </c>
       <c r="L28" t="n">
-        <v>797.95</v>
+        <v>375.58</v>
       </c>
     </row>
     <row r="29">
@@ -1270,13 +1270,13 @@
         <v>24</v>
       </c>
       <c r="J29" t="n">
-        <v>59.56</v>
+        <v>47.07</v>
       </c>
       <c r="K29" t="n">
-        <v>-177.57</v>
+        <v>-140.35</v>
       </c>
       <c r="L29" t="n">
-        <v>187.29</v>
+        <v>148.04</v>
       </c>
     </row>
     <row r="30">
@@ -1312,13 +1312,13 @@
         <v>20</v>
       </c>
       <c r="J30" t="n">
-        <v>-22.39</v>
+        <v>-15.11</v>
       </c>
       <c r="K30" t="n">
-        <v>257.02</v>
+        <v>173.48</v>
       </c>
       <c r="L30" t="n">
-        <v>257.99</v>
+        <v>174.13</v>
       </c>
     </row>
     <row r="31">
@@ -1354,13 +1354,13 @@
         <v>24</v>
       </c>
       <c r="J31" t="n">
-        <v>45.47</v>
+        <v>35.29</v>
       </c>
       <c r="K31" t="n">
-        <v>-119.98</v>
+        <v>-93.13</v>
       </c>
       <c r="L31" t="n">
-        <v>128.31</v>
+        <v>99.59</v>
       </c>
     </row>
     <row r="32">
@@ -1396,13 +1396,13 @@
         <v>20</v>
       </c>
       <c r="J32" t="n">
-        <v>-384.76</v>
+        <v>-251.43</v>
       </c>
       <c r="K32" t="n">
-        <v>57.96</v>
+        <v>37.88</v>
       </c>
       <c r="L32" t="n">
-        <v>389.1</v>
+        <v>254.27</v>
       </c>
     </row>
     <row r="33">
@@ -1438,13 +1438,13 @@
         <v>20</v>
       </c>
       <c r="J33" t="n">
-        <v>162.59</v>
+        <v>102.39</v>
       </c>
       <c r="K33" t="n">
-        <v>-439.02</v>
+        <v>-276.47</v>
       </c>
       <c r="L33" t="n">
-        <v>468.16</v>
+        <v>294.83</v>
       </c>
     </row>
     <row r="34">
@@ -1480,13 +1480,13 @@
         <v>19</v>
       </c>
       <c r="J34" t="n">
-        <v>-137.57</v>
+        <v>-85.79000000000001</v>
       </c>
       <c r="K34" t="n">
-        <v>-147.97</v>
+        <v>-92.27</v>
       </c>
       <c r="L34" t="n">
-        <v>202.04</v>
+        <v>125.99</v>
       </c>
     </row>
     <row r="35">
@@ -1522,13 +1522,13 @@
         <v>22</v>
       </c>
       <c r="J35" t="n">
-        <v>24.85</v>
+        <v>14.95</v>
       </c>
       <c r="K35" t="n">
-        <v>368.31</v>
+        <v>221.48</v>
       </c>
       <c r="L35" t="n">
-        <v>369.15</v>
+        <v>221.98</v>
       </c>
     </row>
     <row r="36">
@@ -1564,13 +1564,13 @@
         <v>22</v>
       </c>
       <c r="J36" t="n">
-        <v>192.86</v>
+        <v>115.36</v>
       </c>
       <c r="K36" t="n">
-        <v>-301.65</v>
+        <v>-180.43</v>
       </c>
       <c r="L36" t="n">
-        <v>358.03</v>
+        <v>214.15</v>
       </c>
     </row>
     <row r="37">
@@ -1606,13 +1606,13 @@
         <v>25</v>
       </c>
       <c r="J37" t="n">
-        <v>-183.5</v>
+        <v>-122.41</v>
       </c>
       <c r="K37" t="n">
-        <v>140.12</v>
+        <v>93.47</v>
       </c>
       <c r="L37" t="n">
-        <v>230.88</v>
+        <v>154.02</v>
       </c>
     </row>
     <row r="38">
@@ -1648,13 +1648,13 @@
         <v>20</v>
       </c>
       <c r="J38" t="n">
-        <v>435.53</v>
+        <v>218.08</v>
       </c>
       <c r="K38" t="n">
-        <v>198.31</v>
+        <v>99.3</v>
       </c>
       <c r="L38" t="n">
-        <v>478.55</v>
+        <v>239.63</v>
       </c>
     </row>
     <row r="39">
@@ -1690,13 +1690,13 @@
         <v>23</v>
       </c>
       <c r="J39" t="n">
-        <v>-2.41</v>
+        <v>-1.3</v>
       </c>
       <c r="K39" t="n">
-        <v>674.85</v>
+        <v>363.98</v>
       </c>
       <c r="L39" t="n">
-        <v>674.85</v>
+        <v>363.98</v>
       </c>
     </row>
     <row r="40">
@@ -1732,13 +1732,13 @@
         <v>23</v>
       </c>
       <c r="J40" t="n">
-        <v>181.58</v>
+        <v>97.12</v>
       </c>
       <c r="K40" t="n">
-        <v>-708.15</v>
+        <v>-378.74</v>
       </c>
       <c r="L40" t="n">
-        <v>731.0599999999999</v>
+        <v>390.99</v>
       </c>
     </row>
     <row r="41">
@@ -1774,13 +1774,13 @@
         <v>21</v>
       </c>
       <c r="J41" t="n">
-        <v>-664.4299999999999</v>
+        <v>-313.91</v>
       </c>
       <c r="K41" t="n">
-        <v>-101.76</v>
+        <v>-48.08</v>
       </c>
       <c r="L41" t="n">
-        <v>672.17</v>
+        <v>317.57</v>
       </c>
     </row>
     <row r="42">
@@ -1816,13 +1816,13 @@
         <v>21</v>
       </c>
       <c r="J42" t="n">
-        <v>-647.58</v>
+        <v>-302.26</v>
       </c>
       <c r="K42" t="n">
-        <v>173.35</v>
+        <v>80.91</v>
       </c>
       <c r="L42" t="n">
-        <v>670.38</v>
+        <v>312.9</v>
       </c>
     </row>
     <row r="43">
@@ -1858,13 +1858,13 @@
         <v>24</v>
       </c>
       <c r="J43" t="n">
-        <v>-631.63</v>
+        <v>-328.99</v>
       </c>
       <c r="K43" t="n">
-        <v>-93.53</v>
+        <v>-48.71</v>
       </c>
       <c r="L43" t="n">
-        <v>638.52</v>
+        <v>332.57</v>
       </c>
     </row>
     <row r="44">
@@ -1900,13 +1900,13 @@
         <v>25</v>
       </c>
       <c r="J44" t="n">
-        <v>-169.58</v>
+        <v>-134.62</v>
       </c>
       <c r="K44" t="n">
-        <v>-119.81</v>
+        <v>-95.11</v>
       </c>
       <c r="L44" t="n">
-        <v>207.63</v>
+        <v>164.83</v>
       </c>
     </row>
     <row r="45">
@@ -1942,13 +1942,13 @@
         <v>22</v>
       </c>
       <c r="J45" t="n">
-        <v>-67.3</v>
+        <v>-49.15</v>
       </c>
       <c r="K45" t="n">
-        <v>93.23</v>
+        <v>68.08</v>
       </c>
       <c r="L45" t="n">
-        <v>114.98</v>
+        <v>83.97</v>
       </c>
     </row>
     <row r="46">
@@ -1984,13 +1984,13 @@
         <v>25</v>
       </c>
       <c r="J46" t="n">
-        <v>76.66</v>
+        <v>62.65</v>
       </c>
       <c r="K46" t="n">
-        <v>76.67</v>
+        <v>62.66</v>
       </c>
       <c r="L46" t="n">
-        <v>108.42</v>
+        <v>88.59999999999999</v>
       </c>
     </row>
     <row r="47">
@@ -2026,13 +2026,13 @@
         <v>19</v>
       </c>
       <c r="J47" t="n">
-        <v>-329.01</v>
+        <v>-208.68</v>
       </c>
       <c r="K47" t="n">
-        <v>-5.27</v>
+        <v>-3.34</v>
       </c>
       <c r="L47" t="n">
-        <v>329.05</v>
+        <v>208.71</v>
       </c>
     </row>
     <row r="48">
@@ -2068,13 +2068,13 @@
         <v>25</v>
       </c>
       <c r="J48" t="n">
-        <v>-196.11</v>
+        <v>-146.13</v>
       </c>
       <c r="K48" t="n">
-        <v>58.32</v>
+        <v>43.45</v>
       </c>
       <c r="L48" t="n">
-        <v>204.6</v>
+        <v>152.45</v>
       </c>
     </row>
     <row r="49">
@@ -2110,13 +2110,13 @@
         <v>23</v>
       </c>
       <c r="J49" t="n">
-        <v>-32.67</v>
+        <v>-23.41</v>
       </c>
       <c r="K49" t="n">
-        <v>295.68</v>
+        <v>211.85</v>
       </c>
       <c r="L49" t="n">
-        <v>297.48</v>
+        <v>213.14</v>
       </c>
     </row>
     <row r="50">
@@ -2152,13 +2152,13 @@
         <v>25</v>
       </c>
       <c r="J50" t="n">
-        <v>-453.29</v>
+        <v>-297.29</v>
       </c>
       <c r="K50" t="n">
-        <v>-312.63</v>
+        <v>-205.04</v>
       </c>
       <c r="L50" t="n">
-        <v>550.64</v>
+        <v>361.14</v>
       </c>
     </row>
     <row r="51">
@@ -2194,13 +2194,13 @@
         <v>19</v>
       </c>
       <c r="J51" t="n">
-        <v>8.19</v>
+        <v>4.5</v>
       </c>
       <c r="K51" t="n">
-        <v>-398.42</v>
+        <v>-219.06</v>
       </c>
       <c r="L51" t="n">
-        <v>398.5</v>
+        <v>219.11</v>
       </c>
     </row>
     <row r="52">
@@ -2236,13 +2236,13 @@
         <v>22</v>
       </c>
       <c r="J52" t="n">
-        <v>-275.05</v>
+        <v>-159.66</v>
       </c>
       <c r="K52" t="n">
-        <v>363.44</v>
+        <v>210.97</v>
       </c>
       <c r="L52" t="n">
-        <v>455.78</v>
+        <v>264.58</v>
       </c>
     </row>
     <row r="53">
@@ -2278,13 +2278,13 @@
         <v>21</v>
       </c>
       <c r="J53" t="n">
-        <v>710.7</v>
+        <v>359.61</v>
       </c>
       <c r="K53" t="n">
-        <v>-452.49</v>
+        <v>-228.95</v>
       </c>
       <c r="L53" t="n">
-        <v>842.52</v>
+        <v>426.31</v>
       </c>
     </row>
     <row r="54">
@@ -2320,13 +2320,13 @@
         <v>23</v>
       </c>
       <c r="J54" t="n">
-        <v>-425.29</v>
+        <v>-228.13</v>
       </c>
       <c r="K54" t="n">
-        <v>378.76</v>
+        <v>203.17</v>
       </c>
       <c r="L54" t="n">
-        <v>569.5</v>
+        <v>305.49</v>
       </c>
     </row>
     <row r="55">
@@ -2362,13 +2362,13 @@
         <v>23</v>
       </c>
       <c r="J55" t="n">
-        <v>-165.25</v>
+        <v>-89.56999999999999</v>
       </c>
       <c r="K55" t="n">
-        <v>-558.8099999999999</v>
+        <v>-302.9</v>
       </c>
       <c r="L55" t="n">
-        <v>582.73</v>
+        <v>315.86</v>
       </c>
     </row>
     <row r="56">
@@ -2404,13 +2404,13 @@
         <v>22</v>
       </c>
       <c r="J56" t="n">
-        <v>-583.54</v>
+        <v>-285.63</v>
       </c>
       <c r="K56" t="n">
-        <v>191.27</v>
+        <v>93.62</v>
       </c>
       <c r="L56" t="n">
-        <v>614.08</v>
+        <v>300.58</v>
       </c>
     </row>
     <row r="57">
@@ -2446,13 +2446,13 @@
         <v>22</v>
       </c>
       <c r="J57" t="n">
-        <v>-34.86</v>
+        <v>-16.24</v>
       </c>
       <c r="K57" t="n">
-        <v>-748.02</v>
+        <v>-348.54</v>
       </c>
       <c r="L57" t="n">
-        <v>748.83</v>
+        <v>348.92</v>
       </c>
     </row>
     <row r="58">
@@ -2488,13 +2488,13 @@
         <v>19</v>
       </c>
       <c r="J58" t="n">
-        <v>-803.79</v>
+        <v>-354.64</v>
       </c>
       <c r="K58" t="n">
-        <v>-848.24</v>
+        <v>-374.25</v>
       </c>
       <c r="L58" t="n">
-        <v>1168.58</v>
+        <v>515.59</v>
       </c>
     </row>
     <row r="59">
@@ -2530,13 +2530,13 @@
         <v>22</v>
       </c>
       <c r="J59" t="n">
-        <v>307.63</v>
+        <v>209.79</v>
       </c>
       <c r="K59" t="n">
-        <v>-10.7</v>
+        <v>-7.3</v>
       </c>
       <c r="L59" t="n">
-        <v>307.82</v>
+        <v>209.92</v>
       </c>
     </row>
     <row r="60">
@@ -2572,13 +2572,13 @@
         <v>20</v>
       </c>
       <c r="J60" t="n">
-        <v>243.2</v>
+        <v>163.44</v>
       </c>
       <c r="K60" t="n">
-        <v>217.14</v>
+        <v>145.93</v>
       </c>
       <c r="L60" t="n">
-        <v>326.03</v>
+        <v>219.1</v>
       </c>
     </row>
     <row r="61">
@@ -2614,13 +2614,13 @@
         <v>24</v>
       </c>
       <c r="J61" t="n">
-        <v>-108.71</v>
+        <v>-82.94</v>
       </c>
       <c r="K61" t="n">
-        <v>-66.29000000000001</v>
+        <v>-50.58</v>
       </c>
       <c r="L61" t="n">
-        <v>127.33</v>
+        <v>97.15000000000001</v>
       </c>
     </row>
     <row r="62">
@@ -2656,13 +2656,13 @@
         <v>22</v>
       </c>
       <c r="J62" t="n">
-        <v>-229.03</v>
+        <v>-158.26</v>
       </c>
       <c r="K62" t="n">
-        <v>-134.54</v>
+        <v>-92.97</v>
       </c>
       <c r="L62" t="n">
-        <v>265.63</v>
+        <v>183.55</v>
       </c>
     </row>
     <row r="63">
@@ -2698,13 +2698,13 @@
         <v>23</v>
       </c>
       <c r="J63" t="n">
-        <v>-212.38</v>
+        <v>-146.55</v>
       </c>
       <c r="K63" t="n">
-        <v>-70.8</v>
+        <v>-48.85</v>
       </c>
       <c r="L63" t="n">
-        <v>223.87</v>
+        <v>154.47</v>
       </c>
     </row>
     <row r="64">
@@ -2740,13 +2740,13 @@
         <v>19</v>
       </c>
       <c r="J64" t="n">
-        <v>-80.73999999999999</v>
+        <v>-50.06</v>
       </c>
       <c r="K64" t="n">
-        <v>-306.74</v>
+        <v>-190.18</v>
       </c>
       <c r="L64" t="n">
-        <v>317.18</v>
+        <v>196.66</v>
       </c>
     </row>
     <row r="65">
@@ -2782,13 +2782,13 @@
         <v>20</v>
       </c>
       <c r="J65" t="n">
-        <v>486.61</v>
+        <v>273.88</v>
       </c>
       <c r="K65" t="n">
-        <v>233.08</v>
+        <v>131.18</v>
       </c>
       <c r="L65" t="n">
-        <v>539.55</v>
+        <v>303.67</v>
       </c>
     </row>
     <row r="66">
@@ -2824,13 +2824,13 @@
         <v>19</v>
       </c>
       <c r="J66" t="n">
-        <v>-10.84</v>
+        <v>-5.83</v>
       </c>
       <c r="K66" t="n">
-        <v>-355.67</v>
+        <v>-191.4</v>
       </c>
       <c r="L66" t="n">
-        <v>355.84</v>
+        <v>191.48</v>
       </c>
     </row>
     <row r="67">
@@ -2866,13 +2866,13 @@
         <v>19</v>
       </c>
       <c r="J67" t="n">
-        <v>977.78</v>
+        <v>525.99</v>
       </c>
       <c r="K67" t="n">
-        <v>-709.64</v>
+        <v>-381.75</v>
       </c>
       <c r="L67" t="n">
-        <v>1208.16</v>
+        <v>649.92</v>
       </c>
     </row>
     <row r="68">
@@ -2908,13 +2908,13 @@
         <v>22</v>
       </c>
       <c r="J68" t="n">
-        <v>108.02</v>
+        <v>56.07</v>
       </c>
       <c r="K68" t="n">
-        <v>481.12</v>
+        <v>249.71</v>
       </c>
       <c r="L68" t="n">
-        <v>493.09</v>
+        <v>255.92</v>
       </c>
     </row>
     <row r="69">
@@ -2950,13 +2950,13 @@
         <v>23</v>
       </c>
       <c r="J69" t="n">
-        <v>152.17</v>
+        <v>80.86</v>
       </c>
       <c r="K69" t="n">
-        <v>-869.25</v>
+        <v>-461.89</v>
       </c>
       <c r="L69" t="n">
-        <v>882.47</v>
+        <v>468.92</v>
       </c>
     </row>
     <row r="70">
@@ -2992,13 +2992,13 @@
         <v>23</v>
       </c>
       <c r="J70" t="n">
-        <v>108.25</v>
+        <v>58.7</v>
       </c>
       <c r="K70" t="n">
-        <v>-529.11</v>
+        <v>-286.92</v>
       </c>
       <c r="L70" t="n">
-        <v>540.0700000000001</v>
+        <v>292.86</v>
       </c>
     </row>
     <row r="71">
@@ -3034,13 +3034,13 @@
         <v>21</v>
       </c>
       <c r="J71" t="n">
-        <v>-275.58</v>
+        <v>-129.93</v>
       </c>
       <c r="K71" t="n">
-        <v>-528.78</v>
+        <v>-249.31</v>
       </c>
       <c r="L71" t="n">
-        <v>596.28</v>
+        <v>281.13</v>
       </c>
     </row>
     <row r="72">
@@ -3076,13 +3076,13 @@
         <v>23</v>
       </c>
       <c r="J72" t="n">
-        <v>475.87</v>
+        <v>235.79</v>
       </c>
       <c r="K72" t="n">
-        <v>974.84</v>
+        <v>483.02</v>
       </c>
       <c r="L72" t="n">
-        <v>1084.79</v>
+        <v>537.5</v>
       </c>
     </row>
     <row r="73">
@@ -3118,13 +3118,13 @@
         <v>20</v>
       </c>
       <c r="J73" t="n">
-        <v>-573.85</v>
+        <v>-261.95</v>
       </c>
       <c r="K73" t="n">
-        <v>-34.67</v>
+        <v>-15.82</v>
       </c>
       <c r="L73" t="n">
-        <v>574.9</v>
+        <v>262.43</v>
       </c>
     </row>
     <row r="74">
@@ -3160,13 +3160,13 @@
         <v>21</v>
       </c>
       <c r="J74" t="n">
-        <v>142.06</v>
+        <v>98.40000000000001</v>
       </c>
       <c r="K74" t="n">
-        <v>-53.57</v>
+        <v>-37.1</v>
       </c>
       <c r="L74" t="n">
-        <v>151.83</v>
+        <v>105.16</v>
       </c>
     </row>
     <row r="75">
@@ -3202,13 +3202,13 @@
         <v>20</v>
       </c>
       <c r="J75" t="n">
-        <v>-106.28</v>
+        <v>-71.77</v>
       </c>
       <c r="K75" t="n">
-        <v>363.09</v>
+        <v>245.2</v>
       </c>
       <c r="L75" t="n">
-        <v>378.33</v>
+        <v>255.48</v>
       </c>
     </row>
     <row r="76">
@@ -3244,13 +3244,13 @@
         <v>22</v>
       </c>
       <c r="J76" t="n">
-        <v>-123.13</v>
+        <v>-88.27</v>
       </c>
       <c r="K76" t="n">
-        <v>282.94</v>
+        <v>202.84</v>
       </c>
       <c r="L76" t="n">
-        <v>308.57</v>
+        <v>221.22</v>
       </c>
     </row>
     <row r="77">
@@ -3286,13 +3286,13 @@
         <v>24</v>
       </c>
       <c r="J77" t="n">
-        <v>-328.34</v>
+        <v>-243.06</v>
       </c>
       <c r="K77" t="n">
-        <v>-199.38</v>
+        <v>-147.59</v>
       </c>
       <c r="L77" t="n">
-        <v>384.13</v>
+        <v>284.36</v>
       </c>
     </row>
     <row r="78">
@@ -3328,13 +3328,13 @@
         <v>24</v>
       </c>
       <c r="J78" t="n">
-        <v>169.8</v>
+        <v>121.11</v>
       </c>
       <c r="K78" t="n">
-        <v>-379.29</v>
+        <v>-270.52</v>
       </c>
       <c r="L78" t="n">
-        <v>415.57</v>
+        <v>296.39</v>
       </c>
     </row>
     <row r="79">
@@ -3370,13 +3370,13 @@
         <v>24</v>
       </c>
       <c r="J79" t="n">
-        <v>399.62</v>
+        <v>284.42</v>
       </c>
       <c r="K79" t="n">
-        <v>-173.3</v>
+        <v>-123.34</v>
       </c>
       <c r="L79" t="n">
-        <v>435.58</v>
+        <v>310.01</v>
       </c>
     </row>
     <row r="80">
@@ -3412,13 +3412,13 @@
         <v>25</v>
       </c>
       <c r="J80" t="n">
-        <v>200.8</v>
+        <v>132.88</v>
       </c>
       <c r="K80" t="n">
-        <v>122.57</v>
+        <v>81.11</v>
       </c>
       <c r="L80" t="n">
-        <v>235.25</v>
+        <v>155.68</v>
       </c>
     </row>
     <row r="81">
@@ -3454,13 +3454,13 @@
         <v>23</v>
       </c>
       <c r="J81" t="n">
-        <v>248.94</v>
+        <v>150.63</v>
       </c>
       <c r="K81" t="n">
-        <v>470.97</v>
+        <v>284.97</v>
       </c>
       <c r="L81" t="n">
-        <v>532.72</v>
+        <v>322.33</v>
       </c>
     </row>
     <row r="82">
@@ -3496,13 +3496,13 @@
         <v>20</v>
       </c>
       <c r="J82" t="n">
-        <v>60.9</v>
+        <v>34</v>
       </c>
       <c r="K82" t="n">
-        <v>403.97</v>
+        <v>225.55</v>
       </c>
       <c r="L82" t="n">
-        <v>408.54</v>
+        <v>228.1</v>
       </c>
     </row>
     <row r="83">
@@ -3538,13 +3538,13 @@
         <v>21</v>
       </c>
       <c r="J83" t="n">
-        <v>227.05</v>
+        <v>113.91</v>
       </c>
       <c r="K83" t="n">
-        <v>-527.78</v>
+        <v>-264.77</v>
       </c>
       <c r="L83" t="n">
-        <v>574.55</v>
+        <v>288.24</v>
       </c>
     </row>
     <row r="84">
@@ -3580,13 +3580,13 @@
         <v>19</v>
       </c>
       <c r="J84" t="n">
-        <v>580</v>
+        <v>274.18</v>
       </c>
       <c r="K84" t="n">
-        <v>212.18</v>
+        <v>100.3</v>
       </c>
       <c r="L84" t="n">
-        <v>617.59</v>
+        <v>291.96</v>
       </c>
     </row>
     <row r="85">
@@ -3622,13 +3622,13 @@
         <v>19</v>
       </c>
       <c r="J85" t="n">
-        <v>596.22</v>
+        <v>282.17</v>
       </c>
       <c r="K85" t="n">
-        <v>557.87</v>
+        <v>264.02</v>
       </c>
       <c r="L85" t="n">
-        <v>816.51</v>
+        <v>386.43</v>
       </c>
     </row>
     <row r="86">
@@ -3664,13 +3664,13 @@
         <v>20</v>
       </c>
       <c r="J86" t="n">
-        <v>792.34</v>
+        <v>353.08</v>
       </c>
       <c r="K86" t="n">
-        <v>-467.76</v>
+        <v>-208.44</v>
       </c>
       <c r="L86" t="n">
-        <v>920.11</v>
+        <v>410.02</v>
       </c>
     </row>
     <row r="87">
@@ -3706,13 +3706,13 @@
         <v>25</v>
       </c>
       <c r="J87" t="n">
-        <v>27.67</v>
+        <v>14.7</v>
       </c>
       <c r="K87" t="n">
-        <v>389.72</v>
+        <v>207.06</v>
       </c>
       <c r="L87" t="n">
-        <v>390.7</v>
+        <v>207.58</v>
       </c>
     </row>
     <row r="88">
@@ -3748,13 +3748,13 @@
         <v>25</v>
       </c>
       <c r="J88" t="n">
-        <v>-495.19</v>
+        <v>-265.15</v>
       </c>
       <c r="K88" t="n">
-        <v>-257.88</v>
+        <v>-138.08</v>
       </c>
       <c r="L88" t="n">
-        <v>558.3099999999999</v>
+        <v>298.95</v>
       </c>
     </row>
   </sheetData>

--- a/output/2024-10-08.xlsx
+++ b/output/2024-10-08.xlsx
@@ -640,13 +640,13 @@
         <v>23</v>
       </c>
       <c r="J14" t="n">
-        <v>98.16</v>
+        <v>105.02</v>
       </c>
       <c r="K14" t="n">
-        <v>-52.76</v>
+        <v>-56.45</v>
       </c>
       <c r="L14" t="n">
-        <v>111.44</v>
+        <v>119.23</v>
       </c>
     </row>
     <row r="15">
@@ -682,13 +682,13 @@
         <v>23</v>
       </c>
       <c r="J15" t="n">
-        <v>-77.31</v>
+        <v>-83.52</v>
       </c>
       <c r="K15" t="n">
-        <v>105.27</v>
+        <v>113.73</v>
       </c>
       <c r="L15" t="n">
-        <v>130.61</v>
+        <v>141.1</v>
       </c>
     </row>
     <row r="16">
@@ -724,13 +724,13 @@
         <v>20</v>
       </c>
       <c r="J16" t="n">
-        <v>-72.43000000000001</v>
+        <v>-77.06999999999999</v>
       </c>
       <c r="K16" t="n">
-        <v>170.93</v>
+        <v>181.88</v>
       </c>
       <c r="L16" t="n">
-        <v>185.65</v>
+        <v>197.54</v>
       </c>
     </row>
     <row r="17">
@@ -766,13 +766,13 @@
         <v>25</v>
       </c>
       <c r="J17" t="n">
-        <v>-95.28</v>
+        <v>-104.44</v>
       </c>
       <c r="K17" t="n">
-        <v>95.59999999999999</v>
+        <v>104.79</v>
       </c>
       <c r="L17" t="n">
-        <v>134.97</v>
+        <v>147.95</v>
       </c>
     </row>
     <row r="18">
@@ -808,13 +808,13 @@
         <v>23</v>
       </c>
       <c r="J18" t="n">
-        <v>-84.15000000000001</v>
+        <v>-92.84999999999999</v>
       </c>
       <c r="K18" t="n">
-        <v>-105.62</v>
+        <v>-116.53</v>
       </c>
       <c r="L18" t="n">
-        <v>135.04</v>
+        <v>148.99</v>
       </c>
     </row>
     <row r="19">
@@ -850,13 +850,13 @@
         <v>19</v>
       </c>
       <c r="J19" t="n">
-        <v>193.96</v>
+        <v>215.73</v>
       </c>
       <c r="K19" t="n">
-        <v>19.95</v>
+        <v>22.19</v>
       </c>
       <c r="L19" t="n">
-        <v>194.99</v>
+        <v>216.87</v>
       </c>
     </row>
     <row r="20">
@@ -892,13 +892,13 @@
         <v>22</v>
       </c>
       <c r="J20" t="n">
-        <v>88.67</v>
+        <v>101.21</v>
       </c>
       <c r="K20" t="n">
-        <v>320.99</v>
+        <v>366.4</v>
       </c>
       <c r="L20" t="n">
-        <v>333.01</v>
+        <v>380.12</v>
       </c>
     </row>
     <row r="21">
@@ -934,13 +934,13 @@
         <v>25</v>
       </c>
       <c r="J21" t="n">
-        <v>304.73</v>
+        <v>343.87</v>
       </c>
       <c r="K21" t="n">
-        <v>23.27</v>
+        <v>26.26</v>
       </c>
       <c r="L21" t="n">
-        <v>305.62</v>
+        <v>344.87</v>
       </c>
     </row>
     <row r="22">
@@ -976,13 +976,13 @@
         <v>19</v>
       </c>
       <c r="J22" t="n">
-        <v>-18.27</v>
+        <v>-21.16</v>
       </c>
       <c r="K22" t="n">
-        <v>203.48</v>
+        <v>235.63</v>
       </c>
       <c r="L22" t="n">
-        <v>204.3</v>
+        <v>236.58</v>
       </c>
     </row>
     <row r="23">
@@ -1018,13 +1018,13 @@
         <v>22</v>
       </c>
       <c r="J23" t="n">
-        <v>-248.87</v>
+        <v>-291.14</v>
       </c>
       <c r="K23" t="n">
-        <v>-242.9</v>
+        <v>-284.15</v>
       </c>
       <c r="L23" t="n">
-        <v>347.76</v>
+        <v>406.82</v>
       </c>
     </row>
     <row r="24">
@@ -1060,13 +1060,13 @@
         <v>25</v>
       </c>
       <c r="J24" t="n">
-        <v>-0.36</v>
+        <v>-0.42</v>
       </c>
       <c r="K24" t="n">
-        <v>170.39</v>
+        <v>196.69</v>
       </c>
       <c r="L24" t="n">
-        <v>170.39</v>
+        <v>196.69</v>
       </c>
     </row>
     <row r="25">
@@ -1102,13 +1102,13 @@
         <v>23</v>
       </c>
       <c r="J25" t="n">
-        <v>-207.08</v>
+        <v>-241.41</v>
       </c>
       <c r="K25" t="n">
-        <v>123.07</v>
+        <v>143.47</v>
       </c>
       <c r="L25" t="n">
-        <v>240.9</v>
+        <v>280.82</v>
       </c>
     </row>
     <row r="26">
@@ -1144,13 +1144,13 @@
         <v>23</v>
       </c>
       <c r="J26" t="n">
-        <v>-455.12</v>
+        <v>-537.15</v>
       </c>
       <c r="K26" t="n">
-        <v>-43.31</v>
+        <v>-51.12</v>
       </c>
       <c r="L26" t="n">
-        <v>457.17</v>
+        <v>539.58</v>
       </c>
     </row>
     <row r="27">
@@ -1186,13 +1186,13 @@
         <v>20</v>
       </c>
       <c r="J27" t="n">
-        <v>18.55</v>
+        <v>22.44</v>
       </c>
       <c r="K27" t="n">
-        <v>330.9</v>
+        <v>400.22</v>
       </c>
       <c r="L27" t="n">
-        <v>331.42</v>
+        <v>400.85</v>
       </c>
     </row>
     <row r="28">
@@ -1228,13 +1228,13 @@
         <v>21</v>
       </c>
       <c r="J28" t="n">
-        <v>338.17</v>
+        <v>407.71</v>
       </c>
       <c r="K28" t="n">
-        <v>163.4</v>
+        <v>197</v>
       </c>
       <c r="L28" t="n">
-        <v>375.58</v>
+        <v>452.81</v>
       </c>
     </row>
     <row r="29">
@@ -1270,13 +1270,13 @@
         <v>24</v>
       </c>
       <c r="J29" t="n">
-        <v>47.07</v>
+        <v>49.83</v>
       </c>
       <c r="K29" t="n">
-        <v>-140.35</v>
+        <v>-148.56</v>
       </c>
       <c r="L29" t="n">
-        <v>148.04</v>
+        <v>156.69</v>
       </c>
     </row>
     <row r="30">
@@ -1312,13 +1312,13 @@
         <v>20</v>
       </c>
       <c r="J30" t="n">
-        <v>-15.11</v>
+        <v>-16.48</v>
       </c>
       <c r="K30" t="n">
-        <v>173.48</v>
+        <v>189.2</v>
       </c>
       <c r="L30" t="n">
-        <v>174.13</v>
+        <v>189.92</v>
       </c>
     </row>
     <row r="31">
@@ -1354,13 +1354,13 @@
         <v>24</v>
       </c>
       <c r="J31" t="n">
-        <v>35.29</v>
+        <v>37.17</v>
       </c>
       <c r="K31" t="n">
-        <v>-93.13</v>
+        <v>-98.09</v>
       </c>
       <c r="L31" t="n">
-        <v>99.59</v>
+        <v>104.9</v>
       </c>
     </row>
     <row r="32">
@@ -1396,13 +1396,13 @@
         <v>20</v>
       </c>
       <c r="J32" t="n">
-        <v>-251.43</v>
+        <v>-278.07</v>
       </c>
       <c r="K32" t="n">
-        <v>37.88</v>
+        <v>41.89</v>
       </c>
       <c r="L32" t="n">
-        <v>254.27</v>
+        <v>281.21</v>
       </c>
     </row>
     <row r="33">
@@ -1438,13 +1438,13 @@
         <v>20</v>
       </c>
       <c r="J33" t="n">
-        <v>102.39</v>
+        <v>113.79</v>
       </c>
       <c r="K33" t="n">
-        <v>-276.47</v>
+        <v>-307.25</v>
       </c>
       <c r="L33" t="n">
-        <v>294.83</v>
+        <v>327.65</v>
       </c>
     </row>
     <row r="34">
@@ -1480,13 +1480,13 @@
         <v>19</v>
       </c>
       <c r="J34" t="n">
-        <v>-85.79000000000001</v>
+        <v>-95.98999999999999</v>
       </c>
       <c r="K34" t="n">
-        <v>-92.27</v>
+        <v>-103.25</v>
       </c>
       <c r="L34" t="n">
-        <v>125.99</v>
+        <v>140.98</v>
       </c>
     </row>
     <row r="35">
@@ -1522,13 +1522,13 @@
         <v>22</v>
       </c>
       <c r="J35" t="n">
-        <v>14.95</v>
+        <v>17.12</v>
       </c>
       <c r="K35" t="n">
-        <v>221.48</v>
+        <v>253.63</v>
       </c>
       <c r="L35" t="n">
-        <v>221.98</v>
+        <v>254.21</v>
       </c>
     </row>
     <row r="36">
@@ -1564,13 +1564,13 @@
         <v>22</v>
       </c>
       <c r="J36" t="n">
-        <v>115.36</v>
+        <v>132.1</v>
       </c>
       <c r="K36" t="n">
-        <v>-180.43</v>
+        <v>-206.62</v>
       </c>
       <c r="L36" t="n">
-        <v>214.15</v>
+        <v>245.25</v>
       </c>
     </row>
     <row r="37">
@@ -1606,13 +1606,13 @@
         <v>25</v>
       </c>
       <c r="J37" t="n">
-        <v>-122.41</v>
+        <v>-137.59</v>
       </c>
       <c r="K37" t="n">
-        <v>93.47</v>
+        <v>105.06</v>
       </c>
       <c r="L37" t="n">
-        <v>154.02</v>
+        <v>173.12</v>
       </c>
     </row>
     <row r="38">
@@ -1648,13 +1648,13 @@
         <v>20</v>
       </c>
       <c r="J38" t="n">
-        <v>218.08</v>
+        <v>258.24</v>
       </c>
       <c r="K38" t="n">
-        <v>99.3</v>
+        <v>117.58</v>
       </c>
       <c r="L38" t="n">
-        <v>239.63</v>
+        <v>283.75</v>
       </c>
     </row>
     <row r="39">
@@ -1690,13 +1690,13 @@
         <v>23</v>
       </c>
       <c r="J39" t="n">
-        <v>-1.3</v>
+        <v>-1.52</v>
       </c>
       <c r="K39" t="n">
-        <v>363.98</v>
+        <v>425.61</v>
       </c>
       <c r="L39" t="n">
-        <v>363.98</v>
+        <v>425.62</v>
       </c>
     </row>
     <row r="40">
@@ -1732,13 +1732,13 @@
         <v>23</v>
       </c>
       <c r="J40" t="n">
-        <v>97.12</v>
+        <v>113.91</v>
       </c>
       <c r="K40" t="n">
-        <v>-378.74</v>
+        <v>-444.23</v>
       </c>
       <c r="L40" t="n">
-        <v>390.99</v>
+        <v>458.6</v>
       </c>
     </row>
     <row r="41">
@@ -1774,13 +1774,13 @@
         <v>21</v>
       </c>
       <c r="J41" t="n">
-        <v>-313.91</v>
+        <v>-375.51</v>
       </c>
       <c r="K41" t="n">
-        <v>-48.08</v>
+        <v>-57.51</v>
       </c>
       <c r="L41" t="n">
-        <v>317.57</v>
+        <v>379.89</v>
       </c>
     </row>
     <row r="42">
@@ -1816,13 +1816,13 @@
         <v>21</v>
       </c>
       <c r="J42" t="n">
-        <v>-302.26</v>
+        <v>-366.02</v>
       </c>
       <c r="K42" t="n">
-        <v>80.91</v>
+        <v>97.98</v>
       </c>
       <c r="L42" t="n">
-        <v>312.9</v>
+        <v>378.91</v>
       </c>
     </row>
     <row r="43">
@@ -1858,13 +1858,13 @@
         <v>24</v>
       </c>
       <c r="J43" t="n">
-        <v>-328.99</v>
+        <v>-387.1</v>
       </c>
       <c r="K43" t="n">
-        <v>-48.71</v>
+        <v>-57.32</v>
       </c>
       <c r="L43" t="n">
-        <v>332.57</v>
+        <v>391.32</v>
       </c>
     </row>
     <row r="44">
@@ -1900,13 +1900,13 @@
         <v>25</v>
       </c>
       <c r="J44" t="n">
-        <v>-134.62</v>
+        <v>-143.52</v>
       </c>
       <c r="K44" t="n">
-        <v>-95.11</v>
+        <v>-101.4</v>
       </c>
       <c r="L44" t="n">
-        <v>164.83</v>
+        <v>175.73</v>
       </c>
     </row>
     <row r="45">
@@ -1942,13 +1942,13 @@
         <v>22</v>
       </c>
       <c r="J45" t="n">
-        <v>-49.15</v>
+        <v>-52.8</v>
       </c>
       <c r="K45" t="n">
-        <v>68.08</v>
+        <v>73.14</v>
       </c>
       <c r="L45" t="n">
-        <v>83.97</v>
+        <v>90.20999999999999</v>
       </c>
     </row>
     <row r="46">
@@ -1984,13 +1984,13 @@
         <v>25</v>
       </c>
       <c r="J46" t="n">
-        <v>62.65</v>
+        <v>65.73999999999999</v>
       </c>
       <c r="K46" t="n">
-        <v>62.66</v>
+        <v>65.75</v>
       </c>
       <c r="L46" t="n">
-        <v>88.59999999999999</v>
+        <v>92.97</v>
       </c>
     </row>
     <row r="47">
@@ -2026,13 +2026,13 @@
         <v>19</v>
       </c>
       <c r="J47" t="n">
-        <v>-208.68</v>
+        <v>-234.11</v>
       </c>
       <c r="K47" t="n">
-        <v>-3.34</v>
+        <v>-3.75</v>
       </c>
       <c r="L47" t="n">
-        <v>208.71</v>
+        <v>234.14</v>
       </c>
     </row>
     <row r="48">
@@ -2068,13 +2068,13 @@
         <v>25</v>
       </c>
       <c r="J48" t="n">
-        <v>-146.13</v>
+        <v>-158.01</v>
       </c>
       <c r="K48" t="n">
-        <v>43.45</v>
+        <v>46.99</v>
       </c>
       <c r="L48" t="n">
-        <v>152.45</v>
+        <v>164.85</v>
       </c>
     </row>
     <row r="49">
@@ -2110,13 +2110,13 @@
         <v>23</v>
       </c>
       <c r="J49" t="n">
-        <v>-23.41</v>
+        <v>-25.79</v>
       </c>
       <c r="K49" t="n">
-        <v>211.85</v>
+        <v>233.4</v>
       </c>
       <c r="L49" t="n">
-        <v>213.14</v>
+        <v>234.82</v>
       </c>
     </row>
     <row r="50">
@@ -2152,13 +2152,13 @@
         <v>25</v>
       </c>
       <c r="J50" t="n">
-        <v>-297.29</v>
+        <v>-334.47</v>
       </c>
       <c r="K50" t="n">
-        <v>-205.04</v>
+        <v>-230.68</v>
       </c>
       <c r="L50" t="n">
-        <v>361.14</v>
+        <v>406.31</v>
       </c>
     </row>
     <row r="51">
@@ -2194,13 +2194,13 @@
         <v>19</v>
       </c>
       <c r="J51" t="n">
-        <v>4.5</v>
+        <v>5.22</v>
       </c>
       <c r="K51" t="n">
-        <v>-219.06</v>
+        <v>-254.24</v>
       </c>
       <c r="L51" t="n">
-        <v>219.11</v>
+        <v>254.29</v>
       </c>
     </row>
     <row r="52">
@@ -2236,13 +2236,13 @@
         <v>22</v>
       </c>
       <c r="J52" t="n">
-        <v>-159.66</v>
+        <v>-182.7</v>
       </c>
       <c r="K52" t="n">
-        <v>210.97</v>
+        <v>241.42</v>
       </c>
       <c r="L52" t="n">
-        <v>264.58</v>
+        <v>302.76</v>
       </c>
     </row>
     <row r="53">
@@ -2278,13 +2278,13 @@
         <v>21</v>
       </c>
       <c r="J53" t="n">
-        <v>359.61</v>
+        <v>423.83</v>
       </c>
       <c r="K53" t="n">
-        <v>-228.95</v>
+        <v>-269.84</v>
       </c>
       <c r="L53" t="n">
-        <v>426.31</v>
+        <v>502.44</v>
       </c>
     </row>
     <row r="54">
@@ -2320,13 +2320,13 @@
         <v>23</v>
       </c>
       <c r="J54" t="n">
-        <v>-228.13</v>
+        <v>-264.1</v>
       </c>
       <c r="K54" t="n">
-        <v>203.17</v>
+        <v>235.21</v>
       </c>
       <c r="L54" t="n">
-        <v>305.49</v>
+        <v>353.66</v>
       </c>
     </row>
     <row r="55">
@@ -2362,13 +2362,13 @@
         <v>23</v>
       </c>
       <c r="J55" t="n">
-        <v>-89.56999999999999</v>
+        <v>-104.81</v>
       </c>
       <c r="K55" t="n">
-        <v>-302.9</v>
+        <v>-354.43</v>
       </c>
       <c r="L55" t="n">
-        <v>315.86</v>
+        <v>369.6</v>
       </c>
     </row>
     <row r="56">
@@ -2404,13 +2404,13 @@
         <v>22</v>
       </c>
       <c r="J56" t="n">
-        <v>-285.63</v>
+        <v>-341.14</v>
       </c>
       <c r="K56" t="n">
-        <v>93.62</v>
+        <v>111.82</v>
       </c>
       <c r="L56" t="n">
-        <v>300.58</v>
+        <v>359</v>
       </c>
     </row>
     <row r="57">
@@ -2446,13 +2446,13 @@
         <v>22</v>
       </c>
       <c r="J57" t="n">
-        <v>-16.24</v>
+        <v>-19.69</v>
       </c>
       <c r="K57" t="n">
-        <v>-348.54</v>
+        <v>-422.63</v>
       </c>
       <c r="L57" t="n">
-        <v>348.92</v>
+        <v>423.09</v>
       </c>
     </row>
     <row r="58">
@@ -2488,13 +2488,13 @@
         <v>19</v>
       </c>
       <c r="J58" t="n">
-        <v>-354.64</v>
+        <v>-429.1</v>
       </c>
       <c r="K58" t="n">
-        <v>-374.25</v>
+        <v>-452.83</v>
       </c>
       <c r="L58" t="n">
-        <v>515.59</v>
+        <v>623.84</v>
       </c>
     </row>
     <row r="59">
@@ -2530,13 +2530,13 @@
         <v>22</v>
       </c>
       <c r="J59" t="n">
-        <v>209.79</v>
+        <v>231.44</v>
       </c>
       <c r="K59" t="n">
-        <v>-7.3</v>
+        <v>-8.050000000000001</v>
       </c>
       <c r="L59" t="n">
-        <v>209.92</v>
+        <v>231.58</v>
       </c>
     </row>
     <row r="60">
@@ -2572,13 +2572,13 @@
         <v>20</v>
       </c>
       <c r="J60" t="n">
-        <v>163.44</v>
+        <v>178.88</v>
       </c>
       <c r="K60" t="n">
-        <v>145.93</v>
+        <v>159.71</v>
       </c>
       <c r="L60" t="n">
-        <v>219.1</v>
+        <v>239.8</v>
       </c>
     </row>
     <row r="61">
@@ -2614,13 +2614,13 @@
         <v>24</v>
       </c>
       <c r="J61" t="n">
-        <v>-82.94</v>
+        <v>-89</v>
       </c>
       <c r="K61" t="n">
-        <v>-50.58</v>
+        <v>-54.27</v>
       </c>
       <c r="L61" t="n">
-        <v>97.15000000000001</v>
+        <v>104.24</v>
       </c>
     </row>
     <row r="62">
@@ -2656,13 +2656,13 @@
         <v>22</v>
       </c>
       <c r="J62" t="n">
-        <v>-158.26</v>
+        <v>-175.21</v>
       </c>
       <c r="K62" t="n">
-        <v>-92.97</v>
+        <v>-102.93</v>
       </c>
       <c r="L62" t="n">
-        <v>183.55</v>
+        <v>203.21</v>
       </c>
     </row>
     <row r="63">
@@ -2698,13 +2698,13 @@
         <v>23</v>
       </c>
       <c r="J63" t="n">
-        <v>-146.55</v>
+        <v>-160.66</v>
       </c>
       <c r="K63" t="n">
-        <v>-48.85</v>
+        <v>-53.56</v>
       </c>
       <c r="L63" t="n">
-        <v>154.47</v>
+        <v>169.35</v>
       </c>
     </row>
     <row r="64">
@@ -2740,13 +2740,13 @@
         <v>19</v>
       </c>
       <c r="J64" t="n">
-        <v>-50.06</v>
+        <v>-55.97</v>
       </c>
       <c r="K64" t="n">
-        <v>-190.18</v>
+        <v>-212.62</v>
       </c>
       <c r="L64" t="n">
-        <v>196.66</v>
+        <v>219.87</v>
       </c>
     </row>
     <row r="65">
@@ -2782,13 +2782,13 @@
         <v>20</v>
       </c>
       <c r="J65" t="n">
-        <v>273.88</v>
+        <v>315.13</v>
       </c>
       <c r="K65" t="n">
-        <v>131.18</v>
+        <v>150.94</v>
       </c>
       <c r="L65" t="n">
-        <v>303.67</v>
+        <v>349.41</v>
       </c>
     </row>
     <row r="66">
@@ -2824,13 +2824,13 @@
         <v>19</v>
       </c>
       <c r="J66" t="n">
-        <v>-5.83</v>
+        <v>-6.77</v>
       </c>
       <c r="K66" t="n">
-        <v>-191.4</v>
+        <v>-222.13</v>
       </c>
       <c r="L66" t="n">
-        <v>191.48</v>
+        <v>222.23</v>
       </c>
     </row>
     <row r="67">
@@ -2866,13 +2866,13 @@
         <v>19</v>
       </c>
       <c r="J67" t="n">
-        <v>525.99</v>
+        <v>607.8200000000001</v>
       </c>
       <c r="K67" t="n">
-        <v>-381.75</v>
+        <v>-441.14</v>
       </c>
       <c r="L67" t="n">
-        <v>649.92</v>
+        <v>751.03</v>
       </c>
     </row>
     <row r="68">
@@ -2908,13 +2908,13 @@
         <v>22</v>
       </c>
       <c r="J68" t="n">
-        <v>56.07</v>
+        <v>65.98999999999999</v>
       </c>
       <c r="K68" t="n">
-        <v>249.71</v>
+        <v>293.92</v>
       </c>
       <c r="L68" t="n">
-        <v>255.92</v>
+        <v>301.23</v>
       </c>
     </row>
     <row r="69">
@@ -2950,13 +2950,13 @@
         <v>23</v>
       </c>
       <c r="J69" t="n">
-        <v>80.86</v>
+        <v>95.03</v>
       </c>
       <c r="K69" t="n">
-        <v>-461.89</v>
+        <v>-542.84</v>
       </c>
       <c r="L69" t="n">
-        <v>468.92</v>
+        <v>551.1</v>
       </c>
     </row>
     <row r="70">
@@ -2992,13 +2992,13 @@
         <v>23</v>
       </c>
       <c r="J70" t="n">
-        <v>58.7</v>
+        <v>68.47</v>
       </c>
       <c r="K70" t="n">
-        <v>-286.92</v>
+        <v>-334.66</v>
       </c>
       <c r="L70" t="n">
-        <v>292.86</v>
+        <v>341.6</v>
       </c>
     </row>
     <row r="71">
@@ -3034,13 +3034,13 @@
         <v>21</v>
       </c>
       <c r="J71" t="n">
-        <v>-129.93</v>
+        <v>-156.51</v>
       </c>
       <c r="K71" t="n">
-        <v>-249.31</v>
+        <v>-300.3</v>
       </c>
       <c r="L71" t="n">
-        <v>281.13</v>
+        <v>338.64</v>
       </c>
     </row>
     <row r="72">
@@ -3076,13 +3076,13 @@
         <v>23</v>
       </c>
       <c r="J72" t="n">
-        <v>235.79</v>
+        <v>282.01</v>
       </c>
       <c r="K72" t="n">
-        <v>483.02</v>
+        <v>577.71</v>
       </c>
       <c r="L72" t="n">
-        <v>537.5</v>
+        <v>642.86</v>
       </c>
     </row>
     <row r="73">
@@ -3118,13 +3118,13 @@
         <v>20</v>
       </c>
       <c r="J73" t="n">
-        <v>-261.95</v>
+        <v>-317.61</v>
       </c>
       <c r="K73" t="n">
-        <v>-15.82</v>
+        <v>-19.19</v>
       </c>
       <c r="L73" t="n">
-        <v>262.43</v>
+        <v>318.19</v>
       </c>
     </row>
     <row r="74">
@@ -3160,13 +3160,13 @@
         <v>21</v>
       </c>
       <c r="J74" t="n">
-        <v>98.40000000000001</v>
+        <v>107.14</v>
       </c>
       <c r="K74" t="n">
-        <v>-37.1</v>
+        <v>-40.4</v>
       </c>
       <c r="L74" t="n">
-        <v>105.16</v>
+        <v>114.5</v>
       </c>
     </row>
     <row r="75">
@@ -3202,13 +3202,13 @@
         <v>20</v>
       </c>
       <c r="J75" t="n">
-        <v>-71.77</v>
+        <v>-77.84</v>
       </c>
       <c r="K75" t="n">
-        <v>245.2</v>
+        <v>265.94</v>
       </c>
       <c r="L75" t="n">
-        <v>255.48</v>
+        <v>277.1</v>
       </c>
     </row>
     <row r="76">
@@ -3244,13 +3244,13 @@
         <v>22</v>
       </c>
       <c r="J76" t="n">
-        <v>-88.27</v>
+        <v>-95.42</v>
       </c>
       <c r="K76" t="n">
-        <v>202.84</v>
+        <v>219.27</v>
       </c>
       <c r="L76" t="n">
-        <v>221.22</v>
+        <v>239.13</v>
       </c>
     </row>
     <row r="77">
@@ -3286,13 +3286,13 @@
         <v>24</v>
       </c>
       <c r="J77" t="n">
-        <v>-243.06</v>
+        <v>-266.63</v>
       </c>
       <c r="K77" t="n">
-        <v>-147.59</v>
+        <v>-161.9</v>
       </c>
       <c r="L77" t="n">
-        <v>284.36</v>
+        <v>311.93</v>
       </c>
     </row>
     <row r="78">
@@ -3328,13 +3328,13 @@
         <v>24</v>
       </c>
       <c r="J78" t="n">
-        <v>121.11</v>
+        <v>132.1</v>
       </c>
       <c r="K78" t="n">
-        <v>-270.52</v>
+        <v>-295.08</v>
       </c>
       <c r="L78" t="n">
-        <v>296.39</v>
+        <v>323.3</v>
       </c>
     </row>
     <row r="79">
@@ -3370,13 +3370,13 @@
         <v>24</v>
       </c>
       <c r="J79" t="n">
-        <v>284.42</v>
+        <v>307.56</v>
       </c>
       <c r="K79" t="n">
-        <v>-123.34</v>
+        <v>-133.37</v>
       </c>
       <c r="L79" t="n">
-        <v>310.01</v>
+        <v>335.24</v>
       </c>
     </row>
     <row r="80">
@@ -3412,13 +3412,13 @@
         <v>25</v>
       </c>
       <c r="J80" t="n">
-        <v>132.88</v>
+        <v>149.89</v>
       </c>
       <c r="K80" t="n">
-        <v>81.11</v>
+        <v>91.48999999999999</v>
       </c>
       <c r="L80" t="n">
-        <v>155.68</v>
+        <v>175.6</v>
       </c>
     </row>
     <row r="81">
@@ -3454,13 +3454,13 @@
         <v>23</v>
       </c>
       <c r="J81" t="n">
-        <v>150.63</v>
+        <v>171.3</v>
       </c>
       <c r="K81" t="n">
-        <v>284.97</v>
+        <v>324.08</v>
       </c>
       <c r="L81" t="n">
-        <v>322.33</v>
+        <v>366.57</v>
       </c>
     </row>
     <row r="82">
@@ -3496,13 +3496,13 @@
         <v>20</v>
       </c>
       <c r="J82" t="n">
-        <v>34</v>
+        <v>39.14</v>
       </c>
       <c r="K82" t="n">
-        <v>225.55</v>
+        <v>259.66</v>
       </c>
       <c r="L82" t="n">
-        <v>228.1</v>
+        <v>262.59</v>
       </c>
     </row>
     <row r="83">
@@ -3538,13 +3538,13 @@
         <v>21</v>
       </c>
       <c r="J83" t="n">
-        <v>113.91</v>
+        <v>134.31</v>
       </c>
       <c r="K83" t="n">
-        <v>-264.77</v>
+        <v>-312.21</v>
       </c>
       <c r="L83" t="n">
-        <v>288.24</v>
+        <v>339.87</v>
       </c>
     </row>
     <row r="84">
@@ -3580,13 +3580,13 @@
         <v>19</v>
       </c>
       <c r="J84" t="n">
-        <v>274.18</v>
+        <v>328.12</v>
       </c>
       <c r="K84" t="n">
-        <v>100.3</v>
+        <v>120.03</v>
       </c>
       <c r="L84" t="n">
-        <v>291.96</v>
+        <v>349.38</v>
       </c>
     </row>
     <row r="85">
@@ -3622,13 +3622,13 @@
         <v>19</v>
       </c>
       <c r="J85" t="n">
-        <v>282.17</v>
+        <v>337.52</v>
       </c>
       <c r="K85" t="n">
-        <v>264.02</v>
+        <v>315.81</v>
       </c>
       <c r="L85" t="n">
-        <v>386.43</v>
+        <v>462.23</v>
       </c>
     </row>
     <row r="86">
@@ -3664,13 +3664,13 @@
         <v>20</v>
       </c>
       <c r="J86" t="n">
-        <v>353.08</v>
+        <v>429.91</v>
       </c>
       <c r="K86" t="n">
-        <v>-208.44</v>
+        <v>-253.8</v>
       </c>
       <c r="L86" t="n">
-        <v>410.02</v>
+        <v>499.24</v>
       </c>
     </row>
     <row r="87">
@@ -3706,13 +3706,13 @@
         <v>25</v>
       </c>
       <c r="J87" t="n">
-        <v>14.7</v>
+        <v>17.48</v>
       </c>
       <c r="K87" t="n">
-        <v>207.06</v>
+        <v>246.24</v>
       </c>
       <c r="L87" t="n">
-        <v>207.58</v>
+        <v>246.86</v>
       </c>
     </row>
     <row r="88">
@@ -3748,13 +3748,13 @@
         <v>25</v>
       </c>
       <c r="J88" t="n">
-        <v>-265.15</v>
+        <v>-312.08</v>
       </c>
       <c r="K88" t="n">
-        <v>-138.08</v>
+        <v>-162.53</v>
       </c>
       <c r="L88" t="n">
-        <v>298.95</v>
+        <v>351.87</v>
       </c>
     </row>
   </sheetData>

--- a/output/2024-10-08.xlsx
+++ b/output/2024-10-08.xlsx
@@ -640,13 +640,13 @@
         <v>23</v>
       </c>
       <c r="J14" t="n">
-        <v>105.02</v>
+        <v>51.8</v>
       </c>
       <c r="K14" t="n">
-        <v>-56.45</v>
+        <v>-27.84</v>
       </c>
       <c r="L14" t="n">
-        <v>119.23</v>
+        <v>58.81</v>
       </c>
     </row>
     <row r="15">
@@ -682,13 +682,13 @@
         <v>23</v>
       </c>
       <c r="J15" t="n">
-        <v>-83.52</v>
+        <v>-37.19</v>
       </c>
       <c r="K15" t="n">
-        <v>113.73</v>
+        <v>50.64</v>
       </c>
       <c r="L15" t="n">
-        <v>141.1</v>
+        <v>62.83</v>
       </c>
     </row>
     <row r="16">
@@ -724,13 +724,13 @@
         <v>20</v>
       </c>
       <c r="J16" t="n">
-        <v>-77.06999999999999</v>
+        <v>-42.44</v>
       </c>
       <c r="K16" t="n">
-        <v>181.88</v>
+        <v>100.16</v>
       </c>
       <c r="L16" t="n">
-        <v>197.54</v>
+        <v>108.78</v>
       </c>
     </row>
     <row r="17">
@@ -766,13 +766,13 @@
         <v>25</v>
       </c>
       <c r="J17" t="n">
-        <v>-104.44</v>
+        <v>-56.27</v>
       </c>
       <c r="K17" t="n">
-        <v>104.79</v>
+        <v>56.45</v>
       </c>
       <c r="L17" t="n">
-        <v>147.95</v>
+        <v>79.70999999999999</v>
       </c>
     </row>
     <row r="18">
@@ -808,13 +808,13 @@
         <v>23</v>
       </c>
       <c r="J18" t="n">
-        <v>-92.84999999999999</v>
+        <v>-46.64</v>
       </c>
       <c r="K18" t="n">
-        <v>-116.53</v>
+        <v>-58.54</v>
       </c>
       <c r="L18" t="n">
-        <v>148.99</v>
+        <v>74.84</v>
       </c>
     </row>
     <row r="19">
@@ -850,13 +850,13 @@
         <v>19</v>
       </c>
       <c r="J19" t="n">
-        <v>215.73</v>
+        <v>97.83</v>
       </c>
       <c r="K19" t="n">
-        <v>22.19</v>
+        <v>10.06</v>
       </c>
       <c r="L19" t="n">
-        <v>216.87</v>
+        <v>98.34999999999999</v>
       </c>
     </row>
     <row r="20">
@@ -892,13 +892,13 @@
         <v>22</v>
       </c>
       <c r="J20" t="n">
-        <v>101.21</v>
+        <v>51.61</v>
       </c>
       <c r="K20" t="n">
-        <v>366.4</v>
+        <v>186.82</v>
       </c>
       <c r="L20" t="n">
-        <v>380.12</v>
+        <v>193.82</v>
       </c>
     </row>
     <row r="21">
@@ -934,13 +934,13 @@
         <v>25</v>
       </c>
       <c r="J21" t="n">
-        <v>343.87</v>
+        <v>187.32</v>
       </c>
       <c r="K21" t="n">
-        <v>26.26</v>
+        <v>14.3</v>
       </c>
       <c r="L21" t="n">
-        <v>344.87</v>
+        <v>187.86</v>
       </c>
     </row>
     <row r="22">
@@ -976,13 +976,13 @@
         <v>19</v>
       </c>
       <c r="J22" t="n">
-        <v>-21.16</v>
+        <v>-10.6</v>
       </c>
       <c r="K22" t="n">
-        <v>235.63</v>
+        <v>118.01</v>
       </c>
       <c r="L22" t="n">
-        <v>236.58</v>
+        <v>118.49</v>
       </c>
     </row>
     <row r="23">
@@ -1018,13 +1018,13 @@
         <v>22</v>
       </c>
       <c r="J23" t="n">
-        <v>-291.14</v>
+        <v>-160.56</v>
       </c>
       <c r="K23" t="n">
-        <v>-284.15</v>
+        <v>-156.7</v>
       </c>
       <c r="L23" t="n">
-        <v>406.82</v>
+        <v>224.35</v>
       </c>
     </row>
     <row r="24">
@@ -1060,13 +1060,13 @@
         <v>25</v>
       </c>
       <c r="J24" t="n">
-        <v>-0.42</v>
+        <v>-0.22</v>
       </c>
       <c r="K24" t="n">
-        <v>196.69</v>
+        <v>105.02</v>
       </c>
       <c r="L24" t="n">
-        <v>196.69</v>
+        <v>105.02</v>
       </c>
     </row>
     <row r="25">
@@ -1102,13 +1102,13 @@
         <v>23</v>
       </c>
       <c r="J25" t="n">
-        <v>-241.41</v>
+        <v>-129.44</v>
       </c>
       <c r="K25" t="n">
-        <v>143.47</v>
+        <v>76.93000000000001</v>
       </c>
       <c r="L25" t="n">
-        <v>280.82</v>
+        <v>150.58</v>
       </c>
     </row>
     <row r="26">
@@ -1144,13 +1144,13 @@
         <v>23</v>
       </c>
       <c r="J26" t="n">
-        <v>-537.15</v>
+        <v>-291.92</v>
       </c>
       <c r="K26" t="n">
-        <v>-51.12</v>
+        <v>-27.78</v>
       </c>
       <c r="L26" t="n">
-        <v>539.58</v>
+        <v>293.24</v>
       </c>
     </row>
     <row r="27">
@@ -1186,13 +1186,13 @@
         <v>20</v>
       </c>
       <c r="J27" t="n">
-        <v>22.44</v>
+        <v>12.26</v>
       </c>
       <c r="K27" t="n">
-        <v>400.22</v>
+        <v>218.75</v>
       </c>
       <c r="L27" t="n">
-        <v>400.85</v>
+        <v>219.09</v>
       </c>
     </row>
     <row r="28">
@@ -1228,13 +1228,13 @@
         <v>21</v>
       </c>
       <c r="J28" t="n">
-        <v>407.71</v>
+        <v>222.09</v>
       </c>
       <c r="K28" t="n">
-        <v>197</v>
+        <v>107.31</v>
       </c>
       <c r="L28" t="n">
-        <v>452.81</v>
+        <v>246.66</v>
       </c>
     </row>
     <row r="29">
@@ -1270,13 +1270,13 @@
         <v>24</v>
       </c>
       <c r="J29" t="n">
-        <v>49.83</v>
+        <v>26.03</v>
       </c>
       <c r="K29" t="n">
-        <v>-148.56</v>
+        <v>-77.59999999999999</v>
       </c>
       <c r="L29" t="n">
-        <v>156.69</v>
+        <v>81.84999999999999</v>
       </c>
     </row>
     <row r="30">
@@ -1312,13 +1312,13 @@
         <v>20</v>
       </c>
       <c r="J30" t="n">
-        <v>-16.48</v>
+        <v>-7.54</v>
       </c>
       <c r="K30" t="n">
-        <v>189.2</v>
+        <v>86.51000000000001</v>
       </c>
       <c r="L30" t="n">
-        <v>189.92</v>
+        <v>86.84</v>
       </c>
     </row>
     <row r="31">
@@ -1354,13 +1354,13 @@
         <v>24</v>
       </c>
       <c r="J31" t="n">
-        <v>37.17</v>
+        <v>18.12</v>
       </c>
       <c r="K31" t="n">
-        <v>-98.09</v>
+        <v>-47.82</v>
       </c>
       <c r="L31" t="n">
-        <v>104.9</v>
+        <v>51.13</v>
       </c>
     </row>
     <row r="32">
@@ -1396,13 +1396,13 @@
         <v>20</v>
       </c>
       <c r="J32" t="n">
-        <v>-278.07</v>
+        <v>-136.92</v>
       </c>
       <c r="K32" t="n">
-        <v>41.89</v>
+        <v>20.63</v>
       </c>
       <c r="L32" t="n">
-        <v>281.21</v>
+        <v>138.47</v>
       </c>
     </row>
     <row r="33">
@@ -1438,13 +1438,13 @@
         <v>20</v>
       </c>
       <c r="J33" t="n">
-        <v>113.79</v>
+        <v>49.4</v>
       </c>
       <c r="K33" t="n">
-        <v>-307.25</v>
+        <v>-133.38</v>
       </c>
       <c r="L33" t="n">
-        <v>327.65</v>
+        <v>142.24</v>
       </c>
     </row>
     <row r="34">
@@ -1480,13 +1480,13 @@
         <v>19</v>
       </c>
       <c r="J34" t="n">
-        <v>-95.98999999999999</v>
+        <v>-44.26</v>
       </c>
       <c r="K34" t="n">
-        <v>-103.25</v>
+        <v>-47.61</v>
       </c>
       <c r="L34" t="n">
-        <v>140.98</v>
+        <v>65.01000000000001</v>
       </c>
     </row>
     <row r="35">
@@ -1522,13 +1522,13 @@
         <v>22</v>
       </c>
       <c r="J35" t="n">
-        <v>17.12</v>
+        <v>8.550000000000001</v>
       </c>
       <c r="K35" t="n">
-        <v>253.63</v>
+        <v>126.68</v>
       </c>
       <c r="L35" t="n">
-        <v>254.21</v>
+        <v>126.96</v>
       </c>
     </row>
     <row r="36">
@@ -1564,13 +1564,13 @@
         <v>22</v>
       </c>
       <c r="J36" t="n">
-        <v>132.1</v>
+        <v>65.55</v>
       </c>
       <c r="K36" t="n">
-        <v>-206.62</v>
+        <v>-102.53</v>
       </c>
       <c r="L36" t="n">
-        <v>245.25</v>
+        <v>121.7</v>
       </c>
     </row>
     <row r="37">
@@ -1606,13 +1606,13 @@
         <v>25</v>
       </c>
       <c r="J37" t="n">
-        <v>-137.59</v>
+        <v>-68.87</v>
       </c>
       <c r="K37" t="n">
-        <v>105.06</v>
+        <v>52.59</v>
       </c>
       <c r="L37" t="n">
-        <v>173.12</v>
+        <v>86.66</v>
       </c>
     </row>
     <row r="38">
@@ -1648,13 +1648,13 @@
         <v>20</v>
       </c>
       <c r="J38" t="n">
-        <v>258.24</v>
+        <v>132.62</v>
       </c>
       <c r="K38" t="n">
-        <v>117.58</v>
+        <v>60.39</v>
       </c>
       <c r="L38" t="n">
-        <v>283.75</v>
+        <v>145.73</v>
       </c>
     </row>
     <row r="39">
@@ -1690,13 +1690,13 @@
         <v>23</v>
       </c>
       <c r="J39" t="n">
-        <v>-1.52</v>
+        <v>-0.73</v>
       </c>
       <c r="K39" t="n">
-        <v>425.61</v>
+        <v>204.22</v>
       </c>
       <c r="L39" t="n">
-        <v>425.62</v>
+        <v>204.22</v>
       </c>
     </row>
     <row r="40">
@@ -1732,13 +1732,13 @@
         <v>23</v>
       </c>
       <c r="J40" t="n">
-        <v>113.91</v>
+        <v>52.6</v>
       </c>
       <c r="K40" t="n">
-        <v>-444.23</v>
+        <v>-205.13</v>
       </c>
       <c r="L40" t="n">
-        <v>458.6</v>
+        <v>211.77</v>
       </c>
     </row>
     <row r="41">
@@ -1774,13 +1774,13 @@
         <v>21</v>
       </c>
       <c r="J41" t="n">
-        <v>-375.51</v>
+        <v>-205.64</v>
       </c>
       <c r="K41" t="n">
-        <v>-57.51</v>
+        <v>-31.49</v>
       </c>
       <c r="L41" t="n">
-        <v>379.89</v>
+        <v>208.03</v>
       </c>
     </row>
     <row r="42">
@@ -1816,13 +1816,13 @@
         <v>21</v>
       </c>
       <c r="J42" t="n">
-        <v>-366.02</v>
+        <v>-197.05</v>
       </c>
       <c r="K42" t="n">
-        <v>97.98</v>
+        <v>52.75</v>
       </c>
       <c r="L42" t="n">
-        <v>378.91</v>
+        <v>203.99</v>
       </c>
     </row>
     <row r="43">
@@ -1858,13 +1858,13 @@
         <v>24</v>
       </c>
       <c r="J43" t="n">
-        <v>-387.1</v>
+        <v>-212.51</v>
       </c>
       <c r="K43" t="n">
-        <v>-57.32</v>
+        <v>-31.47</v>
       </c>
       <c r="L43" t="n">
-        <v>391.32</v>
+        <v>214.83</v>
       </c>
     </row>
     <row r="44">
@@ -1900,13 +1900,13 @@
         <v>25</v>
       </c>
       <c r="J44" t="n">
-        <v>-143.52</v>
+        <v>-66.18000000000001</v>
       </c>
       <c r="K44" t="n">
-        <v>-101.4</v>
+        <v>-46.76</v>
       </c>
       <c r="L44" t="n">
-        <v>175.73</v>
+        <v>81.03</v>
       </c>
     </row>
     <row r="45">
@@ -1942,13 +1942,13 @@
         <v>22</v>
       </c>
       <c r="J45" t="n">
-        <v>-52.8</v>
+        <v>-26.23</v>
       </c>
       <c r="K45" t="n">
-        <v>73.14</v>
+        <v>36.33</v>
       </c>
       <c r="L45" t="n">
-        <v>90.20999999999999</v>
+        <v>44.81</v>
       </c>
     </row>
     <row r="46">
@@ -1984,13 +1984,13 @@
         <v>25</v>
       </c>
       <c r="J46" t="n">
-        <v>65.73999999999999</v>
+        <v>33.98</v>
       </c>
       <c r="K46" t="n">
-        <v>65.75</v>
+        <v>33.99</v>
       </c>
       <c r="L46" t="n">
-        <v>92.97</v>
+        <v>48.06</v>
       </c>
     </row>
     <row r="47">
@@ -2026,13 +2026,13 @@
         <v>19</v>
       </c>
       <c r="J47" t="n">
-        <v>-234.11</v>
+        <v>-114.16</v>
       </c>
       <c r="K47" t="n">
-        <v>-3.75</v>
+        <v>-1.83</v>
       </c>
       <c r="L47" t="n">
-        <v>234.14</v>
+        <v>114.18</v>
       </c>
     </row>
     <row r="48">
@@ -2068,13 +2068,13 @@
         <v>25</v>
       </c>
       <c r="J48" t="n">
-        <v>-158.01</v>
+        <v>-70.63</v>
       </c>
       <c r="K48" t="n">
-        <v>46.99</v>
+        <v>21</v>
       </c>
       <c r="L48" t="n">
-        <v>164.85</v>
+        <v>73.68000000000001</v>
       </c>
     </row>
     <row r="49">
@@ -2110,13 +2110,13 @@
         <v>23</v>
       </c>
       <c r="J49" t="n">
-        <v>-25.79</v>
+        <v>-12.77</v>
       </c>
       <c r="K49" t="n">
-        <v>233.4</v>
+        <v>115.61</v>
       </c>
       <c r="L49" t="n">
-        <v>234.82</v>
+        <v>116.31</v>
       </c>
     </row>
     <row r="50">
@@ -2152,13 +2152,13 @@
         <v>25</v>
       </c>
       <c r="J50" t="n">
-        <v>-334.47</v>
+        <v>-163.98</v>
       </c>
       <c r="K50" t="n">
-        <v>-230.68</v>
+        <v>-113.09</v>
       </c>
       <c r="L50" t="n">
-        <v>406.31</v>
+        <v>199.2</v>
       </c>
     </row>
     <row r="51">
@@ -2194,13 +2194,13 @@
         <v>19</v>
       </c>
       <c r="J51" t="n">
-        <v>5.22</v>
+        <v>2.59</v>
       </c>
       <c r="K51" t="n">
-        <v>-254.24</v>
+        <v>-126.29</v>
       </c>
       <c r="L51" t="n">
-        <v>254.29</v>
+        <v>126.32</v>
       </c>
     </row>
     <row r="52">
@@ -2236,13 +2236,13 @@
         <v>22</v>
       </c>
       <c r="J52" t="n">
-        <v>-182.7</v>
+        <v>-87.37</v>
       </c>
       <c r="K52" t="n">
-        <v>241.42</v>
+        <v>115.45</v>
       </c>
       <c r="L52" t="n">
-        <v>302.76</v>
+        <v>144.78</v>
       </c>
     </row>
     <row r="53">
@@ -2278,13 +2278,13 @@
         <v>21</v>
       </c>
       <c r="J53" t="n">
-        <v>423.83</v>
+        <v>201.56</v>
       </c>
       <c r="K53" t="n">
-        <v>-269.84</v>
+        <v>-128.33</v>
       </c>
       <c r="L53" t="n">
-        <v>502.44</v>
+        <v>238.94</v>
       </c>
     </row>
     <row r="54">
@@ -2320,13 +2320,13 @@
         <v>23</v>
       </c>
       <c r="J54" t="n">
-        <v>-264.1</v>
+        <v>-123.64</v>
       </c>
       <c r="K54" t="n">
-        <v>235.21</v>
+        <v>110.11</v>
       </c>
       <c r="L54" t="n">
-        <v>353.66</v>
+        <v>165.56</v>
       </c>
     </row>
     <row r="55">
@@ -2362,13 +2362,13 @@
         <v>23</v>
       </c>
       <c r="J55" t="n">
-        <v>-104.81</v>
+        <v>-51.4</v>
       </c>
       <c r="K55" t="n">
-        <v>-354.43</v>
+        <v>-173.83</v>
       </c>
       <c r="L55" t="n">
-        <v>369.6</v>
+        <v>181.27</v>
       </c>
     </row>
     <row r="56">
@@ -2404,13 +2404,13 @@
         <v>22</v>
       </c>
       <c r="J56" t="n">
-        <v>-341.14</v>
+        <v>-188.23</v>
       </c>
       <c r="K56" t="n">
-        <v>111.82</v>
+        <v>61.7</v>
       </c>
       <c r="L56" t="n">
-        <v>359</v>
+        <v>198.08</v>
       </c>
     </row>
     <row r="57">
@@ -2446,13 +2446,13 @@
         <v>22</v>
       </c>
       <c r="J57" t="n">
-        <v>-19.69</v>
+        <v>-10.43</v>
       </c>
       <c r="K57" t="n">
-        <v>-422.63</v>
+        <v>-223.86</v>
       </c>
       <c r="L57" t="n">
-        <v>423.09</v>
+        <v>224.1</v>
       </c>
     </row>
     <row r="58">
@@ -2488,13 +2488,13 @@
         <v>19</v>
       </c>
       <c r="J58" t="n">
-        <v>-429.1</v>
+        <v>-230.61</v>
       </c>
       <c r="K58" t="n">
-        <v>-452.83</v>
+        <v>-243.36</v>
       </c>
       <c r="L58" t="n">
-        <v>623.84</v>
+        <v>335.27</v>
       </c>
     </row>
     <row r="59">
@@ -2530,13 +2530,13 @@
         <v>22</v>
       </c>
       <c r="J59" t="n">
-        <v>231.44</v>
+        <v>93.08</v>
       </c>
       <c r="K59" t="n">
-        <v>-8.050000000000001</v>
+        <v>-3.24</v>
       </c>
       <c r="L59" t="n">
-        <v>231.58</v>
+        <v>93.13</v>
       </c>
     </row>
     <row r="60">
@@ -2572,13 +2572,13 @@
         <v>20</v>
       </c>
       <c r="J60" t="n">
-        <v>178.88</v>
+        <v>80.3</v>
       </c>
       <c r="K60" t="n">
-        <v>159.71</v>
+        <v>71.69</v>
       </c>
       <c r="L60" t="n">
-        <v>239.8</v>
+        <v>107.64</v>
       </c>
     </row>
     <row r="61">
@@ -2614,13 +2614,13 @@
         <v>24</v>
       </c>
       <c r="J61" t="n">
-        <v>-89</v>
+        <v>-40.44</v>
       </c>
       <c r="K61" t="n">
-        <v>-54.27</v>
+        <v>-24.66</v>
       </c>
       <c r="L61" t="n">
-        <v>104.24</v>
+        <v>47.37</v>
       </c>
     </row>
     <row r="62">
@@ -2656,13 +2656,13 @@
         <v>22</v>
       </c>
       <c r="J62" t="n">
-        <v>-175.21</v>
+        <v>-85.61</v>
       </c>
       <c r="K62" t="n">
-        <v>-102.93</v>
+        <v>-50.29</v>
       </c>
       <c r="L62" t="n">
-        <v>203.21</v>
+        <v>99.29000000000001</v>
       </c>
     </row>
     <row r="63">
@@ -2698,13 +2698,13 @@
         <v>23</v>
       </c>
       <c r="J63" t="n">
-        <v>-160.66</v>
+        <v>-70.06</v>
       </c>
       <c r="K63" t="n">
-        <v>-53.56</v>
+        <v>-23.35</v>
       </c>
       <c r="L63" t="n">
-        <v>169.35</v>
+        <v>73.84999999999999</v>
       </c>
     </row>
     <row r="64">
@@ -2740,13 +2740,13 @@
         <v>19</v>
       </c>
       <c r="J64" t="n">
-        <v>-55.97</v>
+        <v>-25.3</v>
       </c>
       <c r="K64" t="n">
-        <v>-212.62</v>
+        <v>-96.11</v>
       </c>
       <c r="L64" t="n">
-        <v>219.87</v>
+        <v>99.38</v>
       </c>
     </row>
     <row r="65">
@@ -2782,13 +2782,13 @@
         <v>20</v>
       </c>
       <c r="J65" t="n">
-        <v>315.13</v>
+        <v>155.89</v>
       </c>
       <c r="K65" t="n">
-        <v>150.94</v>
+        <v>74.67</v>
       </c>
       <c r="L65" t="n">
-        <v>349.41</v>
+        <v>172.85</v>
       </c>
     </row>
     <row r="66">
@@ -2824,13 +2824,13 @@
         <v>19</v>
       </c>
       <c r="J66" t="n">
-        <v>-6.77</v>
+        <v>-3.27</v>
       </c>
       <c r="K66" t="n">
-        <v>-222.13</v>
+        <v>-107.42</v>
       </c>
       <c r="L66" t="n">
-        <v>222.23</v>
+        <v>107.47</v>
       </c>
     </row>
     <row r="67">
@@ -2866,13 +2866,13 @@
         <v>19</v>
       </c>
       <c r="J67" t="n">
-        <v>607.8200000000001</v>
+        <v>293.81</v>
       </c>
       <c r="K67" t="n">
-        <v>-441.14</v>
+        <v>-213.24</v>
       </c>
       <c r="L67" t="n">
-        <v>751.03</v>
+        <v>363.03</v>
       </c>
     </row>
     <row r="68">
@@ -2908,13 +2908,13 @@
         <v>22</v>
       </c>
       <c r="J68" t="n">
-        <v>65.98999999999999</v>
+        <v>30.73</v>
       </c>
       <c r="K68" t="n">
-        <v>293.92</v>
+        <v>136.88</v>
       </c>
       <c r="L68" t="n">
-        <v>301.23</v>
+        <v>140.29</v>
       </c>
     </row>
     <row r="69">
@@ -2950,13 +2950,13 @@
         <v>23</v>
       </c>
       <c r="J69" t="n">
-        <v>95.03</v>
+        <v>41.59</v>
       </c>
       <c r="K69" t="n">
-        <v>-542.84</v>
+        <v>-237.6</v>
       </c>
       <c r="L69" t="n">
-        <v>551.1</v>
+        <v>241.22</v>
       </c>
     </row>
     <row r="70">
@@ -2992,13 +2992,13 @@
         <v>23</v>
       </c>
       <c r="J70" t="n">
-        <v>68.47</v>
+        <v>33.64</v>
       </c>
       <c r="K70" t="n">
-        <v>-334.66</v>
+        <v>-164.44</v>
       </c>
       <c r="L70" t="n">
-        <v>341.6</v>
+        <v>167.84</v>
       </c>
     </row>
     <row r="71">
@@ -3034,13 +3034,13 @@
         <v>21</v>
       </c>
       <c r="J71" t="n">
-        <v>-156.51</v>
+        <v>-85.45999999999999</v>
       </c>
       <c r="K71" t="n">
-        <v>-300.3</v>
+        <v>-163.98</v>
       </c>
       <c r="L71" t="n">
-        <v>338.64</v>
+        <v>184.91</v>
       </c>
     </row>
     <row r="72">
@@ -3076,13 +3076,13 @@
         <v>23</v>
       </c>
       <c r="J72" t="n">
-        <v>282.01</v>
+        <v>151.36</v>
       </c>
       <c r="K72" t="n">
-        <v>577.71</v>
+        <v>310.08</v>
       </c>
       <c r="L72" t="n">
-        <v>642.86</v>
+        <v>345.05</v>
       </c>
     </row>
     <row r="73">
@@ -3118,13 +3118,13 @@
         <v>20</v>
       </c>
       <c r="J73" t="n">
-        <v>-317.61</v>
+        <v>-172.45</v>
       </c>
       <c r="K73" t="n">
-        <v>-19.19</v>
+        <v>-10.42</v>
       </c>
       <c r="L73" t="n">
-        <v>318.19</v>
+        <v>172.76</v>
       </c>
     </row>
     <row r="74">
@@ -3160,13 +3160,13 @@
         <v>21</v>
       </c>
       <c r="J74" t="n">
-        <v>107.14</v>
+        <v>48.49</v>
       </c>
       <c r="K74" t="n">
-        <v>-40.4</v>
+        <v>-18.28</v>
       </c>
       <c r="L74" t="n">
-        <v>114.5</v>
+        <v>51.82</v>
       </c>
     </row>
     <row r="75">
@@ -3202,13 +3202,13 @@
         <v>20</v>
       </c>
       <c r="J75" t="n">
-        <v>-77.84</v>
+        <v>-35.67</v>
       </c>
       <c r="K75" t="n">
-        <v>265.94</v>
+        <v>121.86</v>
       </c>
       <c r="L75" t="n">
-        <v>277.1</v>
+        <v>126.97</v>
       </c>
     </row>
     <row r="76">
@@ -3244,13 +3244,13 @@
         <v>22</v>
       </c>
       <c r="J76" t="n">
-        <v>-95.42</v>
+        <v>-44</v>
       </c>
       <c r="K76" t="n">
-        <v>219.27</v>
+        <v>101.11</v>
       </c>
       <c r="L76" t="n">
-        <v>239.13</v>
+        <v>110.27</v>
       </c>
     </row>
     <row r="77">
@@ -3286,13 +3286,13 @@
         <v>24</v>
       </c>
       <c r="J77" t="n">
-        <v>-266.63</v>
+        <v>-131.54</v>
       </c>
       <c r="K77" t="n">
-        <v>-161.9</v>
+        <v>-79.88</v>
       </c>
       <c r="L77" t="n">
-        <v>311.93</v>
+        <v>153.9</v>
       </c>
     </row>
     <row r="78">
@@ -3328,13 +3328,13 @@
         <v>24</v>
       </c>
       <c r="J78" t="n">
-        <v>132.1</v>
+        <v>57.43</v>
       </c>
       <c r="K78" t="n">
-        <v>-295.08</v>
+        <v>-128.29</v>
       </c>
       <c r="L78" t="n">
-        <v>323.3</v>
+        <v>140.56</v>
       </c>
     </row>
     <row r="79">
@@ -3370,13 +3370,13 @@
         <v>24</v>
       </c>
       <c r="J79" t="n">
-        <v>307.56</v>
+        <v>129.21</v>
       </c>
       <c r="K79" t="n">
-        <v>-133.37</v>
+        <v>-56.03</v>
       </c>
       <c r="L79" t="n">
-        <v>335.24</v>
+        <v>140.83</v>
       </c>
     </row>
     <row r="80">
@@ -3412,13 +3412,13 @@
         <v>25</v>
       </c>
       <c r="J80" t="n">
-        <v>149.89</v>
+        <v>74.3</v>
       </c>
       <c r="K80" t="n">
-        <v>91.48999999999999</v>
+        <v>45.35</v>
       </c>
       <c r="L80" t="n">
-        <v>175.6</v>
+        <v>87.05</v>
       </c>
     </row>
     <row r="81">
@@ -3454,13 +3454,13 @@
         <v>23</v>
       </c>
       <c r="J81" t="n">
-        <v>171.3</v>
+        <v>82.88</v>
       </c>
       <c r="K81" t="n">
-        <v>324.08</v>
+        <v>156.79</v>
       </c>
       <c r="L81" t="n">
-        <v>366.57</v>
+        <v>177.35</v>
       </c>
     </row>
     <row r="82">
@@ -3496,13 +3496,13 @@
         <v>20</v>
       </c>
       <c r="J82" t="n">
-        <v>39.14</v>
+        <v>19.17</v>
       </c>
       <c r="K82" t="n">
-        <v>259.66</v>
+        <v>127.18</v>
       </c>
       <c r="L82" t="n">
-        <v>262.59</v>
+        <v>128.62</v>
       </c>
     </row>
     <row r="83">
@@ -3538,13 +3538,13 @@
         <v>21</v>
       </c>
       <c r="J83" t="n">
-        <v>134.31</v>
+        <v>61.4</v>
       </c>
       <c r="K83" t="n">
-        <v>-312.21</v>
+        <v>-142.72</v>
       </c>
       <c r="L83" t="n">
-        <v>339.87</v>
+        <v>155.37</v>
       </c>
     </row>
     <row r="84">
@@ -3580,13 +3580,13 @@
         <v>19</v>
       </c>
       <c r="J84" t="n">
-        <v>328.12</v>
+        <v>143.62</v>
       </c>
       <c r="K84" t="n">
-        <v>120.03</v>
+        <v>52.54</v>
       </c>
       <c r="L84" t="n">
-        <v>349.38</v>
+        <v>152.93</v>
       </c>
     </row>
     <row r="85">
@@ -3622,13 +3622,13 @@
         <v>19</v>
       </c>
       <c r="J85" t="n">
-        <v>337.52</v>
+        <v>149.6</v>
       </c>
       <c r="K85" t="n">
-        <v>315.81</v>
+        <v>139.98</v>
       </c>
       <c r="L85" t="n">
-        <v>462.23</v>
+        <v>204.88</v>
       </c>
     </row>
     <row r="86">
@@ -3664,13 +3664,13 @@
         <v>20</v>
       </c>
       <c r="J86" t="n">
-        <v>429.91</v>
+        <v>228.12</v>
       </c>
       <c r="K86" t="n">
-        <v>-253.8</v>
+        <v>-134.67</v>
       </c>
       <c r="L86" t="n">
-        <v>499.24</v>
+        <v>264.91</v>
       </c>
     </row>
     <row r="87">
@@ -3706,13 +3706,13 @@
         <v>25</v>
       </c>
       <c r="J87" t="n">
-        <v>17.48</v>
+        <v>4.98</v>
       </c>
       <c r="K87" t="n">
-        <v>246.24</v>
+        <v>70.17</v>
       </c>
       <c r="L87" t="n">
-        <v>246.86</v>
+        <v>70.34999999999999</v>
       </c>
     </row>
     <row r="88">
@@ -3748,13 +3748,13 @@
         <v>25</v>
       </c>
       <c r="J88" t="n">
-        <v>-312.08</v>
+        <v>-169.29</v>
       </c>
       <c r="K88" t="n">
-        <v>-162.53</v>
+        <v>-88.16</v>
       </c>
       <c r="L88" t="n">
-        <v>351.87</v>
+        <v>190.87</v>
       </c>
     </row>
   </sheetData>

--- a/output/2024-10-08.xlsx
+++ b/output/2024-10-08.xlsx
@@ -640,13 +640,13 @@
         <v>23</v>
       </c>
       <c r="J14" t="n">
-        <v>51.8</v>
+        <v>53.24</v>
       </c>
       <c r="K14" t="n">
-        <v>-27.84</v>
+        <v>-28.61</v>
       </c>
       <c r="L14" t="n">
-        <v>58.81</v>
+        <v>60.44</v>
       </c>
     </row>
     <row r="15">
@@ -682,13 +682,13 @@
         <v>23</v>
       </c>
       <c r="J15" t="n">
-        <v>-37.19</v>
+        <v>-37.51</v>
       </c>
       <c r="K15" t="n">
-        <v>50.64</v>
+        <v>51.07</v>
       </c>
       <c r="L15" t="n">
-        <v>62.83</v>
+        <v>63.36</v>
       </c>
     </row>
     <row r="16">
@@ -724,13 +724,13 @@
         <v>20</v>
       </c>
       <c r="J16" t="n">
-        <v>-42.44</v>
+        <v>-40.99</v>
       </c>
       <c r="K16" t="n">
-        <v>100.16</v>
+        <v>96.73</v>
       </c>
       <c r="L16" t="n">
-        <v>108.78</v>
+        <v>105.05</v>
       </c>
     </row>
     <row r="17">
@@ -766,13 +766,13 @@
         <v>25</v>
       </c>
       <c r="J17" t="n">
-        <v>-56.27</v>
+        <v>-56.7</v>
       </c>
       <c r="K17" t="n">
-        <v>56.45</v>
+        <v>56.89</v>
       </c>
       <c r="L17" t="n">
-        <v>79.70999999999999</v>
+        <v>80.31999999999999</v>
       </c>
     </row>
     <row r="18">
@@ -808,13 +808,13 @@
         <v>23</v>
       </c>
       <c r="J18" t="n">
-        <v>-46.64</v>
+        <v>-47.4</v>
       </c>
       <c r="K18" t="n">
-        <v>-58.54</v>
+        <v>-59.49</v>
       </c>
       <c r="L18" t="n">
-        <v>74.84</v>
+        <v>76.06</v>
       </c>
     </row>
     <row r="19">
@@ -850,13 +850,13 @@
         <v>19</v>
       </c>
       <c r="J19" t="n">
-        <v>97.83</v>
+        <v>95.81999999999999</v>
       </c>
       <c r="K19" t="n">
-        <v>10.06</v>
+        <v>9.859999999999999</v>
       </c>
       <c r="L19" t="n">
-        <v>98.34999999999999</v>
+        <v>96.31999999999999</v>
       </c>
     </row>
     <row r="20">
@@ -892,13 +892,13 @@
         <v>22</v>
       </c>
       <c r="J20" t="n">
-        <v>51.61</v>
+        <v>49.36</v>
       </c>
       <c r="K20" t="n">
-        <v>186.82</v>
+        <v>178.69</v>
       </c>
       <c r="L20" t="n">
-        <v>193.82</v>
+        <v>185.38</v>
       </c>
     </row>
     <row r="21">
@@ -934,13 +934,13 @@
         <v>25</v>
       </c>
       <c r="J21" t="n">
-        <v>187.32</v>
+        <v>178.34</v>
       </c>
       <c r="K21" t="n">
-        <v>14.3</v>
+        <v>13.62</v>
       </c>
       <c r="L21" t="n">
-        <v>187.86</v>
+        <v>178.86</v>
       </c>
     </row>
     <row r="22">
@@ -976,13 +976,13 @@
         <v>19</v>
       </c>
       <c r="J22" t="n">
-        <v>-10.6</v>
+        <v>-10.81</v>
       </c>
       <c r="K22" t="n">
-        <v>118.01</v>
+        <v>120.34</v>
       </c>
       <c r="L22" t="n">
-        <v>118.49</v>
+        <v>120.83</v>
       </c>
     </row>
     <row r="23">
@@ -1018,13 +1018,13 @@
         <v>22</v>
       </c>
       <c r="J23" t="n">
-        <v>-160.56</v>
+        <v>-156.83</v>
       </c>
       <c r="K23" t="n">
-        <v>-156.7</v>
+        <v>-153.06</v>
       </c>
       <c r="L23" t="n">
-        <v>224.35</v>
+        <v>219.14</v>
       </c>
     </row>
     <row r="24">
@@ -1060,13 +1060,13 @@
         <v>25</v>
       </c>
       <c r="J24" t="n">
-        <v>-0.22</v>
+        <v>-0.24</v>
       </c>
       <c r="K24" t="n">
-        <v>105.02</v>
+        <v>113.37</v>
       </c>
       <c r="L24" t="n">
-        <v>105.02</v>
+        <v>113.37</v>
       </c>
     </row>
     <row r="25">
@@ -1102,13 +1102,13 @@
         <v>23</v>
       </c>
       <c r="J25" t="n">
-        <v>-129.44</v>
+        <v>-132.6</v>
       </c>
       <c r="K25" t="n">
-        <v>76.93000000000001</v>
+        <v>78.81</v>
       </c>
       <c r="L25" t="n">
-        <v>150.58</v>
+        <v>154.25</v>
       </c>
     </row>
     <row r="26">
@@ -1144,13 +1144,13 @@
         <v>23</v>
       </c>
       <c r="J26" t="n">
-        <v>-291.92</v>
+        <v>-299.79</v>
       </c>
       <c r="K26" t="n">
-        <v>-27.78</v>
+        <v>-28.53</v>
       </c>
       <c r="L26" t="n">
-        <v>293.24</v>
+        <v>301.14</v>
       </c>
     </row>
     <row r="27">
@@ -1186,13 +1186,13 @@
         <v>20</v>
       </c>
       <c r="J27" t="n">
-        <v>12.26</v>
+        <v>13.08</v>
       </c>
       <c r="K27" t="n">
-        <v>218.75</v>
+        <v>233.34</v>
       </c>
       <c r="L27" t="n">
-        <v>219.09</v>
+        <v>233.71</v>
       </c>
     </row>
     <row r="28">
@@ -1228,13 +1228,13 @@
         <v>21</v>
       </c>
       <c r="J28" t="n">
-        <v>222.09</v>
+        <v>233.55</v>
       </c>
       <c r="K28" t="n">
-        <v>107.31</v>
+        <v>112.85</v>
       </c>
       <c r="L28" t="n">
-        <v>246.66</v>
+        <v>259.39</v>
       </c>
     </row>
     <row r="29">
@@ -1270,13 +1270,13 @@
         <v>24</v>
       </c>
       <c r="J29" t="n">
-        <v>26.03</v>
+        <v>24.5</v>
       </c>
       <c r="K29" t="n">
-        <v>-77.59999999999999</v>
+        <v>-73.04000000000001</v>
       </c>
       <c r="L29" t="n">
-        <v>81.84999999999999</v>
+        <v>77.04000000000001</v>
       </c>
     </row>
     <row r="30">
@@ -1312,13 +1312,13 @@
         <v>20</v>
       </c>
       <c r="J30" t="n">
-        <v>-7.54</v>
+        <v>-7.35</v>
       </c>
       <c r="K30" t="n">
-        <v>86.51000000000001</v>
+        <v>84.39</v>
       </c>
       <c r="L30" t="n">
-        <v>86.84</v>
+        <v>84.7</v>
       </c>
     </row>
     <row r="31">
@@ -1354,13 +1354,13 @@
         <v>24</v>
       </c>
       <c r="J31" t="n">
-        <v>18.12</v>
+        <v>18.96</v>
       </c>
       <c r="K31" t="n">
-        <v>-47.82</v>
+        <v>-50.04</v>
       </c>
       <c r="L31" t="n">
-        <v>51.13</v>
+        <v>53.51</v>
       </c>
     </row>
     <row r="32">
@@ -1396,13 +1396,13 @@
         <v>20</v>
       </c>
       <c r="J32" t="n">
-        <v>-136.92</v>
+        <v>-130.11</v>
       </c>
       <c r="K32" t="n">
-        <v>20.63</v>
+        <v>19.6</v>
       </c>
       <c r="L32" t="n">
-        <v>138.47</v>
+        <v>131.58</v>
       </c>
     </row>
     <row r="33">
@@ -1438,13 +1438,13 @@
         <v>20</v>
       </c>
       <c r="J33" t="n">
-        <v>49.4</v>
+        <v>46.18</v>
       </c>
       <c r="K33" t="n">
-        <v>-133.38</v>
+        <v>-124.7</v>
       </c>
       <c r="L33" t="n">
-        <v>142.24</v>
+        <v>132.98</v>
       </c>
     </row>
     <row r="34">
@@ -1480,13 +1480,13 @@
         <v>19</v>
       </c>
       <c r="J34" t="n">
-        <v>-44.26</v>
+        <v>-46.37</v>
       </c>
       <c r="K34" t="n">
-        <v>-47.61</v>
+        <v>-49.88</v>
       </c>
       <c r="L34" t="n">
-        <v>65.01000000000001</v>
+        <v>68.09999999999999</v>
       </c>
     </row>
     <row r="35">
@@ -1522,13 +1522,13 @@
         <v>22</v>
       </c>
       <c r="J35" t="n">
-        <v>8.550000000000001</v>
+        <v>8.58</v>
       </c>
       <c r="K35" t="n">
-        <v>126.68</v>
+        <v>127.19</v>
       </c>
       <c r="L35" t="n">
-        <v>126.96</v>
+        <v>127.48</v>
       </c>
     </row>
     <row r="36">
@@ -1564,13 +1564,13 @@
         <v>22</v>
       </c>
       <c r="J36" t="n">
-        <v>65.55</v>
+        <v>66.29000000000001</v>
       </c>
       <c r="K36" t="n">
-        <v>-102.53</v>
+        <v>-103.69</v>
       </c>
       <c r="L36" t="n">
-        <v>121.7</v>
+        <v>123.07</v>
       </c>
     </row>
     <row r="37">
@@ -1606,13 +1606,13 @@
         <v>25</v>
       </c>
       <c r="J37" t="n">
-        <v>-68.87</v>
+        <v>-72.52</v>
       </c>
       <c r="K37" t="n">
-        <v>52.59</v>
+        <v>55.38</v>
       </c>
       <c r="L37" t="n">
-        <v>86.66</v>
+        <v>91.25</v>
       </c>
     </row>
     <row r="38">
@@ -1648,13 +1648,13 @@
         <v>20</v>
       </c>
       <c r="J38" t="n">
-        <v>132.62</v>
+        <v>138.34</v>
       </c>
       <c r="K38" t="n">
-        <v>60.39</v>
+        <v>62.99</v>
       </c>
       <c r="L38" t="n">
-        <v>145.73</v>
+        <v>152.01</v>
       </c>
     </row>
     <row r="39">
@@ -1693,10 +1693,10 @@
         <v>-0.73</v>
       </c>
       <c r="K39" t="n">
-        <v>204.22</v>
+        <v>203.3</v>
       </c>
       <c r="L39" t="n">
-        <v>204.22</v>
+        <v>203.3</v>
       </c>
     </row>
     <row r="40">
@@ -1732,13 +1732,13 @@
         <v>23</v>
       </c>
       <c r="J40" t="n">
-        <v>52.6</v>
+        <v>52.33</v>
       </c>
       <c r="K40" t="n">
-        <v>-205.13</v>
+        <v>-204.09</v>
       </c>
       <c r="L40" t="n">
-        <v>211.77</v>
+        <v>210.69</v>
       </c>
     </row>
     <row r="41">
@@ -1774,13 +1774,13 @@
         <v>21</v>
       </c>
       <c r="J41" t="n">
-        <v>-205.64</v>
+        <v>-188.71</v>
       </c>
       <c r="K41" t="n">
-        <v>-31.49</v>
+        <v>-28.9</v>
       </c>
       <c r="L41" t="n">
-        <v>208.03</v>
+        <v>190.91</v>
       </c>
     </row>
     <row r="42">
@@ -1816,13 +1816,13 @@
         <v>21</v>
       </c>
       <c r="J42" t="n">
-        <v>-197.05</v>
+        <v>-217.03</v>
       </c>
       <c r="K42" t="n">
-        <v>52.75</v>
+        <v>58.1</v>
       </c>
       <c r="L42" t="n">
-        <v>203.99</v>
+        <v>224.67</v>
       </c>
     </row>
     <row r="43">
@@ -1858,13 +1858,13 @@
         <v>24</v>
       </c>
       <c r="J43" t="n">
-        <v>-212.51</v>
+        <v>-223.39</v>
       </c>
       <c r="K43" t="n">
-        <v>-31.47</v>
+        <v>-33.08</v>
       </c>
       <c r="L43" t="n">
-        <v>214.83</v>
+        <v>225.82</v>
       </c>
     </row>
     <row r="44">
@@ -1900,13 +1900,13 @@
         <v>25</v>
       </c>
       <c r="J44" t="n">
-        <v>-66.18000000000001</v>
+        <v>-64.40000000000001</v>
       </c>
       <c r="K44" t="n">
-        <v>-46.76</v>
+        <v>-45.5</v>
       </c>
       <c r="L44" t="n">
-        <v>81.03</v>
+        <v>78.84999999999999</v>
       </c>
     </row>
     <row r="45">
@@ -1942,13 +1942,13 @@
         <v>22</v>
       </c>
       <c r="J45" t="n">
-        <v>-26.23</v>
+        <v>-28.44</v>
       </c>
       <c r="K45" t="n">
-        <v>36.33</v>
+        <v>39.39</v>
       </c>
       <c r="L45" t="n">
-        <v>44.81</v>
+        <v>48.58</v>
       </c>
     </row>
     <row r="46">
@@ -1984,13 +1984,13 @@
         <v>25</v>
       </c>
       <c r="J46" t="n">
-        <v>33.98</v>
+        <v>36.01</v>
       </c>
       <c r="K46" t="n">
-        <v>33.99</v>
+        <v>36.02</v>
       </c>
       <c r="L46" t="n">
-        <v>48.06</v>
+        <v>50.94</v>
       </c>
     </row>
     <row r="47">
@@ -2026,13 +2026,13 @@
         <v>19</v>
       </c>
       <c r="J47" t="n">
-        <v>-114.16</v>
+        <v>-110.79</v>
       </c>
       <c r="K47" t="n">
-        <v>-1.83</v>
+        <v>-1.78</v>
       </c>
       <c r="L47" t="n">
-        <v>114.18</v>
+        <v>110.8</v>
       </c>
     </row>
     <row r="48">
@@ -2068,13 +2068,13 @@
         <v>25</v>
       </c>
       <c r="J48" t="n">
-        <v>-70.63</v>
+        <v>-70.84</v>
       </c>
       <c r="K48" t="n">
-        <v>21</v>
+        <v>21.06</v>
       </c>
       <c r="L48" t="n">
-        <v>73.68000000000001</v>
+        <v>73.90000000000001</v>
       </c>
     </row>
     <row r="49">
@@ -2110,13 +2110,13 @@
         <v>23</v>
       </c>
       <c r="J49" t="n">
-        <v>-12.77</v>
+        <v>-12.29</v>
       </c>
       <c r="K49" t="n">
-        <v>115.61</v>
+        <v>111.25</v>
       </c>
       <c r="L49" t="n">
-        <v>116.31</v>
+        <v>111.93</v>
       </c>
     </row>
     <row r="50">
@@ -2152,13 +2152,13 @@
         <v>25</v>
       </c>
       <c r="J50" t="n">
-        <v>-163.98</v>
+        <v>-156.14</v>
       </c>
       <c r="K50" t="n">
-        <v>-113.09</v>
+        <v>-107.69</v>
       </c>
       <c r="L50" t="n">
-        <v>199.2</v>
+        <v>189.68</v>
       </c>
     </row>
     <row r="51">
@@ -2194,13 +2194,13 @@
         <v>19</v>
       </c>
       <c r="J51" t="n">
-        <v>2.59</v>
+        <v>2.63</v>
       </c>
       <c r="K51" t="n">
-        <v>-126.29</v>
+        <v>-128.01</v>
       </c>
       <c r="L51" t="n">
-        <v>126.32</v>
+        <v>128.03</v>
       </c>
     </row>
     <row r="52">
@@ -2236,13 +2236,13 @@
         <v>22</v>
       </c>
       <c r="J52" t="n">
-        <v>-87.37</v>
+        <v>-87.09</v>
       </c>
       <c r="K52" t="n">
-        <v>115.45</v>
+        <v>115.08</v>
       </c>
       <c r="L52" t="n">
-        <v>144.78</v>
+        <v>144.31</v>
       </c>
     </row>
     <row r="53">
@@ -2278,13 +2278,13 @@
         <v>21</v>
       </c>
       <c r="J53" t="n">
-        <v>201.56</v>
+        <v>198.21</v>
       </c>
       <c r="K53" t="n">
-        <v>-128.33</v>
+        <v>-126.2</v>
       </c>
       <c r="L53" t="n">
-        <v>238.94</v>
+        <v>234.98</v>
       </c>
     </row>
     <row r="54">
@@ -2320,13 +2320,13 @@
         <v>23</v>
       </c>
       <c r="J54" t="n">
-        <v>-123.64</v>
+        <v>-126.41</v>
       </c>
       <c r="K54" t="n">
-        <v>110.11</v>
+        <v>112.58</v>
       </c>
       <c r="L54" t="n">
-        <v>165.56</v>
+        <v>169.27</v>
       </c>
     </row>
     <row r="55">
@@ -2362,13 +2362,13 @@
         <v>23</v>
       </c>
       <c r="J55" t="n">
-        <v>-51.4</v>
+        <v>-51.81</v>
       </c>
       <c r="K55" t="n">
-        <v>-173.83</v>
+        <v>-175.19</v>
       </c>
       <c r="L55" t="n">
-        <v>181.27</v>
+        <v>182.69</v>
       </c>
     </row>
     <row r="56">
@@ -2404,13 +2404,13 @@
         <v>22</v>
       </c>
       <c r="J56" t="n">
-        <v>-188.23</v>
+        <v>-200.06</v>
       </c>
       <c r="K56" t="n">
-        <v>61.7</v>
+        <v>65.56999999999999</v>
       </c>
       <c r="L56" t="n">
-        <v>198.08</v>
+        <v>210.53</v>
       </c>
     </row>
     <row r="57">
@@ -2446,13 +2446,13 @@
         <v>22</v>
       </c>
       <c r="J57" t="n">
-        <v>-10.43</v>
+        <v>-12.33</v>
       </c>
       <c r="K57" t="n">
-        <v>-223.86</v>
+        <v>-264.68</v>
       </c>
       <c r="L57" t="n">
-        <v>224.1</v>
+        <v>264.97</v>
       </c>
     </row>
     <row r="58">
@@ -2488,13 +2488,13 @@
         <v>19</v>
       </c>
       <c r="J58" t="n">
-        <v>-230.61</v>
+        <v>-239.15</v>
       </c>
       <c r="K58" t="n">
-        <v>-243.36</v>
+        <v>-252.37</v>
       </c>
       <c r="L58" t="n">
-        <v>335.27</v>
+        <v>347.68</v>
       </c>
     </row>
     <row r="59">
@@ -2530,13 +2530,13 @@
         <v>22</v>
       </c>
       <c r="J59" t="n">
-        <v>93.08</v>
+        <v>80.31999999999999</v>
       </c>
       <c r="K59" t="n">
-        <v>-3.24</v>
+        <v>-2.79</v>
       </c>
       <c r="L59" t="n">
-        <v>93.13</v>
+        <v>80.37</v>
       </c>
     </row>
     <row r="60">
@@ -2572,13 +2572,13 @@
         <v>20</v>
       </c>
       <c r="J60" t="n">
-        <v>80.3</v>
+        <v>76.3</v>
       </c>
       <c r="K60" t="n">
-        <v>71.69</v>
+        <v>68.12</v>
       </c>
       <c r="L60" t="n">
-        <v>107.64</v>
+        <v>102.28</v>
       </c>
     </row>
     <row r="61">
@@ -2614,13 +2614,13 @@
         <v>24</v>
       </c>
       <c r="J61" t="n">
-        <v>-40.44</v>
+        <v>-42.73</v>
       </c>
       <c r="K61" t="n">
-        <v>-24.66</v>
+        <v>-26.06</v>
       </c>
       <c r="L61" t="n">
-        <v>47.37</v>
+        <v>50.05</v>
       </c>
     </row>
     <row r="62">
@@ -2656,13 +2656,13 @@
         <v>22</v>
       </c>
       <c r="J62" t="n">
-        <v>-85.61</v>
+        <v>-83.83</v>
       </c>
       <c r="K62" t="n">
-        <v>-50.29</v>
+        <v>-49.25</v>
       </c>
       <c r="L62" t="n">
-        <v>99.29000000000001</v>
+        <v>97.23</v>
       </c>
     </row>
     <row r="63">
@@ -2698,13 +2698,13 @@
         <v>23</v>
       </c>
       <c r="J63" t="n">
-        <v>-70.06</v>
+        <v>-70.53</v>
       </c>
       <c r="K63" t="n">
-        <v>-23.35</v>
+        <v>-23.51</v>
       </c>
       <c r="L63" t="n">
-        <v>73.84999999999999</v>
+        <v>74.34999999999999</v>
       </c>
     </row>
     <row r="64">
@@ -2740,13 +2740,13 @@
         <v>19</v>
       </c>
       <c r="J64" t="n">
-        <v>-25.3</v>
+        <v>-24.75</v>
       </c>
       <c r="K64" t="n">
-        <v>-96.11</v>
+        <v>-94.04000000000001</v>
       </c>
       <c r="L64" t="n">
-        <v>99.38</v>
+        <v>97.23999999999999</v>
       </c>
     </row>
     <row r="65">
@@ -2782,13 +2782,13 @@
         <v>20</v>
       </c>
       <c r="J65" t="n">
-        <v>155.89</v>
+        <v>151.65</v>
       </c>
       <c r="K65" t="n">
-        <v>74.67</v>
+        <v>72.64</v>
       </c>
       <c r="L65" t="n">
-        <v>172.85</v>
+        <v>168.15</v>
       </c>
     </row>
     <row r="66">
@@ -2824,13 +2824,13 @@
         <v>19</v>
       </c>
       <c r="J66" t="n">
-        <v>-3.27</v>
+        <v>-3.43</v>
       </c>
       <c r="K66" t="n">
-        <v>-107.42</v>
+        <v>-112.5</v>
       </c>
       <c r="L66" t="n">
-        <v>107.47</v>
+        <v>112.55</v>
       </c>
     </row>
     <row r="67">
@@ -2866,13 +2866,13 @@
         <v>19</v>
       </c>
       <c r="J67" t="n">
-        <v>293.81</v>
+        <v>270.19</v>
       </c>
       <c r="K67" t="n">
-        <v>-213.24</v>
+        <v>-196.1</v>
       </c>
       <c r="L67" t="n">
-        <v>363.03</v>
+        <v>333.85</v>
       </c>
     </row>
     <row r="68">
@@ -2908,13 +2908,13 @@
         <v>22</v>
       </c>
       <c r="J68" t="n">
-        <v>30.73</v>
+        <v>32.34</v>
       </c>
       <c r="K68" t="n">
-        <v>136.88</v>
+        <v>144.01</v>
       </c>
       <c r="L68" t="n">
-        <v>140.29</v>
+        <v>147.6</v>
       </c>
     </row>
     <row r="69">
@@ -2950,13 +2950,13 @@
         <v>23</v>
       </c>
       <c r="J69" t="n">
-        <v>41.59</v>
+        <v>42.55</v>
       </c>
       <c r="K69" t="n">
-        <v>-237.6</v>
+        <v>-243.06</v>
       </c>
       <c r="L69" t="n">
-        <v>241.22</v>
+        <v>246.75</v>
       </c>
     </row>
     <row r="70">
@@ -2992,13 +2992,13 @@
         <v>23</v>
       </c>
       <c r="J70" t="n">
-        <v>33.64</v>
+        <v>34.2</v>
       </c>
       <c r="K70" t="n">
-        <v>-164.44</v>
+        <v>-167.16</v>
       </c>
       <c r="L70" t="n">
-        <v>167.84</v>
+        <v>170.62</v>
       </c>
     </row>
     <row r="71">
@@ -3034,13 +3034,13 @@
         <v>21</v>
       </c>
       <c r="J71" t="n">
-        <v>-85.45999999999999</v>
+        <v>-93.48999999999999</v>
       </c>
       <c r="K71" t="n">
-        <v>-163.98</v>
+        <v>-179.38</v>
       </c>
       <c r="L71" t="n">
-        <v>184.91</v>
+        <v>202.28</v>
       </c>
     </row>
     <row r="72">
@@ -3076,13 +3076,13 @@
         <v>23</v>
       </c>
       <c r="J72" t="n">
-        <v>151.36</v>
+        <v>155.74</v>
       </c>
       <c r="K72" t="n">
-        <v>310.08</v>
+        <v>319.03</v>
       </c>
       <c r="L72" t="n">
-        <v>345.05</v>
+        <v>355.01</v>
       </c>
     </row>
     <row r="73">
@@ -3118,13 +3118,13 @@
         <v>20</v>
       </c>
       <c r="J73" t="n">
-        <v>-172.45</v>
+        <v>-193.24</v>
       </c>
       <c r="K73" t="n">
-        <v>-10.42</v>
+        <v>-11.67</v>
       </c>
       <c r="L73" t="n">
-        <v>172.76</v>
+        <v>193.59</v>
       </c>
     </row>
     <row r="74">
@@ -3160,13 +3160,13 @@
         <v>21</v>
       </c>
       <c r="J74" t="n">
-        <v>48.49</v>
+        <v>51.05</v>
       </c>
       <c r="K74" t="n">
-        <v>-18.28</v>
+        <v>-19.25</v>
       </c>
       <c r="L74" t="n">
-        <v>51.82</v>
+        <v>54.56</v>
       </c>
     </row>
     <row r="75">
@@ -3202,13 +3202,13 @@
         <v>20</v>
       </c>
       <c r="J75" t="n">
-        <v>-35.67</v>
+        <v>-33.47</v>
       </c>
       <c r="K75" t="n">
-        <v>121.86</v>
+        <v>114.36</v>
       </c>
       <c r="L75" t="n">
-        <v>126.97</v>
+        <v>119.16</v>
       </c>
     </row>
     <row r="76">
@@ -3244,13 +3244,13 @@
         <v>22</v>
       </c>
       <c r="J76" t="n">
-        <v>-44</v>
+        <v>-41.73</v>
       </c>
       <c r="K76" t="n">
-        <v>101.11</v>
+        <v>95.90000000000001</v>
       </c>
       <c r="L76" t="n">
-        <v>110.27</v>
+        <v>104.59</v>
       </c>
     </row>
     <row r="77">
@@ -3286,13 +3286,13 @@
         <v>24</v>
       </c>
       <c r="J77" t="n">
-        <v>-131.54</v>
+        <v>-123.34</v>
       </c>
       <c r="K77" t="n">
-        <v>-79.88</v>
+        <v>-74.89</v>
       </c>
       <c r="L77" t="n">
-        <v>153.9</v>
+        <v>144.29</v>
       </c>
     </row>
     <row r="78">
@@ -3328,13 +3328,13 @@
         <v>24</v>
       </c>
       <c r="J78" t="n">
-        <v>57.43</v>
+        <v>53.42</v>
       </c>
       <c r="K78" t="n">
-        <v>-128.29</v>
+        <v>-119.33</v>
       </c>
       <c r="L78" t="n">
-        <v>140.56</v>
+        <v>130.75</v>
       </c>
     </row>
     <row r="79">
@@ -3370,13 +3370,13 @@
         <v>24</v>
       </c>
       <c r="J79" t="n">
-        <v>129.21</v>
+        <v>119.56</v>
       </c>
       <c r="K79" t="n">
-        <v>-56.03</v>
+        <v>-51.85</v>
       </c>
       <c r="L79" t="n">
-        <v>140.83</v>
+        <v>130.32</v>
       </c>
     </row>
     <row r="80">
@@ -3412,13 +3412,13 @@
         <v>25</v>
       </c>
       <c r="J80" t="n">
-        <v>74.3</v>
+        <v>78.59</v>
       </c>
       <c r="K80" t="n">
-        <v>45.35</v>
+        <v>47.97</v>
       </c>
       <c r="L80" t="n">
-        <v>87.05</v>
+        <v>92.06999999999999</v>
       </c>
     </row>
     <row r="81">
@@ -3454,13 +3454,13 @@
         <v>23</v>
       </c>
       <c r="J81" t="n">
-        <v>82.88</v>
+        <v>80.31999999999999</v>
       </c>
       <c r="K81" t="n">
-        <v>156.79</v>
+        <v>151.96</v>
       </c>
       <c r="L81" t="n">
-        <v>177.35</v>
+        <v>171.88</v>
       </c>
     </row>
     <row r="82">
@@ -3496,13 +3496,13 @@
         <v>20</v>
       </c>
       <c r="J82" t="n">
-        <v>19.17</v>
+        <v>19.42</v>
       </c>
       <c r="K82" t="n">
-        <v>127.18</v>
+        <v>128.79</v>
       </c>
       <c r="L82" t="n">
-        <v>128.62</v>
+        <v>130.25</v>
       </c>
     </row>
     <row r="83">
@@ -3538,13 +3538,13 @@
         <v>21</v>
       </c>
       <c r="J83" t="n">
-        <v>61.4</v>
+        <v>64.01000000000001</v>
       </c>
       <c r="K83" t="n">
-        <v>-142.72</v>
+        <v>-148.78</v>
       </c>
       <c r="L83" t="n">
-        <v>155.37</v>
+        <v>161.97</v>
       </c>
     </row>
     <row r="84">
@@ -3580,13 +3580,13 @@
         <v>19</v>
       </c>
       <c r="J84" t="n">
-        <v>143.62</v>
+        <v>157.57</v>
       </c>
       <c r="K84" t="n">
-        <v>52.54</v>
+        <v>57.64</v>
       </c>
       <c r="L84" t="n">
-        <v>152.93</v>
+        <v>167.78</v>
       </c>
     </row>
     <row r="85">
@@ -3622,13 +3622,13 @@
         <v>19</v>
       </c>
       <c r="J85" t="n">
-        <v>149.6</v>
+        <v>154.58</v>
       </c>
       <c r="K85" t="n">
-        <v>139.98</v>
+        <v>144.63</v>
       </c>
       <c r="L85" t="n">
-        <v>204.88</v>
+        <v>211.69</v>
       </c>
     </row>
     <row r="86">
@@ -3664,13 +3664,13 @@
         <v>20</v>
       </c>
       <c r="J86" t="n">
-        <v>228.12</v>
+        <v>256.48</v>
       </c>
       <c r="K86" t="n">
-        <v>-134.67</v>
+        <v>-151.41</v>
       </c>
       <c r="L86" t="n">
-        <v>264.91</v>
+        <v>297.84</v>
       </c>
     </row>
     <row r="87">
@@ -3706,13 +3706,13 @@
         <v>25</v>
       </c>
       <c r="J87" t="n">
-        <v>4.98</v>
+        <v>5.16</v>
       </c>
       <c r="K87" t="n">
-        <v>70.17</v>
+        <v>72.73999999999999</v>
       </c>
       <c r="L87" t="n">
-        <v>70.34999999999999</v>
+        <v>72.93000000000001</v>
       </c>
     </row>
     <row r="88">
@@ -3748,13 +3748,13 @@
         <v>25</v>
       </c>
       <c r="J88" t="n">
-        <v>-169.29</v>
+        <v>-184</v>
       </c>
       <c r="K88" t="n">
-        <v>-88.16</v>
+        <v>-95.81999999999999</v>
       </c>
       <c r="L88" t="n">
-        <v>190.87</v>
+        <v>207.46</v>
       </c>
     </row>
   </sheetData>

--- a/output/2024-10-08.xlsx
+++ b/output/2024-10-08.xlsx
@@ -640,13 +640,13 @@
         <v>23</v>
       </c>
       <c r="J14" t="n">
-        <v>53.24</v>
+        <v>55.55</v>
       </c>
       <c r="K14" t="n">
-        <v>-28.61</v>
+        <v>-29.86</v>
       </c>
       <c r="L14" t="n">
-        <v>60.44</v>
+        <v>63.07</v>
       </c>
     </row>
     <row r="15">
@@ -682,13 +682,13 @@
         <v>23</v>
       </c>
       <c r="J15" t="n">
-        <v>-37.51</v>
+        <v>-38.89</v>
       </c>
       <c r="K15" t="n">
-        <v>51.07</v>
+        <v>52.96</v>
       </c>
       <c r="L15" t="n">
-        <v>63.36</v>
+        <v>65.70999999999999</v>
       </c>
     </row>
     <row r="16">
@@ -724,13 +724,13 @@
         <v>20</v>
       </c>
       <c r="J16" t="n">
-        <v>-40.99</v>
+        <v>-39.32</v>
       </c>
       <c r="K16" t="n">
-        <v>96.73</v>
+        <v>92.8</v>
       </c>
       <c r="L16" t="n">
-        <v>105.05</v>
+        <v>100.79</v>
       </c>
     </row>
     <row r="17">
@@ -766,13 +766,13 @@
         <v>25</v>
       </c>
       <c r="J17" t="n">
-        <v>-56.7</v>
+        <v>-57.21</v>
       </c>
       <c r="K17" t="n">
-        <v>56.89</v>
+        <v>57.41</v>
       </c>
       <c r="L17" t="n">
-        <v>80.31999999999999</v>
+        <v>81.05</v>
       </c>
     </row>
     <row r="18">
@@ -808,13 +808,13 @@
         <v>23</v>
       </c>
       <c r="J18" t="n">
-        <v>-47.4</v>
+        <v>-48.79</v>
       </c>
       <c r="K18" t="n">
-        <v>-59.49</v>
+        <v>-61.23</v>
       </c>
       <c r="L18" t="n">
-        <v>76.06</v>
+        <v>78.29000000000001</v>
       </c>
     </row>
     <row r="19">
@@ -850,13 +850,13 @@
         <v>19</v>
       </c>
       <c r="J19" t="n">
-        <v>95.81999999999999</v>
+        <v>96.31999999999999</v>
       </c>
       <c r="K19" t="n">
-        <v>9.859999999999999</v>
+        <v>9.91</v>
       </c>
       <c r="L19" t="n">
-        <v>96.31999999999999</v>
+        <v>96.83</v>
       </c>
     </row>
     <row r="20">
@@ -892,13 +892,13 @@
         <v>22</v>
       </c>
       <c r="J20" t="n">
-        <v>49.36</v>
+        <v>46.91</v>
       </c>
       <c r="K20" t="n">
-        <v>178.69</v>
+        <v>169.81</v>
       </c>
       <c r="L20" t="n">
-        <v>185.38</v>
+        <v>176.17</v>
       </c>
     </row>
     <row r="21">
@@ -934,13 +934,13 @@
         <v>25</v>
       </c>
       <c r="J21" t="n">
-        <v>178.34</v>
+        <v>168.09</v>
       </c>
       <c r="K21" t="n">
-        <v>13.62</v>
+        <v>12.83</v>
       </c>
       <c r="L21" t="n">
-        <v>178.86</v>
+        <v>168.58</v>
       </c>
     </row>
     <row r="22">
@@ -976,13 +976,13 @@
         <v>19</v>
       </c>
       <c r="J22" t="n">
-        <v>-10.81</v>
+        <v>-11.11</v>
       </c>
       <c r="K22" t="n">
-        <v>120.34</v>
+        <v>123.69</v>
       </c>
       <c r="L22" t="n">
-        <v>120.83</v>
+        <v>124.19</v>
       </c>
     </row>
     <row r="23">
@@ -1018,13 +1018,13 @@
         <v>22</v>
       </c>
       <c r="J23" t="n">
-        <v>-156.83</v>
+        <v>-152.28</v>
       </c>
       <c r="K23" t="n">
-        <v>-153.06</v>
+        <v>-148.62</v>
       </c>
       <c r="L23" t="n">
-        <v>219.14</v>
+        <v>212.79</v>
       </c>
     </row>
     <row r="24">
@@ -1060,13 +1060,13 @@
         <v>25</v>
       </c>
       <c r="J24" t="n">
-        <v>-0.24</v>
+        <v>-0.26</v>
       </c>
       <c r="K24" t="n">
-        <v>113.37</v>
+        <v>122.6</v>
       </c>
       <c r="L24" t="n">
-        <v>113.37</v>
+        <v>122.6</v>
       </c>
     </row>
     <row r="25">
@@ -1102,13 +1102,13 @@
         <v>23</v>
       </c>
       <c r="J25" t="n">
-        <v>-132.6</v>
+        <v>-135.84</v>
       </c>
       <c r="K25" t="n">
-        <v>78.81</v>
+        <v>80.73</v>
       </c>
       <c r="L25" t="n">
-        <v>154.25</v>
+        <v>158.02</v>
       </c>
     </row>
     <row r="26">
@@ -1144,13 +1144,13 @@
         <v>23</v>
       </c>
       <c r="J26" t="n">
-        <v>-299.79</v>
+        <v>-295.65</v>
       </c>
       <c r="K26" t="n">
-        <v>-28.53</v>
+        <v>-28.13</v>
       </c>
       <c r="L26" t="n">
-        <v>301.14</v>
+        <v>296.98</v>
       </c>
     </row>
     <row r="27">
@@ -1186,13 +1186,13 @@
         <v>20</v>
       </c>
       <c r="J27" t="n">
-        <v>13.08</v>
+        <v>13.54</v>
       </c>
       <c r="K27" t="n">
-        <v>233.34</v>
+        <v>241.6</v>
       </c>
       <c r="L27" t="n">
-        <v>233.71</v>
+        <v>241.98</v>
       </c>
     </row>
     <row r="28">
@@ -1228,13 +1228,13 @@
         <v>21</v>
       </c>
       <c r="J28" t="n">
-        <v>233.55</v>
+        <v>237.27</v>
       </c>
       <c r="K28" t="n">
-        <v>112.85</v>
+        <v>114.64</v>
       </c>
       <c r="L28" t="n">
-        <v>259.39</v>
+        <v>263.51</v>
       </c>
     </row>
     <row r="29">
@@ -1270,13 +1270,13 @@
         <v>24</v>
       </c>
       <c r="J29" t="n">
-        <v>24.5</v>
+        <v>24.87</v>
       </c>
       <c r="K29" t="n">
-        <v>-73.04000000000001</v>
+        <v>-74.14</v>
       </c>
       <c r="L29" t="n">
-        <v>77.04000000000001</v>
+        <v>78.2</v>
       </c>
     </row>
     <row r="30">
@@ -1312,13 +1312,13 @@
         <v>20</v>
       </c>
       <c r="J30" t="n">
-        <v>-7.35</v>
+        <v>-7.32</v>
       </c>
       <c r="K30" t="n">
-        <v>84.39</v>
+        <v>84.02</v>
       </c>
       <c r="L30" t="n">
-        <v>84.7</v>
+        <v>84.34</v>
       </c>
     </row>
     <row r="31">
@@ -1354,13 +1354,13 @@
         <v>24</v>
       </c>
       <c r="J31" t="n">
-        <v>18.96</v>
+        <v>20.19</v>
       </c>
       <c r="K31" t="n">
-        <v>-50.04</v>
+        <v>-53.27</v>
       </c>
       <c r="L31" t="n">
-        <v>53.51</v>
+        <v>56.97</v>
       </c>
     </row>
     <row r="32">
@@ -1396,13 +1396,13 @@
         <v>20</v>
       </c>
       <c r="J32" t="n">
-        <v>-130.11</v>
+        <v>-124.34</v>
       </c>
       <c r="K32" t="n">
-        <v>19.6</v>
+        <v>18.73</v>
       </c>
       <c r="L32" t="n">
-        <v>131.58</v>
+        <v>125.74</v>
       </c>
     </row>
     <row r="33">
@@ -1438,13 +1438,13 @@
         <v>20</v>
       </c>
       <c r="J33" t="n">
-        <v>46.18</v>
+        <v>44.33</v>
       </c>
       <c r="K33" t="n">
-        <v>-124.7</v>
+        <v>-119.7</v>
       </c>
       <c r="L33" t="n">
-        <v>132.98</v>
+        <v>127.65</v>
       </c>
     </row>
     <row r="34">
@@ -1480,13 +1480,13 @@
         <v>19</v>
       </c>
       <c r="J34" t="n">
-        <v>-46.37</v>
+        <v>-49.9</v>
       </c>
       <c r="K34" t="n">
-        <v>-49.88</v>
+        <v>-53.68</v>
       </c>
       <c r="L34" t="n">
-        <v>68.09999999999999</v>
+        <v>73.29000000000001</v>
       </c>
     </row>
     <row r="35">
@@ -1522,13 +1522,13 @@
         <v>22</v>
       </c>
       <c r="J35" t="n">
-        <v>8.58</v>
+        <v>8.68</v>
       </c>
       <c r="K35" t="n">
-        <v>127.19</v>
+        <v>128.59</v>
       </c>
       <c r="L35" t="n">
-        <v>127.48</v>
+        <v>128.88</v>
       </c>
     </row>
     <row r="36">
@@ -1564,13 +1564,13 @@
         <v>22</v>
       </c>
       <c r="J36" t="n">
-        <v>66.29000000000001</v>
+        <v>67.64</v>
       </c>
       <c r="K36" t="n">
-        <v>-103.69</v>
+        <v>-105.8</v>
       </c>
       <c r="L36" t="n">
-        <v>123.07</v>
+        <v>125.57</v>
       </c>
     </row>
     <row r="37">
@@ -1606,13 +1606,13 @@
         <v>25</v>
       </c>
       <c r="J37" t="n">
-        <v>-72.52</v>
+        <v>-77.09</v>
       </c>
       <c r="K37" t="n">
-        <v>55.38</v>
+        <v>58.87</v>
       </c>
       <c r="L37" t="n">
-        <v>91.25</v>
+        <v>97</v>
       </c>
     </row>
     <row r="38">
@@ -1648,13 +1648,13 @@
         <v>20</v>
       </c>
       <c r="J38" t="n">
-        <v>138.34</v>
+        <v>144.27</v>
       </c>
       <c r="K38" t="n">
-        <v>62.99</v>
+        <v>65.69</v>
       </c>
       <c r="L38" t="n">
-        <v>152.01</v>
+        <v>158.53</v>
       </c>
     </row>
     <row r="39">
@@ -1690,13 +1690,13 @@
         <v>23</v>
       </c>
       <c r="J39" t="n">
-        <v>-0.73</v>
+        <v>-0.72</v>
       </c>
       <c r="K39" t="n">
-        <v>203.3</v>
+        <v>200.74</v>
       </c>
       <c r="L39" t="n">
-        <v>203.3</v>
+        <v>200.74</v>
       </c>
     </row>
     <row r="40">
@@ -1732,13 +1732,13 @@
         <v>23</v>
       </c>
       <c r="J40" t="n">
-        <v>52.33</v>
+        <v>51.55</v>
       </c>
       <c r="K40" t="n">
-        <v>-204.09</v>
+        <v>-201.03</v>
       </c>
       <c r="L40" t="n">
-        <v>210.69</v>
+        <v>207.54</v>
       </c>
     </row>
     <row r="41">
@@ -1774,13 +1774,13 @@
         <v>21</v>
       </c>
       <c r="J41" t="n">
-        <v>-188.71</v>
+        <v>-202.33</v>
       </c>
       <c r="K41" t="n">
-        <v>-28.9</v>
+        <v>-30.99</v>
       </c>
       <c r="L41" t="n">
-        <v>190.91</v>
+        <v>204.69</v>
       </c>
     </row>
     <row r="42">
@@ -1816,13 +1816,13 @@
         <v>21</v>
       </c>
       <c r="J42" t="n">
-        <v>-217.03</v>
+        <v>-229.12</v>
       </c>
       <c r="K42" t="n">
-        <v>58.1</v>
+        <v>61.33</v>
       </c>
       <c r="L42" t="n">
-        <v>224.67</v>
+        <v>237.19</v>
       </c>
     </row>
     <row r="43">
@@ -1858,13 +1858,13 @@
         <v>24</v>
       </c>
       <c r="J43" t="n">
-        <v>-223.39</v>
+        <v>-228.61</v>
       </c>
       <c r="K43" t="n">
-        <v>-33.08</v>
+        <v>-33.85</v>
       </c>
       <c r="L43" t="n">
-        <v>225.82</v>
+        <v>231.1</v>
       </c>
     </row>
     <row r="44">
@@ -1900,13 +1900,13 @@
         <v>25</v>
       </c>
       <c r="J44" t="n">
-        <v>-64.40000000000001</v>
+        <v>-63.87</v>
       </c>
       <c r="K44" t="n">
-        <v>-45.5</v>
+        <v>-45.12</v>
       </c>
       <c r="L44" t="n">
-        <v>78.84999999999999</v>
+        <v>78.2</v>
       </c>
     </row>
     <row r="45">
@@ -1942,13 +1942,13 @@
         <v>22</v>
       </c>
       <c r="J45" t="n">
-        <v>-28.44</v>
+        <v>-31.27</v>
       </c>
       <c r="K45" t="n">
-        <v>39.39</v>
+        <v>43.31</v>
       </c>
       <c r="L45" t="n">
-        <v>48.58</v>
+        <v>53.42</v>
       </c>
     </row>
     <row r="46">
@@ -1984,13 +1984,13 @@
         <v>25</v>
       </c>
       <c r="J46" t="n">
-        <v>36.01</v>
+        <v>38.57</v>
       </c>
       <c r="K46" t="n">
-        <v>36.02</v>
+        <v>38.57</v>
       </c>
       <c r="L46" t="n">
-        <v>50.94</v>
+        <v>54.54</v>
       </c>
     </row>
     <row r="47">
@@ -2026,13 +2026,13 @@
         <v>19</v>
       </c>
       <c r="J47" t="n">
-        <v>-110.79</v>
+        <v>-108.77</v>
       </c>
       <c r="K47" t="n">
-        <v>-1.78</v>
+        <v>-1.74</v>
       </c>
       <c r="L47" t="n">
-        <v>110.8</v>
+        <v>108.79</v>
       </c>
     </row>
     <row r="48">
@@ -2068,13 +2068,13 @@
         <v>25</v>
       </c>
       <c r="J48" t="n">
-        <v>-70.84</v>
+        <v>-73.28</v>
       </c>
       <c r="K48" t="n">
-        <v>21.06</v>
+        <v>21.79</v>
       </c>
       <c r="L48" t="n">
-        <v>73.90000000000001</v>
+        <v>76.45</v>
       </c>
     </row>
     <row r="49">
@@ -2110,13 +2110,13 @@
         <v>23</v>
       </c>
       <c r="J49" t="n">
-        <v>-12.29</v>
+        <v>-11.92</v>
       </c>
       <c r="K49" t="n">
-        <v>111.25</v>
+        <v>107.86</v>
       </c>
       <c r="L49" t="n">
-        <v>111.93</v>
+        <v>108.51</v>
       </c>
     </row>
     <row r="50">
@@ -2152,13 +2152,13 @@
         <v>25</v>
       </c>
       <c r="J50" t="n">
-        <v>-156.14</v>
+        <v>-148.86</v>
       </c>
       <c r="K50" t="n">
-        <v>-107.69</v>
+        <v>-102.67</v>
       </c>
       <c r="L50" t="n">
-        <v>189.68</v>
+        <v>180.83</v>
       </c>
     </row>
     <row r="51">
@@ -2194,13 +2194,13 @@
         <v>19</v>
       </c>
       <c r="J51" t="n">
-        <v>2.63</v>
+        <v>2.69</v>
       </c>
       <c r="K51" t="n">
-        <v>-128.01</v>
+        <v>-130.9</v>
       </c>
       <c r="L51" t="n">
-        <v>128.03</v>
+        <v>130.93</v>
       </c>
     </row>
     <row r="52">
@@ -2236,13 +2236,13 @@
         <v>22</v>
       </c>
       <c r="J52" t="n">
-        <v>-87.09</v>
+        <v>-88.09999999999999</v>
       </c>
       <c r="K52" t="n">
-        <v>115.08</v>
+        <v>116.42</v>
       </c>
       <c r="L52" t="n">
-        <v>144.31</v>
+        <v>146</v>
       </c>
     </row>
     <row r="53">
@@ -2278,13 +2278,13 @@
         <v>21</v>
       </c>
       <c r="J53" t="n">
-        <v>198.21</v>
+        <v>192.82</v>
       </c>
       <c r="K53" t="n">
-        <v>-126.2</v>
+        <v>-122.76</v>
       </c>
       <c r="L53" t="n">
-        <v>234.98</v>
+        <v>228.58</v>
       </c>
     </row>
     <row r="54">
@@ -2320,13 +2320,13 @@
         <v>23</v>
       </c>
       <c r="J54" t="n">
-        <v>-126.41</v>
+        <v>-128.53</v>
       </c>
       <c r="K54" t="n">
-        <v>112.58</v>
+        <v>114.47</v>
       </c>
       <c r="L54" t="n">
-        <v>169.27</v>
+        <v>172.11</v>
       </c>
     </row>
     <row r="55">
@@ -2362,13 +2362,13 @@
         <v>23</v>
       </c>
       <c r="J55" t="n">
-        <v>-51.81</v>
+        <v>-51.94</v>
       </c>
       <c r="K55" t="n">
-        <v>-175.19</v>
+        <v>-175.63</v>
       </c>
       <c r="L55" t="n">
-        <v>182.69</v>
+        <v>183.15</v>
       </c>
     </row>
     <row r="56">
@@ -2404,13 +2404,13 @@
         <v>22</v>
       </c>
       <c r="J56" t="n">
-        <v>-200.06</v>
+        <v>-208.22</v>
       </c>
       <c r="K56" t="n">
-        <v>65.56999999999999</v>
+        <v>68.25</v>
       </c>
       <c r="L56" t="n">
-        <v>210.53</v>
+        <v>219.12</v>
       </c>
     </row>
     <row r="57">
@@ -2446,13 +2446,13 @@
         <v>22</v>
       </c>
       <c r="J57" t="n">
-        <v>-12.33</v>
+        <v>-13.07</v>
       </c>
       <c r="K57" t="n">
-        <v>-264.68</v>
+        <v>-280.44</v>
       </c>
       <c r="L57" t="n">
-        <v>264.97</v>
+        <v>280.75</v>
       </c>
     </row>
     <row r="58">
@@ -2488,13 +2488,13 @@
         <v>19</v>
       </c>
       <c r="J58" t="n">
-        <v>-239.15</v>
+        <v>-235.99</v>
       </c>
       <c r="K58" t="n">
-        <v>-252.37</v>
+        <v>-249.04</v>
       </c>
       <c r="L58" t="n">
-        <v>347.68</v>
+        <v>343.09</v>
       </c>
     </row>
     <row r="59">
@@ -2530,13 +2530,13 @@
         <v>22</v>
       </c>
       <c r="J59" t="n">
-        <v>80.31999999999999</v>
+        <v>80.61</v>
       </c>
       <c r="K59" t="n">
-        <v>-2.79</v>
+        <v>-2.8</v>
       </c>
       <c r="L59" t="n">
-        <v>80.37</v>
+        <v>80.66</v>
       </c>
     </row>
     <row r="60">
@@ -2572,13 +2572,13 @@
         <v>20</v>
       </c>
       <c r="J60" t="n">
-        <v>76.3</v>
+        <v>73.88</v>
       </c>
       <c r="K60" t="n">
-        <v>68.12</v>
+        <v>65.95999999999999</v>
       </c>
       <c r="L60" t="n">
-        <v>102.28</v>
+        <v>99.04000000000001</v>
       </c>
     </row>
     <row r="61">
@@ -2614,13 +2614,13 @@
         <v>24</v>
       </c>
       <c r="J61" t="n">
-        <v>-42.73</v>
+        <v>-46.33</v>
       </c>
       <c r="K61" t="n">
-        <v>-26.06</v>
+        <v>-28.25</v>
       </c>
       <c r="L61" t="n">
-        <v>50.05</v>
+        <v>54.27</v>
       </c>
     </row>
     <row r="62">
@@ -2656,13 +2656,13 @@
         <v>22</v>
       </c>
       <c r="J62" t="n">
-        <v>-83.83</v>
+        <v>-83.16</v>
       </c>
       <c r="K62" t="n">
-        <v>-49.25</v>
+        <v>-48.85</v>
       </c>
       <c r="L62" t="n">
-        <v>97.23</v>
+        <v>96.45</v>
       </c>
     </row>
     <row r="63">
@@ -2698,13 +2698,13 @@
         <v>23</v>
       </c>
       <c r="J63" t="n">
-        <v>-70.53</v>
+        <v>-73.56999999999999</v>
       </c>
       <c r="K63" t="n">
-        <v>-23.51</v>
+        <v>-24.52</v>
       </c>
       <c r="L63" t="n">
-        <v>74.34999999999999</v>
+        <v>77.55</v>
       </c>
     </row>
     <row r="64">
@@ -2740,13 +2740,13 @@
         <v>19</v>
       </c>
       <c r="J64" t="n">
-        <v>-24.75</v>
+        <v>-24.87</v>
       </c>
       <c r="K64" t="n">
-        <v>-94.04000000000001</v>
+        <v>-94.48999999999999</v>
       </c>
       <c r="L64" t="n">
-        <v>97.23999999999999</v>
+        <v>97.70999999999999</v>
       </c>
     </row>
     <row r="65">
@@ -2782,13 +2782,13 @@
         <v>20</v>
       </c>
       <c r="J65" t="n">
-        <v>151.65</v>
+        <v>148.1</v>
       </c>
       <c r="K65" t="n">
-        <v>72.64</v>
+        <v>70.94</v>
       </c>
       <c r="L65" t="n">
-        <v>168.15</v>
+        <v>164.22</v>
       </c>
     </row>
     <row r="66">
@@ -2824,13 +2824,13 @@
         <v>19</v>
       </c>
       <c r="J66" t="n">
-        <v>-3.43</v>
+        <v>-3.65</v>
       </c>
       <c r="K66" t="n">
-        <v>-112.5</v>
+        <v>-119.68</v>
       </c>
       <c r="L66" t="n">
-        <v>112.55</v>
+        <v>119.74</v>
       </c>
     </row>
     <row r="67">
@@ -2866,13 +2866,13 @@
         <v>19</v>
       </c>
       <c r="J67" t="n">
-        <v>270.19</v>
+        <v>247.1</v>
       </c>
       <c r="K67" t="n">
-        <v>-196.1</v>
+        <v>-179.34</v>
       </c>
       <c r="L67" t="n">
-        <v>333.85</v>
+        <v>305.32</v>
       </c>
     </row>
     <row r="68">
@@ -2908,13 +2908,13 @@
         <v>22</v>
       </c>
       <c r="J68" t="n">
-        <v>32.34</v>
+        <v>33.9</v>
       </c>
       <c r="K68" t="n">
-        <v>144.01</v>
+        <v>150.98</v>
       </c>
       <c r="L68" t="n">
-        <v>147.6</v>
+        <v>154.74</v>
       </c>
     </row>
     <row r="69">
@@ -2950,13 +2950,13 @@
         <v>23</v>
       </c>
       <c r="J69" t="n">
-        <v>42.55</v>
+        <v>41.51</v>
       </c>
       <c r="K69" t="n">
-        <v>-243.06</v>
+        <v>-237.09</v>
       </c>
       <c r="L69" t="n">
-        <v>246.75</v>
+        <v>240.7</v>
       </c>
     </row>
     <row r="70">
@@ -2992,13 +2992,13 @@
         <v>23</v>
       </c>
       <c r="J70" t="n">
-        <v>34.2</v>
+        <v>34.62</v>
       </c>
       <c r="K70" t="n">
-        <v>-167.16</v>
+        <v>-169.22</v>
       </c>
       <c r="L70" t="n">
-        <v>170.62</v>
+        <v>172.73</v>
       </c>
     </row>
     <row r="71">
@@ -3034,13 +3034,13 @@
         <v>21</v>
       </c>
       <c r="J71" t="n">
-        <v>-93.48999999999999</v>
+        <v>-99.3</v>
       </c>
       <c r="K71" t="n">
-        <v>-179.38</v>
+        <v>-190.53</v>
       </c>
       <c r="L71" t="n">
-        <v>202.28</v>
+        <v>214.86</v>
       </c>
     </row>
     <row r="72">
@@ -3076,13 +3076,13 @@
         <v>23</v>
       </c>
       <c r="J72" t="n">
-        <v>155.74</v>
+        <v>152.24</v>
       </c>
       <c r="K72" t="n">
-        <v>319.03</v>
+        <v>311.88</v>
       </c>
       <c r="L72" t="n">
-        <v>355.01</v>
+        <v>347.05</v>
       </c>
     </row>
     <row r="73">
@@ -3118,13 +3118,13 @@
         <v>20</v>
       </c>
       <c r="J73" t="n">
-        <v>-193.24</v>
+        <v>-209.21</v>
       </c>
       <c r="K73" t="n">
-        <v>-11.67</v>
+        <v>-12.64</v>
       </c>
       <c r="L73" t="n">
-        <v>193.59</v>
+        <v>209.59</v>
       </c>
     </row>
     <row r="74">
@@ -3160,13 +3160,13 @@
         <v>21</v>
       </c>
       <c r="J74" t="n">
-        <v>51.05</v>
+        <v>55.19</v>
       </c>
       <c r="K74" t="n">
-        <v>-19.25</v>
+        <v>-20.81</v>
       </c>
       <c r="L74" t="n">
-        <v>54.56</v>
+        <v>58.99</v>
       </c>
     </row>
     <row r="75">
@@ -3202,13 +3202,13 @@
         <v>20</v>
       </c>
       <c r="J75" t="n">
-        <v>-33.47</v>
+        <v>-31.81</v>
       </c>
       <c r="K75" t="n">
-        <v>114.36</v>
+        <v>108.69</v>
       </c>
       <c r="L75" t="n">
-        <v>119.16</v>
+        <v>113.25</v>
       </c>
     </row>
     <row r="76">
@@ -3244,13 +3244,13 @@
         <v>22</v>
       </c>
       <c r="J76" t="n">
-        <v>-41.73</v>
+        <v>-40.15</v>
       </c>
       <c r="K76" t="n">
-        <v>95.90000000000001</v>
+        <v>92.26000000000001</v>
       </c>
       <c r="L76" t="n">
-        <v>104.59</v>
+        <v>100.62</v>
       </c>
     </row>
     <row r="77">
@@ -3286,13 +3286,13 @@
         <v>24</v>
       </c>
       <c r="J77" t="n">
-        <v>-123.34</v>
+        <v>-115.84</v>
       </c>
       <c r="K77" t="n">
-        <v>-74.89</v>
+        <v>-70.34</v>
       </c>
       <c r="L77" t="n">
-        <v>144.29</v>
+        <v>135.53</v>
       </c>
     </row>
     <row r="78">
@@ -3328,13 +3328,13 @@
         <v>24</v>
       </c>
       <c r="J78" t="n">
-        <v>53.42</v>
+        <v>50.95</v>
       </c>
       <c r="K78" t="n">
-        <v>-119.33</v>
+        <v>-113.8</v>
       </c>
       <c r="L78" t="n">
-        <v>130.75</v>
+        <v>124.69</v>
       </c>
     </row>
     <row r="79">
@@ -3370,13 +3370,13 @@
         <v>24</v>
       </c>
       <c r="J79" t="n">
-        <v>119.56</v>
+        <v>114.12</v>
       </c>
       <c r="K79" t="n">
-        <v>-51.85</v>
+        <v>-49.49</v>
       </c>
       <c r="L79" t="n">
-        <v>130.32</v>
+        <v>124.39</v>
       </c>
     </row>
     <row r="80">
@@ -3412,13 +3412,13 @@
         <v>25</v>
       </c>
       <c r="J80" t="n">
-        <v>78.59</v>
+        <v>84.06999999999999</v>
       </c>
       <c r="K80" t="n">
-        <v>47.97</v>
+        <v>51.32</v>
       </c>
       <c r="L80" t="n">
-        <v>92.06999999999999</v>
+        <v>98.5</v>
       </c>
     </row>
     <row r="81">
@@ -3454,13 +3454,13 @@
         <v>23</v>
       </c>
       <c r="J81" t="n">
-        <v>80.31999999999999</v>
+        <v>78.48</v>
       </c>
       <c r="K81" t="n">
-        <v>151.96</v>
+        <v>148.47</v>
       </c>
       <c r="L81" t="n">
-        <v>171.88</v>
+        <v>167.93</v>
       </c>
     </row>
     <row r="82">
@@ -3496,13 +3496,13 @@
         <v>20</v>
       </c>
       <c r="J82" t="n">
-        <v>19.42</v>
+        <v>19.89</v>
       </c>
       <c r="K82" t="n">
-        <v>128.79</v>
+        <v>131.95</v>
       </c>
       <c r="L82" t="n">
-        <v>130.25</v>
+        <v>133.44</v>
       </c>
     </row>
     <row r="83">
@@ -3538,13 +3538,13 @@
         <v>21</v>
       </c>
       <c r="J83" t="n">
-        <v>64.01000000000001</v>
+        <v>66.40000000000001</v>
       </c>
       <c r="K83" t="n">
-        <v>-148.78</v>
+        <v>-154.36</v>
       </c>
       <c r="L83" t="n">
-        <v>161.97</v>
+        <v>168.03</v>
       </c>
     </row>
     <row r="84">
@@ -3580,13 +3580,13 @@
         <v>19</v>
       </c>
       <c r="J84" t="n">
-        <v>157.57</v>
+        <v>166.27</v>
       </c>
       <c r="K84" t="n">
-        <v>57.64</v>
+        <v>60.83</v>
       </c>
       <c r="L84" t="n">
-        <v>167.78</v>
+        <v>177.04</v>
       </c>
     </row>
     <row r="85">
@@ -3622,13 +3622,13 @@
         <v>19</v>
       </c>
       <c r="J85" t="n">
-        <v>154.58</v>
+        <v>155.74</v>
       </c>
       <c r="K85" t="n">
-        <v>144.63</v>
+        <v>145.72</v>
       </c>
       <c r="L85" t="n">
-        <v>211.69</v>
+        <v>213.28</v>
       </c>
     </row>
     <row r="86">
@@ -3664,13 +3664,13 @@
         <v>20</v>
       </c>
       <c r="J86" t="n">
-        <v>256.48</v>
+        <v>264.29</v>
       </c>
       <c r="K86" t="n">
-        <v>-151.41</v>
+        <v>-156.02</v>
       </c>
       <c r="L86" t="n">
-        <v>297.84</v>
+        <v>306.91</v>
       </c>
     </row>
     <row r="87">
@@ -3706,13 +3706,13 @@
         <v>25</v>
       </c>
       <c r="J87" t="n">
-        <v>5.16</v>
+        <v>5.65</v>
       </c>
       <c r="K87" t="n">
-        <v>72.73999999999999</v>
+        <v>79.61</v>
       </c>
       <c r="L87" t="n">
-        <v>72.93000000000001</v>
+        <v>79.81</v>
       </c>
     </row>
     <row r="88">
@@ -3748,13 +3748,13 @@
         <v>25</v>
       </c>
       <c r="J88" t="n">
-        <v>-184</v>
+        <v>-192.95</v>
       </c>
       <c r="K88" t="n">
-        <v>-95.81999999999999</v>
+        <v>-100.48</v>
       </c>
       <c r="L88" t="n">
-        <v>207.46</v>
+        <v>217.54</v>
       </c>
     </row>
   </sheetData>

--- a/output/2024-10-08.xlsx
+++ b/output/2024-10-08.xlsx
@@ -625,34 +625,34 @@
         <v>1</v>
       </c>
       <c r="E14" t="n">
-        <v>3.64</v>
+        <v>3.44</v>
       </c>
       <c r="F14" t="n">
-        <v>9.31</v>
+        <v>8.720000000000001</v>
       </c>
       <c r="G14" t="n">
-        <v>29.4</v>
+        <v>59.9</v>
       </c>
       <c r="H14" t="n">
-        <v>100</v>
+        <v>98.59999999999999</v>
       </c>
       <c r="I14" t="n">
-        <v>23</v>
+        <v>16</v>
       </c>
       <c r="J14" t="n">
-        <v>55.55</v>
+        <v>-106.64</v>
       </c>
       <c r="K14" t="n">
-        <v>-29.86</v>
+        <v>25.79</v>
       </c>
       <c r="L14" t="n">
-        <v>63.07</v>
+        <v>109.71</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>07:33:19</t>
+          <t>07:32:58</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -667,34 +667,34 @@
         <v>2</v>
       </c>
       <c r="E15" t="n">
-        <v>4.11</v>
+        <v>2.98</v>
       </c>
       <c r="F15" t="n">
-        <v>9.07</v>
+        <v>7.7</v>
       </c>
       <c r="G15" t="n">
-        <v>29.9</v>
+        <v>34.8</v>
       </c>
       <c r="H15" t="n">
         <v>100</v>
       </c>
       <c r="I15" t="n">
-        <v>23</v>
+        <v>16</v>
       </c>
       <c r="J15" t="n">
-        <v>-38.89</v>
+        <v>-82.39</v>
       </c>
       <c r="K15" t="n">
-        <v>52.96</v>
+        <v>66.64</v>
       </c>
       <c r="L15" t="n">
-        <v>65.70999999999999</v>
+        <v>105.97</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>07:35:17</t>
+          <t>07:34:07</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -709,34 +709,34 @@
         <v>3</v>
       </c>
       <c r="E16" t="n">
-        <v>3.18</v>
+        <v>3.38</v>
       </c>
       <c r="F16" t="n">
-        <v>9.210000000000001</v>
+        <v>6.49</v>
       </c>
       <c r="G16" t="n">
-        <v>54.6</v>
+        <v>36.4</v>
       </c>
       <c r="H16" t="n">
-        <v>93.2</v>
+        <v>100</v>
       </c>
       <c r="I16" t="n">
-        <v>20</v>
+        <v>16</v>
       </c>
       <c r="J16" t="n">
-        <v>-39.32</v>
+        <v>4.6</v>
       </c>
       <c r="K16" t="n">
-        <v>92.8</v>
+        <v>84.7</v>
       </c>
       <c r="L16" t="n">
-        <v>100.79</v>
+        <v>84.83</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>07:38:44</t>
+          <t>07:38:38</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -751,34 +751,34 @@
         <v>1</v>
       </c>
       <c r="E17" t="n">
-        <v>3.26</v>
+        <v>3.78</v>
       </c>
       <c r="F17" t="n">
-        <v>9.869999999999999</v>
+        <v>9.85</v>
       </c>
       <c r="G17" t="n">
-        <v>50.4</v>
+        <v>44.8</v>
       </c>
       <c r="H17" t="n">
         <v>100</v>
       </c>
       <c r="I17" t="n">
-        <v>25</v>
+        <v>18</v>
       </c>
       <c r="J17" t="n">
-        <v>-57.21</v>
+        <v>62.53</v>
       </c>
       <c r="K17" t="n">
-        <v>57.41</v>
+        <v>2.72</v>
       </c>
       <c r="L17" t="n">
-        <v>81.05</v>
+        <v>62.59</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>07:40:27</t>
+          <t>07:39:50</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -793,34 +793,34 @@
         <v>2</v>
       </c>
       <c r="E18" t="n">
-        <v>3.58</v>
+        <v>3.98</v>
       </c>
       <c r="F18" t="n">
-        <v>9.970000000000001</v>
+        <v>8.32</v>
       </c>
       <c r="G18" t="n">
-        <v>43.6</v>
+        <v>59.3</v>
       </c>
       <c r="H18" t="n">
-        <v>100</v>
+        <v>97.2</v>
       </c>
       <c r="I18" t="n">
-        <v>23</v>
+        <v>16</v>
       </c>
       <c r="J18" t="n">
-        <v>-48.79</v>
+        <v>96.01000000000001</v>
       </c>
       <c r="K18" t="n">
-        <v>-61.23</v>
+        <v>-68.09999999999999</v>
       </c>
       <c r="L18" t="n">
-        <v>78.29000000000001</v>
+        <v>117.71</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>07:42:21</t>
+          <t>07:41:07</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -835,34 +835,34 @@
         <v>3</v>
       </c>
       <c r="E19" t="n">
-        <v>4.14</v>
+        <v>3.71</v>
       </c>
       <c r="F19" t="n">
-        <v>9.51</v>
+        <v>10.33</v>
       </c>
       <c r="G19" t="n">
-        <v>48.2</v>
+        <v>39.8</v>
       </c>
       <c r="H19" t="n">
-        <v>95.90000000000001</v>
+        <v>100</v>
       </c>
       <c r="I19" t="n">
-        <v>19</v>
+        <v>16</v>
       </c>
       <c r="J19" t="n">
-        <v>96.31999999999999</v>
+        <v>-36.14</v>
       </c>
       <c r="K19" t="n">
-        <v>9.91</v>
+        <v>-137.42</v>
       </c>
       <c r="L19" t="n">
-        <v>96.83</v>
+        <v>142.09</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>07:45:40</t>
+          <t>07:47:01</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -877,34 +877,34 @@
         <v>1</v>
       </c>
       <c r="E20" t="n">
-        <v>3.42</v>
+        <v>3.03</v>
       </c>
       <c r="F20" t="n">
-        <v>8.66</v>
+        <v>7.87</v>
       </c>
       <c r="G20" t="n">
-        <v>26</v>
+        <v>27.8</v>
       </c>
       <c r="H20" t="n">
-        <v>97.5</v>
+        <v>100</v>
       </c>
       <c r="I20" t="n">
-        <v>22</v>
+        <v>18</v>
       </c>
       <c r="J20" t="n">
-        <v>46.91</v>
+        <v>15.86</v>
       </c>
       <c r="K20" t="n">
-        <v>169.81</v>
+        <v>154.13</v>
       </c>
       <c r="L20" t="n">
-        <v>176.17</v>
+        <v>154.94</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>07:48:17</t>
+          <t>07:48:01</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -919,34 +919,34 @@
         <v>2</v>
       </c>
       <c r="E21" t="n">
-        <v>2.98</v>
+        <v>3.36</v>
       </c>
       <c r="F21" t="n">
-        <v>9.640000000000001</v>
+        <v>7.41</v>
       </c>
       <c r="G21" t="n">
-        <v>37.8</v>
+        <v>46.9</v>
       </c>
       <c r="H21" t="n">
         <v>100</v>
       </c>
       <c r="I21" t="n">
-        <v>25</v>
+        <v>16</v>
       </c>
       <c r="J21" t="n">
-        <v>168.09</v>
+        <v>-31.99</v>
       </c>
       <c r="K21" t="n">
-        <v>12.83</v>
+        <v>132.35</v>
       </c>
       <c r="L21" t="n">
-        <v>168.58</v>
+        <v>136.16</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>07:50:23</t>
+          <t>07:49:33</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -961,34 +961,34 @@
         <v>3</v>
       </c>
       <c r="E22" t="n">
-        <v>3.72</v>
+        <v>3.26</v>
       </c>
       <c r="F22" t="n">
-        <v>8.94</v>
+        <v>7.34</v>
       </c>
       <c r="G22" t="n">
-        <v>51.7</v>
+        <v>39.5</v>
       </c>
       <c r="H22" t="n">
-        <v>98.3</v>
+        <v>100</v>
       </c>
       <c r="I22" t="n">
-        <v>19</v>
+        <v>16</v>
       </c>
       <c r="J22" t="n">
-        <v>-11.11</v>
+        <v>-104.02</v>
       </c>
       <c r="K22" t="n">
-        <v>123.69</v>
+        <v>115.86</v>
       </c>
       <c r="L22" t="n">
-        <v>124.19</v>
+        <v>155.71</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>07:54:57</t>
+          <t>07:53:52</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -1003,34 +1003,34 @@
         <v>1</v>
       </c>
       <c r="E23" t="n">
-        <v>3.46</v>
+        <v>3.82</v>
       </c>
       <c r="F23" t="n">
-        <v>9.41</v>
+        <v>9.140000000000001</v>
       </c>
       <c r="G23" t="n">
-        <v>49.3</v>
+        <v>43.1</v>
       </c>
       <c r="H23" t="n">
-        <v>100</v>
+        <v>94.59999999999999</v>
       </c>
       <c r="I23" t="n">
-        <v>22</v>
+        <v>16</v>
       </c>
       <c r="J23" t="n">
-        <v>-152.28</v>
+        <v>181.44</v>
       </c>
       <c r="K23" t="n">
-        <v>-148.62</v>
+        <v>-15.65</v>
       </c>
       <c r="L23" t="n">
-        <v>212.79</v>
+        <v>182.11</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>07:57:08</t>
+          <t>07:54:58</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -1045,34 +1045,34 @@
         <v>2</v>
       </c>
       <c r="E24" t="n">
-        <v>3.61</v>
+        <v>3.86</v>
       </c>
       <c r="F24" t="n">
-        <v>9.699999999999999</v>
+        <v>8.859999999999999</v>
       </c>
       <c r="G24" t="n">
-        <v>41.2</v>
+        <v>42.4</v>
       </c>
       <c r="H24" t="n">
         <v>100</v>
       </c>
       <c r="I24" t="n">
-        <v>25</v>
+        <v>17</v>
       </c>
       <c r="J24" t="n">
-        <v>-0.26</v>
+        <v>54.08</v>
       </c>
       <c r="K24" t="n">
-        <v>122.6</v>
+        <v>246.03</v>
       </c>
       <c r="L24" t="n">
-        <v>122.6</v>
+        <v>251.9</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>07:58:23</t>
+          <t>07:56:55</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -1087,34 +1087,34 @@
         <v>3</v>
       </c>
       <c r="E25" t="n">
-        <v>3.59</v>
+        <v>3.92</v>
       </c>
       <c r="F25" t="n">
-        <v>9.73</v>
+        <v>8.49</v>
       </c>
       <c r="G25" t="n">
-        <v>51.4</v>
+        <v>54</v>
       </c>
       <c r="H25" t="n">
         <v>100</v>
       </c>
       <c r="I25" t="n">
-        <v>23</v>
+        <v>16</v>
       </c>
       <c r="J25" t="n">
-        <v>-135.84</v>
+        <v>-210.34</v>
       </c>
       <c r="K25" t="n">
-        <v>80.73</v>
+        <v>264.93</v>
       </c>
       <c r="L25" t="n">
-        <v>158.02</v>
+        <v>338.28</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>08:02:21</t>
+          <t>08:00:45</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
@@ -1129,34 +1129,34 @@
         <v>1</v>
       </c>
       <c r="E26" t="n">
-        <v>4.05</v>
+        <v>3.79</v>
       </c>
       <c r="F26" t="n">
-        <v>9.57</v>
+        <v>6.34</v>
       </c>
       <c r="G26" t="n">
-        <v>63.7</v>
+        <v>50.7</v>
       </c>
       <c r="H26" t="n">
-        <v>90.2</v>
+        <v>99.09999999999999</v>
       </c>
       <c r="I26" t="n">
-        <v>23</v>
+        <v>16</v>
       </c>
       <c r="J26" t="n">
-        <v>-295.65</v>
+        <v>-381.87</v>
       </c>
       <c r="K26" t="n">
-        <v>-28.13</v>
+        <v>87.2</v>
       </c>
       <c r="L26" t="n">
-        <v>296.98</v>
+        <v>391.7</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>08:04:36</t>
+          <t>08:01:32</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
@@ -1171,34 +1171,34 @@
         <v>2</v>
       </c>
       <c r="E27" t="n">
-        <v>3.93</v>
+        <v>3.65</v>
       </c>
       <c r="F27" t="n">
-        <v>9.98</v>
+        <v>8.32</v>
       </c>
       <c r="G27" t="n">
-        <v>43.7</v>
+        <v>52.4</v>
       </c>
       <c r="H27" t="n">
         <v>100</v>
       </c>
       <c r="I27" t="n">
-        <v>20</v>
+        <v>16</v>
       </c>
       <c r="J27" t="n">
-        <v>13.54</v>
+        <v>282.13</v>
       </c>
       <c r="K27" t="n">
-        <v>241.6</v>
+        <v>-62.11</v>
       </c>
       <c r="L27" t="n">
-        <v>241.98</v>
+        <v>288.89</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>08:06:39</t>
+          <t>08:03:09</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
@@ -1213,34 +1213,34 @@
         <v>3</v>
       </c>
       <c r="E28" t="n">
-        <v>4</v>
+        <v>3.68</v>
       </c>
       <c r="F28" t="n">
-        <v>9.41</v>
+        <v>9.869999999999999</v>
       </c>
       <c r="G28" t="n">
-        <v>39.9</v>
+        <v>35.5</v>
       </c>
       <c r="H28" t="n">
         <v>100</v>
       </c>
       <c r="I28" t="n">
-        <v>21</v>
+        <v>16</v>
       </c>
       <c r="J28" t="n">
-        <v>237.27</v>
+        <v>10.32</v>
       </c>
       <c r="K28" t="n">
-        <v>114.64</v>
+        <v>302.03</v>
       </c>
       <c r="L28" t="n">
-        <v>263.51</v>
+        <v>302.2</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>08:15:29</t>
+          <t>08:11:19</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
@@ -1255,34 +1255,34 @@
         <v>1</v>
       </c>
       <c r="E29" t="n">
-        <v>3.41</v>
+        <v>3.85</v>
       </c>
       <c r="F29" t="n">
-        <v>9.5</v>
+        <v>9.1</v>
       </c>
       <c r="G29" t="n">
-        <v>47.7</v>
+        <v>50.3</v>
       </c>
       <c r="H29" t="n">
-        <v>100</v>
+        <v>96</v>
       </c>
       <c r="I29" t="n">
-        <v>24</v>
+        <v>16</v>
       </c>
       <c r="J29" t="n">
-        <v>24.87</v>
+        <v>-39.99</v>
       </c>
       <c r="K29" t="n">
-        <v>-74.14</v>
+        <v>59.09</v>
       </c>
       <c r="L29" t="n">
-        <v>78.2</v>
+        <v>71.34999999999999</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>08:16:28</t>
+          <t>08:13:10</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
@@ -1297,34 +1297,34 @@
         <v>2</v>
       </c>
       <c r="E30" t="n">
-        <v>3.98</v>
+        <v>3.21</v>
       </c>
       <c r="F30" t="n">
-        <v>8.710000000000001</v>
+        <v>7.41</v>
       </c>
       <c r="G30" t="n">
-        <v>47.6</v>
+        <v>42.5</v>
       </c>
       <c r="H30" t="n">
-        <v>98.59999999999999</v>
+        <v>100</v>
       </c>
       <c r="I30" t="n">
-        <v>20</v>
+        <v>16</v>
       </c>
       <c r="J30" t="n">
-        <v>-7.32</v>
+        <v>-17.9</v>
       </c>
       <c r="K30" t="n">
-        <v>84.02</v>
+        <v>-111.16</v>
       </c>
       <c r="L30" t="n">
-        <v>84.34</v>
+        <v>112.59</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>08:18:12</t>
+          <t>08:15:27</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
@@ -1339,34 +1339,34 @@
         <v>3</v>
       </c>
       <c r="E31" t="n">
-        <v>3.69</v>
+        <v>3.67</v>
       </c>
       <c r="F31" t="n">
-        <v>9.48</v>
+        <v>8.93</v>
       </c>
       <c r="G31" t="n">
-        <v>42.3</v>
+        <v>41.5</v>
       </c>
       <c r="H31" t="n">
-        <v>90.90000000000001</v>
+        <v>98</v>
       </c>
       <c r="I31" t="n">
-        <v>24</v>
+        <v>16</v>
       </c>
       <c r="J31" t="n">
-        <v>20.19</v>
+        <v>-108.38</v>
       </c>
       <c r="K31" t="n">
-        <v>-53.27</v>
+        <v>-3.92</v>
       </c>
       <c r="L31" t="n">
-        <v>56.97</v>
+        <v>108.45</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>08:22:38</t>
+          <t>08:18:23</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
@@ -1381,34 +1381,34 @@
         <v>1</v>
       </c>
       <c r="E32" t="n">
-        <v>3.68</v>
+        <v>3.53</v>
       </c>
       <c r="F32" t="n">
-        <v>9.1</v>
+        <v>5.22</v>
       </c>
       <c r="G32" t="n">
-        <v>43.2</v>
+        <v>61.1</v>
       </c>
       <c r="H32" t="n">
-        <v>92</v>
+        <v>100</v>
       </c>
       <c r="I32" t="n">
-        <v>20</v>
+        <v>16</v>
       </c>
       <c r="J32" t="n">
-        <v>-124.34</v>
+        <v>11.56</v>
       </c>
       <c r="K32" t="n">
-        <v>18.73</v>
+        <v>72.77</v>
       </c>
       <c r="L32" t="n">
-        <v>125.74</v>
+        <v>73.68000000000001</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>08:24:47</t>
+          <t>08:19:54</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
@@ -1423,34 +1423,34 @@
         <v>2</v>
       </c>
       <c r="E33" t="n">
-        <v>4.42</v>
+        <v>3.91</v>
       </c>
       <c r="F33" t="n">
-        <v>9.24</v>
+        <v>7.85</v>
       </c>
       <c r="G33" t="n">
-        <v>48.1</v>
+        <v>50.8</v>
       </c>
       <c r="H33" t="n">
-        <v>100</v>
+        <v>92.40000000000001</v>
       </c>
       <c r="I33" t="n">
-        <v>20</v>
+        <v>16</v>
       </c>
       <c r="J33" t="n">
-        <v>44.33</v>
+        <v>13.17</v>
       </c>
       <c r="K33" t="n">
-        <v>-119.7</v>
+        <v>-77.52</v>
       </c>
       <c r="L33" t="n">
-        <v>127.65</v>
+        <v>78.63</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>08:25:45</t>
+          <t>08:21:57</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
@@ -1465,34 +1465,34 @@
         <v>3</v>
       </c>
       <c r="E34" t="n">
-        <v>4.04</v>
+        <v>4.2</v>
       </c>
       <c r="F34" t="n">
-        <v>9.970000000000001</v>
+        <v>9.56</v>
       </c>
       <c r="G34" t="n">
-        <v>39.9</v>
+        <v>42.9</v>
       </c>
       <c r="H34" t="n">
-        <v>100</v>
+        <v>98.59999999999999</v>
       </c>
       <c r="I34" t="n">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="J34" t="n">
-        <v>-49.9</v>
+        <v>-87.88</v>
       </c>
       <c r="K34" t="n">
-        <v>-53.68</v>
+        <v>81.81999999999999</v>
       </c>
       <c r="L34" t="n">
-        <v>73.29000000000001</v>
+        <v>120.07</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>08:30:54</t>
+          <t>08:26:47</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
@@ -1507,34 +1507,34 @@
         <v>1</v>
       </c>
       <c r="E35" t="n">
-        <v>3.77</v>
+        <v>3.97</v>
       </c>
       <c r="F35" t="n">
-        <v>10.02</v>
+        <v>10.44</v>
       </c>
       <c r="G35" t="n">
-        <v>48.6</v>
+        <v>45.9</v>
       </c>
       <c r="H35" t="n">
         <v>100</v>
       </c>
       <c r="I35" t="n">
-        <v>22</v>
+        <v>17</v>
       </c>
       <c r="J35" t="n">
-        <v>8.68</v>
+        <v>174.55</v>
       </c>
       <c r="K35" t="n">
-        <v>128.59</v>
+        <v>28.58</v>
       </c>
       <c r="L35" t="n">
-        <v>128.88</v>
+        <v>176.87</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>08:32:23</t>
+          <t>08:27:47</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
@@ -1549,34 +1549,34 @@
         <v>2</v>
       </c>
       <c r="E36" t="n">
-        <v>3.89</v>
+        <v>3.67</v>
       </c>
       <c r="F36" t="n">
-        <v>9.23</v>
+        <v>9.470000000000001</v>
       </c>
       <c r="G36" t="n">
-        <v>44.8</v>
+        <v>41.3</v>
       </c>
       <c r="H36" t="n">
-        <v>100</v>
+        <v>96.5</v>
       </c>
       <c r="I36" t="n">
-        <v>22</v>
+        <v>18</v>
       </c>
       <c r="J36" t="n">
-        <v>67.64</v>
+        <v>98.65000000000001</v>
       </c>
       <c r="K36" t="n">
-        <v>-105.8</v>
+        <v>-87.41</v>
       </c>
       <c r="L36" t="n">
-        <v>125.57</v>
+        <v>131.81</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>08:34:30</t>
+          <t>08:30:21</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
@@ -1591,34 +1591,34 @@
         <v>3</v>
       </c>
       <c r="E37" t="n">
-        <v>3.73</v>
+        <v>3.43</v>
       </c>
       <c r="F37" t="n">
-        <v>8.960000000000001</v>
+        <v>7.42</v>
       </c>
       <c r="G37" t="n">
-        <v>33.8</v>
+        <v>42.8</v>
       </c>
       <c r="H37" t="n">
-        <v>97</v>
+        <v>100</v>
       </c>
       <c r="I37" t="n">
-        <v>25</v>
+        <v>16</v>
       </c>
       <c r="J37" t="n">
-        <v>-77.09</v>
+        <v>74.79000000000001</v>
       </c>
       <c r="K37" t="n">
-        <v>58.87</v>
+        <v>112.73</v>
       </c>
       <c r="L37" t="n">
-        <v>97</v>
+        <v>135.29</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>08:38:04</t>
+          <t>08:35:24</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
@@ -1633,34 +1633,34 @@
         <v>1</v>
       </c>
       <c r="E38" t="n">
-        <v>3.8</v>
+        <v>3.27</v>
       </c>
       <c r="F38" t="n">
-        <v>8.640000000000001</v>
+        <v>8.710000000000001</v>
       </c>
       <c r="G38" t="n">
-        <v>50</v>
+        <v>51.9</v>
       </c>
       <c r="H38" t="n">
         <v>100</v>
       </c>
       <c r="I38" t="n">
-        <v>20</v>
+        <v>17</v>
       </c>
       <c r="J38" t="n">
-        <v>144.27</v>
+        <v>-96.92</v>
       </c>
       <c r="K38" t="n">
-        <v>65.69</v>
+        <v>-40.3</v>
       </c>
       <c r="L38" t="n">
-        <v>158.53</v>
+        <v>104.96</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>08:39:59</t>
+          <t>08:37:13</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
@@ -1675,34 +1675,34 @@
         <v>2</v>
       </c>
       <c r="E39" t="n">
-        <v>4.16</v>
+        <v>3.9</v>
       </c>
       <c r="F39" t="n">
-        <v>9.41</v>
+        <v>10.12</v>
       </c>
       <c r="G39" t="n">
-        <v>45.4</v>
+        <v>57.6</v>
       </c>
       <c r="H39" t="n">
-        <v>98.8</v>
+        <v>100</v>
       </c>
       <c r="I39" t="n">
-        <v>23</v>
+        <v>16</v>
       </c>
       <c r="J39" t="n">
-        <v>-0.72</v>
+        <v>71.98999999999999</v>
       </c>
       <c r="K39" t="n">
-        <v>200.74</v>
+        <v>190.35</v>
       </c>
       <c r="L39" t="n">
-        <v>200.74</v>
+        <v>203.5</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>08:41:47</t>
+          <t>08:39:25</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
@@ -1717,34 +1717,34 @@
         <v>3</v>
       </c>
       <c r="E40" t="n">
-        <v>4.38</v>
+        <v>4.03</v>
       </c>
       <c r="F40" t="n">
-        <v>9.630000000000001</v>
+        <v>10.14</v>
       </c>
       <c r="G40" t="n">
-        <v>50.5</v>
+        <v>43.9</v>
       </c>
       <c r="H40" t="n">
-        <v>100</v>
+        <v>93.7</v>
       </c>
       <c r="I40" t="n">
-        <v>23</v>
+        <v>16</v>
       </c>
       <c r="J40" t="n">
-        <v>51.55</v>
+        <v>141.87</v>
       </c>
       <c r="K40" t="n">
-        <v>-201.03</v>
+        <v>-149.53</v>
       </c>
       <c r="L40" t="n">
-        <v>207.54</v>
+        <v>206.12</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>08:47:17</t>
+          <t>08:44:21</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
@@ -1759,34 +1759,34 @@
         <v>1</v>
       </c>
       <c r="E41" t="n">
-        <v>3.89</v>
+        <v>3.93</v>
       </c>
       <c r="F41" t="n">
-        <v>9.529999999999999</v>
+        <v>9.68</v>
       </c>
       <c r="G41" t="n">
-        <v>45.4</v>
+        <v>53.5</v>
       </c>
       <c r="H41" t="n">
-        <v>95.5</v>
+        <v>99.2</v>
       </c>
       <c r="I41" t="n">
-        <v>21</v>
+        <v>16</v>
       </c>
       <c r="J41" t="n">
-        <v>-202.33</v>
+        <v>173.62</v>
       </c>
       <c r="K41" t="n">
-        <v>-30.99</v>
+        <v>-161.41</v>
       </c>
       <c r="L41" t="n">
-        <v>204.69</v>
+        <v>237.06</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>08:48:34</t>
+          <t>08:45:35</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
@@ -1801,34 +1801,34 @@
         <v>2</v>
       </c>
       <c r="E42" t="n">
-        <v>4.26</v>
+        <v>4.19</v>
       </c>
       <c r="F42" t="n">
-        <v>9.81</v>
+        <v>9.1</v>
       </c>
       <c r="G42" t="n">
-        <v>39.6</v>
+        <v>42.2</v>
       </c>
       <c r="H42" t="n">
         <v>100</v>
       </c>
       <c r="I42" t="n">
-        <v>21</v>
+        <v>16</v>
       </c>
       <c r="J42" t="n">
-        <v>-229.12</v>
+        <v>61.33</v>
       </c>
       <c r="K42" t="n">
-        <v>61.33</v>
+        <v>-297.47</v>
       </c>
       <c r="L42" t="n">
-        <v>237.19</v>
+        <v>303.72</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>08:51:10</t>
+          <t>08:46:41</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
@@ -1843,34 +1843,34 @@
         <v>3</v>
       </c>
       <c r="E43" t="n">
-        <v>3.84</v>
+        <v>4.04</v>
       </c>
       <c r="F43" t="n">
-        <v>10.11</v>
+        <v>10.81</v>
       </c>
       <c r="G43" t="n">
-        <v>48.1</v>
+        <v>43.9</v>
       </c>
       <c r="H43" t="n">
-        <v>94.5</v>
+        <v>98.90000000000001</v>
       </c>
       <c r="I43" t="n">
-        <v>24</v>
+        <v>17</v>
       </c>
       <c r="J43" t="n">
-        <v>-228.61</v>
+        <v>259.92</v>
       </c>
       <c r="K43" t="n">
-        <v>-33.85</v>
+        <v>-22.06</v>
       </c>
       <c r="L43" t="n">
-        <v>231.1</v>
+        <v>260.86</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>08:58:16</t>
+          <t>08:55:03</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
@@ -1885,34 +1885,34 @@
         <v>1</v>
       </c>
       <c r="E44" t="n">
-        <v>3.94</v>
+        <v>3.66</v>
       </c>
       <c r="F44" t="n">
-        <v>9.029999999999999</v>
+        <v>7.35</v>
       </c>
       <c r="G44" t="n">
-        <v>41.3</v>
+        <v>35.1</v>
       </c>
       <c r="H44" t="n">
-        <v>100</v>
+        <v>96.8</v>
       </c>
       <c r="I44" t="n">
-        <v>25</v>
+        <v>16</v>
       </c>
       <c r="J44" t="n">
-        <v>-63.87</v>
+        <v>10.79</v>
       </c>
       <c r="K44" t="n">
-        <v>-45.12</v>
+        <v>74.51000000000001</v>
       </c>
       <c r="L44" t="n">
-        <v>78.2</v>
+        <v>75.29000000000001</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>08:59:56</t>
+          <t>08:56:30</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
@@ -1927,34 +1927,34 @@
         <v>2</v>
       </c>
       <c r="E45" t="n">
-        <v>3.61</v>
+        <v>3.7</v>
       </c>
       <c r="F45" t="n">
-        <v>8.9</v>
+        <v>8.449999999999999</v>
       </c>
       <c r="G45" t="n">
-        <v>37.8</v>
+        <v>30.6</v>
       </c>
       <c r="H45" t="n">
         <v>100</v>
       </c>
       <c r="I45" t="n">
-        <v>22</v>
+        <v>18</v>
       </c>
       <c r="J45" t="n">
-        <v>-31.27</v>
+        <v>-64.15000000000001</v>
       </c>
       <c r="K45" t="n">
-        <v>43.31</v>
+        <v>-44.72</v>
       </c>
       <c r="L45" t="n">
-        <v>53.42</v>
+        <v>78.2</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>09:01:11</t>
+          <t>08:57:58</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
@@ -1969,34 +1969,34 @@
         <v>3</v>
       </c>
       <c r="E46" t="n">
-        <v>3.45</v>
+        <v>4.3</v>
       </c>
       <c r="F46" t="n">
-        <v>9.869999999999999</v>
+        <v>10.81</v>
       </c>
       <c r="G46" t="n">
-        <v>38.9</v>
+        <v>37.5</v>
       </c>
       <c r="H46" t="n">
-        <v>96.40000000000001</v>
+        <v>100</v>
       </c>
       <c r="I46" t="n">
-        <v>25</v>
+        <v>17</v>
       </c>
       <c r="J46" t="n">
-        <v>38.57</v>
+        <v>62.39</v>
       </c>
       <c r="K46" t="n">
-        <v>38.57</v>
+        <v>99.78</v>
       </c>
       <c r="L46" t="n">
-        <v>54.54</v>
+        <v>117.68</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>09:05:12</t>
+          <t>09:03:05</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
@@ -2011,34 +2011,34 @@
         <v>1</v>
       </c>
       <c r="E47" t="n">
-        <v>3.73</v>
+        <v>4.29</v>
       </c>
       <c r="F47" t="n">
-        <v>10.15</v>
+        <v>9.59</v>
       </c>
       <c r="G47" t="n">
-        <v>52.6</v>
+        <v>50.5</v>
       </c>
       <c r="H47" t="n">
-        <v>100</v>
+        <v>99.8</v>
       </c>
       <c r="I47" t="n">
-        <v>19</v>
+        <v>16</v>
       </c>
       <c r="J47" t="n">
-        <v>-108.77</v>
+        <v>-75.56999999999999</v>
       </c>
       <c r="K47" t="n">
-        <v>-1.74</v>
+        <v>-66.93000000000001</v>
       </c>
       <c r="L47" t="n">
-        <v>108.79</v>
+        <v>100.95</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>09:07:51</t>
+          <t>09:05:01</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
@@ -2053,34 +2053,34 @@
         <v>2</v>
       </c>
       <c r="E48" t="n">
-        <v>4.23</v>
+        <v>4.08</v>
       </c>
       <c r="F48" t="n">
-        <v>9.539999999999999</v>
+        <v>8.960000000000001</v>
       </c>
       <c r="G48" t="n">
-        <v>37.6</v>
+        <v>34.9</v>
       </c>
       <c r="H48" t="n">
-        <v>96.3</v>
+        <v>100</v>
       </c>
       <c r="I48" t="n">
-        <v>25</v>
+        <v>16</v>
       </c>
       <c r="J48" t="n">
-        <v>-73.28</v>
+        <v>-101.47</v>
       </c>
       <c r="K48" t="n">
-        <v>21.79</v>
+        <v>-5.6</v>
       </c>
       <c r="L48" t="n">
-        <v>76.45</v>
+        <v>101.63</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>09:09:08</t>
+          <t>09:07:36</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
@@ -2095,34 +2095,34 @@
         <v>3</v>
       </c>
       <c r="E49" t="n">
-        <v>3.65</v>
+        <v>3.75</v>
       </c>
       <c r="F49" t="n">
-        <v>9.68</v>
+        <v>9.26</v>
       </c>
       <c r="G49" t="n">
-        <v>37.7</v>
+        <v>47.2</v>
       </c>
       <c r="H49" t="n">
-        <v>99.40000000000001</v>
+        <v>100</v>
       </c>
       <c r="I49" t="n">
-        <v>23</v>
+        <v>16</v>
       </c>
       <c r="J49" t="n">
-        <v>-11.92</v>
+        <v>-42.9</v>
       </c>
       <c r="K49" t="n">
-        <v>107.86</v>
+        <v>-93.09999999999999</v>
       </c>
       <c r="L49" t="n">
-        <v>108.51</v>
+        <v>102.51</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>09:13:34</t>
+          <t>09:12:19</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
@@ -2137,34 +2137,34 @@
         <v>1</v>
       </c>
       <c r="E50" t="n">
-        <v>4.13</v>
+        <v>3.99</v>
       </c>
       <c r="F50" t="n">
-        <v>9.369999999999999</v>
+        <v>7.13</v>
       </c>
       <c r="G50" t="n">
-        <v>34.7</v>
+        <v>40</v>
       </c>
       <c r="H50" t="n">
-        <v>97.7</v>
+        <v>94.5</v>
       </c>
       <c r="I50" t="n">
-        <v>25</v>
+        <v>16</v>
       </c>
       <c r="J50" t="n">
-        <v>-148.86</v>
+        <v>52.03</v>
       </c>
       <c r="K50" t="n">
-        <v>-102.67</v>
+        <v>95.79000000000001</v>
       </c>
       <c r="L50" t="n">
-        <v>180.83</v>
+        <v>109.01</v>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>09:15:03</t>
+          <t>09:14:42</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
@@ -2179,34 +2179,34 @@
         <v>2</v>
       </c>
       <c r="E51" t="n">
-        <v>3.87</v>
+        <v>3.98</v>
       </c>
       <c r="F51" t="n">
-        <v>9.619999999999999</v>
+        <v>9.06</v>
       </c>
       <c r="G51" t="n">
-        <v>43.1</v>
+        <v>46.4</v>
       </c>
       <c r="H51" t="n">
-        <v>100</v>
+        <v>96</v>
       </c>
       <c r="I51" t="n">
-        <v>19</v>
+        <v>16</v>
       </c>
       <c r="J51" t="n">
-        <v>2.69</v>
+        <v>-141.06</v>
       </c>
       <c r="K51" t="n">
-        <v>-130.9</v>
+        <v>1.91</v>
       </c>
       <c r="L51" t="n">
-        <v>130.93</v>
+        <v>141.08</v>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>09:16:38</t>
+          <t>09:15:36</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
@@ -2221,34 +2221,34 @@
         <v>3</v>
       </c>
       <c r="E52" t="n">
-        <v>4.7</v>
+        <v>4.01</v>
       </c>
       <c r="F52" t="n">
-        <v>9.51</v>
+        <v>10.46</v>
       </c>
       <c r="G52" t="n">
-        <v>43.8</v>
+        <v>50.2</v>
       </c>
       <c r="H52" t="n">
-        <v>99.40000000000001</v>
+        <v>97.09999999999999</v>
       </c>
       <c r="I52" t="n">
-        <v>22</v>
+        <v>16</v>
       </c>
       <c r="J52" t="n">
-        <v>-88.09999999999999</v>
+        <v>-72.03</v>
       </c>
       <c r="K52" t="n">
-        <v>116.42</v>
+        <v>-132.59</v>
       </c>
       <c r="L52" t="n">
-        <v>146</v>
+        <v>150.89</v>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>09:22:10</t>
+          <t>09:21:48</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
@@ -2263,34 +2263,34 @@
         <v>1</v>
       </c>
       <c r="E53" t="n">
-        <v>4.21</v>
+        <v>3.86</v>
       </c>
       <c r="F53" t="n">
-        <v>9.48</v>
+        <v>9.970000000000001</v>
       </c>
       <c r="G53" t="n">
-        <v>32.3</v>
+        <v>35.4</v>
       </c>
       <c r="H53" t="n">
-        <v>97.40000000000001</v>
+        <v>100</v>
       </c>
       <c r="I53" t="n">
-        <v>21</v>
+        <v>16</v>
       </c>
       <c r="J53" t="n">
-        <v>192.82</v>
+        <v>38.94</v>
       </c>
       <c r="K53" t="n">
-        <v>-122.76</v>
+        <v>-254.93</v>
       </c>
       <c r="L53" t="n">
-        <v>228.58</v>
+        <v>257.88</v>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>09:24:22</t>
+          <t>09:22:50</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
@@ -2305,34 +2305,34 @@
         <v>2</v>
       </c>
       <c r="E54" t="n">
-        <v>4.3</v>
+        <v>3.95</v>
       </c>
       <c r="F54" t="n">
-        <v>9.220000000000001</v>
+        <v>10.81</v>
       </c>
       <c r="G54" t="n">
-        <v>41.4</v>
+        <v>48.6</v>
       </c>
       <c r="H54" t="n">
-        <v>90.40000000000001</v>
+        <v>96.5</v>
       </c>
       <c r="I54" t="n">
-        <v>23</v>
+        <v>16</v>
       </c>
       <c r="J54" t="n">
-        <v>-128.53</v>
+        <v>-199.34</v>
       </c>
       <c r="K54" t="n">
-        <v>114.47</v>
+        <v>-50.05</v>
       </c>
       <c r="L54" t="n">
-        <v>172.11</v>
+        <v>205.52</v>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>09:26:29</t>
+          <t>09:24:09</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
@@ -2347,34 +2347,34 @@
         <v>3</v>
       </c>
       <c r="E55" t="n">
-        <v>4.04</v>
+        <v>4.52</v>
       </c>
       <c r="F55" t="n">
-        <v>9.76</v>
+        <v>10.81</v>
       </c>
       <c r="G55" t="n">
-        <v>42.7</v>
+        <v>33.8</v>
       </c>
       <c r="H55" t="n">
-        <v>100</v>
+        <v>98.2</v>
       </c>
       <c r="I55" t="n">
-        <v>23</v>
+        <v>16</v>
       </c>
       <c r="J55" t="n">
-        <v>-51.94</v>
+        <v>234.27</v>
       </c>
       <c r="K55" t="n">
-        <v>-175.63</v>
+        <v>67.73999999999999</v>
       </c>
       <c r="L55" t="n">
-        <v>183.15</v>
+        <v>243.87</v>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>09:30:06</t>
+          <t>09:29:44</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
@@ -2389,28 +2389,28 @@
         <v>1</v>
       </c>
       <c r="E56" t="n">
-        <v>3.74</v>
+        <v>3.56</v>
       </c>
       <c r="F56" t="n">
-        <v>9.73</v>
+        <v>6.36</v>
       </c>
       <c r="G56" t="n">
-        <v>30.2</v>
+        <v>44.8</v>
       </c>
       <c r="H56" t="n">
-        <v>100</v>
+        <v>96.7</v>
       </c>
       <c r="I56" t="n">
-        <v>22</v>
+        <v>17</v>
       </c>
       <c r="J56" t="n">
-        <v>-208.22</v>
+        <v>239.16</v>
       </c>
       <c r="K56" t="n">
-        <v>68.25</v>
+        <v>-43.25</v>
       </c>
       <c r="L56" t="n">
-        <v>219.12</v>
+        <v>243.04</v>
       </c>
     </row>
     <row r="57">
@@ -2431,34 +2431,34 @@
         <v>2</v>
       </c>
       <c r="E57" t="n">
-        <v>4.85</v>
+        <v>4.1</v>
       </c>
       <c r="F57" t="n">
-        <v>9.970000000000001</v>
+        <v>10.15</v>
       </c>
       <c r="G57" t="n">
-        <v>51.5</v>
+        <v>42.4</v>
       </c>
       <c r="H57" t="n">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="I57" t="n">
-        <v>22</v>
+        <v>17</v>
       </c>
       <c r="J57" t="n">
-        <v>-13.07</v>
+        <v>194.75</v>
       </c>
       <c r="K57" t="n">
-        <v>-280.44</v>
+        <v>275.26</v>
       </c>
       <c r="L57" t="n">
-        <v>280.75</v>
+        <v>337.19</v>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>09:34:37</t>
+          <t>09:34:32</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
@@ -2473,34 +2473,34 @@
         <v>3</v>
       </c>
       <c r="E58" t="n">
-        <v>4.3</v>
+        <v>3.52</v>
       </c>
       <c r="F58" t="n">
-        <v>8.91</v>
+        <v>7.12</v>
       </c>
       <c r="G58" t="n">
-        <v>40.9</v>
+        <v>34.2</v>
       </c>
       <c r="H58" t="n">
-        <v>92.2</v>
+        <v>100</v>
       </c>
       <c r="I58" t="n">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="J58" t="n">
-        <v>-235.99</v>
+        <v>259.33</v>
       </c>
       <c r="K58" t="n">
-        <v>-249.04</v>
+        <v>31.78</v>
       </c>
       <c r="L58" t="n">
-        <v>343.09</v>
+        <v>261.27</v>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>09:47:53</t>
+          <t>09:42:21</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
@@ -2515,34 +2515,34 @@
         <v>1</v>
       </c>
       <c r="E59" t="n">
-        <v>5.3</v>
+        <v>4.11</v>
       </c>
       <c r="F59" t="n">
-        <v>9.24</v>
+        <v>10.81</v>
       </c>
       <c r="G59" t="n">
-        <v>40.8</v>
+        <v>41</v>
       </c>
       <c r="H59" t="n">
-        <v>100</v>
+        <v>98.40000000000001</v>
       </c>
       <c r="I59" t="n">
-        <v>22</v>
+        <v>18</v>
       </c>
       <c r="J59" t="n">
-        <v>80.61</v>
+        <v>-7.53</v>
       </c>
       <c r="K59" t="n">
-        <v>-2.8</v>
+        <v>-56.57</v>
       </c>
       <c r="L59" t="n">
-        <v>80.66</v>
+        <v>57.07</v>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>09:49:09</t>
+          <t>09:43:35</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
@@ -2557,34 +2557,34 @@
         <v>2</v>
       </c>
       <c r="E60" t="n">
-        <v>4.07</v>
+        <v>4.25</v>
       </c>
       <c r="F60" t="n">
-        <v>9.289999999999999</v>
+        <v>10.81</v>
       </c>
       <c r="G60" t="n">
-        <v>44.7</v>
+        <v>59.6</v>
       </c>
       <c r="H60" t="n">
-        <v>100</v>
+        <v>98.90000000000001</v>
       </c>
       <c r="I60" t="n">
-        <v>20</v>
+        <v>16</v>
       </c>
       <c r="J60" t="n">
-        <v>73.88</v>
+        <v>89.69</v>
       </c>
       <c r="K60" t="n">
-        <v>65.95999999999999</v>
+        <v>-34.43</v>
       </c>
       <c r="L60" t="n">
-        <v>99.04000000000001</v>
+        <v>96.06999999999999</v>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>09:50:06</t>
+          <t>09:44:40</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
@@ -2599,34 +2599,34 @@
         <v>3</v>
       </c>
       <c r="E61" t="n">
-        <v>4.01</v>
+        <v>3.96</v>
       </c>
       <c r="F61" t="n">
-        <v>8.68</v>
+        <v>10.81</v>
       </c>
       <c r="G61" t="n">
-        <v>44.7</v>
+        <v>53.7</v>
       </c>
       <c r="H61" t="n">
-        <v>100</v>
+        <v>92.8</v>
       </c>
       <c r="I61" t="n">
-        <v>24</v>
+        <v>16</v>
       </c>
       <c r="J61" t="n">
-        <v>-46.33</v>
+        <v>-67.20999999999999</v>
       </c>
       <c r="K61" t="n">
-        <v>-28.25</v>
+        <v>-37.04</v>
       </c>
       <c r="L61" t="n">
-        <v>54.27</v>
+        <v>76.73999999999999</v>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>09:54:33</t>
+          <t>09:49:27</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
@@ -2641,10 +2641,10 @@
         <v>1</v>
       </c>
       <c r="E62" t="n">
-        <v>3.72</v>
+        <v>4.09</v>
       </c>
       <c r="F62" t="n">
-        <v>9.23</v>
+        <v>10.81</v>
       </c>
       <c r="G62" t="n">
         <v>43.7</v>
@@ -2653,22 +2653,22 @@
         <v>100</v>
       </c>
       <c r="I62" t="n">
-        <v>22</v>
+        <v>16</v>
       </c>
       <c r="J62" t="n">
-        <v>-83.16</v>
+        <v>154.77</v>
       </c>
       <c r="K62" t="n">
-        <v>-48.85</v>
+        <v>-64.81999999999999</v>
       </c>
       <c r="L62" t="n">
-        <v>96.45</v>
+        <v>167.8</v>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>09:55:21</t>
+          <t>09:50:53</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
@@ -2683,10 +2683,10 @@
         <v>2</v>
       </c>
       <c r="E63" t="n">
-        <v>4.39</v>
+        <v>3.95</v>
       </c>
       <c r="F63" t="n">
-        <v>9.59</v>
+        <v>8.6</v>
       </c>
       <c r="G63" t="n">
         <v>48.9</v>
@@ -2695,22 +2695,22 @@
         <v>100</v>
       </c>
       <c r="I63" t="n">
-        <v>23</v>
+        <v>16</v>
       </c>
       <c r="J63" t="n">
-        <v>-73.56999999999999</v>
+        <v>33.47</v>
       </c>
       <c r="K63" t="n">
-        <v>-24.52</v>
+        <v>-81.93000000000001</v>
       </c>
       <c r="L63" t="n">
-        <v>77.55</v>
+        <v>88.51000000000001</v>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>09:57:43</t>
+          <t>09:53:19</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
@@ -2725,10 +2725,10 @@
         <v>3</v>
       </c>
       <c r="E64" t="n">
-        <v>4.16</v>
+        <v>4.1</v>
       </c>
       <c r="F64" t="n">
-        <v>9.720000000000001</v>
+        <v>10.81</v>
       </c>
       <c r="G64" t="n">
         <v>36.7</v>
@@ -2737,22 +2737,22 @@
         <v>100</v>
       </c>
       <c r="I64" t="n">
-        <v>19</v>
+        <v>16</v>
       </c>
       <c r="J64" t="n">
-        <v>-24.87</v>
+        <v>-123.71</v>
       </c>
       <c r="K64" t="n">
-        <v>-94.48999999999999</v>
+        <v>-18.22</v>
       </c>
       <c r="L64" t="n">
-        <v>97.70999999999999</v>
+        <v>125.04</v>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>10:02:48</t>
+          <t>09:58:43</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
@@ -2767,10 +2767,10 @@
         <v>1</v>
       </c>
       <c r="E65" t="n">
-        <v>3.95</v>
+        <v>3.85</v>
       </c>
       <c r="F65" t="n">
-        <v>9.210000000000001</v>
+        <v>10.81</v>
       </c>
       <c r="G65" t="n">
         <v>48.2</v>
@@ -2779,22 +2779,22 @@
         <v>96.7</v>
       </c>
       <c r="I65" t="n">
-        <v>20</v>
+        <v>16</v>
       </c>
       <c r="J65" t="n">
-        <v>148.1</v>
+        <v>37.07</v>
       </c>
       <c r="K65" t="n">
-        <v>70.94</v>
+        <v>177.16</v>
       </c>
       <c r="L65" t="n">
-        <v>164.22</v>
+        <v>180.99</v>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>10:04:41</t>
+          <t>09:59:57</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
@@ -2809,34 +2809,34 @@
         <v>2</v>
       </c>
       <c r="E66" t="n">
-        <v>4.43</v>
+        <v>4.39</v>
       </c>
       <c r="F66" t="n">
-        <v>9.539999999999999</v>
+        <v>10.81</v>
       </c>
       <c r="G66" t="n">
-        <v>44.3</v>
+        <v>49.2</v>
       </c>
       <c r="H66" t="n">
         <v>100</v>
       </c>
       <c r="I66" t="n">
-        <v>19</v>
+        <v>16</v>
       </c>
       <c r="J66" t="n">
-        <v>-3.65</v>
+        <v>107.18</v>
       </c>
       <c r="K66" t="n">
-        <v>-119.68</v>
+        <v>102.05</v>
       </c>
       <c r="L66" t="n">
-        <v>119.74</v>
+        <v>147.99</v>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>10:06:40</t>
+          <t>10:01:10</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
@@ -2851,34 +2851,34 @@
         <v>3</v>
       </c>
       <c r="E67" t="n">
-        <v>4.44</v>
+        <v>4.17</v>
       </c>
       <c r="F67" t="n">
-        <v>9.32</v>
+        <v>10.81</v>
       </c>
       <c r="G67" t="n">
-        <v>40.3</v>
+        <v>37.5</v>
       </c>
       <c r="H67" t="n">
-        <v>96.7</v>
+        <v>91.7</v>
       </c>
       <c r="I67" t="n">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="J67" t="n">
-        <v>247.1</v>
+        <v>-5.37</v>
       </c>
       <c r="K67" t="n">
-        <v>-179.34</v>
+        <v>168.36</v>
       </c>
       <c r="L67" t="n">
-        <v>305.32</v>
+        <v>168.45</v>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>10:11:18</t>
+          <t>10:07:14</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
@@ -2893,34 +2893,34 @@
         <v>1</v>
       </c>
       <c r="E68" t="n">
-        <v>4.33</v>
+        <v>5.18</v>
       </c>
       <c r="F68" t="n">
-        <v>9.460000000000001</v>
+        <v>10.81</v>
       </c>
       <c r="G68" t="n">
-        <v>48.4</v>
+        <v>42.7</v>
       </c>
       <c r="H68" t="n">
-        <v>99.3</v>
+        <v>100</v>
       </c>
       <c r="I68" t="n">
-        <v>22</v>
+        <v>17</v>
       </c>
       <c r="J68" t="n">
-        <v>33.9</v>
+        <v>191.58</v>
       </c>
       <c r="K68" t="n">
-        <v>150.98</v>
+        <v>-30.7</v>
       </c>
       <c r="L68" t="n">
-        <v>154.74</v>
+        <v>194.03</v>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>10:12:33</t>
+          <t>10:09:33</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
@@ -2935,34 +2935,34 @@
         <v>2</v>
       </c>
       <c r="E69" t="n">
-        <v>4.71</v>
+        <v>4.24</v>
       </c>
       <c r="F69" t="n">
-        <v>9.199999999999999</v>
+        <v>10.81</v>
       </c>
       <c r="G69" t="n">
-        <v>50.2</v>
+        <v>66.7</v>
       </c>
       <c r="H69" t="n">
-        <v>100</v>
+        <v>97.7</v>
       </c>
       <c r="I69" t="n">
-        <v>23</v>
+        <v>18</v>
       </c>
       <c r="J69" t="n">
-        <v>41.51</v>
+        <v>199.88</v>
       </c>
       <c r="K69" t="n">
-        <v>-237.09</v>
+        <v>-61.85</v>
       </c>
       <c r="L69" t="n">
-        <v>240.7</v>
+        <v>209.23</v>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>10:14:49</t>
+          <t>10:11:22</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
@@ -2977,34 +2977,34 @@
         <v>3</v>
       </c>
       <c r="E70" t="n">
-        <v>4.03</v>
+        <v>4.29</v>
       </c>
       <c r="F70" t="n">
-        <v>9.42</v>
+        <v>8.289999999999999</v>
       </c>
       <c r="G70" t="n">
-        <v>35.5</v>
+        <v>38.2</v>
       </c>
       <c r="H70" t="n">
-        <v>97.59999999999999</v>
+        <v>97.09999999999999</v>
       </c>
       <c r="I70" t="n">
-        <v>23</v>
+        <v>16</v>
       </c>
       <c r="J70" t="n">
-        <v>34.62</v>
+        <v>-171.95</v>
       </c>
       <c r="K70" t="n">
-        <v>-169.22</v>
+        <v>74.89</v>
       </c>
       <c r="L70" t="n">
-        <v>172.73</v>
+        <v>187.55</v>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>10:20:31</t>
+          <t>10:14:27</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
@@ -3019,34 +3019,34 @@
         <v>1</v>
       </c>
       <c r="E71" t="n">
-        <v>3.95</v>
+        <v>4.66</v>
       </c>
       <c r="F71" t="n">
-        <v>9.17</v>
+        <v>10.33</v>
       </c>
       <c r="G71" t="n">
-        <v>54.9</v>
+        <v>32.8</v>
       </c>
       <c r="H71" t="n">
-        <v>100</v>
+        <v>98.5</v>
       </c>
       <c r="I71" t="n">
-        <v>21</v>
+        <v>16</v>
       </c>
       <c r="J71" t="n">
-        <v>-99.3</v>
+        <v>400.49</v>
       </c>
       <c r="K71" t="n">
-        <v>-190.53</v>
+        <v>-61.15</v>
       </c>
       <c r="L71" t="n">
-        <v>214.86</v>
+        <v>405.13</v>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>10:22:45</t>
+          <t>10:16:22</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
@@ -3061,34 +3061,34 @@
         <v>2</v>
       </c>
       <c r="E72" t="n">
-        <v>4.33</v>
+        <v>4.27</v>
       </c>
       <c r="F72" t="n">
-        <v>9.43</v>
+        <v>10.13</v>
       </c>
       <c r="G72" t="n">
-        <v>31.1</v>
+        <v>38.8</v>
       </c>
       <c r="H72" t="n">
-        <v>96.8</v>
+        <v>100</v>
       </c>
       <c r="I72" t="n">
-        <v>23</v>
+        <v>17</v>
       </c>
       <c r="J72" t="n">
-        <v>152.24</v>
+        <v>-330.72</v>
       </c>
       <c r="K72" t="n">
-        <v>311.88</v>
+        <v>90.93000000000001</v>
       </c>
       <c r="L72" t="n">
-        <v>347.05</v>
+        <v>342.99</v>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>10:23:50</t>
+          <t>10:18:14</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
@@ -3103,34 +3103,34 @@
         <v>3</v>
       </c>
       <c r="E73" t="n">
-        <v>4.07</v>
+        <v>4.58</v>
       </c>
       <c r="F73" t="n">
-        <v>9.6</v>
+        <v>10.81</v>
       </c>
       <c r="G73" t="n">
-        <v>57.3</v>
+        <v>35.3</v>
       </c>
       <c r="H73" t="n">
         <v>100</v>
       </c>
       <c r="I73" t="n">
-        <v>20</v>
+        <v>16</v>
       </c>
       <c r="J73" t="n">
-        <v>-209.21</v>
+        <v>413.13</v>
       </c>
       <c r="K73" t="n">
-        <v>-12.64</v>
+        <v>181.71</v>
       </c>
       <c r="L73" t="n">
-        <v>209.59</v>
+        <v>451.33</v>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>10:35:56</t>
+          <t>10:31:33</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
@@ -3145,34 +3145,34 @@
         <v>1</v>
       </c>
       <c r="E74" t="n">
-        <v>4.03</v>
+        <v>4.79</v>
       </c>
       <c r="F74" t="n">
-        <v>9.210000000000001</v>
+        <v>10.81</v>
       </c>
       <c r="G74" t="n">
-        <v>44.3</v>
+        <v>44.4</v>
       </c>
       <c r="H74" t="n">
-        <v>100</v>
+        <v>96.3</v>
       </c>
       <c r="I74" t="n">
-        <v>21</v>
+        <v>18</v>
       </c>
       <c r="J74" t="n">
-        <v>55.19</v>
+        <v>10.26</v>
       </c>
       <c r="K74" t="n">
-        <v>-20.81</v>
+        <v>-63.84</v>
       </c>
       <c r="L74" t="n">
-        <v>58.99</v>
+        <v>64.66</v>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>10:38:23</t>
+          <t>10:33:37</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
@@ -3187,34 +3187,34 @@
         <v>2</v>
       </c>
       <c r="E75" t="n">
-        <v>3.97</v>
+        <v>4.15</v>
       </c>
       <c r="F75" t="n">
-        <v>9.23</v>
+        <v>10.6</v>
       </c>
       <c r="G75" t="n">
-        <v>37.4</v>
+        <v>39.3</v>
       </c>
       <c r="H75" t="n">
-        <v>94.5</v>
+        <v>92.40000000000001</v>
       </c>
       <c r="I75" t="n">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="J75" t="n">
-        <v>-31.81</v>
+        <v>-68.23</v>
       </c>
       <c r="K75" t="n">
-        <v>108.69</v>
+        <v>-32.51</v>
       </c>
       <c r="L75" t="n">
-        <v>113.25</v>
+        <v>75.58</v>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>10:40:41</t>
+          <t>10:35:00</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
@@ -3229,34 +3229,34 @@
         <v>3</v>
       </c>
       <c r="E76" t="n">
-        <v>3.94</v>
+        <v>4.26</v>
       </c>
       <c r="F76" t="n">
-        <v>9.640000000000001</v>
+        <v>10.81</v>
       </c>
       <c r="G76" t="n">
-        <v>38.8</v>
+        <v>53.8</v>
       </c>
       <c r="H76" t="n">
-        <v>99.3</v>
+        <v>95</v>
       </c>
       <c r="I76" t="n">
-        <v>22</v>
+        <v>16</v>
       </c>
       <c r="J76" t="n">
-        <v>-40.15</v>
+        <v>-55.14</v>
       </c>
       <c r="K76" t="n">
-        <v>92.26000000000001</v>
+        <v>55.74</v>
       </c>
       <c r="L76" t="n">
-        <v>100.62</v>
+        <v>78.40000000000001</v>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>10:46:10</t>
+          <t>10:38:19</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
@@ -3271,34 +3271,34 @@
         <v>1</v>
       </c>
       <c r="E77" t="n">
-        <v>3.67</v>
+        <v>4.18</v>
       </c>
       <c r="F77" t="n">
-        <v>10.46</v>
+        <v>10.81</v>
       </c>
       <c r="G77" t="n">
-        <v>40.9</v>
+        <v>45.6</v>
       </c>
       <c r="H77" t="n">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="I77" t="n">
-        <v>24</v>
+        <v>16</v>
       </c>
       <c r="J77" t="n">
-        <v>-115.84</v>
+        <v>-17.97</v>
       </c>
       <c r="K77" t="n">
-        <v>-70.34</v>
+        <v>151.72</v>
       </c>
       <c r="L77" t="n">
-        <v>135.53</v>
+        <v>152.78</v>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>10:47:01</t>
+          <t>10:40:15</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
@@ -3313,34 +3313,34 @@
         <v>2</v>
       </c>
       <c r="E78" t="n">
-        <v>4.41</v>
+        <v>4.55</v>
       </c>
       <c r="F78" t="n">
-        <v>8.92</v>
+        <v>9.789999999999999</v>
       </c>
       <c r="G78" t="n">
-        <v>40.5</v>
+        <v>34.9</v>
       </c>
       <c r="H78" t="n">
         <v>100</v>
       </c>
       <c r="I78" t="n">
-        <v>24</v>
+        <v>16</v>
       </c>
       <c r="J78" t="n">
-        <v>50.95</v>
+        <v>-33.87</v>
       </c>
       <c r="K78" t="n">
-        <v>-113.8</v>
+        <v>-96.09</v>
       </c>
       <c r="L78" t="n">
-        <v>124.69</v>
+        <v>101.88</v>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>10:48:16</t>
+          <t>10:42:01</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
@@ -3355,34 +3355,34 @@
         <v>3</v>
       </c>
       <c r="E79" t="n">
-        <v>4.65</v>
+        <v>4.03</v>
       </c>
       <c r="F79" t="n">
-        <v>9.210000000000001</v>
+        <v>7.6</v>
       </c>
       <c r="G79" t="n">
-        <v>48.5</v>
+        <v>41.4</v>
       </c>
       <c r="H79" t="n">
-        <v>94.40000000000001</v>
+        <v>100</v>
       </c>
       <c r="I79" t="n">
-        <v>24</v>
+        <v>16</v>
       </c>
       <c r="J79" t="n">
-        <v>114.12</v>
+        <v>69.75</v>
       </c>
       <c r="K79" t="n">
-        <v>-49.49</v>
+        <v>-46.03</v>
       </c>
       <c r="L79" t="n">
-        <v>124.39</v>
+        <v>83.56999999999999</v>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>10:53:25</t>
+          <t>10:46:58</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
@@ -3397,34 +3397,34 @@
         <v>1</v>
       </c>
       <c r="E80" t="n">
-        <v>3.91</v>
+        <v>3.88</v>
       </c>
       <c r="F80" t="n">
-        <v>9.25</v>
+        <v>8.890000000000001</v>
       </c>
       <c r="G80" t="n">
-        <v>56</v>
+        <v>46.4</v>
       </c>
       <c r="H80" t="n">
-        <v>99.7</v>
+        <v>94.09999999999999</v>
       </c>
       <c r="I80" t="n">
-        <v>25</v>
+        <v>18</v>
       </c>
       <c r="J80" t="n">
-        <v>84.06999999999999</v>
+        <v>158.17</v>
       </c>
       <c r="K80" t="n">
-        <v>51.32</v>
+        <v>-20.58</v>
       </c>
       <c r="L80" t="n">
-        <v>98.5</v>
+        <v>159.51</v>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>10:54:01</t>
+          <t>10:48:57</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
@@ -3439,34 +3439,34 @@
         <v>2</v>
       </c>
       <c r="E81" t="n">
-        <v>4.42</v>
+        <v>4.23</v>
       </c>
       <c r="F81" t="n">
-        <v>9.26</v>
+        <v>10.81</v>
       </c>
       <c r="G81" t="n">
-        <v>50.8</v>
+        <v>45.4</v>
       </c>
       <c r="H81" t="n">
-        <v>98.3</v>
+        <v>100</v>
       </c>
       <c r="I81" t="n">
-        <v>23</v>
+        <v>16</v>
       </c>
       <c r="J81" t="n">
-        <v>78.48</v>
+        <v>147.22</v>
       </c>
       <c r="K81" t="n">
-        <v>148.47</v>
+        <v>-25.61</v>
       </c>
       <c r="L81" t="n">
-        <v>167.93</v>
+        <v>149.43</v>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>10:56:27</t>
+          <t>10:51:29</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
@@ -3481,34 +3481,34 @@
         <v>3</v>
       </c>
       <c r="E82" t="n">
-        <v>4.15</v>
+        <v>4.59</v>
       </c>
       <c r="F82" t="n">
-        <v>9.619999999999999</v>
+        <v>10.81</v>
       </c>
       <c r="G82" t="n">
-        <v>38.5</v>
+        <v>38.4</v>
       </c>
       <c r="H82" t="n">
-        <v>97.09999999999999</v>
+        <v>100</v>
       </c>
       <c r="I82" t="n">
-        <v>20</v>
+        <v>16</v>
       </c>
       <c r="J82" t="n">
-        <v>19.89</v>
+        <v>111.13</v>
       </c>
       <c r="K82" t="n">
-        <v>131.95</v>
+        <v>102.98</v>
       </c>
       <c r="L82" t="n">
-        <v>133.44</v>
+        <v>151.51</v>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>11:02:02</t>
+          <t>10:55:34</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
@@ -3523,34 +3523,34 @@
         <v>1</v>
       </c>
       <c r="E83" t="n">
-        <v>4.44</v>
+        <v>4.38</v>
       </c>
       <c r="F83" t="n">
-        <v>9.59</v>
+        <v>10.81</v>
       </c>
       <c r="G83" t="n">
-        <v>39.7</v>
+        <v>37.3</v>
       </c>
       <c r="H83" t="n">
-        <v>96.59999999999999</v>
+        <v>99.8</v>
       </c>
       <c r="I83" t="n">
-        <v>21</v>
+        <v>16</v>
       </c>
       <c r="J83" t="n">
-        <v>66.40000000000001</v>
+        <v>131.97</v>
       </c>
       <c r="K83" t="n">
-        <v>-154.36</v>
+        <v>148.69</v>
       </c>
       <c r="L83" t="n">
-        <v>168.03</v>
+        <v>198.81</v>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>11:04:17</t>
+          <t>10:57:40</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
@@ -3565,34 +3565,34 @@
         <v>2</v>
       </c>
       <c r="E84" t="n">
-        <v>4.71</v>
+        <v>4.42</v>
       </c>
       <c r="F84" t="n">
-        <v>9.75</v>
+        <v>10.81</v>
       </c>
       <c r="G84" t="n">
-        <v>58.6</v>
+        <v>44.3</v>
       </c>
       <c r="H84" t="n">
         <v>100</v>
       </c>
       <c r="I84" t="n">
-        <v>19</v>
+        <v>16</v>
       </c>
       <c r="J84" t="n">
-        <v>166.27</v>
+        <v>126.12</v>
       </c>
       <c r="K84" t="n">
-        <v>60.83</v>
+        <v>275.76</v>
       </c>
       <c r="L84" t="n">
-        <v>177.04</v>
+        <v>303.23</v>
       </c>
     </row>
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>11:05:20</t>
+          <t>10:58:38</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
@@ -3607,34 +3607,34 @@
         <v>3</v>
       </c>
       <c r="E85" t="n">
-        <v>4.63</v>
+        <v>4.5</v>
       </c>
       <c r="F85" t="n">
-        <v>9.390000000000001</v>
+        <v>10.81</v>
       </c>
       <c r="G85" t="n">
-        <v>50.7</v>
+        <v>54.7</v>
       </c>
       <c r="H85" t="n">
         <v>100</v>
       </c>
       <c r="I85" t="n">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="J85" t="n">
-        <v>155.74</v>
+        <v>90.09</v>
       </c>
       <c r="K85" t="n">
-        <v>145.72</v>
+        <v>131.57</v>
       </c>
       <c r="L85" t="n">
-        <v>213.28</v>
+        <v>159.46</v>
       </c>
     </row>
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>11:10:09</t>
+          <t>11:03:27</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
@@ -3649,34 +3649,34 @@
         <v>1</v>
       </c>
       <c r="E86" t="n">
-        <v>4.61</v>
+        <v>4.6</v>
       </c>
       <c r="F86" t="n">
-        <v>9.58</v>
+        <v>10.81</v>
       </c>
       <c r="G86" t="n">
-        <v>38.8</v>
+        <v>37.5</v>
       </c>
       <c r="H86" t="n">
-        <v>96.7</v>
+        <v>100</v>
       </c>
       <c r="I86" t="n">
-        <v>20</v>
+        <v>16</v>
       </c>
       <c r="J86" t="n">
-        <v>264.29</v>
+        <v>186.09</v>
       </c>
       <c r="K86" t="n">
-        <v>-156.02</v>
+        <v>303.37</v>
       </c>
       <c r="L86" t="n">
-        <v>306.91</v>
+        <v>355.89</v>
       </c>
     </row>
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>11:11:44</t>
+          <t>11:05:44</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
@@ -3691,34 +3691,34 @@
         <v>2</v>
       </c>
       <c r="E87" t="n">
-        <v>4.34</v>
+        <v>4.59</v>
       </c>
       <c r="F87" t="n">
-        <v>9.44</v>
+        <v>10.81</v>
       </c>
       <c r="G87" t="n">
-        <v>55</v>
+        <v>44.8</v>
       </c>
       <c r="H87" t="n">
-        <v>100</v>
+        <v>94.40000000000001</v>
       </c>
       <c r="I87" t="n">
-        <v>25</v>
+        <v>16</v>
       </c>
       <c r="J87" t="n">
-        <v>5.65</v>
+        <v>75.68000000000001</v>
       </c>
       <c r="K87" t="n">
-        <v>79.61</v>
+        <v>434.64</v>
       </c>
       <c r="L87" t="n">
-        <v>79.81</v>
+        <v>441.18</v>
       </c>
     </row>
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>11:12:36</t>
+          <t>11:06:45</t>
         </is>
       </c>
       <c r="B88" t="inlineStr">
@@ -3733,28 +3733,28 @@
         <v>3</v>
       </c>
       <c r="E88" t="n">
-        <v>4.09</v>
+        <v>4.33</v>
       </c>
       <c r="F88" t="n">
-        <v>8.93</v>
+        <v>9.99</v>
       </c>
       <c r="G88" t="n">
-        <v>31.7</v>
+        <v>34.6</v>
       </c>
       <c r="H88" t="n">
-        <v>95.2</v>
+        <v>98.59999999999999</v>
       </c>
       <c r="I88" t="n">
-        <v>25</v>
+        <v>16</v>
       </c>
       <c r="J88" t="n">
-        <v>-192.95</v>
+        <v>-270.9</v>
       </c>
       <c r="K88" t="n">
-        <v>-100.48</v>
+        <v>118.73</v>
       </c>
       <c r="L88" t="n">
-        <v>217.54</v>
+        <v>295.77</v>
       </c>
     </row>
   </sheetData>

--- a/output/2024-10-08.xlsx
+++ b/output/2024-10-08.xlsx
@@ -640,13 +640,13 @@
         <v>16</v>
       </c>
       <c r="J14" t="n">
-        <v>-106.64</v>
+        <v>-121.23</v>
       </c>
       <c r="K14" t="n">
-        <v>25.79</v>
+        <v>29.32</v>
       </c>
       <c r="L14" t="n">
-        <v>109.71</v>
+        <v>124.73</v>
       </c>
     </row>
     <row r="15">
@@ -682,13 +682,13 @@
         <v>16</v>
       </c>
       <c r="J15" t="n">
-        <v>-82.39</v>
+        <v>-93.75</v>
       </c>
       <c r="K15" t="n">
-        <v>66.64</v>
+        <v>75.83</v>
       </c>
       <c r="L15" t="n">
-        <v>105.97</v>
+        <v>120.58</v>
       </c>
     </row>
     <row r="16">
@@ -724,13 +724,13 @@
         <v>16</v>
       </c>
       <c r="J16" t="n">
-        <v>4.6</v>
+        <v>5.23</v>
       </c>
       <c r="K16" t="n">
-        <v>84.7</v>
+        <v>96.33</v>
       </c>
       <c r="L16" t="n">
-        <v>84.83</v>
+        <v>96.47</v>
       </c>
     </row>
     <row r="17">
@@ -766,13 +766,13 @@
         <v>18</v>
       </c>
       <c r="J17" t="n">
-        <v>62.53</v>
+        <v>69.05</v>
       </c>
       <c r="K17" t="n">
-        <v>2.72</v>
+        <v>3.01</v>
       </c>
       <c r="L17" t="n">
-        <v>62.59</v>
+        <v>69.12</v>
       </c>
     </row>
     <row r="18">
@@ -808,13 +808,13 @@
         <v>16</v>
       </c>
       <c r="J18" t="n">
-        <v>96.01000000000001</v>
+        <v>108.86</v>
       </c>
       <c r="K18" t="n">
-        <v>-68.09999999999999</v>
+        <v>-77.22</v>
       </c>
       <c r="L18" t="n">
-        <v>117.71</v>
+        <v>133.47</v>
       </c>
     </row>
     <row r="19">
@@ -850,13 +850,13 @@
         <v>16</v>
       </c>
       <c r="J19" t="n">
-        <v>-36.14</v>
+        <v>-41.03</v>
       </c>
       <c r="K19" t="n">
-        <v>-137.42</v>
+        <v>-156.02</v>
       </c>
       <c r="L19" t="n">
-        <v>142.09</v>
+        <v>161.32</v>
       </c>
     </row>
     <row r="20">
@@ -892,13 +892,13 @@
         <v>18</v>
       </c>
       <c r="J20" t="n">
-        <v>15.86</v>
+        <v>17.56</v>
       </c>
       <c r="K20" t="n">
-        <v>154.13</v>
+        <v>170.64</v>
       </c>
       <c r="L20" t="n">
-        <v>154.94</v>
+        <v>171.55</v>
       </c>
     </row>
     <row r="21">
@@ -934,13 +934,13 @@
         <v>16</v>
       </c>
       <c r="J21" t="n">
-        <v>-31.99</v>
+        <v>-36.39</v>
       </c>
       <c r="K21" t="n">
-        <v>132.35</v>
+        <v>150.57</v>
       </c>
       <c r="L21" t="n">
-        <v>136.16</v>
+        <v>154.91</v>
       </c>
     </row>
     <row r="22">
@@ -976,13 +976,13 @@
         <v>16</v>
       </c>
       <c r="J22" t="n">
-        <v>-104.02</v>
+        <v>-118.37</v>
       </c>
       <c r="K22" t="n">
-        <v>115.86</v>
+        <v>131.84</v>
       </c>
       <c r="L22" t="n">
-        <v>155.71</v>
+        <v>177.18</v>
       </c>
     </row>
     <row r="23">
@@ -1018,13 +1018,13 @@
         <v>16</v>
       </c>
       <c r="J23" t="n">
-        <v>181.44</v>
+        <v>206.6</v>
       </c>
       <c r="K23" t="n">
-        <v>-15.65</v>
+        <v>-17.82</v>
       </c>
       <c r="L23" t="n">
-        <v>182.11</v>
+        <v>207.37</v>
       </c>
     </row>
     <row r="24">
@@ -1060,13 +1060,13 @@
         <v>17</v>
       </c>
       <c r="J24" t="n">
-        <v>54.08</v>
+        <v>60.76</v>
       </c>
       <c r="K24" t="n">
-        <v>246.03</v>
+        <v>276.45</v>
       </c>
       <c r="L24" t="n">
-        <v>251.9</v>
+        <v>283.04</v>
       </c>
     </row>
     <row r="25">
@@ -1102,13 +1102,13 @@
         <v>16</v>
       </c>
       <c r="J25" t="n">
-        <v>-210.34</v>
+        <v>-239.54</v>
       </c>
       <c r="K25" t="n">
-        <v>264.93</v>
+        <v>301.7</v>
       </c>
       <c r="L25" t="n">
-        <v>338.28</v>
+        <v>385.24</v>
       </c>
     </row>
     <row r="26">
@@ -1144,13 +1144,13 @@
         <v>16</v>
       </c>
       <c r="J26" t="n">
-        <v>-381.87</v>
+        <v>-436.43</v>
       </c>
       <c r="K26" t="n">
-        <v>87.2</v>
+        <v>99.66</v>
       </c>
       <c r="L26" t="n">
-        <v>391.7</v>
+        <v>447.67</v>
       </c>
     </row>
     <row r="27">
@@ -1186,13 +1186,13 @@
         <v>16</v>
       </c>
       <c r="J27" t="n">
-        <v>282.13</v>
+        <v>322.12</v>
       </c>
       <c r="K27" t="n">
-        <v>-62.11</v>
+        <v>-70.91</v>
       </c>
       <c r="L27" t="n">
-        <v>288.89</v>
+        <v>329.83</v>
       </c>
     </row>
     <row r="28">
@@ -1228,13 +1228,13 @@
         <v>16</v>
       </c>
       <c r="J28" t="n">
-        <v>10.32</v>
+        <v>11.79</v>
       </c>
       <c r="K28" t="n">
-        <v>302.03</v>
+        <v>344.91</v>
       </c>
       <c r="L28" t="n">
-        <v>302.2</v>
+        <v>345.11</v>
       </c>
     </row>
     <row r="29">
@@ -1270,13 +1270,13 @@
         <v>16</v>
       </c>
       <c r="J29" t="n">
-        <v>-39.99</v>
+        <v>-45.37</v>
       </c>
       <c r="K29" t="n">
-        <v>59.09</v>
+        <v>67.04000000000001</v>
       </c>
       <c r="L29" t="n">
-        <v>71.34999999999999</v>
+        <v>80.95</v>
       </c>
     </row>
     <row r="30">
@@ -1312,13 +1312,13 @@
         <v>16</v>
       </c>
       <c r="J30" t="n">
-        <v>-17.9</v>
+        <v>-20.37</v>
       </c>
       <c r="K30" t="n">
-        <v>-111.16</v>
+        <v>-126.49</v>
       </c>
       <c r="L30" t="n">
-        <v>112.59</v>
+        <v>128.12</v>
       </c>
     </row>
     <row r="31">
@@ -1354,13 +1354,13 @@
         <v>16</v>
       </c>
       <c r="J31" t="n">
-        <v>-108.38</v>
+        <v>-123.08</v>
       </c>
       <c r="K31" t="n">
-        <v>-3.92</v>
+        <v>-4.45</v>
       </c>
       <c r="L31" t="n">
-        <v>108.45</v>
+        <v>123.16</v>
       </c>
     </row>
     <row r="32">
@@ -1396,13 +1396,13 @@
         <v>16</v>
       </c>
       <c r="J32" t="n">
-        <v>11.56</v>
+        <v>13.13</v>
       </c>
       <c r="K32" t="n">
-        <v>72.77</v>
+        <v>82.69</v>
       </c>
       <c r="L32" t="n">
-        <v>73.68000000000001</v>
+        <v>83.73</v>
       </c>
     </row>
     <row r="33">
@@ -1438,13 +1438,13 @@
         <v>16</v>
       </c>
       <c r="J33" t="n">
-        <v>13.17</v>
+        <v>14.94</v>
       </c>
       <c r="K33" t="n">
-        <v>-77.52</v>
+        <v>-87.93000000000001</v>
       </c>
       <c r="L33" t="n">
-        <v>78.63</v>
+        <v>89.19</v>
       </c>
     </row>
     <row r="34">
@@ -1480,13 +1480,13 @@
         <v>17</v>
       </c>
       <c r="J34" t="n">
-        <v>-87.88</v>
+        <v>-98.22</v>
       </c>
       <c r="K34" t="n">
-        <v>81.81999999999999</v>
+        <v>91.45</v>
       </c>
       <c r="L34" t="n">
-        <v>120.07</v>
+        <v>134.21</v>
       </c>
     </row>
     <row r="35">
@@ -1522,13 +1522,13 @@
         <v>17</v>
       </c>
       <c r="J35" t="n">
-        <v>174.55</v>
+        <v>195.74</v>
       </c>
       <c r="K35" t="n">
-        <v>28.58</v>
+        <v>32.05</v>
       </c>
       <c r="L35" t="n">
-        <v>176.87</v>
+        <v>198.35</v>
       </c>
     </row>
     <row r="36">
@@ -1564,13 +1564,13 @@
         <v>18</v>
       </c>
       <c r="J36" t="n">
-        <v>98.65000000000001</v>
+        <v>109.14</v>
       </c>
       <c r="K36" t="n">
-        <v>-87.41</v>
+        <v>-96.7</v>
       </c>
       <c r="L36" t="n">
-        <v>131.81</v>
+        <v>145.82</v>
       </c>
     </row>
     <row r="37">
@@ -1606,13 +1606,13 @@
         <v>16</v>
       </c>
       <c r="J37" t="n">
-        <v>74.79000000000001</v>
+        <v>85.08</v>
       </c>
       <c r="K37" t="n">
-        <v>112.73</v>
+        <v>128.24</v>
       </c>
       <c r="L37" t="n">
-        <v>135.29</v>
+        <v>153.9</v>
       </c>
     </row>
     <row r="38">
@@ -1648,13 +1648,13 @@
         <v>17</v>
       </c>
       <c r="J38" t="n">
-        <v>-96.92</v>
+        <v>-108.82</v>
       </c>
       <c r="K38" t="n">
-        <v>-40.3</v>
+        <v>-45.25</v>
       </c>
       <c r="L38" t="n">
-        <v>104.96</v>
+        <v>117.85</v>
       </c>
     </row>
     <row r="39">
@@ -1690,13 +1690,13 @@
         <v>16</v>
       </c>
       <c r="J39" t="n">
-        <v>71.98999999999999</v>
+        <v>81.98</v>
       </c>
       <c r="K39" t="n">
-        <v>190.35</v>
+        <v>216.77</v>
       </c>
       <c r="L39" t="n">
-        <v>203.5</v>
+        <v>231.75</v>
       </c>
     </row>
     <row r="40">
@@ -1732,13 +1732,13 @@
         <v>16</v>
       </c>
       <c r="J40" t="n">
-        <v>141.87</v>
+        <v>161.58</v>
       </c>
       <c r="K40" t="n">
-        <v>-149.53</v>
+        <v>-170.31</v>
       </c>
       <c r="L40" t="n">
-        <v>206.12</v>
+        <v>234.76</v>
       </c>
     </row>
     <row r="41">
@@ -1774,13 +1774,13 @@
         <v>16</v>
       </c>
       <c r="J41" t="n">
-        <v>173.62</v>
+        <v>198.62</v>
       </c>
       <c r="K41" t="n">
-        <v>-161.41</v>
+        <v>-184.66</v>
       </c>
       <c r="L41" t="n">
-        <v>237.06</v>
+        <v>271.2</v>
       </c>
     </row>
     <row r="42">
@@ -1816,13 +1816,13 @@
         <v>16</v>
       </c>
       <c r="J42" t="n">
-        <v>61.33</v>
+        <v>70.28</v>
       </c>
       <c r="K42" t="n">
-        <v>-297.47</v>
+        <v>-340.88</v>
       </c>
       <c r="L42" t="n">
-        <v>303.72</v>
+        <v>348.05</v>
       </c>
     </row>
     <row r="43">
@@ -1858,13 +1858,13 @@
         <v>17</v>
       </c>
       <c r="J43" t="n">
-        <v>259.92</v>
+        <v>293.62</v>
       </c>
       <c r="K43" t="n">
-        <v>-22.06</v>
+        <v>-24.92</v>
       </c>
       <c r="L43" t="n">
-        <v>260.86</v>
+        <v>294.68</v>
       </c>
     </row>
     <row r="44">
@@ -1900,13 +1900,13 @@
         <v>16</v>
       </c>
       <c r="J44" t="n">
-        <v>10.79</v>
+        <v>12.26</v>
       </c>
       <c r="K44" t="n">
-        <v>74.51000000000001</v>
+        <v>84.62</v>
       </c>
       <c r="L44" t="n">
-        <v>75.29000000000001</v>
+        <v>85.5</v>
       </c>
     </row>
     <row r="45">
@@ -1942,13 +1942,13 @@
         <v>18</v>
       </c>
       <c r="J45" t="n">
-        <v>-64.15000000000001</v>
+        <v>-70.87</v>
       </c>
       <c r="K45" t="n">
-        <v>-44.72</v>
+        <v>-49.4</v>
       </c>
       <c r="L45" t="n">
-        <v>78.2</v>
+        <v>86.39</v>
       </c>
     </row>
     <row r="46">
@@ -1984,13 +1984,13 @@
         <v>17</v>
       </c>
       <c r="J46" t="n">
-        <v>62.39</v>
+        <v>69.7</v>
       </c>
       <c r="K46" t="n">
-        <v>99.78</v>
+        <v>111.48</v>
       </c>
       <c r="L46" t="n">
-        <v>117.68</v>
+        <v>131.47</v>
       </c>
     </row>
     <row r="47">
@@ -2026,13 +2026,13 @@
         <v>16</v>
       </c>
       <c r="J47" t="n">
-        <v>-75.56999999999999</v>
+        <v>-85.56999999999999</v>
       </c>
       <c r="K47" t="n">
-        <v>-66.93000000000001</v>
+        <v>-75.78</v>
       </c>
       <c r="L47" t="n">
-        <v>100.95</v>
+        <v>114.31</v>
       </c>
     </row>
     <row r="48">
@@ -2068,13 +2068,13 @@
         <v>16</v>
       </c>
       <c r="J48" t="n">
-        <v>-101.47</v>
+        <v>-115.01</v>
       </c>
       <c r="K48" t="n">
-        <v>-5.6</v>
+        <v>-6.35</v>
       </c>
       <c r="L48" t="n">
-        <v>101.63</v>
+        <v>115.18</v>
       </c>
     </row>
     <row r="49">
@@ -2110,13 +2110,13 @@
         <v>16</v>
       </c>
       <c r="J49" t="n">
-        <v>-42.9</v>
+        <v>-48.7</v>
       </c>
       <c r="K49" t="n">
-        <v>-93.09999999999999</v>
+        <v>-105.68</v>
       </c>
       <c r="L49" t="n">
-        <v>102.51</v>
+        <v>116.36</v>
       </c>
     </row>
     <row r="50">
@@ -2152,13 +2152,13 @@
         <v>16</v>
       </c>
       <c r="J50" t="n">
-        <v>52.03</v>
+        <v>59.13</v>
       </c>
       <c r="K50" t="n">
-        <v>95.79000000000001</v>
+        <v>108.87</v>
       </c>
       <c r="L50" t="n">
-        <v>109.01</v>
+        <v>123.89</v>
       </c>
     </row>
     <row r="51">
@@ -2194,13 +2194,13 @@
         <v>16</v>
       </c>
       <c r="J51" t="n">
-        <v>-141.06</v>
+        <v>-160.32</v>
       </c>
       <c r="K51" t="n">
-        <v>1.91</v>
+        <v>2.17</v>
       </c>
       <c r="L51" t="n">
-        <v>141.08</v>
+        <v>160.33</v>
       </c>
     </row>
     <row r="52">
@@ -2236,13 +2236,13 @@
         <v>16</v>
       </c>
       <c r="J52" t="n">
-        <v>-72.03</v>
+        <v>-81.86</v>
       </c>
       <c r="K52" t="n">
-        <v>-132.59</v>
+        <v>-150.68</v>
       </c>
       <c r="L52" t="n">
-        <v>150.89</v>
+        <v>171.48</v>
       </c>
     </row>
     <row r="53">
@@ -2278,13 +2278,13 @@
         <v>16</v>
       </c>
       <c r="J53" t="n">
-        <v>38.94</v>
+        <v>44.35</v>
       </c>
       <c r="K53" t="n">
-        <v>-254.93</v>
+        <v>-290.3</v>
       </c>
       <c r="L53" t="n">
-        <v>257.88</v>
+        <v>293.67</v>
       </c>
     </row>
     <row r="54">
@@ -2320,13 +2320,13 @@
         <v>16</v>
       </c>
       <c r="J54" t="n">
-        <v>-199.34</v>
+        <v>-227.02</v>
       </c>
       <c r="K54" t="n">
-        <v>-50.05</v>
+        <v>-57</v>
       </c>
       <c r="L54" t="n">
-        <v>205.52</v>
+        <v>234.06</v>
       </c>
     </row>
     <row r="55">
@@ -2362,13 +2362,13 @@
         <v>16</v>
       </c>
       <c r="J55" t="n">
-        <v>234.27</v>
+        <v>268.57</v>
       </c>
       <c r="K55" t="n">
-        <v>67.73999999999999</v>
+        <v>77.66</v>
       </c>
       <c r="L55" t="n">
-        <v>243.87</v>
+        <v>279.58</v>
       </c>
     </row>
     <row r="56">
@@ -2404,13 +2404,13 @@
         <v>17</v>
       </c>
       <c r="J56" t="n">
-        <v>239.16</v>
+        <v>269.23</v>
       </c>
       <c r="K56" t="n">
-        <v>-43.25</v>
+        <v>-48.69</v>
       </c>
       <c r="L56" t="n">
-        <v>243.04</v>
+        <v>273.6</v>
       </c>
     </row>
     <row r="57">
@@ -2446,13 +2446,13 @@
         <v>17</v>
       </c>
       <c r="J57" t="n">
-        <v>194.75</v>
+        <v>220.09</v>
       </c>
       <c r="K57" t="n">
-        <v>275.26</v>
+        <v>311.07</v>
       </c>
       <c r="L57" t="n">
-        <v>337.19</v>
+        <v>381.05</v>
       </c>
     </row>
     <row r="58">
@@ -2488,13 +2488,13 @@
         <v>18</v>
       </c>
       <c r="J58" t="n">
-        <v>259.33</v>
+        <v>287.78</v>
       </c>
       <c r="K58" t="n">
-        <v>31.78</v>
+        <v>35.27</v>
       </c>
       <c r="L58" t="n">
-        <v>261.27</v>
+        <v>289.93</v>
       </c>
     </row>
     <row r="59">
@@ -2530,13 +2530,13 @@
         <v>18</v>
       </c>
       <c r="J59" t="n">
-        <v>-7.53</v>
+        <v>-8.300000000000001</v>
       </c>
       <c r="K59" t="n">
-        <v>-56.57</v>
+        <v>-62.37</v>
       </c>
       <c r="L59" t="n">
-        <v>57.07</v>
+        <v>62.92</v>
       </c>
     </row>
     <row r="60">
@@ -2572,13 +2572,13 @@
         <v>16</v>
       </c>
       <c r="J60" t="n">
-        <v>89.69</v>
+        <v>101.57</v>
       </c>
       <c r="K60" t="n">
-        <v>-34.43</v>
+        <v>-39</v>
       </c>
       <c r="L60" t="n">
-        <v>96.06999999999999</v>
+        <v>108.8</v>
       </c>
     </row>
     <row r="61">
@@ -2614,13 +2614,13 @@
         <v>16</v>
       </c>
       <c r="J61" t="n">
-        <v>-67.20999999999999</v>
+        <v>-76.20999999999999</v>
       </c>
       <c r="K61" t="n">
-        <v>-37.04</v>
+        <v>-42</v>
       </c>
       <c r="L61" t="n">
-        <v>76.73999999999999</v>
+        <v>87.02</v>
       </c>
     </row>
     <row r="62">
@@ -2656,13 +2656,13 @@
         <v>16</v>
       </c>
       <c r="J62" t="n">
-        <v>154.77</v>
+        <v>175.41</v>
       </c>
       <c r="K62" t="n">
-        <v>-64.81999999999999</v>
+        <v>-73.45999999999999</v>
       </c>
       <c r="L62" t="n">
-        <v>167.8</v>
+        <v>190.17</v>
       </c>
     </row>
     <row r="63">
@@ -2698,13 +2698,13 @@
         <v>16</v>
       </c>
       <c r="J63" t="n">
-        <v>33.47</v>
+        <v>37.95</v>
       </c>
       <c r="K63" t="n">
-        <v>-81.93000000000001</v>
+        <v>-92.92</v>
       </c>
       <c r="L63" t="n">
-        <v>88.51000000000001</v>
+        <v>100.37</v>
       </c>
     </row>
     <row r="64">
@@ -2740,13 +2740,13 @@
         <v>16</v>
       </c>
       <c r="J64" t="n">
-        <v>-123.71</v>
+        <v>-140.19</v>
       </c>
       <c r="K64" t="n">
-        <v>-18.22</v>
+        <v>-20.65</v>
       </c>
       <c r="L64" t="n">
-        <v>125.04</v>
+        <v>141.71</v>
       </c>
     </row>
     <row r="65">
@@ -2782,13 +2782,13 @@
         <v>16</v>
       </c>
       <c r="J65" t="n">
-        <v>37.07</v>
+        <v>42.14</v>
       </c>
       <c r="K65" t="n">
-        <v>177.16</v>
+        <v>201.38</v>
       </c>
       <c r="L65" t="n">
-        <v>180.99</v>
+        <v>205.74</v>
       </c>
     </row>
     <row r="66">
@@ -2824,13 +2824,13 @@
         <v>16</v>
       </c>
       <c r="J66" t="n">
-        <v>107.18</v>
+        <v>121.73</v>
       </c>
       <c r="K66" t="n">
-        <v>102.05</v>
+        <v>115.92</v>
       </c>
       <c r="L66" t="n">
-        <v>147.99</v>
+        <v>168.09</v>
       </c>
     </row>
     <row r="67">
@@ -2866,13 +2866,13 @@
         <v>18</v>
       </c>
       <c r="J67" t="n">
-        <v>-5.37</v>
+        <v>-5.94</v>
       </c>
       <c r="K67" t="n">
-        <v>168.36</v>
+        <v>186.11</v>
       </c>
       <c r="L67" t="n">
-        <v>168.45</v>
+        <v>186.21</v>
       </c>
     </row>
     <row r="68">
@@ -2908,13 +2908,13 @@
         <v>17</v>
       </c>
       <c r="J68" t="n">
-        <v>191.58</v>
+        <v>217.17</v>
       </c>
       <c r="K68" t="n">
-        <v>-30.7</v>
+        <v>-34.8</v>
       </c>
       <c r="L68" t="n">
-        <v>194.03</v>
+        <v>219.94</v>
       </c>
     </row>
     <row r="69">
@@ -2950,13 +2950,13 @@
         <v>18</v>
       </c>
       <c r="J69" t="n">
-        <v>199.88</v>
+        <v>221.55</v>
       </c>
       <c r="K69" t="n">
-        <v>-61.85</v>
+        <v>-68.55</v>
       </c>
       <c r="L69" t="n">
-        <v>209.23</v>
+        <v>231.92</v>
       </c>
     </row>
     <row r="70">
@@ -2992,13 +2992,13 @@
         <v>16</v>
       </c>
       <c r="J70" t="n">
-        <v>-171.95</v>
+        <v>-195.91</v>
       </c>
       <c r="K70" t="n">
-        <v>74.89</v>
+        <v>85.31999999999999</v>
       </c>
       <c r="L70" t="n">
-        <v>187.55</v>
+        <v>213.68</v>
       </c>
     </row>
     <row r="71">
@@ -3034,13 +3034,13 @@
         <v>16</v>
       </c>
       <c r="J71" t="n">
-        <v>400.49</v>
+        <v>463.11</v>
       </c>
       <c r="K71" t="n">
-        <v>-61.15</v>
+        <v>-70.70999999999999</v>
       </c>
       <c r="L71" t="n">
-        <v>405.13</v>
+        <v>468.48</v>
       </c>
     </row>
     <row r="72">
@@ -3076,13 +3076,13 @@
         <v>17</v>
       </c>
       <c r="J72" t="n">
-        <v>-330.72</v>
+        <v>-375.15</v>
       </c>
       <c r="K72" t="n">
-        <v>90.93000000000001</v>
+        <v>103.15</v>
       </c>
       <c r="L72" t="n">
-        <v>342.99</v>
+        <v>389.07</v>
       </c>
     </row>
     <row r="73">
@@ -3118,13 +3118,13 @@
         <v>16</v>
       </c>
       <c r="J73" t="n">
-        <v>413.13</v>
+        <v>477.46</v>
       </c>
       <c r="K73" t="n">
-        <v>181.71</v>
+        <v>210</v>
       </c>
       <c r="L73" t="n">
-        <v>451.33</v>
+        <v>521.6</v>
       </c>
     </row>
     <row r="74">
@@ -3160,13 +3160,13 @@
         <v>18</v>
       </c>
       <c r="J74" t="n">
-        <v>10.26</v>
+        <v>11.28</v>
       </c>
       <c r="K74" t="n">
-        <v>-63.84</v>
+        <v>-70.17</v>
       </c>
       <c r="L74" t="n">
-        <v>64.66</v>
+        <v>71.08</v>
       </c>
     </row>
     <row r="75">
@@ -3202,13 +3202,13 @@
         <v>18</v>
       </c>
       <c r="J75" t="n">
-        <v>-68.23</v>
+        <v>-75.22</v>
       </c>
       <c r="K75" t="n">
-        <v>-32.51</v>
+        <v>-35.84</v>
       </c>
       <c r="L75" t="n">
-        <v>75.58</v>
+        <v>83.31999999999999</v>
       </c>
     </row>
     <row r="76">
@@ -3244,13 +3244,13 @@
         <v>16</v>
       </c>
       <c r="J76" t="n">
-        <v>-55.14</v>
+        <v>-62.44</v>
       </c>
       <c r="K76" t="n">
-        <v>55.74</v>
+        <v>63.12</v>
       </c>
       <c r="L76" t="n">
-        <v>78.40000000000001</v>
+        <v>88.78</v>
       </c>
     </row>
     <row r="77">
@@ -3286,13 +3286,13 @@
         <v>16</v>
       </c>
       <c r="J77" t="n">
-        <v>-17.97</v>
+        <v>-20.35</v>
       </c>
       <c r="K77" t="n">
-        <v>151.72</v>
+        <v>171.88</v>
       </c>
       <c r="L77" t="n">
-        <v>152.78</v>
+        <v>173.08</v>
       </c>
     </row>
     <row r="78">
@@ -3328,13 +3328,13 @@
         <v>16</v>
       </c>
       <c r="J78" t="n">
-        <v>-33.87</v>
+        <v>-38.3</v>
       </c>
       <c r="K78" t="n">
-        <v>-96.09</v>
+        <v>-108.68</v>
       </c>
       <c r="L78" t="n">
-        <v>101.88</v>
+        <v>115.23</v>
       </c>
     </row>
     <row r="79">
@@ -3370,13 +3370,13 @@
         <v>16</v>
       </c>
       <c r="J79" t="n">
-        <v>69.75</v>
+        <v>79.08</v>
       </c>
       <c r="K79" t="n">
-        <v>-46.03</v>
+        <v>-52.19</v>
       </c>
       <c r="L79" t="n">
-        <v>83.56999999999999</v>
+        <v>94.73999999999999</v>
       </c>
     </row>
     <row r="80">
@@ -3412,13 +3412,13 @@
         <v>18</v>
       </c>
       <c r="J80" t="n">
-        <v>158.17</v>
+        <v>174.93</v>
       </c>
       <c r="K80" t="n">
-        <v>-20.58</v>
+        <v>-22.76</v>
       </c>
       <c r="L80" t="n">
-        <v>159.51</v>
+        <v>176.4</v>
       </c>
     </row>
     <row r="81">
@@ -3454,13 +3454,13 @@
         <v>16</v>
       </c>
       <c r="J81" t="n">
-        <v>147.22</v>
+        <v>167.26</v>
       </c>
       <c r="K81" t="n">
-        <v>-25.61</v>
+        <v>-29.1</v>
       </c>
       <c r="L81" t="n">
-        <v>149.43</v>
+        <v>169.77</v>
       </c>
     </row>
     <row r="82">
@@ -3496,13 +3496,13 @@
         <v>16</v>
       </c>
       <c r="J82" t="n">
-        <v>111.13</v>
+        <v>126.2</v>
       </c>
       <c r="K82" t="n">
-        <v>102.98</v>
+        <v>116.93</v>
       </c>
       <c r="L82" t="n">
-        <v>151.51</v>
+        <v>172.04</v>
       </c>
     </row>
     <row r="83">
@@ -3538,13 +3538,13 @@
         <v>16</v>
       </c>
       <c r="J83" t="n">
-        <v>131.97</v>
+        <v>150.37</v>
       </c>
       <c r="K83" t="n">
-        <v>148.69</v>
+        <v>169.42</v>
       </c>
       <c r="L83" t="n">
-        <v>198.81</v>
+        <v>226.53</v>
       </c>
     </row>
     <row r="84">
@@ -3580,13 +3580,13 @@
         <v>16</v>
       </c>
       <c r="J84" t="n">
-        <v>126.12</v>
+        <v>143.7</v>
       </c>
       <c r="K84" t="n">
-        <v>275.76</v>
+        <v>314.22</v>
       </c>
       <c r="L84" t="n">
-        <v>303.23</v>
+        <v>345.52</v>
       </c>
     </row>
     <row r="85">
@@ -3622,13 +3622,13 @@
         <v>18</v>
       </c>
       <c r="J85" t="n">
-        <v>90.09</v>
+        <v>100.03</v>
       </c>
       <c r="K85" t="n">
-        <v>131.57</v>
+        <v>146.08</v>
       </c>
       <c r="L85" t="n">
-        <v>159.46</v>
+        <v>177.05</v>
       </c>
     </row>
     <row r="86">
@@ -3664,13 +3664,13 @@
         <v>16</v>
       </c>
       <c r="J86" t="n">
-        <v>186.09</v>
+        <v>215.09</v>
       </c>
       <c r="K86" t="n">
-        <v>303.37</v>
+        <v>350.65</v>
       </c>
       <c r="L86" t="n">
-        <v>355.89</v>
+        <v>411.37</v>
       </c>
     </row>
     <row r="87">
@@ -3706,13 +3706,13 @@
         <v>16</v>
       </c>
       <c r="J87" t="n">
-        <v>75.68000000000001</v>
+        <v>87.47</v>
       </c>
       <c r="K87" t="n">
-        <v>434.64</v>
+        <v>502.36</v>
       </c>
       <c r="L87" t="n">
-        <v>441.18</v>
+        <v>509.91</v>
       </c>
     </row>
     <row r="88">
@@ -3748,13 +3748,13 @@
         <v>16</v>
       </c>
       <c r="J88" t="n">
-        <v>-270.9</v>
+        <v>-312.47</v>
       </c>
       <c r="K88" t="n">
-        <v>118.73</v>
+        <v>136.95</v>
       </c>
       <c r="L88" t="n">
-        <v>295.77</v>
+        <v>341.16</v>
       </c>
     </row>
   </sheetData>

--- a/output/2024-10-08.xlsx
+++ b/output/2024-10-08.xlsx
@@ -625,34 +625,34 @@
         <v>1</v>
       </c>
       <c r="E14" t="n">
-        <v>3.44</v>
+        <v>3.18</v>
       </c>
       <c r="F14" t="n">
-        <v>8.720000000000001</v>
+        <v>6.29</v>
       </c>
       <c r="G14" t="n">
-        <v>59.9</v>
+        <v>52.1</v>
       </c>
       <c r="H14" t="n">
-        <v>98.59999999999999</v>
+        <v>15.2</v>
       </c>
       <c r="I14" t="n">
-        <v>16</v>
+        <v>22</v>
       </c>
       <c r="J14" t="n">
-        <v>-121.23</v>
+        <v>39.55</v>
       </c>
       <c r="K14" t="n">
-        <v>29.32</v>
+        <v>-28.4</v>
       </c>
       <c r="L14" t="n">
-        <v>124.73</v>
+        <v>48.69</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>07:32:58</t>
+          <t>07:33:44</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -667,34 +667,34 @@
         <v>2</v>
       </c>
       <c r="E15" t="n">
-        <v>2.98</v>
+        <v>3.64</v>
       </c>
       <c r="F15" t="n">
-        <v>7.7</v>
+        <v>8.93</v>
       </c>
       <c r="G15" t="n">
-        <v>34.8</v>
+        <v>53.9</v>
       </c>
       <c r="H15" t="n">
-        <v>100</v>
+        <v>41.2</v>
       </c>
       <c r="I15" t="n">
-        <v>16</v>
+        <v>22</v>
       </c>
       <c r="J15" t="n">
-        <v>-93.75</v>
+        <v>-34.4</v>
       </c>
       <c r="K15" t="n">
-        <v>75.83</v>
+        <v>35.26</v>
       </c>
       <c r="L15" t="n">
-        <v>120.58</v>
+        <v>49.26</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>07:34:07</t>
+          <t>07:35:08</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -709,34 +709,34 @@
         <v>3</v>
       </c>
       <c r="E16" t="n">
-        <v>3.38</v>
+        <v>4.33</v>
       </c>
       <c r="F16" t="n">
-        <v>6.49</v>
+        <v>10.81</v>
       </c>
       <c r="G16" t="n">
-        <v>36.4</v>
+        <v>36.8</v>
       </c>
       <c r="H16" t="n">
-        <v>100</v>
+        <v>92.5</v>
       </c>
       <c r="I16" t="n">
-        <v>16</v>
+        <v>26</v>
       </c>
       <c r="J16" t="n">
-        <v>5.23</v>
+        <v>-72.93000000000001</v>
       </c>
       <c r="K16" t="n">
-        <v>96.33</v>
+        <v>25.18</v>
       </c>
       <c r="L16" t="n">
-        <v>96.47</v>
+        <v>77.15000000000001</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>07:38:38</t>
+          <t>07:38:34</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -751,34 +751,34 @@
         <v>1</v>
       </c>
       <c r="E17" t="n">
-        <v>3.78</v>
+        <v>3.55</v>
       </c>
       <c r="F17" t="n">
-        <v>9.85</v>
+        <v>9.07</v>
       </c>
       <c r="G17" t="n">
-        <v>44.8</v>
+        <v>48</v>
       </c>
       <c r="H17" t="n">
-        <v>100</v>
+        <v>60.8</v>
       </c>
       <c r="I17" t="n">
-        <v>18</v>
+        <v>22</v>
       </c>
       <c r="J17" t="n">
-        <v>69.05</v>
+        <v>-44.09</v>
       </c>
       <c r="K17" t="n">
-        <v>3.01</v>
+        <v>-70.7</v>
       </c>
       <c r="L17" t="n">
-        <v>69.12</v>
+        <v>83.31999999999999</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>07:39:50</t>
+          <t>07:40:40</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -793,34 +793,34 @@
         <v>2</v>
       </c>
       <c r="E18" t="n">
-        <v>3.98</v>
+        <v>3.68</v>
       </c>
       <c r="F18" t="n">
-        <v>8.32</v>
+        <v>6.38</v>
       </c>
       <c r="G18" t="n">
-        <v>59.3</v>
+        <v>43.5</v>
       </c>
       <c r="H18" t="n">
-        <v>97.2</v>
+        <v>52.3</v>
       </c>
       <c r="I18" t="n">
-        <v>16</v>
+        <v>20</v>
       </c>
       <c r="J18" t="n">
-        <v>108.86</v>
+        <v>53.61</v>
       </c>
       <c r="K18" t="n">
-        <v>-77.22</v>
+        <v>32.79</v>
       </c>
       <c r="L18" t="n">
-        <v>133.47</v>
+        <v>62.84</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>07:41:07</t>
+          <t>07:42:06</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -835,34 +835,34 @@
         <v>3</v>
       </c>
       <c r="E19" t="n">
-        <v>3.71</v>
+        <v>3.44</v>
       </c>
       <c r="F19" t="n">
-        <v>10.33</v>
+        <v>8.69</v>
       </c>
       <c r="G19" t="n">
-        <v>39.8</v>
+        <v>42.3</v>
       </c>
       <c r="H19" t="n">
-        <v>100</v>
+        <v>80.09999999999999</v>
       </c>
       <c r="I19" t="n">
-        <v>16</v>
+        <v>19</v>
       </c>
       <c r="J19" t="n">
-        <v>-41.03</v>
+        <v>21.57</v>
       </c>
       <c r="K19" t="n">
-        <v>-156.02</v>
+        <v>-84.12</v>
       </c>
       <c r="L19" t="n">
-        <v>161.32</v>
+        <v>86.84</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>07:47:01</t>
+          <t>07:46:38</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -877,34 +877,34 @@
         <v>1</v>
       </c>
       <c r="E20" t="n">
-        <v>3.03</v>
+        <v>3.77</v>
       </c>
       <c r="F20" t="n">
-        <v>7.87</v>
+        <v>9.98</v>
       </c>
       <c r="G20" t="n">
-        <v>27.8</v>
+        <v>36.5</v>
       </c>
       <c r="H20" t="n">
-        <v>100</v>
+        <v>86.40000000000001</v>
       </c>
       <c r="I20" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="J20" t="n">
-        <v>17.56</v>
+        <v>-55.58</v>
       </c>
       <c r="K20" t="n">
-        <v>170.64</v>
+        <v>79.69</v>
       </c>
       <c r="L20" t="n">
-        <v>171.55</v>
+        <v>97.16</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>07:48:01</t>
+          <t>07:48:54</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -919,34 +919,34 @@
         <v>2</v>
       </c>
       <c r="E21" t="n">
-        <v>3.36</v>
+        <v>3.13</v>
       </c>
       <c r="F21" t="n">
-        <v>7.41</v>
+        <v>9.789999999999999</v>
       </c>
       <c r="G21" t="n">
-        <v>46.9</v>
+        <v>36.8</v>
       </c>
       <c r="H21" t="n">
-        <v>100</v>
+        <v>49.8</v>
       </c>
       <c r="I21" t="n">
-        <v>16</v>
+        <v>23</v>
       </c>
       <c r="J21" t="n">
-        <v>-36.39</v>
+        <v>-48.23</v>
       </c>
       <c r="K21" t="n">
-        <v>150.57</v>
+        <v>-94.13</v>
       </c>
       <c r="L21" t="n">
-        <v>154.91</v>
+        <v>105.76</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>07:49:33</t>
+          <t>07:50:52</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -961,34 +961,34 @@
         <v>3</v>
       </c>
       <c r="E22" t="n">
-        <v>3.26</v>
+        <v>3.33</v>
       </c>
       <c r="F22" t="n">
-        <v>7.34</v>
+        <v>6.97</v>
       </c>
       <c r="G22" t="n">
-        <v>39.5</v>
+        <v>39.6</v>
       </c>
       <c r="H22" t="n">
-        <v>100</v>
+        <v>48.9</v>
       </c>
       <c r="I22" t="n">
-        <v>16</v>
+        <v>20</v>
       </c>
       <c r="J22" t="n">
-        <v>-118.37</v>
+        <v>72.09</v>
       </c>
       <c r="K22" t="n">
-        <v>131.84</v>
+        <v>92.22</v>
       </c>
       <c r="L22" t="n">
-        <v>177.18</v>
+        <v>117.05</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>07:53:52</t>
+          <t>07:56:26</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -1003,34 +1003,34 @@
         <v>1</v>
       </c>
       <c r="E23" t="n">
-        <v>3.82</v>
+        <v>3.19</v>
       </c>
       <c r="F23" t="n">
-        <v>9.140000000000001</v>
+        <v>8.380000000000001</v>
       </c>
       <c r="G23" t="n">
-        <v>43.1</v>
+        <v>41</v>
       </c>
       <c r="H23" t="n">
-        <v>94.59999999999999</v>
+        <v>63.9</v>
       </c>
       <c r="I23" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="J23" t="n">
-        <v>206.6</v>
+        <v>-151.93</v>
       </c>
       <c r="K23" t="n">
-        <v>-17.82</v>
+        <v>12.75</v>
       </c>
       <c r="L23" t="n">
-        <v>207.37</v>
+        <v>152.47</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>07:54:58</t>
+          <t>07:58:15</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -1045,34 +1045,34 @@
         <v>2</v>
       </c>
       <c r="E24" t="n">
-        <v>3.86</v>
+        <v>3.32</v>
       </c>
       <c r="F24" t="n">
-        <v>8.859999999999999</v>
+        <v>6.97</v>
       </c>
       <c r="G24" t="n">
-        <v>42.4</v>
+        <v>57.8</v>
       </c>
       <c r="H24" t="n">
-        <v>100</v>
+        <v>54</v>
       </c>
       <c r="I24" t="n">
-        <v>17</v>
+        <v>24</v>
       </c>
       <c r="J24" t="n">
-        <v>60.76</v>
+        <v>-36.27</v>
       </c>
       <c r="K24" t="n">
-        <v>276.45</v>
+        <v>136.89</v>
       </c>
       <c r="L24" t="n">
-        <v>283.04</v>
+        <v>141.61</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>07:56:55</t>
+          <t>08:00:01</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -1087,34 +1087,34 @@
         <v>3</v>
       </c>
       <c r="E25" t="n">
-        <v>3.92</v>
+        <v>3.23</v>
       </c>
       <c r="F25" t="n">
-        <v>8.49</v>
+        <v>7.13</v>
       </c>
       <c r="G25" t="n">
-        <v>54</v>
+        <v>43.5</v>
       </c>
       <c r="H25" t="n">
-        <v>100</v>
+        <v>65.5</v>
       </c>
       <c r="I25" t="n">
-        <v>16</v>
+        <v>27</v>
       </c>
       <c r="J25" t="n">
-        <v>-239.54</v>
+        <v>-60.33</v>
       </c>
       <c r="K25" t="n">
-        <v>301.7</v>
+        <v>-129.7</v>
       </c>
       <c r="L25" t="n">
-        <v>385.24</v>
+        <v>143.04</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>08:00:45</t>
+          <t>08:04:45</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
@@ -1129,34 +1129,34 @@
         <v>1</v>
       </c>
       <c r="E26" t="n">
-        <v>3.79</v>
+        <v>3.52</v>
       </c>
       <c r="F26" t="n">
-        <v>6.34</v>
+        <v>10.81</v>
       </c>
       <c r="G26" t="n">
-        <v>50.7</v>
+        <v>44.1</v>
       </c>
       <c r="H26" t="n">
-        <v>99.09999999999999</v>
+        <v>61.7</v>
       </c>
       <c r="I26" t="n">
-        <v>16</v>
+        <v>27</v>
       </c>
       <c r="J26" t="n">
-        <v>-436.43</v>
+        <v>185</v>
       </c>
       <c r="K26" t="n">
-        <v>99.66</v>
+        <v>-81.88</v>
       </c>
       <c r="L26" t="n">
-        <v>447.67</v>
+        <v>202.31</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>08:01:32</t>
+          <t>08:06:25</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
@@ -1171,34 +1171,34 @@
         <v>2</v>
       </c>
       <c r="E27" t="n">
-        <v>3.65</v>
+        <v>3.93</v>
       </c>
       <c r="F27" t="n">
-        <v>8.32</v>
+        <v>9.970000000000001</v>
       </c>
       <c r="G27" t="n">
-        <v>52.4</v>
+        <v>41.2</v>
       </c>
       <c r="H27" t="n">
-        <v>100</v>
+        <v>65</v>
       </c>
       <c r="I27" t="n">
-        <v>16</v>
+        <v>22</v>
       </c>
       <c r="J27" t="n">
-        <v>322.12</v>
+        <v>230.47</v>
       </c>
       <c r="K27" t="n">
-        <v>-70.91</v>
+        <v>98.23</v>
       </c>
       <c r="L27" t="n">
-        <v>329.83</v>
+        <v>250.53</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>08:03:09</t>
+          <t>08:08:25</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
@@ -1213,34 +1213,34 @@
         <v>3</v>
       </c>
       <c r="E28" t="n">
-        <v>3.68</v>
+        <v>3.49</v>
       </c>
       <c r="F28" t="n">
-        <v>9.869999999999999</v>
+        <v>8.32</v>
       </c>
       <c r="G28" t="n">
-        <v>35.5</v>
+        <v>51</v>
       </c>
       <c r="H28" t="n">
-        <v>100</v>
+        <v>55.2</v>
       </c>
       <c r="I28" t="n">
-        <v>16</v>
+        <v>25</v>
       </c>
       <c r="J28" t="n">
-        <v>11.79</v>
+        <v>-186.59</v>
       </c>
       <c r="K28" t="n">
-        <v>344.91</v>
+        <v>-84.04000000000001</v>
       </c>
       <c r="L28" t="n">
-        <v>345.11</v>
+        <v>204.64</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>08:11:19</t>
+          <t>08:19:05</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
@@ -1255,34 +1255,34 @@
         <v>1</v>
       </c>
       <c r="E29" t="n">
-        <v>3.85</v>
+        <v>3.82</v>
       </c>
       <c r="F29" t="n">
-        <v>9.1</v>
+        <v>8.94</v>
       </c>
       <c r="G29" t="n">
-        <v>50.3</v>
+        <v>53.3</v>
       </c>
       <c r="H29" t="n">
-        <v>96</v>
+        <v>100</v>
       </c>
       <c r="I29" t="n">
-        <v>16</v>
+        <v>25</v>
       </c>
       <c r="J29" t="n">
-        <v>-45.37</v>
+        <v>-12.42</v>
       </c>
       <c r="K29" t="n">
-        <v>67.04000000000001</v>
+        <v>35.86</v>
       </c>
       <c r="L29" t="n">
-        <v>80.95</v>
+        <v>37.95</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>08:13:10</t>
+          <t>08:21:17</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
@@ -1297,34 +1297,34 @@
         <v>2</v>
       </c>
       <c r="E30" t="n">
-        <v>3.21</v>
+        <v>4.08</v>
       </c>
       <c r="F30" t="n">
-        <v>7.41</v>
+        <v>8.19</v>
       </c>
       <c r="G30" t="n">
-        <v>42.5</v>
+        <v>44.1</v>
       </c>
       <c r="H30" t="n">
-        <v>100</v>
+        <v>87.5</v>
       </c>
       <c r="I30" t="n">
-        <v>16</v>
+        <v>20</v>
       </c>
       <c r="J30" t="n">
-        <v>-20.37</v>
+        <v>58.32</v>
       </c>
       <c r="K30" t="n">
-        <v>-126.49</v>
+        <v>-18.27</v>
       </c>
       <c r="L30" t="n">
-        <v>128.12</v>
+        <v>61.12</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>08:15:27</t>
+          <t>08:22:21</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
@@ -1339,34 +1339,34 @@
         <v>3</v>
       </c>
       <c r="E31" t="n">
-        <v>3.67</v>
+        <v>4.18</v>
       </c>
       <c r="F31" t="n">
-        <v>8.93</v>
+        <v>10.81</v>
       </c>
       <c r="G31" t="n">
-        <v>41.5</v>
+        <v>35.7</v>
       </c>
       <c r="H31" t="n">
-        <v>98</v>
+        <v>97.8</v>
       </c>
       <c r="I31" t="n">
-        <v>16</v>
+        <v>19</v>
       </c>
       <c r="J31" t="n">
-        <v>-123.08</v>
+        <v>-48.46</v>
       </c>
       <c r="K31" t="n">
-        <v>-4.45</v>
+        <v>-20.37</v>
       </c>
       <c r="L31" t="n">
-        <v>123.16</v>
+        <v>52.56</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>08:18:23</t>
+          <t>08:27:16</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
@@ -1381,34 +1381,34 @@
         <v>1</v>
       </c>
       <c r="E32" t="n">
-        <v>3.53</v>
+        <v>3.49</v>
       </c>
       <c r="F32" t="n">
-        <v>5.22</v>
+        <v>8.24</v>
       </c>
       <c r="G32" t="n">
-        <v>61.1</v>
+        <v>44.5</v>
       </c>
       <c r="H32" t="n">
-        <v>100</v>
+        <v>79.3</v>
       </c>
       <c r="I32" t="n">
-        <v>16</v>
+        <v>26</v>
       </c>
       <c r="J32" t="n">
-        <v>13.13</v>
+        <v>63.18</v>
       </c>
       <c r="K32" t="n">
-        <v>82.69</v>
+        <v>57.34</v>
       </c>
       <c r="L32" t="n">
-        <v>83.73</v>
+        <v>85.31999999999999</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>08:19:54</t>
+          <t>08:29:02</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
@@ -1423,34 +1423,34 @@
         <v>2</v>
       </c>
       <c r="E33" t="n">
-        <v>3.91</v>
+        <v>3.73</v>
       </c>
       <c r="F33" t="n">
-        <v>7.85</v>
+        <v>9.66</v>
       </c>
       <c r="G33" t="n">
-        <v>50.8</v>
+        <v>47.9</v>
       </c>
       <c r="H33" t="n">
-        <v>92.40000000000001</v>
+        <v>33.2</v>
       </c>
       <c r="I33" t="n">
-        <v>16</v>
+        <v>20</v>
       </c>
       <c r="J33" t="n">
-        <v>14.94</v>
+        <v>81.16</v>
       </c>
       <c r="K33" t="n">
-        <v>-87.93000000000001</v>
+        <v>17.63</v>
       </c>
       <c r="L33" t="n">
-        <v>89.19</v>
+        <v>83.05</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>08:21:57</t>
+          <t>08:30:07</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
@@ -1465,34 +1465,34 @@
         <v>3</v>
       </c>
       <c r="E34" t="n">
-        <v>4.2</v>
+        <v>3.74</v>
       </c>
       <c r="F34" t="n">
-        <v>9.56</v>
+        <v>10.81</v>
       </c>
       <c r="G34" t="n">
-        <v>42.9</v>
+        <v>62.2</v>
       </c>
       <c r="H34" t="n">
-        <v>98.59999999999999</v>
+        <v>69.3</v>
       </c>
       <c r="I34" t="n">
-        <v>17</v>
+        <v>21</v>
       </c>
       <c r="J34" t="n">
-        <v>-98.22</v>
+        <v>-60.23</v>
       </c>
       <c r="K34" t="n">
-        <v>91.45</v>
+        <v>54.9</v>
       </c>
       <c r="L34" t="n">
-        <v>134.21</v>
+        <v>81.48999999999999</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>08:26:47</t>
+          <t>08:35:52</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
@@ -1507,34 +1507,34 @@
         <v>1</v>
       </c>
       <c r="E35" t="n">
-        <v>3.97</v>
+        <v>3.87</v>
       </c>
       <c r="F35" t="n">
-        <v>10.44</v>
+        <v>7.98</v>
       </c>
       <c r="G35" t="n">
-        <v>45.9</v>
+        <v>52.1</v>
       </c>
       <c r="H35" t="n">
-        <v>100</v>
+        <v>45.8</v>
       </c>
       <c r="I35" t="n">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="J35" t="n">
-        <v>195.74</v>
+        <v>81.59</v>
       </c>
       <c r="K35" t="n">
-        <v>32.05</v>
+        <v>-49.9</v>
       </c>
       <c r="L35" t="n">
-        <v>198.35</v>
+        <v>95.64</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>08:27:47</t>
+          <t>08:36:43</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
@@ -1549,34 +1549,34 @@
         <v>2</v>
       </c>
       <c r="E36" t="n">
-        <v>3.67</v>
+        <v>3.54</v>
       </c>
       <c r="F36" t="n">
-        <v>9.470000000000001</v>
+        <v>9.84</v>
       </c>
       <c r="G36" t="n">
-        <v>41.3</v>
+        <v>52.5</v>
       </c>
       <c r="H36" t="n">
-        <v>96.5</v>
+        <v>48.1</v>
       </c>
       <c r="I36" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="J36" t="n">
-        <v>109.14</v>
+        <v>-104.32</v>
       </c>
       <c r="K36" t="n">
-        <v>-96.7</v>
+        <v>-53.22</v>
       </c>
       <c r="L36" t="n">
-        <v>145.82</v>
+        <v>117.11</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>08:30:21</t>
+          <t>08:38:14</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
@@ -1591,34 +1591,34 @@
         <v>3</v>
       </c>
       <c r="E37" t="n">
-        <v>3.43</v>
+        <v>3.92</v>
       </c>
       <c r="F37" t="n">
-        <v>7.42</v>
+        <v>8.039999999999999</v>
       </c>
       <c r="G37" t="n">
-        <v>42.8</v>
+        <v>40</v>
       </c>
       <c r="H37" t="n">
-        <v>100</v>
+        <v>60.8</v>
       </c>
       <c r="I37" t="n">
-        <v>16</v>
+        <v>29</v>
       </c>
       <c r="J37" t="n">
-        <v>85.08</v>
+        <v>12.61</v>
       </c>
       <c r="K37" t="n">
-        <v>128.24</v>
+        <v>169.48</v>
       </c>
       <c r="L37" t="n">
-        <v>153.9</v>
+        <v>169.95</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>08:35:24</t>
+          <t>08:42:25</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
@@ -1633,34 +1633,34 @@
         <v>1</v>
       </c>
       <c r="E38" t="n">
-        <v>3.27</v>
+        <v>3.57</v>
       </c>
       <c r="F38" t="n">
-        <v>8.710000000000001</v>
+        <v>10.53</v>
       </c>
       <c r="G38" t="n">
-        <v>51.9</v>
+        <v>46.2</v>
       </c>
       <c r="H38" t="n">
-        <v>100</v>
+        <v>52.2</v>
       </c>
       <c r="I38" t="n">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="J38" t="n">
-        <v>-108.82</v>
+        <v>149.9</v>
       </c>
       <c r="K38" t="n">
-        <v>-45.25</v>
+        <v>39.96</v>
       </c>
       <c r="L38" t="n">
-        <v>117.85</v>
+        <v>155.14</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>08:37:13</t>
+          <t>08:44:16</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
@@ -1675,34 +1675,34 @@
         <v>2</v>
       </c>
       <c r="E39" t="n">
-        <v>3.9</v>
+        <v>3.93</v>
       </c>
       <c r="F39" t="n">
-        <v>10.12</v>
+        <v>10.81</v>
       </c>
       <c r="G39" t="n">
-        <v>57.6</v>
+        <v>32.2</v>
       </c>
       <c r="H39" t="n">
-        <v>100</v>
+        <v>63.6</v>
       </c>
       <c r="I39" t="n">
-        <v>16</v>
+        <v>19</v>
       </c>
       <c r="J39" t="n">
-        <v>81.98</v>
+        <v>3.88</v>
       </c>
       <c r="K39" t="n">
-        <v>216.77</v>
+        <v>-166.82</v>
       </c>
       <c r="L39" t="n">
-        <v>231.75</v>
+        <v>166.86</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>08:39:25</t>
+          <t>08:45:58</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
@@ -1717,34 +1717,34 @@
         <v>3</v>
       </c>
       <c r="E40" t="n">
-        <v>4.03</v>
+        <v>4.25</v>
       </c>
       <c r="F40" t="n">
-        <v>10.14</v>
+        <v>10.81</v>
       </c>
       <c r="G40" t="n">
-        <v>43.9</v>
+        <v>38.2</v>
       </c>
       <c r="H40" t="n">
-        <v>93.7</v>
+        <v>48.9</v>
       </c>
       <c r="I40" t="n">
-        <v>16</v>
+        <v>20</v>
       </c>
       <c r="J40" t="n">
-        <v>161.58</v>
+        <v>183.99</v>
       </c>
       <c r="K40" t="n">
-        <v>-170.31</v>
+        <v>155.15</v>
       </c>
       <c r="L40" t="n">
-        <v>234.76</v>
+        <v>240.67</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>08:44:21</t>
+          <t>08:49:18</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
@@ -1759,34 +1759,34 @@
         <v>1</v>
       </c>
       <c r="E41" t="n">
-        <v>3.93</v>
+        <v>3.67</v>
       </c>
       <c r="F41" t="n">
-        <v>9.68</v>
+        <v>7.55</v>
       </c>
       <c r="G41" t="n">
-        <v>53.5</v>
+        <v>34.7</v>
       </c>
       <c r="H41" t="n">
-        <v>99.2</v>
+        <v>65.7</v>
       </c>
       <c r="I41" t="n">
-        <v>16</v>
+        <v>22</v>
       </c>
       <c r="J41" t="n">
-        <v>198.62</v>
+        <v>-112.42</v>
       </c>
       <c r="K41" t="n">
-        <v>-184.66</v>
+        <v>216.74</v>
       </c>
       <c r="L41" t="n">
-        <v>271.2</v>
+        <v>244.16</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>08:45:35</t>
+          <t>08:50:59</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
@@ -1801,34 +1801,34 @@
         <v>2</v>
       </c>
       <c r="E42" t="n">
-        <v>4.19</v>
+        <v>3.87</v>
       </c>
       <c r="F42" t="n">
-        <v>9.1</v>
+        <v>10.74</v>
       </c>
       <c r="G42" t="n">
-        <v>42.2</v>
+        <v>50.4</v>
       </c>
       <c r="H42" t="n">
-        <v>100</v>
+        <v>89.7</v>
       </c>
       <c r="I42" t="n">
-        <v>16</v>
+        <v>26</v>
       </c>
       <c r="J42" t="n">
-        <v>70.28</v>
+        <v>135.84</v>
       </c>
       <c r="K42" t="n">
-        <v>-340.88</v>
+        <v>136.61</v>
       </c>
       <c r="L42" t="n">
-        <v>348.05</v>
+        <v>192.65</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>08:46:41</t>
+          <t>08:53:18</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
@@ -1843,34 +1843,34 @@
         <v>3</v>
       </c>
       <c r="E43" t="n">
-        <v>4.04</v>
+        <v>4.58</v>
       </c>
       <c r="F43" t="n">
-        <v>10.81</v>
+        <v>10.55</v>
       </c>
       <c r="G43" t="n">
-        <v>43.9</v>
+        <v>39.7</v>
       </c>
       <c r="H43" t="n">
-        <v>98.90000000000001</v>
+        <v>48.8</v>
       </c>
       <c r="I43" t="n">
-        <v>17</v>
+        <v>23</v>
       </c>
       <c r="J43" t="n">
-        <v>293.62</v>
+        <v>-102.43</v>
       </c>
       <c r="K43" t="n">
-        <v>-24.92</v>
+        <v>68.03</v>
       </c>
       <c r="L43" t="n">
-        <v>294.68</v>
+        <v>122.97</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>08:55:03</t>
+          <t>09:02:14</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
@@ -1885,34 +1885,34 @@
         <v>1</v>
       </c>
       <c r="E44" t="n">
-        <v>3.66</v>
+        <v>3.57</v>
       </c>
       <c r="F44" t="n">
-        <v>7.35</v>
+        <v>6.94</v>
       </c>
       <c r="G44" t="n">
-        <v>35.1</v>
+        <v>47.3</v>
       </c>
       <c r="H44" t="n">
-        <v>96.8</v>
+        <v>95.90000000000001</v>
       </c>
       <c r="I44" t="n">
-        <v>16</v>
+        <v>20</v>
       </c>
       <c r="J44" t="n">
-        <v>12.26</v>
+        <v>-13.96</v>
       </c>
       <c r="K44" t="n">
-        <v>84.62</v>
+        <v>56.67</v>
       </c>
       <c r="L44" t="n">
-        <v>85.5</v>
+        <v>58.36</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>08:56:30</t>
+          <t>09:04:37</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
@@ -1927,34 +1927,34 @@
         <v>2</v>
       </c>
       <c r="E45" t="n">
-        <v>3.7</v>
+        <v>3.96</v>
       </c>
       <c r="F45" t="n">
-        <v>8.449999999999999</v>
+        <v>10.81</v>
       </c>
       <c r="G45" t="n">
-        <v>30.6</v>
+        <v>29.4</v>
       </c>
       <c r="H45" t="n">
-        <v>100</v>
+        <v>63.4</v>
       </c>
       <c r="I45" t="n">
-        <v>18</v>
+        <v>23</v>
       </c>
       <c r="J45" t="n">
-        <v>-70.87</v>
+        <v>31.21</v>
       </c>
       <c r="K45" t="n">
-        <v>-49.4</v>
+        <v>48.91</v>
       </c>
       <c r="L45" t="n">
-        <v>86.39</v>
+        <v>58.02</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>08:57:58</t>
+          <t>09:05:59</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
@@ -1969,34 +1969,34 @@
         <v>3</v>
       </c>
       <c r="E46" t="n">
-        <v>4.3</v>
+        <v>4.54</v>
       </c>
       <c r="F46" t="n">
-        <v>10.81</v>
+        <v>10.07</v>
       </c>
       <c r="G46" t="n">
-        <v>37.5</v>
+        <v>52.1</v>
       </c>
       <c r="H46" t="n">
-        <v>100</v>
+        <v>75.40000000000001</v>
       </c>
       <c r="I46" t="n">
-        <v>17</v>
+        <v>20</v>
       </c>
       <c r="J46" t="n">
-        <v>69.7</v>
+        <v>-36.21</v>
       </c>
       <c r="K46" t="n">
-        <v>111.48</v>
+        <v>100.54</v>
       </c>
       <c r="L46" t="n">
-        <v>131.47</v>
+        <v>106.86</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>09:03:05</t>
+          <t>09:10:10</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
@@ -2011,34 +2011,34 @@
         <v>1</v>
       </c>
       <c r="E47" t="n">
-        <v>4.29</v>
+        <v>3.93</v>
       </c>
       <c r="F47" t="n">
-        <v>9.59</v>
+        <v>6.77</v>
       </c>
       <c r="G47" t="n">
-        <v>50.5</v>
+        <v>37.4</v>
       </c>
       <c r="H47" t="n">
-        <v>99.8</v>
+        <v>63.6</v>
       </c>
       <c r="I47" t="n">
-        <v>16</v>
+        <v>20</v>
       </c>
       <c r="J47" t="n">
-        <v>-85.56999999999999</v>
+        <v>-11.28</v>
       </c>
       <c r="K47" t="n">
-        <v>-75.78</v>
+        <v>75.94</v>
       </c>
       <c r="L47" t="n">
-        <v>114.31</v>
+        <v>76.78</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>09:05:01</t>
+          <t>09:11:15</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
@@ -2053,34 +2053,34 @@
         <v>2</v>
       </c>
       <c r="E48" t="n">
-        <v>4.08</v>
+        <v>3.81</v>
       </c>
       <c r="F48" t="n">
-        <v>8.960000000000001</v>
+        <v>8.27</v>
       </c>
       <c r="G48" t="n">
-        <v>34.9</v>
+        <v>49.2</v>
       </c>
       <c r="H48" t="n">
-        <v>100</v>
+        <v>65.09999999999999</v>
       </c>
       <c r="I48" t="n">
-        <v>16</v>
+        <v>29</v>
       </c>
       <c r="J48" t="n">
-        <v>-115.01</v>
+        <v>-57.8</v>
       </c>
       <c r="K48" t="n">
-        <v>-6.35</v>
+        <v>-57.94</v>
       </c>
       <c r="L48" t="n">
-        <v>115.18</v>
+        <v>81.84</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>09:07:36</t>
+          <t>09:13:07</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
@@ -2095,34 +2095,34 @@
         <v>3</v>
       </c>
       <c r="E49" t="n">
-        <v>3.75</v>
+        <v>3.44</v>
       </c>
       <c r="F49" t="n">
-        <v>9.26</v>
+        <v>7.67</v>
       </c>
       <c r="G49" t="n">
-        <v>47.2</v>
+        <v>50.7</v>
       </c>
       <c r="H49" t="n">
-        <v>100</v>
+        <v>65.3</v>
       </c>
       <c r="I49" t="n">
-        <v>16</v>
+        <v>26</v>
       </c>
       <c r="J49" t="n">
-        <v>-48.7</v>
+        <v>21.37</v>
       </c>
       <c r="K49" t="n">
-        <v>-105.68</v>
+        <v>95.2</v>
       </c>
       <c r="L49" t="n">
-        <v>116.36</v>
+        <v>97.56999999999999</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>09:12:19</t>
+          <t>09:18:44</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
@@ -2137,34 +2137,34 @@
         <v>1</v>
       </c>
       <c r="E50" t="n">
-        <v>3.99</v>
+        <v>4.05</v>
       </c>
       <c r="F50" t="n">
-        <v>7.13</v>
+        <v>9.65</v>
       </c>
       <c r="G50" t="n">
-        <v>40</v>
+        <v>48.6</v>
       </c>
       <c r="H50" t="n">
-        <v>94.5</v>
+        <v>67.5</v>
       </c>
       <c r="I50" t="n">
-        <v>16</v>
+        <v>27</v>
       </c>
       <c r="J50" t="n">
-        <v>59.13</v>
+        <v>147.9</v>
       </c>
       <c r="K50" t="n">
-        <v>108.87</v>
+        <v>30.28</v>
       </c>
       <c r="L50" t="n">
-        <v>123.89</v>
+        <v>150.96</v>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>09:14:42</t>
+          <t>09:20:12</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
@@ -2179,34 +2179,34 @@
         <v>2</v>
       </c>
       <c r="E51" t="n">
-        <v>3.98</v>
+        <v>3.83</v>
       </c>
       <c r="F51" t="n">
-        <v>9.06</v>
+        <v>9.6</v>
       </c>
       <c r="G51" t="n">
-        <v>46.4</v>
+        <v>10</v>
       </c>
       <c r="H51" t="n">
-        <v>96</v>
+        <v>44.1</v>
       </c>
       <c r="I51" t="n">
-        <v>16</v>
+        <v>21</v>
       </c>
       <c r="J51" t="n">
-        <v>-160.32</v>
+        <v>-9.68</v>
       </c>
       <c r="K51" t="n">
-        <v>2.17</v>
+        <v>115.53</v>
       </c>
       <c r="L51" t="n">
-        <v>160.33</v>
+        <v>115.93</v>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>09:15:36</t>
+          <t>09:21:55</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
@@ -2221,34 +2221,34 @@
         <v>3</v>
       </c>
       <c r="E52" t="n">
-        <v>4.01</v>
+        <v>4.38</v>
       </c>
       <c r="F52" t="n">
-        <v>10.46</v>
+        <v>10.34</v>
       </c>
       <c r="G52" t="n">
-        <v>50.2</v>
+        <v>31.7</v>
       </c>
       <c r="H52" t="n">
-        <v>97.09999999999999</v>
+        <v>18.8</v>
       </c>
       <c r="I52" t="n">
-        <v>16</v>
+        <v>24</v>
       </c>
       <c r="J52" t="n">
-        <v>-81.86</v>
+        <v>131.7</v>
       </c>
       <c r="K52" t="n">
-        <v>-150.68</v>
+        <v>27.17</v>
       </c>
       <c r="L52" t="n">
-        <v>171.48</v>
+        <v>134.47</v>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>09:21:48</t>
+          <t>09:25:20</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
@@ -2263,34 +2263,34 @@
         <v>1</v>
       </c>
       <c r="E53" t="n">
-        <v>3.86</v>
+        <v>4.34</v>
       </c>
       <c r="F53" t="n">
-        <v>9.970000000000001</v>
+        <v>10.81</v>
       </c>
       <c r="G53" t="n">
-        <v>35.4</v>
+        <v>40.2</v>
       </c>
       <c r="H53" t="n">
-        <v>100</v>
+        <v>73.2</v>
       </c>
       <c r="I53" t="n">
-        <v>16</v>
+        <v>23</v>
       </c>
       <c r="J53" t="n">
-        <v>44.35</v>
+        <v>191.04</v>
       </c>
       <c r="K53" t="n">
-        <v>-290.3</v>
+        <v>60.84</v>
       </c>
       <c r="L53" t="n">
-        <v>293.67</v>
+        <v>200.49</v>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>09:22:50</t>
+          <t>09:27:36</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
@@ -2305,34 +2305,34 @@
         <v>2</v>
       </c>
       <c r="E54" t="n">
-        <v>3.95</v>
+        <v>3.99</v>
       </c>
       <c r="F54" t="n">
         <v>10.81</v>
       </c>
       <c r="G54" t="n">
-        <v>48.6</v>
+        <v>39.9</v>
       </c>
       <c r="H54" t="n">
-        <v>96.5</v>
+        <v>46.1</v>
       </c>
       <c r="I54" t="n">
-        <v>16</v>
+        <v>29</v>
       </c>
       <c r="J54" t="n">
-        <v>-227.02</v>
+        <v>143.44</v>
       </c>
       <c r="K54" t="n">
-        <v>-57</v>
+        <v>-82.95</v>
       </c>
       <c r="L54" t="n">
-        <v>234.06</v>
+        <v>165.7</v>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>09:24:09</t>
+          <t>09:28:22</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
@@ -2347,34 +2347,34 @@
         <v>3</v>
       </c>
       <c r="E55" t="n">
-        <v>4.52</v>
+        <v>4.03</v>
       </c>
       <c r="F55" t="n">
         <v>10.81</v>
       </c>
       <c r="G55" t="n">
-        <v>33.8</v>
+        <v>47.3</v>
       </c>
       <c r="H55" t="n">
-        <v>98.2</v>
+        <v>30.8</v>
       </c>
       <c r="I55" t="n">
-        <v>16</v>
+        <v>22</v>
       </c>
       <c r="J55" t="n">
-        <v>268.57</v>
+        <v>157.82</v>
       </c>
       <c r="K55" t="n">
-        <v>77.66</v>
+        <v>169.88</v>
       </c>
       <c r="L55" t="n">
-        <v>279.58</v>
+        <v>231.87</v>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>09:29:44</t>
+          <t>09:32:24</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
@@ -2389,34 +2389,34 @@
         <v>1</v>
       </c>
       <c r="E56" t="n">
-        <v>3.56</v>
+        <v>4.35</v>
       </c>
       <c r="F56" t="n">
-        <v>6.36</v>
+        <v>9.69</v>
       </c>
       <c r="G56" t="n">
-        <v>44.8</v>
+        <v>34.7</v>
       </c>
       <c r="H56" t="n">
-        <v>96.7</v>
+        <v>57.8</v>
       </c>
       <c r="I56" t="n">
         <v>17</v>
       </c>
       <c r="J56" t="n">
-        <v>269.23</v>
+        <v>265.06</v>
       </c>
       <c r="K56" t="n">
-        <v>-48.69</v>
+        <v>-49.16</v>
       </c>
       <c r="L56" t="n">
-        <v>273.6</v>
+        <v>269.58</v>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>09:32:37</t>
+          <t>09:33:48</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
@@ -2431,34 +2431,34 @@
         <v>2</v>
       </c>
       <c r="E57" t="n">
-        <v>4.1</v>
+        <v>4.07</v>
       </c>
       <c r="F57" t="n">
-        <v>10.15</v>
+        <v>10.81</v>
       </c>
       <c r="G57" t="n">
-        <v>42.4</v>
+        <v>45.9</v>
       </c>
       <c r="H57" t="n">
-        <v>99</v>
+        <v>43.2</v>
       </c>
       <c r="I57" t="n">
-        <v>17</v>
+        <v>29</v>
       </c>
       <c r="J57" t="n">
-        <v>220.09</v>
+        <v>229.32</v>
       </c>
       <c r="K57" t="n">
-        <v>311.07</v>
+        <v>167.02</v>
       </c>
       <c r="L57" t="n">
-        <v>381.05</v>
+        <v>283.7</v>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>09:34:32</t>
+          <t>09:36:02</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
@@ -2473,34 +2473,34 @@
         <v>3</v>
       </c>
       <c r="E58" t="n">
-        <v>3.52</v>
+        <v>4.28</v>
       </c>
       <c r="F58" t="n">
-        <v>7.12</v>
+        <v>8</v>
       </c>
       <c r="G58" t="n">
-        <v>34.2</v>
+        <v>39.6</v>
       </c>
       <c r="H58" t="n">
-        <v>100</v>
+        <v>65.40000000000001</v>
       </c>
       <c r="I58" t="n">
-        <v>18</v>
+        <v>27</v>
       </c>
       <c r="J58" t="n">
-        <v>287.78</v>
+        <v>114.89</v>
       </c>
       <c r="K58" t="n">
-        <v>35.27</v>
+        <v>224.16</v>
       </c>
       <c r="L58" t="n">
-        <v>289.93</v>
+        <v>251.89</v>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>09:42:21</t>
+          <t>09:45:42</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
@@ -2515,34 +2515,34 @@
         <v>1</v>
       </c>
       <c r="E59" t="n">
-        <v>4.11</v>
+        <v>4.14</v>
       </c>
       <c r="F59" t="n">
-        <v>10.81</v>
+        <v>9.82</v>
       </c>
       <c r="G59" t="n">
-        <v>41</v>
+        <v>32.2</v>
       </c>
       <c r="H59" t="n">
-        <v>98.40000000000001</v>
+        <v>77.5</v>
       </c>
       <c r="I59" t="n">
-        <v>18</v>
+        <v>28</v>
       </c>
       <c r="J59" t="n">
-        <v>-8.300000000000001</v>
+        <v>13.84</v>
       </c>
       <c r="K59" t="n">
-        <v>-62.37</v>
+        <v>-70.22</v>
       </c>
       <c r="L59" t="n">
-        <v>62.92</v>
+        <v>71.56999999999999</v>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>09:43:35</t>
+          <t>09:46:30</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
@@ -2557,34 +2557,34 @@
         <v>2</v>
       </c>
       <c r="E60" t="n">
-        <v>4.25</v>
+        <v>4.19</v>
       </c>
       <c r="F60" t="n">
         <v>10.81</v>
       </c>
       <c r="G60" t="n">
-        <v>59.6</v>
+        <v>32.5</v>
       </c>
       <c r="H60" t="n">
-        <v>98.90000000000001</v>
+        <v>64.8</v>
       </c>
       <c r="I60" t="n">
-        <v>16</v>
+        <v>23</v>
       </c>
       <c r="J60" t="n">
-        <v>101.57</v>
+        <v>41.46</v>
       </c>
       <c r="K60" t="n">
-        <v>-39</v>
+        <v>-62.15</v>
       </c>
       <c r="L60" t="n">
-        <v>108.8</v>
+        <v>74.70999999999999</v>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>09:44:40</t>
+          <t>09:48:07</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
@@ -2599,34 +2599,34 @@
         <v>3</v>
       </c>
       <c r="E61" t="n">
-        <v>3.96</v>
+        <v>3.86</v>
       </c>
       <c r="F61" t="n">
         <v>10.81</v>
       </c>
       <c r="G61" t="n">
-        <v>53.7</v>
+        <v>26.2</v>
       </c>
       <c r="H61" t="n">
-        <v>92.8</v>
+        <v>52.7</v>
       </c>
       <c r="I61" t="n">
-        <v>16</v>
+        <v>26</v>
       </c>
       <c r="J61" t="n">
-        <v>-76.20999999999999</v>
+        <v>55.15</v>
       </c>
       <c r="K61" t="n">
-        <v>-42</v>
+        <v>14.38</v>
       </c>
       <c r="L61" t="n">
-        <v>87.02</v>
+        <v>56.99</v>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>09:49:27</t>
+          <t>09:53:55</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
@@ -2641,34 +2641,34 @@
         <v>1</v>
       </c>
       <c r="E62" t="n">
-        <v>4.09</v>
+        <v>3.81</v>
       </c>
       <c r="F62" t="n">
         <v>10.81</v>
       </c>
       <c r="G62" t="n">
-        <v>43.7</v>
+        <v>30.1</v>
       </c>
       <c r="H62" t="n">
-        <v>100</v>
+        <v>46.1</v>
       </c>
       <c r="I62" t="n">
-        <v>16</v>
+        <v>20</v>
       </c>
       <c r="J62" t="n">
-        <v>175.41</v>
+        <v>55</v>
       </c>
       <c r="K62" t="n">
-        <v>-73.45999999999999</v>
+        <v>81.22</v>
       </c>
       <c r="L62" t="n">
-        <v>190.17</v>
+        <v>98.09</v>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>09:50:53</t>
+          <t>09:55:52</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
@@ -2683,34 +2683,34 @@
         <v>2</v>
       </c>
       <c r="E63" t="n">
-        <v>3.95</v>
+        <v>3.83</v>
       </c>
       <c r="F63" t="n">
-        <v>8.6</v>
+        <v>9.289999999999999</v>
       </c>
       <c r="G63" t="n">
-        <v>48.9</v>
+        <v>51.5</v>
       </c>
       <c r="H63" t="n">
-        <v>100</v>
+        <v>57.3</v>
       </c>
       <c r="I63" t="n">
-        <v>16</v>
+        <v>26</v>
       </c>
       <c r="J63" t="n">
-        <v>37.95</v>
+        <v>-22.71</v>
       </c>
       <c r="K63" t="n">
-        <v>-92.92</v>
+        <v>-61.66</v>
       </c>
       <c r="L63" t="n">
-        <v>100.37</v>
+        <v>65.70999999999999</v>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>09:53:19</t>
+          <t>09:57:35</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
@@ -2725,34 +2725,34 @@
         <v>3</v>
       </c>
       <c r="E64" t="n">
-        <v>4.1</v>
+        <v>3.9</v>
       </c>
       <c r="F64" t="n">
-        <v>10.81</v>
+        <v>9.359999999999999</v>
       </c>
       <c r="G64" t="n">
-        <v>36.7</v>
+        <v>45</v>
       </c>
       <c r="H64" t="n">
-        <v>100</v>
+        <v>41.5</v>
       </c>
       <c r="I64" t="n">
-        <v>16</v>
+        <v>24</v>
       </c>
       <c r="J64" t="n">
-        <v>-140.19</v>
+        <v>-42.42</v>
       </c>
       <c r="K64" t="n">
-        <v>-20.65</v>
+        <v>-51.67</v>
       </c>
       <c r="L64" t="n">
-        <v>141.71</v>
+        <v>66.86</v>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>09:58:43</t>
+          <t>10:03:34</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
@@ -2767,34 +2767,34 @@
         <v>1</v>
       </c>
       <c r="E65" t="n">
-        <v>3.85</v>
+        <v>4.14</v>
       </c>
       <c r="F65" t="n">
         <v>10.81</v>
       </c>
       <c r="G65" t="n">
-        <v>48.2</v>
+        <v>41.6</v>
       </c>
       <c r="H65" t="n">
-        <v>96.7</v>
+        <v>60.1</v>
       </c>
       <c r="I65" t="n">
-        <v>16</v>
+        <v>29</v>
       </c>
       <c r="J65" t="n">
-        <v>42.14</v>
+        <v>-61.8</v>
       </c>
       <c r="K65" t="n">
-        <v>201.38</v>
+        <v>74.7</v>
       </c>
       <c r="L65" t="n">
-        <v>205.74</v>
+        <v>96.95</v>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>09:59:57</t>
+          <t>10:05:32</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
@@ -2809,34 +2809,34 @@
         <v>2</v>
       </c>
       <c r="E66" t="n">
-        <v>4.39</v>
+        <v>3.31</v>
       </c>
       <c r="F66" t="n">
-        <v>10.81</v>
+        <v>9.33</v>
       </c>
       <c r="G66" t="n">
-        <v>49.2</v>
+        <v>41.8</v>
       </c>
       <c r="H66" t="n">
-        <v>100</v>
+        <v>75.8</v>
       </c>
       <c r="I66" t="n">
-        <v>16</v>
+        <v>19</v>
       </c>
       <c r="J66" t="n">
-        <v>121.73</v>
+        <v>103.38</v>
       </c>
       <c r="K66" t="n">
-        <v>115.92</v>
+        <v>0.25</v>
       </c>
       <c r="L66" t="n">
-        <v>168.09</v>
+        <v>103.38</v>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>10:01:10</t>
+          <t>10:07:41</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
@@ -2851,34 +2851,34 @@
         <v>3</v>
       </c>
       <c r="E67" t="n">
-        <v>4.17</v>
+        <v>4.66</v>
       </c>
       <c r="F67" t="n">
-        <v>10.81</v>
+        <v>10.51</v>
       </c>
       <c r="G67" t="n">
-        <v>37.5</v>
+        <v>42.9</v>
       </c>
       <c r="H67" t="n">
-        <v>91.7</v>
+        <v>72.3</v>
       </c>
       <c r="I67" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="J67" t="n">
-        <v>-5.94</v>
+        <v>125.02</v>
       </c>
       <c r="K67" t="n">
-        <v>186.11</v>
+        <v>73.79000000000001</v>
       </c>
       <c r="L67" t="n">
-        <v>186.21</v>
+        <v>145.17</v>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>10:07:14</t>
+          <t>10:11:56</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
@@ -2893,34 +2893,34 @@
         <v>1</v>
       </c>
       <c r="E68" t="n">
-        <v>5.18</v>
+        <v>4.21</v>
       </c>
       <c r="F68" t="n">
         <v>10.81</v>
       </c>
       <c r="G68" t="n">
-        <v>42.7</v>
+        <v>41</v>
       </c>
       <c r="H68" t="n">
-        <v>100</v>
+        <v>64.40000000000001</v>
       </c>
       <c r="I68" t="n">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="J68" t="n">
-        <v>217.17</v>
+        <v>3.52</v>
       </c>
       <c r="K68" t="n">
-        <v>-34.8</v>
+        <v>236.48</v>
       </c>
       <c r="L68" t="n">
-        <v>219.94</v>
+        <v>236.5</v>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>10:09:33</t>
+          <t>10:12:58</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
@@ -2935,34 +2935,34 @@
         <v>2</v>
       </c>
       <c r="E69" t="n">
-        <v>4.24</v>
+        <v>4.37</v>
       </c>
       <c r="F69" t="n">
         <v>10.81</v>
       </c>
       <c r="G69" t="n">
-        <v>66.7</v>
+        <v>49.4</v>
       </c>
       <c r="H69" t="n">
-        <v>97.7</v>
+        <v>40.6</v>
       </c>
       <c r="I69" t="n">
-        <v>18</v>
+        <v>22</v>
       </c>
       <c r="J69" t="n">
-        <v>221.55</v>
+        <v>-87.66</v>
       </c>
       <c r="K69" t="n">
-        <v>-68.55</v>
+        <v>163.08</v>
       </c>
       <c r="L69" t="n">
-        <v>231.92</v>
+        <v>185.15</v>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>10:11:22</t>
+          <t>10:14:43</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
@@ -2977,34 +2977,34 @@
         <v>3</v>
       </c>
       <c r="E70" t="n">
-        <v>4.29</v>
+        <v>4.27</v>
       </c>
       <c r="F70" t="n">
-        <v>8.289999999999999</v>
+        <v>9.02</v>
       </c>
       <c r="G70" t="n">
-        <v>38.2</v>
+        <v>54.9</v>
       </c>
       <c r="H70" t="n">
-        <v>97.09999999999999</v>
+        <v>64</v>
       </c>
       <c r="I70" t="n">
-        <v>16</v>
+        <v>29</v>
       </c>
       <c r="J70" t="n">
-        <v>-195.91</v>
+        <v>97.68000000000001</v>
       </c>
       <c r="K70" t="n">
-        <v>85.31999999999999</v>
+        <v>147.43</v>
       </c>
       <c r="L70" t="n">
-        <v>213.68</v>
+        <v>176.85</v>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>10:14:27</t>
+          <t>10:19:50</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
@@ -3019,34 +3019,34 @@
         <v>1</v>
       </c>
       <c r="E71" t="n">
-        <v>4.66</v>
+        <v>4.65</v>
       </c>
       <c r="F71" t="n">
-        <v>10.33</v>
+        <v>9.35</v>
       </c>
       <c r="G71" t="n">
-        <v>32.8</v>
+        <v>43.2</v>
       </c>
       <c r="H71" t="n">
-        <v>98.5</v>
+        <v>72.3</v>
       </c>
       <c r="I71" t="n">
-        <v>16</v>
+        <v>29</v>
       </c>
       <c r="J71" t="n">
-        <v>463.11</v>
+        <v>-194.57</v>
       </c>
       <c r="K71" t="n">
-        <v>-70.70999999999999</v>
+        <v>202.98</v>
       </c>
       <c r="L71" t="n">
-        <v>468.48</v>
+        <v>281.17</v>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>10:16:22</t>
+          <t>10:21:40</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
@@ -3061,34 +3061,34 @@
         <v>2</v>
       </c>
       <c r="E72" t="n">
-        <v>4.27</v>
+        <v>3.25</v>
       </c>
       <c r="F72" t="n">
-        <v>10.13</v>
+        <v>8.710000000000001</v>
       </c>
       <c r="G72" t="n">
-        <v>38.8</v>
+        <v>42.6</v>
       </c>
       <c r="H72" t="n">
-        <v>100</v>
+        <v>69</v>
       </c>
       <c r="I72" t="n">
-        <v>17</v>
+        <v>25</v>
       </c>
       <c r="J72" t="n">
-        <v>-375.15</v>
+        <v>178.31</v>
       </c>
       <c r="K72" t="n">
-        <v>103.15</v>
+        <v>-17.96</v>
       </c>
       <c r="L72" t="n">
-        <v>389.07</v>
+        <v>179.21</v>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>10:18:14</t>
+          <t>10:23:11</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
@@ -3103,34 +3103,34 @@
         <v>3</v>
       </c>
       <c r="E73" t="n">
-        <v>4.58</v>
+        <v>4.55</v>
       </c>
       <c r="F73" t="n">
         <v>10.81</v>
       </c>
       <c r="G73" t="n">
-        <v>35.3</v>
+        <v>31.8</v>
       </c>
       <c r="H73" t="n">
-        <v>100</v>
+        <v>72.90000000000001</v>
       </c>
       <c r="I73" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="J73" t="n">
-        <v>477.46</v>
+        <v>297.07</v>
       </c>
       <c r="K73" t="n">
-        <v>210</v>
+        <v>-109.82</v>
       </c>
       <c r="L73" t="n">
-        <v>521.6</v>
+        <v>316.72</v>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>10:31:33</t>
+          <t>10:33:51</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
@@ -3145,34 +3145,34 @@
         <v>1</v>
       </c>
       <c r="E74" t="n">
-        <v>4.79</v>
+        <v>4.16</v>
       </c>
       <c r="F74" t="n">
-        <v>10.81</v>
+        <v>9.49</v>
       </c>
       <c r="G74" t="n">
-        <v>44.4</v>
+        <v>53.7</v>
       </c>
       <c r="H74" t="n">
-        <v>96.3</v>
+        <v>100</v>
       </c>
       <c r="I74" t="n">
-        <v>18</v>
+        <v>21</v>
       </c>
       <c r="J74" t="n">
-        <v>11.28</v>
+        <v>63.25</v>
       </c>
       <c r="K74" t="n">
-        <v>-70.17</v>
+        <v>-0.88</v>
       </c>
       <c r="L74" t="n">
-        <v>71.08</v>
+        <v>63.26</v>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>10:33:37</t>
+          <t>10:35:11</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
@@ -3187,34 +3187,34 @@
         <v>2</v>
       </c>
       <c r="E75" t="n">
-        <v>4.15</v>
+        <v>4.24</v>
       </c>
       <c r="F75" t="n">
-        <v>10.6</v>
+        <v>10.81</v>
       </c>
       <c r="G75" t="n">
-        <v>39.3</v>
+        <v>32.4</v>
       </c>
       <c r="H75" t="n">
-        <v>92.40000000000001</v>
+        <v>78.7</v>
       </c>
       <c r="I75" t="n">
-        <v>18</v>
+        <v>26</v>
       </c>
       <c r="J75" t="n">
-        <v>-75.22</v>
+        <v>54.61</v>
       </c>
       <c r="K75" t="n">
-        <v>-35.84</v>
+        <v>-53.64</v>
       </c>
       <c r="L75" t="n">
-        <v>83.31999999999999</v>
+        <v>76.55</v>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>10:35:00</t>
+          <t>10:37:11</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
@@ -3229,34 +3229,34 @@
         <v>3</v>
       </c>
       <c r="E76" t="n">
-        <v>4.26</v>
+        <v>4.36</v>
       </c>
       <c r="F76" t="n">
-        <v>10.81</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="G76" t="n">
-        <v>53.8</v>
+        <v>41.9</v>
       </c>
       <c r="H76" t="n">
-        <v>95</v>
+        <v>43.5</v>
       </c>
       <c r="I76" t="n">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="J76" t="n">
-        <v>-62.44</v>
+        <v>27.88</v>
       </c>
       <c r="K76" t="n">
-        <v>63.12</v>
+        <v>-65.79000000000001</v>
       </c>
       <c r="L76" t="n">
-        <v>88.78</v>
+        <v>71.45999999999999</v>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>10:38:19</t>
+          <t>10:42:39</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
@@ -3271,34 +3271,34 @@
         <v>1</v>
       </c>
       <c r="E77" t="n">
-        <v>4.18</v>
+        <v>4.5</v>
       </c>
       <c r="F77" t="n">
         <v>10.81</v>
       </c>
       <c r="G77" t="n">
-        <v>45.6</v>
+        <v>64.3</v>
       </c>
       <c r="H77" t="n">
-        <v>99</v>
+        <v>61.9</v>
       </c>
       <c r="I77" t="n">
-        <v>16</v>
+        <v>24</v>
       </c>
       <c r="J77" t="n">
-        <v>-20.35</v>
+        <v>88.98</v>
       </c>
       <c r="K77" t="n">
-        <v>171.88</v>
+        <v>15.81</v>
       </c>
       <c r="L77" t="n">
-        <v>173.08</v>
+        <v>90.37</v>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>10:40:15</t>
+          <t>10:44:21</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
@@ -3313,34 +3313,34 @@
         <v>2</v>
       </c>
       <c r="E78" t="n">
-        <v>4.55</v>
+        <v>4.6</v>
       </c>
       <c r="F78" t="n">
-        <v>9.789999999999999</v>
+        <v>10.81</v>
       </c>
       <c r="G78" t="n">
-        <v>34.9</v>
+        <v>27.1</v>
       </c>
       <c r="H78" t="n">
-        <v>100</v>
+        <v>86.59999999999999</v>
       </c>
       <c r="I78" t="n">
-        <v>16</v>
+        <v>21</v>
       </c>
       <c r="J78" t="n">
-        <v>-38.3</v>
+        <v>21.91</v>
       </c>
       <c r="K78" t="n">
-        <v>-108.68</v>
+        <v>-114.31</v>
       </c>
       <c r="L78" t="n">
-        <v>115.23</v>
+        <v>116.39</v>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>10:42:01</t>
+          <t>10:45:52</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
@@ -3355,34 +3355,34 @@
         <v>3</v>
       </c>
       <c r="E79" t="n">
-        <v>4.03</v>
+        <v>4.64</v>
       </c>
       <c r="F79" t="n">
-        <v>7.6</v>
+        <v>10.81</v>
       </c>
       <c r="G79" t="n">
-        <v>41.4</v>
+        <v>58.5</v>
       </c>
       <c r="H79" t="n">
-        <v>100</v>
+        <v>62.1</v>
       </c>
       <c r="I79" t="n">
-        <v>16</v>
+        <v>26</v>
       </c>
       <c r="J79" t="n">
-        <v>79.08</v>
+        <v>-3.67</v>
       </c>
       <c r="K79" t="n">
-        <v>-52.19</v>
+        <v>101.87</v>
       </c>
       <c r="L79" t="n">
-        <v>94.73999999999999</v>
+        <v>101.94</v>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>10:46:58</t>
+          <t>10:50:09</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
@@ -3397,34 +3397,34 @@
         <v>1</v>
       </c>
       <c r="E80" t="n">
-        <v>3.88</v>
+        <v>3.98</v>
       </c>
       <c r="F80" t="n">
-        <v>8.890000000000001</v>
+        <v>9.56</v>
       </c>
       <c r="G80" t="n">
-        <v>46.4</v>
+        <v>46.2</v>
       </c>
       <c r="H80" t="n">
-        <v>94.09999999999999</v>
+        <v>100</v>
       </c>
       <c r="I80" t="n">
-        <v>18</v>
+        <v>24</v>
       </c>
       <c r="J80" t="n">
-        <v>174.93</v>
+        <v>112.22</v>
       </c>
       <c r="K80" t="n">
-        <v>-22.76</v>
+        <v>39.1</v>
       </c>
       <c r="L80" t="n">
-        <v>176.4</v>
+        <v>118.84</v>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>10:48:57</t>
+          <t>10:51:22</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
@@ -3439,34 +3439,34 @@
         <v>2</v>
       </c>
       <c r="E81" t="n">
-        <v>4.23</v>
+        <v>4.08</v>
       </c>
       <c r="F81" t="n">
         <v>10.81</v>
       </c>
       <c r="G81" t="n">
-        <v>45.4</v>
+        <v>42.3</v>
       </c>
       <c r="H81" t="n">
-        <v>100</v>
+        <v>79.90000000000001</v>
       </c>
       <c r="I81" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="J81" t="n">
-        <v>167.26</v>
+        <v>132.19</v>
       </c>
       <c r="K81" t="n">
-        <v>-29.1</v>
+        <v>50.66</v>
       </c>
       <c r="L81" t="n">
-        <v>169.77</v>
+        <v>141.56</v>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>10:51:29</t>
+          <t>10:52:35</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
@@ -3481,34 +3481,34 @@
         <v>3</v>
       </c>
       <c r="E82" t="n">
-        <v>4.59</v>
+        <v>4.53</v>
       </c>
       <c r="F82" t="n">
-        <v>10.81</v>
+        <v>10.71</v>
       </c>
       <c r="G82" t="n">
-        <v>38.4</v>
+        <v>42</v>
       </c>
       <c r="H82" t="n">
-        <v>100</v>
+        <v>40.6</v>
       </c>
       <c r="I82" t="n">
-        <v>16</v>
+        <v>27</v>
       </c>
       <c r="J82" t="n">
-        <v>126.2</v>
+        <v>178.44</v>
       </c>
       <c r="K82" t="n">
-        <v>116.93</v>
+        <v>75.31</v>
       </c>
       <c r="L82" t="n">
-        <v>172.04</v>
+        <v>193.68</v>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>10:55:34</t>
+          <t>10:57:03</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
@@ -3526,31 +3526,31 @@
         <v>4.38</v>
       </c>
       <c r="F83" t="n">
-        <v>10.81</v>
+        <v>9.609999999999999</v>
       </c>
       <c r="G83" t="n">
-        <v>37.3</v>
+        <v>44.7</v>
       </c>
       <c r="H83" t="n">
-        <v>99.8</v>
+        <v>77.40000000000001</v>
       </c>
       <c r="I83" t="n">
-        <v>16</v>
+        <v>21</v>
       </c>
       <c r="J83" t="n">
-        <v>150.37</v>
+        <v>83.75</v>
       </c>
       <c r="K83" t="n">
-        <v>169.42</v>
+        <v>-233.3</v>
       </c>
       <c r="L83" t="n">
-        <v>226.53</v>
+        <v>247.88</v>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>10:57:40</t>
+          <t>10:57:51</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
@@ -3565,34 +3565,34 @@
         <v>2</v>
       </c>
       <c r="E84" t="n">
-        <v>4.42</v>
+        <v>4.35</v>
       </c>
       <c r="F84" t="n">
         <v>10.81</v>
       </c>
       <c r="G84" t="n">
-        <v>44.3</v>
+        <v>41.9</v>
       </c>
       <c r="H84" t="n">
-        <v>100</v>
+        <v>74</v>
       </c>
       <c r="I84" t="n">
-        <v>16</v>
+        <v>19</v>
       </c>
       <c r="J84" t="n">
-        <v>143.7</v>
+        <v>236.27</v>
       </c>
       <c r="K84" t="n">
-        <v>314.22</v>
+        <v>34.96</v>
       </c>
       <c r="L84" t="n">
-        <v>345.52</v>
+        <v>238.84</v>
       </c>
     </row>
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>10:58:38</t>
+          <t>10:58:51</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
@@ -3607,34 +3607,34 @@
         <v>3</v>
       </c>
       <c r="E85" t="n">
-        <v>4.5</v>
+        <v>4.37</v>
       </c>
       <c r="F85" t="n">
         <v>10.81</v>
       </c>
       <c r="G85" t="n">
-        <v>54.7</v>
+        <v>42.8</v>
       </c>
       <c r="H85" t="n">
-        <v>100</v>
+        <v>66.90000000000001</v>
       </c>
       <c r="I85" t="n">
-        <v>18</v>
+        <v>21</v>
       </c>
       <c r="J85" t="n">
-        <v>100.03</v>
+        <v>149.14</v>
       </c>
       <c r="K85" t="n">
-        <v>146.08</v>
+        <v>-173.21</v>
       </c>
       <c r="L85" t="n">
-        <v>177.05</v>
+        <v>228.57</v>
       </c>
     </row>
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>11:03:27</t>
+          <t>11:03:35</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
@@ -3649,34 +3649,34 @@
         <v>1</v>
       </c>
       <c r="E86" t="n">
-        <v>4.6</v>
+        <v>4.68</v>
       </c>
       <c r="F86" t="n">
         <v>10.81</v>
       </c>
       <c r="G86" t="n">
-        <v>37.5</v>
+        <v>47.6</v>
       </c>
       <c r="H86" t="n">
-        <v>100</v>
+        <v>32.1</v>
       </c>
       <c r="I86" t="n">
-        <v>16</v>
+        <v>21</v>
       </c>
       <c r="J86" t="n">
-        <v>215.09</v>
+        <v>-287.84</v>
       </c>
       <c r="K86" t="n">
-        <v>350.65</v>
+        <v>186.94</v>
       </c>
       <c r="L86" t="n">
-        <v>411.37</v>
+        <v>343.22</v>
       </c>
     </row>
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>11:05:44</t>
+          <t>11:05:49</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
@@ -3691,34 +3691,34 @@
         <v>2</v>
       </c>
       <c r="E87" t="n">
-        <v>4.59</v>
+        <v>4.79</v>
       </c>
       <c r="F87" t="n">
         <v>10.81</v>
       </c>
       <c r="G87" t="n">
-        <v>44.8</v>
+        <v>54.3</v>
       </c>
       <c r="H87" t="n">
-        <v>94.40000000000001</v>
+        <v>85.5</v>
       </c>
       <c r="I87" t="n">
-        <v>16</v>
+        <v>19</v>
       </c>
       <c r="J87" t="n">
-        <v>87.47</v>
+        <v>119.69</v>
       </c>
       <c r="K87" t="n">
-        <v>502.36</v>
+        <v>258.82</v>
       </c>
       <c r="L87" t="n">
-        <v>509.91</v>
+        <v>285.15</v>
       </c>
     </row>
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>11:06:45</t>
+          <t>11:07:47</t>
         </is>
       </c>
       <c r="B88" t="inlineStr">
@@ -3733,28 +3733,28 @@
         <v>3</v>
       </c>
       <c r="E88" t="n">
-        <v>4.33</v>
+        <v>4.35</v>
       </c>
       <c r="F88" t="n">
-        <v>9.99</v>
+        <v>10.73</v>
       </c>
       <c r="G88" t="n">
-        <v>34.6</v>
+        <v>47.6</v>
       </c>
       <c r="H88" t="n">
-        <v>98.59999999999999</v>
+        <v>33.1</v>
       </c>
       <c r="I88" t="n">
-        <v>16</v>
+        <v>24</v>
       </c>
       <c r="J88" t="n">
-        <v>-312.47</v>
+        <v>-13.83</v>
       </c>
       <c r="K88" t="n">
-        <v>136.95</v>
+        <v>312.37</v>
       </c>
       <c r="L88" t="n">
-        <v>341.16</v>
+        <v>312.67</v>
       </c>
     </row>
   </sheetData>

--- a/output/2024-10-08.xlsx
+++ b/output/2024-10-08.xlsx
@@ -625,34 +625,34 @@
         <v>1</v>
       </c>
       <c r="E14" t="n">
-        <v>3.18</v>
+        <v>3.74</v>
       </c>
       <c r="F14" t="n">
-        <v>6.29</v>
+        <v>10.27</v>
       </c>
       <c r="G14" t="n">
-        <v>52.1</v>
+        <v>42</v>
       </c>
       <c r="H14" t="n">
-        <v>15.2</v>
+        <v>69.90000000000001</v>
       </c>
       <c r="I14" t="n">
-        <v>22</v>
+        <v>26</v>
       </c>
       <c r="J14" t="n">
-        <v>39.55</v>
+        <v>59.65</v>
       </c>
       <c r="K14" t="n">
-        <v>-28.4</v>
+        <v>11.62</v>
       </c>
       <c r="L14" t="n">
-        <v>48.69</v>
+        <v>60.78</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>07:33:44</t>
+          <t>07:33:21</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -667,34 +667,34 @@
         <v>2</v>
       </c>
       <c r="E15" t="n">
-        <v>3.64</v>
+        <v>3.1</v>
       </c>
       <c r="F15" t="n">
-        <v>8.93</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="G15" t="n">
-        <v>53.9</v>
+        <v>44.9</v>
       </c>
       <c r="H15" t="n">
-        <v>41.2</v>
+        <v>49</v>
       </c>
       <c r="I15" t="n">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="J15" t="n">
-        <v>-34.4</v>
+        <v>6.19</v>
       </c>
       <c r="K15" t="n">
-        <v>35.26</v>
+        <v>-43.33</v>
       </c>
       <c r="L15" t="n">
-        <v>49.26</v>
+        <v>43.77</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>07:35:08</t>
+          <t>07:34:20</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -709,34 +709,34 @@
         <v>3</v>
       </c>
       <c r="E16" t="n">
-        <v>4.33</v>
+        <v>3.37</v>
       </c>
       <c r="F16" t="n">
-        <v>10.81</v>
+        <v>9.48</v>
       </c>
       <c r="G16" t="n">
-        <v>36.8</v>
+        <v>38.5</v>
       </c>
       <c r="H16" t="n">
-        <v>92.5</v>
+        <v>48.8</v>
       </c>
       <c r="I16" t="n">
         <v>26</v>
       </c>
       <c r="J16" t="n">
-        <v>-72.93000000000001</v>
+        <v>1.94</v>
       </c>
       <c r="K16" t="n">
-        <v>25.18</v>
+        <v>58.95</v>
       </c>
       <c r="L16" t="n">
-        <v>77.15000000000001</v>
+        <v>58.98</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>07:38:34</t>
+          <t>07:39:40</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -751,34 +751,34 @@
         <v>1</v>
       </c>
       <c r="E17" t="n">
-        <v>3.55</v>
+        <v>3.67</v>
       </c>
       <c r="F17" t="n">
-        <v>9.07</v>
+        <v>6.33</v>
       </c>
       <c r="G17" t="n">
-        <v>48</v>
+        <v>52.6</v>
       </c>
       <c r="H17" t="n">
-        <v>60.8</v>
+        <v>83.90000000000001</v>
       </c>
       <c r="I17" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="J17" t="n">
-        <v>-44.09</v>
+        <v>30.92</v>
       </c>
       <c r="K17" t="n">
-        <v>-70.7</v>
+        <v>-95.31</v>
       </c>
       <c r="L17" t="n">
-        <v>83.31999999999999</v>
+        <v>100.2</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>07:40:40</t>
+          <t>07:41:54</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -796,31 +796,31 @@
         <v>3.68</v>
       </c>
       <c r="F18" t="n">
-        <v>6.38</v>
+        <v>8.52</v>
       </c>
       <c r="G18" t="n">
-        <v>43.5</v>
+        <v>53.1</v>
       </c>
       <c r="H18" t="n">
-        <v>52.3</v>
+        <v>79.09999999999999</v>
       </c>
       <c r="I18" t="n">
-        <v>20</v>
+        <v>31</v>
       </c>
       <c r="J18" t="n">
-        <v>53.61</v>
+        <v>88.59999999999999</v>
       </c>
       <c r="K18" t="n">
-        <v>32.79</v>
+        <v>19.54</v>
       </c>
       <c r="L18" t="n">
-        <v>62.84</v>
+        <v>90.73</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>07:42:06</t>
+          <t>07:42:32</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -835,34 +835,34 @@
         <v>3</v>
       </c>
       <c r="E19" t="n">
-        <v>3.44</v>
+        <v>3.6</v>
       </c>
       <c r="F19" t="n">
-        <v>8.69</v>
+        <v>8.23</v>
       </c>
       <c r="G19" t="n">
-        <v>42.3</v>
+        <v>38.7</v>
       </c>
       <c r="H19" t="n">
-        <v>80.09999999999999</v>
+        <v>54.5</v>
       </c>
       <c r="I19" t="n">
-        <v>19</v>
+        <v>22</v>
       </c>
       <c r="J19" t="n">
-        <v>21.57</v>
+        <v>54.95</v>
       </c>
       <c r="K19" t="n">
-        <v>-84.12</v>
+        <v>18.79</v>
       </c>
       <c r="L19" t="n">
-        <v>86.84</v>
+        <v>58.07</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>07:46:38</t>
+          <t>07:47:39</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -877,34 +877,34 @@
         <v>1</v>
       </c>
       <c r="E20" t="n">
-        <v>3.77</v>
+        <v>3.38</v>
       </c>
       <c r="F20" t="n">
-        <v>9.98</v>
+        <v>6.89</v>
       </c>
       <c r="G20" t="n">
-        <v>36.5</v>
+        <v>37.8</v>
       </c>
       <c r="H20" t="n">
-        <v>86.40000000000001</v>
+        <v>50.9</v>
       </c>
       <c r="I20" t="n">
-        <v>19</v>
+        <v>27</v>
       </c>
       <c r="J20" t="n">
-        <v>-55.58</v>
+        <v>69.22</v>
       </c>
       <c r="K20" t="n">
-        <v>79.69</v>
+        <v>102.35</v>
       </c>
       <c r="L20" t="n">
-        <v>97.16</v>
+        <v>123.56</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>07:48:54</t>
+          <t>07:48:44</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -919,34 +919,34 @@
         <v>2</v>
       </c>
       <c r="E21" t="n">
-        <v>3.13</v>
+        <v>3.74</v>
       </c>
       <c r="F21" t="n">
-        <v>9.789999999999999</v>
+        <v>10.81</v>
       </c>
       <c r="G21" t="n">
-        <v>36.8</v>
+        <v>50.5</v>
       </c>
       <c r="H21" t="n">
-        <v>49.8</v>
+        <v>81.40000000000001</v>
       </c>
       <c r="I21" t="n">
         <v>23</v>
       </c>
       <c r="J21" t="n">
-        <v>-48.23</v>
+        <v>-96.68000000000001</v>
       </c>
       <c r="K21" t="n">
-        <v>-94.13</v>
+        <v>87.11</v>
       </c>
       <c r="L21" t="n">
-        <v>105.76</v>
+        <v>130.13</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>07:50:52</t>
+          <t>07:50:07</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -961,34 +961,34 @@
         <v>3</v>
       </c>
       <c r="E22" t="n">
-        <v>3.33</v>
+        <v>3.78</v>
       </c>
       <c r="F22" t="n">
-        <v>6.97</v>
+        <v>10.18</v>
       </c>
       <c r="G22" t="n">
-        <v>39.6</v>
+        <v>55.8</v>
       </c>
       <c r="H22" t="n">
-        <v>48.9</v>
+        <v>45.2</v>
       </c>
       <c r="I22" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="J22" t="n">
-        <v>72.09</v>
+        <v>28.81</v>
       </c>
       <c r="K22" t="n">
-        <v>92.22</v>
+        <v>149.14</v>
       </c>
       <c r="L22" t="n">
-        <v>117.05</v>
+        <v>151.89</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>07:56:26</t>
+          <t>07:55:47</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -1003,34 +1003,34 @@
         <v>1</v>
       </c>
       <c r="E23" t="n">
-        <v>3.19</v>
+        <v>3.67</v>
       </c>
       <c r="F23" t="n">
-        <v>8.380000000000001</v>
+        <v>7.72</v>
       </c>
       <c r="G23" t="n">
-        <v>41</v>
+        <v>25.8</v>
       </c>
       <c r="H23" t="n">
-        <v>63.9</v>
+        <v>45.7</v>
       </c>
       <c r="I23" t="n">
-        <v>17</v>
+        <v>28</v>
       </c>
       <c r="J23" t="n">
-        <v>-151.93</v>
+        <v>-49.43</v>
       </c>
       <c r="K23" t="n">
-        <v>12.75</v>
+        <v>216.82</v>
       </c>
       <c r="L23" t="n">
-        <v>152.47</v>
+        <v>222.38</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>07:58:15</t>
+          <t>07:58:18</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -1045,34 +1045,34 @@
         <v>2</v>
       </c>
       <c r="E24" t="n">
-        <v>3.32</v>
+        <v>3.95</v>
       </c>
       <c r="F24" t="n">
-        <v>6.97</v>
+        <v>6.78</v>
       </c>
       <c r="G24" t="n">
-        <v>57.8</v>
+        <v>43.8</v>
       </c>
       <c r="H24" t="n">
-        <v>54</v>
+        <v>36.8</v>
       </c>
       <c r="I24" t="n">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="J24" t="n">
-        <v>-36.27</v>
+        <v>298.72</v>
       </c>
       <c r="K24" t="n">
-        <v>136.89</v>
+        <v>21.37</v>
       </c>
       <c r="L24" t="n">
-        <v>141.61</v>
+        <v>299.48</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>08:00:01</t>
+          <t>07:59:16</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -1087,34 +1087,34 @@
         <v>3</v>
       </c>
       <c r="E25" t="n">
-        <v>3.23</v>
+        <v>3.71</v>
       </c>
       <c r="F25" t="n">
-        <v>7.13</v>
+        <v>9.029999999999999</v>
       </c>
       <c r="G25" t="n">
-        <v>43.5</v>
+        <v>45.1</v>
       </c>
       <c r="H25" t="n">
-        <v>65.5</v>
+        <v>80.5</v>
       </c>
       <c r="I25" t="n">
-        <v>27</v>
+        <v>30</v>
       </c>
       <c r="J25" t="n">
-        <v>-60.33</v>
+        <v>-165.12</v>
       </c>
       <c r="K25" t="n">
-        <v>-129.7</v>
+        <v>-207.82</v>
       </c>
       <c r="L25" t="n">
-        <v>143.04</v>
+        <v>265.44</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>08:04:45</t>
+          <t>08:03:25</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
@@ -1129,34 +1129,34 @@
         <v>1</v>
       </c>
       <c r="E26" t="n">
-        <v>3.52</v>
+        <v>3.53</v>
       </c>
       <c r="F26" t="n">
-        <v>10.81</v>
+        <v>7.69</v>
       </c>
       <c r="G26" t="n">
-        <v>44.1</v>
+        <v>25.9</v>
       </c>
       <c r="H26" t="n">
-        <v>61.7</v>
+        <v>90.3</v>
       </c>
       <c r="I26" t="n">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="J26" t="n">
-        <v>185</v>
+        <v>-239.03</v>
       </c>
       <c r="K26" t="n">
-        <v>-81.88</v>
+        <v>-78.13</v>
       </c>
       <c r="L26" t="n">
-        <v>202.31</v>
+        <v>251.48</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>08:06:25</t>
+          <t>08:04:53</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
@@ -1171,34 +1171,34 @@
         <v>2</v>
       </c>
       <c r="E27" t="n">
-        <v>3.93</v>
+        <v>3.99</v>
       </c>
       <c r="F27" t="n">
-        <v>9.970000000000001</v>
+        <v>9.43</v>
       </c>
       <c r="G27" t="n">
-        <v>41.2</v>
+        <v>48.7</v>
       </c>
       <c r="H27" t="n">
-        <v>65</v>
+        <v>70</v>
       </c>
       <c r="I27" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="J27" t="n">
-        <v>230.47</v>
+        <v>289.49</v>
       </c>
       <c r="K27" t="n">
-        <v>98.23</v>
+        <v>-33.56</v>
       </c>
       <c r="L27" t="n">
-        <v>250.53</v>
+        <v>291.43</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>08:08:25</t>
+          <t>08:06:00</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
@@ -1213,34 +1213,34 @@
         <v>3</v>
       </c>
       <c r="E28" t="n">
-        <v>3.49</v>
+        <v>4.07</v>
       </c>
       <c r="F28" t="n">
-        <v>8.32</v>
+        <v>10.81</v>
       </c>
       <c r="G28" t="n">
-        <v>51</v>
+        <v>35</v>
       </c>
       <c r="H28" t="n">
-        <v>55.2</v>
+        <v>65.09999999999999</v>
       </c>
       <c r="I28" t="n">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="J28" t="n">
-        <v>-186.59</v>
+        <v>309.23</v>
       </c>
       <c r="K28" t="n">
-        <v>-84.04000000000001</v>
+        <v>-135.14</v>
       </c>
       <c r="L28" t="n">
-        <v>204.64</v>
+        <v>337.47</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>08:19:05</t>
+          <t>08:15:06</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
@@ -1255,34 +1255,34 @@
         <v>1</v>
       </c>
       <c r="E29" t="n">
-        <v>3.82</v>
+        <v>3.22</v>
       </c>
       <c r="F29" t="n">
-        <v>8.94</v>
+        <v>5.88</v>
       </c>
       <c r="G29" t="n">
-        <v>53.3</v>
+        <v>33.6</v>
       </c>
       <c r="H29" t="n">
-        <v>100</v>
+        <v>53.7</v>
       </c>
       <c r="I29" t="n">
-        <v>25</v>
+        <v>32</v>
       </c>
       <c r="J29" t="n">
-        <v>-12.42</v>
+        <v>-11.76</v>
       </c>
       <c r="K29" t="n">
-        <v>35.86</v>
+        <v>41.36</v>
       </c>
       <c r="L29" t="n">
-        <v>37.95</v>
+        <v>43</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>08:21:17</t>
+          <t>08:17:26</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
@@ -1297,34 +1297,34 @@
         <v>2</v>
       </c>
       <c r="E30" t="n">
-        <v>4.08</v>
+        <v>3.5</v>
       </c>
       <c r="F30" t="n">
-        <v>8.19</v>
+        <v>8.4</v>
       </c>
       <c r="G30" t="n">
-        <v>44.1</v>
+        <v>46.8</v>
       </c>
       <c r="H30" t="n">
-        <v>87.5</v>
+        <v>89</v>
       </c>
       <c r="I30" t="n">
-        <v>20</v>
+        <v>32</v>
       </c>
       <c r="J30" t="n">
-        <v>58.32</v>
+        <v>46.62</v>
       </c>
       <c r="K30" t="n">
-        <v>-18.27</v>
+        <v>91.94</v>
       </c>
       <c r="L30" t="n">
-        <v>61.12</v>
+        <v>103.08</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>08:22:21</t>
+          <t>08:19:53</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
@@ -1339,34 +1339,34 @@
         <v>3</v>
       </c>
       <c r="E31" t="n">
-        <v>4.18</v>
+        <v>3.43</v>
       </c>
       <c r="F31" t="n">
-        <v>10.81</v>
+        <v>7.72</v>
       </c>
       <c r="G31" t="n">
-        <v>35.7</v>
+        <v>54.8</v>
       </c>
       <c r="H31" t="n">
-        <v>97.8</v>
+        <v>26.1</v>
       </c>
       <c r="I31" t="n">
-        <v>19</v>
+        <v>25</v>
       </c>
       <c r="J31" t="n">
-        <v>-48.46</v>
+        <v>-1.93</v>
       </c>
       <c r="K31" t="n">
-        <v>-20.37</v>
+        <v>-80.84</v>
       </c>
       <c r="L31" t="n">
-        <v>52.56</v>
+        <v>80.86</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>08:27:16</t>
+          <t>08:24:26</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
@@ -1381,34 +1381,34 @@
         <v>1</v>
       </c>
       <c r="E32" t="n">
-        <v>3.49</v>
+        <v>4.01</v>
       </c>
       <c r="F32" t="n">
-        <v>8.24</v>
+        <v>7.33</v>
       </c>
       <c r="G32" t="n">
-        <v>44.5</v>
+        <v>33</v>
       </c>
       <c r="H32" t="n">
-        <v>79.3</v>
+        <v>66.59999999999999</v>
       </c>
       <c r="I32" t="n">
-        <v>26</v>
+        <v>32</v>
       </c>
       <c r="J32" t="n">
-        <v>63.18</v>
+        <v>48.33</v>
       </c>
       <c r="K32" t="n">
-        <v>57.34</v>
+        <v>93.31</v>
       </c>
       <c r="L32" t="n">
-        <v>85.31999999999999</v>
+        <v>105.08</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>08:29:02</t>
+          <t>08:25:18</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
@@ -1423,34 +1423,34 @@
         <v>2</v>
       </c>
       <c r="E33" t="n">
-        <v>3.73</v>
+        <v>3.87</v>
       </c>
       <c r="F33" t="n">
-        <v>9.66</v>
+        <v>9.949999999999999</v>
       </c>
       <c r="G33" t="n">
-        <v>47.9</v>
+        <v>41.2</v>
       </c>
       <c r="H33" t="n">
-        <v>33.2</v>
+        <v>70.8</v>
       </c>
       <c r="I33" t="n">
-        <v>20</v>
+        <v>27</v>
       </c>
       <c r="J33" t="n">
-        <v>81.16</v>
+        <v>-75.59999999999999</v>
       </c>
       <c r="K33" t="n">
-        <v>17.63</v>
+        <v>49.92</v>
       </c>
       <c r="L33" t="n">
-        <v>83.05</v>
+        <v>90.59</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>08:30:07</t>
+          <t>08:27:29</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
@@ -1465,34 +1465,34 @@
         <v>3</v>
       </c>
       <c r="E34" t="n">
-        <v>3.74</v>
+        <v>3.24</v>
       </c>
       <c r="F34" t="n">
-        <v>10.81</v>
+        <v>8.880000000000001</v>
       </c>
       <c r="G34" t="n">
-        <v>62.2</v>
+        <v>38.1</v>
       </c>
       <c r="H34" t="n">
-        <v>69.3</v>
+        <v>31.2</v>
       </c>
       <c r="I34" t="n">
-        <v>21</v>
+        <v>30</v>
       </c>
       <c r="J34" t="n">
-        <v>-60.23</v>
+        <v>91.28</v>
       </c>
       <c r="K34" t="n">
-        <v>54.9</v>
+        <v>-31.68</v>
       </c>
       <c r="L34" t="n">
-        <v>81.48999999999999</v>
+        <v>96.63</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>08:35:52</t>
+          <t>08:32:02</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
@@ -1507,34 +1507,34 @@
         <v>1</v>
       </c>
       <c r="E35" t="n">
-        <v>3.87</v>
+        <v>4.44</v>
       </c>
       <c r="F35" t="n">
-        <v>7.98</v>
+        <v>10.81</v>
       </c>
       <c r="G35" t="n">
-        <v>52.1</v>
+        <v>44.2</v>
       </c>
       <c r="H35" t="n">
-        <v>45.8</v>
+        <v>98.40000000000001</v>
       </c>
       <c r="I35" t="n">
-        <v>19</v>
+        <v>31</v>
       </c>
       <c r="J35" t="n">
-        <v>81.59</v>
+        <v>-49.78</v>
       </c>
       <c r="K35" t="n">
-        <v>-49.9</v>
+        <v>-161.2</v>
       </c>
       <c r="L35" t="n">
-        <v>95.64</v>
+        <v>168.71</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>08:36:43</t>
+          <t>08:33:25</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
@@ -1549,34 +1549,34 @@
         <v>2</v>
       </c>
       <c r="E36" t="n">
-        <v>3.54</v>
+        <v>3.98</v>
       </c>
       <c r="F36" t="n">
-        <v>9.84</v>
+        <v>8.44</v>
       </c>
       <c r="G36" t="n">
-        <v>52.5</v>
+        <v>52</v>
       </c>
       <c r="H36" t="n">
-        <v>48.1</v>
+        <v>77</v>
       </c>
       <c r="I36" t="n">
-        <v>19</v>
+        <v>25</v>
       </c>
       <c r="J36" t="n">
-        <v>-104.32</v>
+        <v>129.5</v>
       </c>
       <c r="K36" t="n">
-        <v>-53.22</v>
+        <v>-84.86</v>
       </c>
       <c r="L36" t="n">
-        <v>117.11</v>
+        <v>154.83</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>08:38:14</t>
+          <t>08:34:59</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
@@ -1591,34 +1591,34 @@
         <v>3</v>
       </c>
       <c r="E37" t="n">
-        <v>3.92</v>
+        <v>3.81</v>
       </c>
       <c r="F37" t="n">
-        <v>8.039999999999999</v>
+        <v>6.13</v>
       </c>
       <c r="G37" t="n">
-        <v>40</v>
+        <v>52.2</v>
       </c>
       <c r="H37" t="n">
-        <v>60.8</v>
+        <v>62.2</v>
       </c>
       <c r="I37" t="n">
-        <v>29</v>
+        <v>24</v>
       </c>
       <c r="J37" t="n">
-        <v>12.61</v>
+        <v>70.20999999999999</v>
       </c>
       <c r="K37" t="n">
-        <v>169.48</v>
+        <v>132.07</v>
       </c>
       <c r="L37" t="n">
-        <v>169.95</v>
+        <v>149.57</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>08:42:25</t>
+          <t>08:39:39</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
@@ -1633,34 +1633,34 @@
         <v>1</v>
       </c>
       <c r="E38" t="n">
-        <v>3.57</v>
+        <v>3.52</v>
       </c>
       <c r="F38" t="n">
-        <v>10.53</v>
+        <v>10.34</v>
       </c>
       <c r="G38" t="n">
-        <v>46.2</v>
+        <v>47.3</v>
       </c>
       <c r="H38" t="n">
-        <v>52.2</v>
+        <v>43.4</v>
       </c>
       <c r="I38" t="n">
-        <v>19</v>
+        <v>30</v>
       </c>
       <c r="J38" t="n">
-        <v>149.9</v>
+        <v>113.77</v>
       </c>
       <c r="K38" t="n">
-        <v>39.96</v>
+        <v>143.06</v>
       </c>
       <c r="L38" t="n">
-        <v>155.14</v>
+        <v>182.78</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>08:44:16</t>
+          <t>08:40:55</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
@@ -1675,34 +1675,34 @@
         <v>2</v>
       </c>
       <c r="E39" t="n">
-        <v>3.93</v>
+        <v>3.89</v>
       </c>
       <c r="F39" t="n">
-        <v>10.81</v>
+        <v>7.98</v>
       </c>
       <c r="G39" t="n">
-        <v>32.2</v>
+        <v>42.8</v>
       </c>
       <c r="H39" t="n">
-        <v>63.6</v>
+        <v>75.7</v>
       </c>
       <c r="I39" t="n">
-        <v>19</v>
+        <v>26</v>
       </c>
       <c r="J39" t="n">
-        <v>3.88</v>
+        <v>300.02</v>
       </c>
       <c r="K39" t="n">
-        <v>-166.82</v>
+        <v>60.2</v>
       </c>
       <c r="L39" t="n">
-        <v>166.86</v>
+        <v>306</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>08:45:58</t>
+          <t>08:41:57</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
@@ -1717,34 +1717,34 @@
         <v>3</v>
       </c>
       <c r="E40" t="n">
-        <v>4.25</v>
+        <v>3.73</v>
       </c>
       <c r="F40" t="n">
-        <v>10.81</v>
+        <v>10.29</v>
       </c>
       <c r="G40" t="n">
-        <v>38.2</v>
+        <v>52.1</v>
       </c>
       <c r="H40" t="n">
-        <v>48.9</v>
+        <v>91.8</v>
       </c>
       <c r="I40" t="n">
-        <v>20</v>
+        <v>28</v>
       </c>
       <c r="J40" t="n">
-        <v>183.99</v>
+        <v>-94.34999999999999</v>
       </c>
       <c r="K40" t="n">
-        <v>155.15</v>
+        <v>-69.79000000000001</v>
       </c>
       <c r="L40" t="n">
-        <v>240.67</v>
+        <v>117.36</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>08:49:18</t>
+          <t>08:46:14</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
@@ -1759,34 +1759,34 @@
         <v>1</v>
       </c>
       <c r="E41" t="n">
-        <v>3.67</v>
+        <v>3.69</v>
       </c>
       <c r="F41" t="n">
-        <v>7.55</v>
+        <v>9.93</v>
       </c>
       <c r="G41" t="n">
-        <v>34.7</v>
+        <v>46.1</v>
       </c>
       <c r="H41" t="n">
-        <v>65.7</v>
+        <v>86.90000000000001</v>
       </c>
       <c r="I41" t="n">
-        <v>22</v>
+        <v>25</v>
       </c>
       <c r="J41" t="n">
-        <v>-112.42</v>
+        <v>177.15</v>
       </c>
       <c r="K41" t="n">
-        <v>216.74</v>
+        <v>-116.61</v>
       </c>
       <c r="L41" t="n">
-        <v>244.16</v>
+        <v>212.08</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>08:50:59</t>
+          <t>08:47:17</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
@@ -1801,34 +1801,34 @@
         <v>2</v>
       </c>
       <c r="E42" t="n">
-        <v>3.87</v>
+        <v>3.92</v>
       </c>
       <c r="F42" t="n">
-        <v>10.74</v>
+        <v>7.61</v>
       </c>
       <c r="G42" t="n">
-        <v>50.4</v>
+        <v>48</v>
       </c>
       <c r="H42" t="n">
-        <v>89.7</v>
+        <v>85.8</v>
       </c>
       <c r="I42" t="n">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="J42" t="n">
-        <v>135.84</v>
+        <v>164.89</v>
       </c>
       <c r="K42" t="n">
-        <v>136.61</v>
+        <v>-221.16</v>
       </c>
       <c r="L42" t="n">
-        <v>192.65</v>
+        <v>275.86</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>08:53:18</t>
+          <t>08:49:04</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
@@ -1843,34 +1843,34 @@
         <v>3</v>
       </c>
       <c r="E43" t="n">
-        <v>4.58</v>
+        <v>3.78</v>
       </c>
       <c r="F43" t="n">
-        <v>10.55</v>
+        <v>10.1</v>
       </c>
       <c r="G43" t="n">
-        <v>39.7</v>
+        <v>39.8</v>
       </c>
       <c r="H43" t="n">
-        <v>48.8</v>
+        <v>13.4</v>
       </c>
       <c r="I43" t="n">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="J43" t="n">
-        <v>-102.43</v>
+        <v>194.4</v>
       </c>
       <c r="K43" t="n">
-        <v>68.03</v>
+        <v>107.53</v>
       </c>
       <c r="L43" t="n">
-        <v>122.97</v>
+        <v>222.16</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>09:02:14</t>
+          <t>08:59:39</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
@@ -1885,34 +1885,34 @@
         <v>1</v>
       </c>
       <c r="E44" t="n">
-        <v>3.57</v>
+        <v>4</v>
       </c>
       <c r="F44" t="n">
-        <v>6.94</v>
+        <v>9.66</v>
       </c>
       <c r="G44" t="n">
-        <v>47.3</v>
+        <v>43.9</v>
       </c>
       <c r="H44" t="n">
-        <v>95.90000000000001</v>
+        <v>58</v>
       </c>
       <c r="I44" t="n">
-        <v>20</v>
+        <v>24</v>
       </c>
       <c r="J44" t="n">
-        <v>-13.96</v>
+        <v>0.31</v>
       </c>
       <c r="K44" t="n">
-        <v>56.67</v>
+        <v>81.23999999999999</v>
       </c>
       <c r="L44" t="n">
-        <v>58.36</v>
+        <v>81.23999999999999</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>09:04:37</t>
+          <t>09:02:15</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
@@ -1927,34 +1927,34 @@
         <v>2</v>
       </c>
       <c r="E45" t="n">
-        <v>3.96</v>
+        <v>3.95</v>
       </c>
       <c r="F45" t="n">
-        <v>10.81</v>
+        <v>7.91</v>
       </c>
       <c r="G45" t="n">
-        <v>29.4</v>
+        <v>48.4</v>
       </c>
       <c r="H45" t="n">
-        <v>63.4</v>
+        <v>60.4</v>
       </c>
       <c r="I45" t="n">
-        <v>23</v>
+        <v>32</v>
       </c>
       <c r="J45" t="n">
-        <v>31.21</v>
+        <v>74.95999999999999</v>
       </c>
       <c r="K45" t="n">
-        <v>48.91</v>
+        <v>16.67</v>
       </c>
       <c r="L45" t="n">
-        <v>58.02</v>
+        <v>76.79000000000001</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>09:05:59</t>
+          <t>09:02:53</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
@@ -1969,34 +1969,34 @@
         <v>3</v>
       </c>
       <c r="E46" t="n">
-        <v>4.54</v>
+        <v>4.01</v>
       </c>
       <c r="F46" t="n">
-        <v>10.07</v>
+        <v>8.52</v>
       </c>
       <c r="G46" t="n">
-        <v>52.1</v>
+        <v>46.7</v>
       </c>
       <c r="H46" t="n">
-        <v>75.40000000000001</v>
+        <v>38.2</v>
       </c>
       <c r="I46" t="n">
-        <v>20</v>
+        <v>23</v>
       </c>
       <c r="J46" t="n">
-        <v>-36.21</v>
+        <v>-41.76</v>
       </c>
       <c r="K46" t="n">
-        <v>100.54</v>
+        <v>-55.83</v>
       </c>
       <c r="L46" t="n">
-        <v>106.86</v>
+        <v>69.72</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>09:10:10</t>
+          <t>09:07:27</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
@@ -2011,34 +2011,34 @@
         <v>1</v>
       </c>
       <c r="E47" t="n">
-        <v>3.93</v>
+        <v>3.88</v>
       </c>
       <c r="F47" t="n">
-        <v>6.77</v>
+        <v>10.56</v>
       </c>
       <c r="G47" t="n">
-        <v>37.4</v>
+        <v>36.4</v>
       </c>
       <c r="H47" t="n">
-        <v>63.6</v>
+        <v>63.5</v>
       </c>
       <c r="I47" t="n">
-        <v>20</v>
+        <v>28</v>
       </c>
       <c r="J47" t="n">
-        <v>-11.28</v>
+        <v>-52.06</v>
       </c>
       <c r="K47" t="n">
-        <v>75.94</v>
+        <v>79.14</v>
       </c>
       <c r="L47" t="n">
-        <v>76.78</v>
+        <v>94.73</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>09:11:15</t>
+          <t>09:08:49</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
@@ -2053,34 +2053,34 @@
         <v>2</v>
       </c>
       <c r="E48" t="n">
-        <v>3.81</v>
+        <v>4.58</v>
       </c>
       <c r="F48" t="n">
-        <v>8.27</v>
+        <v>10.59</v>
       </c>
       <c r="G48" t="n">
-        <v>49.2</v>
+        <v>28.3</v>
       </c>
       <c r="H48" t="n">
-        <v>65.09999999999999</v>
+        <v>57.3</v>
       </c>
       <c r="I48" t="n">
-        <v>29</v>
+        <v>32</v>
       </c>
       <c r="J48" t="n">
-        <v>-57.8</v>
+        <v>-80.84</v>
       </c>
       <c r="K48" t="n">
-        <v>-57.94</v>
+        <v>108.61</v>
       </c>
       <c r="L48" t="n">
-        <v>81.84</v>
+        <v>135.4</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>09:13:07</t>
+          <t>09:10:24</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
@@ -2095,34 +2095,34 @@
         <v>3</v>
       </c>
       <c r="E49" t="n">
-        <v>3.44</v>
+        <v>4.38</v>
       </c>
       <c r="F49" t="n">
-        <v>7.67</v>
+        <v>10.81</v>
       </c>
       <c r="G49" t="n">
-        <v>50.7</v>
+        <v>42.5</v>
       </c>
       <c r="H49" t="n">
-        <v>65.3</v>
+        <v>66.40000000000001</v>
       </c>
       <c r="I49" t="n">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="J49" t="n">
-        <v>21.37</v>
+        <v>86.83</v>
       </c>
       <c r="K49" t="n">
-        <v>95.2</v>
+        <v>-104.8</v>
       </c>
       <c r="L49" t="n">
-        <v>97.56999999999999</v>
+        <v>136.1</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>09:18:44</t>
+          <t>09:14:44</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
@@ -2137,34 +2137,34 @@
         <v>1</v>
       </c>
       <c r="E50" t="n">
-        <v>4.05</v>
+        <v>4.55</v>
       </c>
       <c r="F50" t="n">
-        <v>9.65</v>
+        <v>9.789999999999999</v>
       </c>
       <c r="G50" t="n">
-        <v>48.6</v>
+        <v>46.5</v>
       </c>
       <c r="H50" t="n">
-        <v>67.5</v>
+        <v>54.2</v>
       </c>
       <c r="I50" t="n">
-        <v>27</v>
+        <v>32</v>
       </c>
       <c r="J50" t="n">
-        <v>147.9</v>
+        <v>-78.67</v>
       </c>
       <c r="K50" t="n">
-        <v>30.28</v>
+        <v>148.03</v>
       </c>
       <c r="L50" t="n">
-        <v>150.96</v>
+        <v>167.64</v>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>09:20:12</t>
+          <t>09:15:27</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
@@ -2179,34 +2179,34 @@
         <v>2</v>
       </c>
       <c r="E51" t="n">
-        <v>3.83</v>
+        <v>4.4</v>
       </c>
       <c r="F51" t="n">
-        <v>9.6</v>
+        <v>10.81</v>
       </c>
       <c r="G51" t="n">
-        <v>10</v>
+        <v>47.2</v>
       </c>
       <c r="H51" t="n">
-        <v>44.1</v>
+        <v>24.4</v>
       </c>
       <c r="I51" t="n">
         <v>21</v>
       </c>
       <c r="J51" t="n">
-        <v>-9.68</v>
+        <v>143.59</v>
       </c>
       <c r="K51" t="n">
-        <v>115.53</v>
+        <v>115.33</v>
       </c>
       <c r="L51" t="n">
-        <v>115.93</v>
+        <v>184.18</v>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>09:21:55</t>
+          <t>09:16:40</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
@@ -2221,34 +2221,34 @@
         <v>3</v>
       </c>
       <c r="E52" t="n">
-        <v>4.38</v>
+        <v>3.95</v>
       </c>
       <c r="F52" t="n">
-        <v>10.34</v>
+        <v>10.55</v>
       </c>
       <c r="G52" t="n">
-        <v>31.7</v>
+        <v>32.4</v>
       </c>
       <c r="H52" t="n">
-        <v>18.8</v>
+        <v>46</v>
       </c>
       <c r="I52" t="n">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="J52" t="n">
-        <v>131.7</v>
+        <v>124.74</v>
       </c>
       <c r="K52" t="n">
-        <v>27.17</v>
+        <v>61.49</v>
       </c>
       <c r="L52" t="n">
-        <v>134.47</v>
+        <v>139.07</v>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>09:25:20</t>
+          <t>09:22:23</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
@@ -2263,34 +2263,34 @@
         <v>1</v>
       </c>
       <c r="E53" t="n">
-        <v>4.34</v>
+        <v>3.95</v>
       </c>
       <c r="F53" t="n">
-        <v>10.81</v>
+        <v>10.39</v>
       </c>
       <c r="G53" t="n">
-        <v>40.2</v>
+        <v>48.5</v>
       </c>
       <c r="H53" t="n">
-        <v>73.2</v>
+        <v>77.3</v>
       </c>
       <c r="I53" t="n">
-        <v>23</v>
+        <v>31</v>
       </c>
       <c r="J53" t="n">
-        <v>191.04</v>
+        <v>238.66</v>
       </c>
       <c r="K53" t="n">
-        <v>60.84</v>
+        <v>60.58</v>
       </c>
       <c r="L53" t="n">
-        <v>200.49</v>
+        <v>246.22</v>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>09:27:36</t>
+          <t>09:23:36</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
@@ -2305,34 +2305,34 @@
         <v>2</v>
       </c>
       <c r="E54" t="n">
-        <v>3.99</v>
+        <v>3.77</v>
       </c>
       <c r="F54" t="n">
-        <v>10.81</v>
+        <v>8.24</v>
       </c>
       <c r="G54" t="n">
-        <v>39.9</v>
+        <v>56.1</v>
       </c>
       <c r="H54" t="n">
-        <v>46.1</v>
+        <v>82.5</v>
       </c>
       <c r="I54" t="n">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="J54" t="n">
-        <v>143.44</v>
+        <v>139.01</v>
       </c>
       <c r="K54" t="n">
-        <v>-82.95</v>
+        <v>141.93</v>
       </c>
       <c r="L54" t="n">
-        <v>165.7</v>
+        <v>198.67</v>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>09:28:22</t>
+          <t>09:25:05</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
@@ -2347,34 +2347,34 @@
         <v>3</v>
       </c>
       <c r="E55" t="n">
-        <v>4.03</v>
+        <v>3.91</v>
       </c>
       <c r="F55" t="n">
-        <v>10.81</v>
+        <v>8.77</v>
       </c>
       <c r="G55" t="n">
-        <v>47.3</v>
+        <v>46.4</v>
       </c>
       <c r="H55" t="n">
-        <v>30.8</v>
+        <v>89.8</v>
       </c>
       <c r="I55" t="n">
-        <v>22</v>
+        <v>31</v>
       </c>
       <c r="J55" t="n">
-        <v>157.82</v>
+        <v>161.21</v>
       </c>
       <c r="K55" t="n">
-        <v>169.88</v>
+        <v>138.87</v>
       </c>
       <c r="L55" t="n">
-        <v>231.87</v>
+        <v>212.77</v>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>09:32:24</t>
+          <t>09:29:26</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
@@ -2389,34 +2389,34 @@
         <v>1</v>
       </c>
       <c r="E56" t="n">
-        <v>4.35</v>
+        <v>3.78</v>
       </c>
       <c r="F56" t="n">
-        <v>9.69</v>
+        <v>9.390000000000001</v>
       </c>
       <c r="G56" t="n">
-        <v>34.7</v>
+        <v>35.8</v>
       </c>
       <c r="H56" t="n">
-        <v>57.8</v>
+        <v>52.1</v>
       </c>
       <c r="I56" t="n">
-        <v>17</v>
+        <v>23</v>
       </c>
       <c r="J56" t="n">
-        <v>265.06</v>
+        <v>-324.91</v>
       </c>
       <c r="K56" t="n">
-        <v>-49.16</v>
+        <v>30.2</v>
       </c>
       <c r="L56" t="n">
-        <v>269.58</v>
+        <v>326.31</v>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>09:33:48</t>
+          <t>09:31:39</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
@@ -2431,34 +2431,34 @@
         <v>2</v>
       </c>
       <c r="E57" t="n">
-        <v>4.07</v>
+        <v>3.94</v>
       </c>
       <c r="F57" t="n">
-        <v>10.81</v>
+        <v>10.77</v>
       </c>
       <c r="G57" t="n">
-        <v>45.9</v>
+        <v>38.7</v>
       </c>
       <c r="H57" t="n">
-        <v>43.2</v>
+        <v>64.09999999999999</v>
       </c>
       <c r="I57" t="n">
-        <v>29</v>
+        <v>23</v>
       </c>
       <c r="J57" t="n">
-        <v>229.32</v>
+        <v>-286.88</v>
       </c>
       <c r="K57" t="n">
-        <v>167.02</v>
+        <v>16.39</v>
       </c>
       <c r="L57" t="n">
-        <v>283.7</v>
+        <v>287.35</v>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>09:36:02</t>
+          <t>09:32:38</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
@@ -2473,34 +2473,34 @@
         <v>3</v>
       </c>
       <c r="E58" t="n">
-        <v>4.28</v>
+        <v>4.67</v>
       </c>
       <c r="F58" t="n">
-        <v>8</v>
+        <v>10.81</v>
       </c>
       <c r="G58" t="n">
-        <v>39.6</v>
+        <v>56</v>
       </c>
       <c r="H58" t="n">
-        <v>65.40000000000001</v>
+        <v>32.8</v>
       </c>
       <c r="I58" t="n">
         <v>27</v>
       </c>
       <c r="J58" t="n">
-        <v>114.89</v>
+        <v>-183.72</v>
       </c>
       <c r="K58" t="n">
-        <v>224.16</v>
+        <v>-327.8</v>
       </c>
       <c r="L58" t="n">
-        <v>251.89</v>
+        <v>375.77</v>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>09:45:42</t>
+          <t>09:42:12</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
@@ -2515,34 +2515,34 @@
         <v>1</v>
       </c>
       <c r="E59" t="n">
-        <v>4.14</v>
+        <v>4.49</v>
       </c>
       <c r="F59" t="n">
-        <v>9.82</v>
+        <v>10.81</v>
       </c>
       <c r="G59" t="n">
-        <v>32.2</v>
+        <v>43.2</v>
       </c>
       <c r="H59" t="n">
-        <v>77.5</v>
+        <v>47.8</v>
       </c>
       <c r="I59" t="n">
-        <v>28</v>
+        <v>21</v>
       </c>
       <c r="J59" t="n">
-        <v>13.84</v>
+        <v>-7.35</v>
       </c>
       <c r="K59" t="n">
-        <v>-70.22</v>
+        <v>-76.27</v>
       </c>
       <c r="L59" t="n">
-        <v>71.56999999999999</v>
+        <v>76.63</v>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>09:46:30</t>
+          <t>09:43:38</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
@@ -2557,34 +2557,34 @@
         <v>2</v>
       </c>
       <c r="E60" t="n">
-        <v>4.19</v>
+        <v>4.18</v>
       </c>
       <c r="F60" t="n">
-        <v>10.81</v>
+        <v>9.220000000000001</v>
       </c>
       <c r="G60" t="n">
-        <v>32.5</v>
+        <v>55</v>
       </c>
       <c r="H60" t="n">
-        <v>64.8</v>
+        <v>93.5</v>
       </c>
       <c r="I60" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="J60" t="n">
-        <v>41.46</v>
+        <v>-2.33</v>
       </c>
       <c r="K60" t="n">
-        <v>-62.15</v>
+        <v>82.25</v>
       </c>
       <c r="L60" t="n">
-        <v>74.70999999999999</v>
+        <v>82.29000000000001</v>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>09:48:07</t>
+          <t>09:46:11</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
@@ -2599,34 +2599,34 @@
         <v>3</v>
       </c>
       <c r="E61" t="n">
-        <v>3.86</v>
+        <v>4.56</v>
       </c>
       <c r="F61" t="n">
-        <v>10.81</v>
+        <v>10.38</v>
       </c>
       <c r="G61" t="n">
-        <v>26.2</v>
+        <v>41.5</v>
       </c>
       <c r="H61" t="n">
-        <v>52.7</v>
+        <v>47.1</v>
       </c>
       <c r="I61" t="n">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="J61" t="n">
-        <v>55.15</v>
+        <v>64.34</v>
       </c>
       <c r="K61" t="n">
-        <v>14.38</v>
+        <v>98.15000000000001</v>
       </c>
       <c r="L61" t="n">
-        <v>56.99</v>
+        <v>117.36</v>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>09:53:55</t>
+          <t>09:51:43</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
@@ -2641,34 +2641,34 @@
         <v>1</v>
       </c>
       <c r="E62" t="n">
-        <v>3.81</v>
+        <v>3.96</v>
       </c>
       <c r="F62" t="n">
-        <v>10.81</v>
+        <v>10.22</v>
       </c>
       <c r="G62" t="n">
-        <v>30.1</v>
+        <v>36.6</v>
       </c>
       <c r="H62" t="n">
-        <v>46.1</v>
+        <v>55.9</v>
       </c>
       <c r="I62" t="n">
-        <v>20</v>
+        <v>32</v>
       </c>
       <c r="J62" t="n">
-        <v>55</v>
+        <v>-9.710000000000001</v>
       </c>
       <c r="K62" t="n">
-        <v>81.22</v>
+        <v>-73.36</v>
       </c>
       <c r="L62" t="n">
-        <v>98.09</v>
+        <v>74</v>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>09:55:52</t>
+          <t>09:52:58</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
@@ -2683,34 +2683,34 @@
         <v>2</v>
       </c>
       <c r="E63" t="n">
-        <v>3.83</v>
+        <v>4.35</v>
       </c>
       <c r="F63" t="n">
-        <v>9.289999999999999</v>
+        <v>10.81</v>
       </c>
       <c r="G63" t="n">
-        <v>51.5</v>
+        <v>57.2</v>
       </c>
       <c r="H63" t="n">
-        <v>57.3</v>
+        <v>70.7</v>
       </c>
       <c r="I63" t="n">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="J63" t="n">
-        <v>-22.71</v>
+        <v>121.01</v>
       </c>
       <c r="K63" t="n">
-        <v>-61.66</v>
+        <v>-0.21</v>
       </c>
       <c r="L63" t="n">
-        <v>65.70999999999999</v>
+        <v>121.01</v>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>09:57:35</t>
+          <t>09:54:27</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
@@ -2725,34 +2725,34 @@
         <v>3</v>
       </c>
       <c r="E64" t="n">
-        <v>3.9</v>
+        <v>4.14</v>
       </c>
       <c r="F64" t="n">
-        <v>9.359999999999999</v>
+        <v>10.09</v>
       </c>
       <c r="G64" t="n">
-        <v>45</v>
+        <v>48.2</v>
       </c>
       <c r="H64" t="n">
-        <v>41.5</v>
+        <v>54.3</v>
       </c>
       <c r="I64" t="n">
-        <v>24</v>
+        <v>27</v>
       </c>
       <c r="J64" t="n">
-        <v>-42.42</v>
+        <v>-66.13</v>
       </c>
       <c r="K64" t="n">
-        <v>-51.67</v>
+        <v>84.65000000000001</v>
       </c>
       <c r="L64" t="n">
-        <v>66.86</v>
+        <v>107.42</v>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>10:03:34</t>
+          <t>09:58:36</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
@@ -2767,34 +2767,34 @@
         <v>1</v>
       </c>
       <c r="E65" t="n">
-        <v>4.14</v>
+        <v>4.3</v>
       </c>
       <c r="F65" t="n">
         <v>10.81</v>
       </c>
       <c r="G65" t="n">
-        <v>41.6</v>
+        <v>45.8</v>
       </c>
       <c r="H65" t="n">
-        <v>60.1</v>
+        <v>37.5</v>
       </c>
       <c r="I65" t="n">
-        <v>29</v>
+        <v>24</v>
       </c>
       <c r="J65" t="n">
-        <v>-61.8</v>
+        <v>-88.12</v>
       </c>
       <c r="K65" t="n">
-        <v>74.7</v>
+        <v>-55.9</v>
       </c>
       <c r="L65" t="n">
-        <v>96.95</v>
+        <v>104.35</v>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>10:05:32</t>
+          <t>10:00:33</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
@@ -2809,34 +2809,34 @@
         <v>2</v>
       </c>
       <c r="E66" t="n">
-        <v>3.31</v>
+        <v>4.09</v>
       </c>
       <c r="F66" t="n">
-        <v>9.33</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="G66" t="n">
-        <v>41.8</v>
+        <v>50.7</v>
       </c>
       <c r="H66" t="n">
-        <v>75.8</v>
+        <v>56.7</v>
       </c>
       <c r="I66" t="n">
-        <v>19</v>
+        <v>28</v>
       </c>
       <c r="J66" t="n">
-        <v>103.38</v>
+        <v>48.53</v>
       </c>
       <c r="K66" t="n">
-        <v>0.25</v>
+        <v>103.23</v>
       </c>
       <c r="L66" t="n">
-        <v>103.38</v>
+        <v>114.06</v>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>10:07:41</t>
+          <t>10:01:18</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
@@ -2851,34 +2851,34 @@
         <v>3</v>
       </c>
       <c r="E67" t="n">
-        <v>4.66</v>
+        <v>3.96</v>
       </c>
       <c r="F67" t="n">
-        <v>10.51</v>
+        <v>10.32</v>
       </c>
       <c r="G67" t="n">
-        <v>42.9</v>
+        <v>53.7</v>
       </c>
       <c r="H67" t="n">
-        <v>72.3</v>
+        <v>66</v>
       </c>
       <c r="I67" t="n">
-        <v>19</v>
+        <v>23</v>
       </c>
       <c r="J67" t="n">
-        <v>125.02</v>
+        <v>-32.35</v>
       </c>
       <c r="K67" t="n">
-        <v>73.79000000000001</v>
+        <v>-118.26</v>
       </c>
       <c r="L67" t="n">
-        <v>145.17</v>
+        <v>122.6</v>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>10:11:56</t>
+          <t>10:05:24</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
@@ -2893,34 +2893,34 @@
         <v>1</v>
       </c>
       <c r="E68" t="n">
-        <v>4.21</v>
+        <v>4.13</v>
       </c>
       <c r="F68" t="n">
         <v>10.81</v>
       </c>
       <c r="G68" t="n">
-        <v>41</v>
+        <v>68</v>
       </c>
       <c r="H68" t="n">
-        <v>64.40000000000001</v>
+        <v>66.59999999999999</v>
       </c>
       <c r="I68" t="n">
-        <v>19</v>
+        <v>32</v>
       </c>
       <c r="J68" t="n">
-        <v>3.52</v>
+        <v>100.94</v>
       </c>
       <c r="K68" t="n">
-        <v>236.48</v>
+        <v>-42.93</v>
       </c>
       <c r="L68" t="n">
-        <v>236.5</v>
+        <v>109.7</v>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>10:12:58</t>
+          <t>10:08:02</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
@@ -2935,34 +2935,34 @@
         <v>2</v>
       </c>
       <c r="E69" t="n">
-        <v>4.37</v>
+        <v>4.3</v>
       </c>
       <c r="F69" t="n">
-        <v>10.81</v>
+        <v>10.49</v>
       </c>
       <c r="G69" t="n">
-        <v>49.4</v>
+        <v>51.9</v>
       </c>
       <c r="H69" t="n">
-        <v>40.6</v>
+        <v>88.90000000000001</v>
       </c>
       <c r="I69" t="n">
-        <v>22</v>
+        <v>29</v>
       </c>
       <c r="J69" t="n">
-        <v>-87.66</v>
+        <v>-257.35</v>
       </c>
       <c r="K69" t="n">
-        <v>163.08</v>
+        <v>129.05</v>
       </c>
       <c r="L69" t="n">
-        <v>185.15</v>
+        <v>287.9</v>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>10:14:43</t>
+          <t>10:09:59</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
@@ -2977,34 +2977,34 @@
         <v>3</v>
       </c>
       <c r="E70" t="n">
-        <v>4.27</v>
+        <v>4.23</v>
       </c>
       <c r="F70" t="n">
-        <v>9.02</v>
+        <v>9.57</v>
       </c>
       <c r="G70" t="n">
-        <v>54.9</v>
+        <v>37.9</v>
       </c>
       <c r="H70" t="n">
-        <v>64</v>
+        <v>0</v>
       </c>
       <c r="I70" t="n">
-        <v>29</v>
+        <v>25</v>
       </c>
       <c r="J70" t="n">
-        <v>97.68000000000001</v>
+        <v>265.37</v>
       </c>
       <c r="K70" t="n">
-        <v>147.43</v>
+        <v>22.41</v>
       </c>
       <c r="L70" t="n">
-        <v>176.85</v>
+        <v>266.32</v>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>10:19:50</t>
+          <t>10:15:03</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
@@ -3019,34 +3019,34 @@
         <v>1</v>
       </c>
       <c r="E71" t="n">
-        <v>4.65</v>
+        <v>3.59</v>
       </c>
       <c r="F71" t="n">
-        <v>9.35</v>
+        <v>7.33</v>
       </c>
       <c r="G71" t="n">
-        <v>43.2</v>
+        <v>39.8</v>
       </c>
       <c r="H71" t="n">
-        <v>72.3</v>
+        <v>56.1</v>
       </c>
       <c r="I71" t="n">
-        <v>29</v>
+        <v>27</v>
       </c>
       <c r="J71" t="n">
-        <v>-194.57</v>
+        <v>62.5</v>
       </c>
       <c r="K71" t="n">
-        <v>202.98</v>
+        <v>-271.13</v>
       </c>
       <c r="L71" t="n">
-        <v>281.17</v>
+        <v>278.24</v>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>10:21:40</t>
+          <t>10:16:22</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
@@ -3061,34 +3061,34 @@
         <v>2</v>
       </c>
       <c r="E72" t="n">
-        <v>3.25</v>
+        <v>4.41</v>
       </c>
       <c r="F72" t="n">
-        <v>8.710000000000001</v>
+        <v>10.81</v>
       </c>
       <c r="G72" t="n">
-        <v>42.6</v>
+        <v>41</v>
       </c>
       <c r="H72" t="n">
-        <v>69</v>
+        <v>89.59999999999999</v>
       </c>
       <c r="I72" t="n">
-        <v>25</v>
+        <v>31</v>
       </c>
       <c r="J72" t="n">
-        <v>178.31</v>
+        <v>-248.61</v>
       </c>
       <c r="K72" t="n">
-        <v>-17.96</v>
+        <v>193.62</v>
       </c>
       <c r="L72" t="n">
-        <v>179.21</v>
+        <v>315.12</v>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>10:23:11</t>
+          <t>10:17:39</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
@@ -3103,34 +3103,34 @@
         <v>3</v>
       </c>
       <c r="E73" t="n">
-        <v>4.55</v>
+        <v>4.59</v>
       </c>
       <c r="F73" t="n">
         <v>10.81</v>
       </c>
       <c r="G73" t="n">
-        <v>31.8</v>
+        <v>36.4</v>
       </c>
       <c r="H73" t="n">
-        <v>72.90000000000001</v>
+        <v>57.4</v>
       </c>
       <c r="I73" t="n">
-        <v>17</v>
+        <v>24</v>
       </c>
       <c r="J73" t="n">
-        <v>297.07</v>
+        <v>-51.97</v>
       </c>
       <c r="K73" t="n">
-        <v>-109.82</v>
+        <v>-318.64</v>
       </c>
       <c r="L73" t="n">
-        <v>316.72</v>
+        <v>322.85</v>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>10:33:51</t>
+          <t>10:26:26</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
@@ -3145,34 +3145,34 @@
         <v>1</v>
       </c>
       <c r="E74" t="n">
-        <v>4.16</v>
+        <v>4.14</v>
       </c>
       <c r="F74" t="n">
-        <v>9.49</v>
+        <v>10.81</v>
       </c>
       <c r="G74" t="n">
-        <v>53.7</v>
+        <v>42</v>
       </c>
       <c r="H74" t="n">
-        <v>100</v>
+        <v>62.3</v>
       </c>
       <c r="I74" t="n">
-        <v>21</v>
+        <v>32</v>
       </c>
       <c r="J74" t="n">
-        <v>63.25</v>
+        <v>19.82</v>
       </c>
       <c r="K74" t="n">
-        <v>-0.88</v>
+        <v>23.86</v>
       </c>
       <c r="L74" t="n">
-        <v>63.26</v>
+        <v>31.01</v>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>10:35:11</t>
+          <t>10:28:15</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
@@ -3187,34 +3187,34 @@
         <v>2</v>
       </c>
       <c r="E75" t="n">
-        <v>4.24</v>
+        <v>4.54</v>
       </c>
       <c r="F75" t="n">
-        <v>10.81</v>
+        <v>10.53</v>
       </c>
       <c r="G75" t="n">
-        <v>32.4</v>
+        <v>43.7</v>
       </c>
       <c r="H75" t="n">
-        <v>78.7</v>
+        <v>38.9</v>
       </c>
       <c r="I75" t="n">
-        <v>26</v>
+        <v>32</v>
       </c>
       <c r="J75" t="n">
-        <v>54.61</v>
+        <v>80.01000000000001</v>
       </c>
       <c r="K75" t="n">
-        <v>-53.64</v>
+        <v>-36.3</v>
       </c>
       <c r="L75" t="n">
-        <v>76.55</v>
+        <v>87.86</v>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>10:37:11</t>
+          <t>10:29:12</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
@@ -3229,34 +3229,34 @@
         <v>3</v>
       </c>
       <c r="E76" t="n">
-        <v>4.36</v>
+        <v>4.32</v>
       </c>
       <c r="F76" t="n">
-        <v>9.199999999999999</v>
+        <v>10.4</v>
       </c>
       <c r="G76" t="n">
-        <v>41.9</v>
+        <v>45.9</v>
       </c>
       <c r="H76" t="n">
-        <v>43.5</v>
+        <v>43.2</v>
       </c>
       <c r="I76" t="n">
-        <v>18</v>
+        <v>26</v>
       </c>
       <c r="J76" t="n">
-        <v>27.88</v>
+        <v>78.98999999999999</v>
       </c>
       <c r="K76" t="n">
-        <v>-65.79000000000001</v>
+        <v>52.46</v>
       </c>
       <c r="L76" t="n">
-        <v>71.45999999999999</v>
+        <v>94.81999999999999</v>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>10:42:39</t>
+          <t>10:33:29</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
@@ -3271,34 +3271,34 @@
         <v>1</v>
       </c>
       <c r="E77" t="n">
-        <v>4.5</v>
+        <v>4.47</v>
       </c>
       <c r="F77" t="n">
-        <v>10.81</v>
+        <v>8.84</v>
       </c>
       <c r="G77" t="n">
-        <v>64.3</v>
+        <v>30.3</v>
       </c>
       <c r="H77" t="n">
-        <v>61.9</v>
+        <v>51.2</v>
       </c>
       <c r="I77" t="n">
-        <v>24</v>
+        <v>21</v>
       </c>
       <c r="J77" t="n">
-        <v>88.98</v>
+        <v>153.27</v>
       </c>
       <c r="K77" t="n">
-        <v>15.81</v>
+        <v>11.97</v>
       </c>
       <c r="L77" t="n">
-        <v>90.37</v>
+        <v>153.74</v>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>10:44:21</t>
+          <t>10:34:20</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
@@ -3313,34 +3313,34 @@
         <v>2</v>
       </c>
       <c r="E78" t="n">
-        <v>4.6</v>
+        <v>4.12</v>
       </c>
       <c r="F78" t="n">
         <v>10.81</v>
       </c>
       <c r="G78" t="n">
-        <v>27.1</v>
+        <v>32.2</v>
       </c>
       <c r="H78" t="n">
-        <v>86.59999999999999</v>
+        <v>77.5</v>
       </c>
       <c r="I78" t="n">
-        <v>21</v>
+        <v>30</v>
       </c>
       <c r="J78" t="n">
-        <v>21.91</v>
+        <v>2.11</v>
       </c>
       <c r="K78" t="n">
-        <v>-114.31</v>
+        <v>-120.73</v>
       </c>
       <c r="L78" t="n">
-        <v>116.39</v>
+        <v>120.75</v>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>10:45:52</t>
+          <t>10:35:45</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
@@ -3355,34 +3355,34 @@
         <v>3</v>
       </c>
       <c r="E79" t="n">
-        <v>4.64</v>
+        <v>4.35</v>
       </c>
       <c r="F79" t="n">
         <v>10.81</v>
       </c>
       <c r="G79" t="n">
-        <v>58.5</v>
+        <v>34.4</v>
       </c>
       <c r="H79" t="n">
-        <v>62.1</v>
+        <v>33.6</v>
       </c>
       <c r="I79" t="n">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="J79" t="n">
-        <v>-3.67</v>
+        <v>-12.05</v>
       </c>
       <c r="K79" t="n">
-        <v>101.87</v>
+        <v>-139.4</v>
       </c>
       <c r="L79" t="n">
-        <v>101.94</v>
+        <v>139.92</v>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>10:50:09</t>
+          <t>10:40:14</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
@@ -3397,34 +3397,34 @@
         <v>1</v>
       </c>
       <c r="E80" t="n">
-        <v>3.98</v>
+        <v>4</v>
       </c>
       <c r="F80" t="n">
-        <v>9.56</v>
+        <v>10.4</v>
       </c>
       <c r="G80" t="n">
-        <v>46.2</v>
+        <v>55.2</v>
       </c>
       <c r="H80" t="n">
-        <v>100</v>
+        <v>90.2</v>
       </c>
       <c r="I80" t="n">
-        <v>24</v>
+        <v>30</v>
       </c>
       <c r="J80" t="n">
-        <v>112.22</v>
+        <v>-105.41</v>
       </c>
       <c r="K80" t="n">
-        <v>39.1</v>
+        <v>-55.99</v>
       </c>
       <c r="L80" t="n">
-        <v>118.84</v>
+        <v>119.36</v>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>10:51:22</t>
+          <t>10:41:18</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
@@ -3439,34 +3439,34 @@
         <v>2</v>
       </c>
       <c r="E81" t="n">
-        <v>4.08</v>
+        <v>4.19</v>
       </c>
       <c r="F81" t="n">
-        <v>10.81</v>
+        <v>9.210000000000001</v>
       </c>
       <c r="G81" t="n">
-        <v>42.3</v>
+        <v>37.5</v>
       </c>
       <c r="H81" t="n">
-        <v>79.90000000000001</v>
+        <v>96.90000000000001</v>
       </c>
       <c r="I81" t="n">
-        <v>17</v>
+        <v>28</v>
       </c>
       <c r="J81" t="n">
-        <v>132.19</v>
+        <v>37.11</v>
       </c>
       <c r="K81" t="n">
-        <v>50.66</v>
+        <v>147.08</v>
       </c>
       <c r="L81" t="n">
-        <v>141.56</v>
+        <v>151.69</v>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>10:52:35</t>
+          <t>10:42:42</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
@@ -3481,34 +3481,34 @@
         <v>3</v>
       </c>
       <c r="E82" t="n">
-        <v>4.53</v>
+        <v>4.71</v>
       </c>
       <c r="F82" t="n">
-        <v>10.71</v>
+        <v>10.81</v>
       </c>
       <c r="G82" t="n">
-        <v>42</v>
+        <v>51.5</v>
       </c>
       <c r="H82" t="n">
-        <v>40.6</v>
+        <v>57.3</v>
       </c>
       <c r="I82" t="n">
-        <v>27</v>
+        <v>32</v>
       </c>
       <c r="J82" t="n">
-        <v>178.44</v>
+        <v>-70.68000000000001</v>
       </c>
       <c r="K82" t="n">
-        <v>75.31</v>
+        <v>-142.97</v>
       </c>
       <c r="L82" t="n">
-        <v>193.68</v>
+        <v>159.49</v>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>10:57:03</t>
+          <t>10:46:39</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
@@ -3523,34 +3523,34 @@
         <v>1</v>
       </c>
       <c r="E83" t="n">
-        <v>4.38</v>
+        <v>4.05</v>
       </c>
       <c r="F83" t="n">
-        <v>9.609999999999999</v>
+        <v>9.99</v>
       </c>
       <c r="G83" t="n">
-        <v>44.7</v>
+        <v>45.4</v>
       </c>
       <c r="H83" t="n">
-        <v>77.40000000000001</v>
+        <v>64.59999999999999</v>
       </c>
       <c r="I83" t="n">
-        <v>21</v>
+        <v>30</v>
       </c>
       <c r="J83" t="n">
-        <v>83.75</v>
+        <v>176.39</v>
       </c>
       <c r="K83" t="n">
-        <v>-233.3</v>
+        <v>-121.91</v>
       </c>
       <c r="L83" t="n">
-        <v>247.88</v>
+        <v>214.42</v>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>10:57:51</t>
+          <t>10:49:01</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
@@ -3565,34 +3565,34 @@
         <v>2</v>
       </c>
       <c r="E84" t="n">
-        <v>4.35</v>
+        <v>4.13</v>
       </c>
       <c r="F84" t="n">
-        <v>10.81</v>
+        <v>9.470000000000001</v>
       </c>
       <c r="G84" t="n">
-        <v>41.9</v>
+        <v>41.6</v>
       </c>
       <c r="H84" t="n">
-        <v>74</v>
+        <v>60.1</v>
       </c>
       <c r="I84" t="n">
-        <v>19</v>
+        <v>23</v>
       </c>
       <c r="J84" t="n">
-        <v>236.27</v>
+        <v>-169.48</v>
       </c>
       <c r="K84" t="n">
-        <v>34.96</v>
+        <v>114.4</v>
       </c>
       <c r="L84" t="n">
-        <v>238.84</v>
+        <v>204.48</v>
       </c>
     </row>
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>10:58:51</t>
+          <t>10:50:52</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
@@ -3607,34 +3607,34 @@
         <v>3</v>
       </c>
       <c r="E85" t="n">
-        <v>4.37</v>
+        <v>3.44</v>
       </c>
       <c r="F85" t="n">
-        <v>10.81</v>
+        <v>9.85</v>
       </c>
       <c r="G85" t="n">
-        <v>42.8</v>
+        <v>47.5</v>
       </c>
       <c r="H85" t="n">
-        <v>66.90000000000001</v>
+        <v>56.8</v>
       </c>
       <c r="I85" t="n">
-        <v>21</v>
+        <v>24</v>
       </c>
       <c r="J85" t="n">
-        <v>149.14</v>
+        <v>198.74</v>
       </c>
       <c r="K85" t="n">
-        <v>-173.21</v>
+        <v>-55.83</v>
       </c>
       <c r="L85" t="n">
-        <v>228.57</v>
+        <v>206.43</v>
       </c>
     </row>
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>11:03:35</t>
+          <t>10:55:26</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
@@ -3649,34 +3649,34 @@
         <v>1</v>
       </c>
       <c r="E86" t="n">
-        <v>4.68</v>
+        <v>4.4</v>
       </c>
       <c r="F86" t="n">
         <v>10.81</v>
       </c>
       <c r="G86" t="n">
-        <v>47.6</v>
+        <v>42.9</v>
       </c>
       <c r="H86" t="n">
-        <v>32.1</v>
+        <v>72.3</v>
       </c>
       <c r="I86" t="n">
         <v>21</v>
       </c>
       <c r="J86" t="n">
-        <v>-287.84</v>
+        <v>-274.12</v>
       </c>
       <c r="K86" t="n">
-        <v>186.94</v>
+        <v>-198.01</v>
       </c>
       <c r="L86" t="n">
-        <v>343.22</v>
+        <v>338.15</v>
       </c>
     </row>
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>11:05:49</t>
+          <t>10:56:56</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
@@ -3691,34 +3691,34 @@
         <v>2</v>
       </c>
       <c r="E87" t="n">
-        <v>4.79</v>
+        <v>4.65</v>
       </c>
       <c r="F87" t="n">
-        <v>10.81</v>
+        <v>10.58</v>
       </c>
       <c r="G87" t="n">
-        <v>54.3</v>
+        <v>47.8</v>
       </c>
       <c r="H87" t="n">
-        <v>85.5</v>
+        <v>56.3</v>
       </c>
       <c r="I87" t="n">
-        <v>19</v>
+        <v>23</v>
       </c>
       <c r="J87" t="n">
-        <v>119.69</v>
+        <v>-291.52</v>
       </c>
       <c r="K87" t="n">
-        <v>258.82</v>
+        <v>-202.76</v>
       </c>
       <c r="L87" t="n">
-        <v>285.15</v>
+        <v>355.1</v>
       </c>
     </row>
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>11:07:47</t>
+          <t>10:59:00</t>
         </is>
       </c>
       <c r="B88" t="inlineStr">
@@ -3733,28 +3733,28 @@
         <v>3</v>
       </c>
       <c r="E88" t="n">
-        <v>4.35</v>
+        <v>4.44</v>
       </c>
       <c r="F88" t="n">
-        <v>10.73</v>
+        <v>10.81</v>
       </c>
       <c r="G88" t="n">
-        <v>47.6</v>
+        <v>55</v>
       </c>
       <c r="H88" t="n">
-        <v>33.1</v>
+        <v>56.5</v>
       </c>
       <c r="I88" t="n">
-        <v>24</v>
+        <v>21</v>
       </c>
       <c r="J88" t="n">
-        <v>-13.83</v>
+        <v>237.67</v>
       </c>
       <c r="K88" t="n">
-        <v>312.37</v>
+        <v>-193.75</v>
       </c>
       <c r="L88" t="n">
-        <v>312.67</v>
+        <v>306.64</v>
       </c>
     </row>
   </sheetData>

--- a/output/2024-10-08.xlsx
+++ b/output/2024-10-08.xlsx
@@ -640,13 +640,13 @@
         <v>23</v>
       </c>
       <c r="J14" t="n">
-        <v>55.55</v>
+        <v>66.51000000000001</v>
       </c>
       <c r="K14" t="n">
-        <v>-29.86</v>
+        <v>-35.75</v>
       </c>
       <c r="L14" t="n">
-        <v>63.07</v>
+        <v>75.51000000000001</v>
       </c>
     </row>
     <row r="15">
@@ -682,13 +682,13 @@
         <v>23</v>
       </c>
       <c r="J15" t="n">
-        <v>-38.89</v>
+        <v>-46.49</v>
       </c>
       <c r="K15" t="n">
-        <v>52.96</v>
+        <v>63.3</v>
       </c>
       <c r="L15" t="n">
-        <v>65.70999999999999</v>
+        <v>78.53</v>
       </c>
     </row>
     <row r="16">
@@ -724,13 +724,13 @@
         <v>20</v>
       </c>
       <c r="J16" t="n">
-        <v>-39.32</v>
+        <v>-42.02</v>
       </c>
       <c r="K16" t="n">
-        <v>92.8</v>
+        <v>99.15000000000001</v>
       </c>
       <c r="L16" t="n">
-        <v>100.79</v>
+        <v>107.69</v>
       </c>
     </row>
     <row r="17">
@@ -766,13 +766,13 @@
         <v>25</v>
       </c>
       <c r="J17" t="n">
-        <v>-57.21</v>
+        <v>-66.06</v>
       </c>
       <c r="K17" t="n">
-        <v>57.41</v>
+        <v>66.28</v>
       </c>
       <c r="L17" t="n">
-        <v>81.05</v>
+        <v>93.58</v>
       </c>
     </row>
     <row r="18">
@@ -808,13 +808,13 @@
         <v>23</v>
       </c>
       <c r="J18" t="n">
-        <v>-48.79</v>
+        <v>-58.22</v>
       </c>
       <c r="K18" t="n">
-        <v>-61.23</v>
+        <v>-73.08</v>
       </c>
       <c r="L18" t="n">
-        <v>78.29000000000001</v>
+        <v>93.44</v>
       </c>
     </row>
     <row r="19">
@@ -850,13 +850,13 @@
         <v>19</v>
       </c>
       <c r="J19" t="n">
-        <v>96.31999999999999</v>
+        <v>113.03</v>
       </c>
       <c r="K19" t="n">
-        <v>9.91</v>
+        <v>11.63</v>
       </c>
       <c r="L19" t="n">
-        <v>96.83</v>
+        <v>113.63</v>
       </c>
     </row>
     <row r="20">
@@ -892,13 +892,13 @@
         <v>22</v>
       </c>
       <c r="J20" t="n">
-        <v>46.91</v>
+        <v>52.54</v>
       </c>
       <c r="K20" t="n">
-        <v>169.81</v>
+        <v>190.22</v>
       </c>
       <c r="L20" t="n">
-        <v>176.17</v>
+        <v>197.34</v>
       </c>
     </row>
     <row r="21">
@@ -934,13 +934,13 @@
         <v>25</v>
       </c>
       <c r="J21" t="n">
-        <v>168.09</v>
+        <v>183.78</v>
       </c>
       <c r="K21" t="n">
-        <v>12.83</v>
+        <v>14.03</v>
       </c>
       <c r="L21" t="n">
-        <v>168.58</v>
+        <v>184.32</v>
       </c>
     </row>
     <row r="22">
@@ -976,13 +976,13 @@
         <v>19</v>
       </c>
       <c r="J22" t="n">
-        <v>-11.11</v>
+        <v>-13.95</v>
       </c>
       <c r="K22" t="n">
-        <v>123.69</v>
+        <v>155.36</v>
       </c>
       <c r="L22" t="n">
-        <v>124.19</v>
+        <v>155.99</v>
       </c>
     </row>
     <row r="23">
@@ -1018,13 +1018,13 @@
         <v>22</v>
       </c>
       <c r="J23" t="n">
-        <v>-152.28</v>
+        <v>-182.66</v>
       </c>
       <c r="K23" t="n">
-        <v>-148.62</v>
+        <v>-178.28</v>
       </c>
       <c r="L23" t="n">
-        <v>212.79</v>
+        <v>255.24</v>
       </c>
     </row>
     <row r="24">
@@ -1060,13 +1060,13 @@
         <v>25</v>
       </c>
       <c r="J24" t="n">
-        <v>-0.26</v>
+        <v>-0.35</v>
       </c>
       <c r="K24" t="n">
-        <v>122.6</v>
+        <v>166.59</v>
       </c>
       <c r="L24" t="n">
-        <v>122.6</v>
+        <v>166.59</v>
       </c>
     </row>
     <row r="25">
@@ -1102,13 +1102,13 @@
         <v>23</v>
       </c>
       <c r="J25" t="n">
-        <v>-135.84</v>
+        <v>-174.36</v>
       </c>
       <c r="K25" t="n">
-        <v>80.73</v>
+        <v>103.63</v>
       </c>
       <c r="L25" t="n">
-        <v>158.02</v>
+        <v>202.83</v>
       </c>
     </row>
     <row r="26">
@@ -1144,13 +1144,13 @@
         <v>23</v>
       </c>
       <c r="J26" t="n">
-        <v>-295.65</v>
+        <v>-376.62</v>
       </c>
       <c r="K26" t="n">
-        <v>-28.13</v>
+        <v>-35.84</v>
       </c>
       <c r="L26" t="n">
-        <v>296.98</v>
+        <v>378.32</v>
       </c>
     </row>
     <row r="27">
@@ -1186,13 +1186,13 @@
         <v>20</v>
       </c>
       <c r="J27" t="n">
-        <v>13.54</v>
+        <v>18.54</v>
       </c>
       <c r="K27" t="n">
-        <v>241.6</v>
+        <v>330.81</v>
       </c>
       <c r="L27" t="n">
-        <v>241.98</v>
+        <v>331.33</v>
       </c>
     </row>
     <row r="28">
@@ -1228,13 +1228,13 @@
         <v>21</v>
       </c>
       <c r="J28" t="n">
-        <v>237.27</v>
+        <v>317.67</v>
       </c>
       <c r="K28" t="n">
-        <v>114.64</v>
+        <v>153.49</v>
       </c>
       <c r="L28" t="n">
-        <v>263.51</v>
+        <v>352.81</v>
       </c>
     </row>
     <row r="29">
@@ -1270,13 +1270,13 @@
         <v>24</v>
       </c>
       <c r="J29" t="n">
-        <v>24.87</v>
+        <v>28.69</v>
       </c>
       <c r="K29" t="n">
-        <v>-74.14</v>
+        <v>-85.53</v>
       </c>
       <c r="L29" t="n">
-        <v>78.2</v>
+        <v>90.22</v>
       </c>
     </row>
     <row r="30">
@@ -1312,13 +1312,13 @@
         <v>20</v>
       </c>
       <c r="J30" t="n">
-        <v>-7.32</v>
+        <v>-8.35</v>
       </c>
       <c r="K30" t="n">
-        <v>84.02</v>
+        <v>95.88</v>
       </c>
       <c r="L30" t="n">
-        <v>84.34</v>
+        <v>96.25</v>
       </c>
     </row>
     <row r="31">
@@ -1354,13 +1354,13 @@
         <v>24</v>
       </c>
       <c r="J31" t="n">
-        <v>20.19</v>
+        <v>24.45</v>
       </c>
       <c r="K31" t="n">
-        <v>-53.27</v>
+        <v>-64.52</v>
       </c>
       <c r="L31" t="n">
-        <v>56.97</v>
+        <v>69</v>
       </c>
     </row>
     <row r="32">
@@ -1396,13 +1396,13 @@
         <v>20</v>
       </c>
       <c r="J32" t="n">
-        <v>-124.34</v>
+        <v>-134.85</v>
       </c>
       <c r="K32" t="n">
-        <v>18.73</v>
+        <v>20.32</v>
       </c>
       <c r="L32" t="n">
-        <v>125.74</v>
+        <v>136.38</v>
       </c>
     </row>
     <row r="33">
@@ -1438,13 +1438,13 @@
         <v>20</v>
       </c>
       <c r="J33" t="n">
-        <v>44.33</v>
+        <v>49.33</v>
       </c>
       <c r="K33" t="n">
-        <v>-119.7</v>
+        <v>-133.2</v>
       </c>
       <c r="L33" t="n">
-        <v>127.65</v>
+        <v>142.04</v>
       </c>
     </row>
     <row r="34">
@@ -1480,13 +1480,13 @@
         <v>19</v>
       </c>
       <c r="J34" t="n">
-        <v>-49.9</v>
+        <v>-63.47</v>
       </c>
       <c r="K34" t="n">
-        <v>-53.68</v>
+        <v>-68.26000000000001</v>
       </c>
       <c r="L34" t="n">
-        <v>73.29000000000001</v>
+        <v>93.20999999999999</v>
       </c>
     </row>
     <row r="35">
@@ -1522,13 +1522,13 @@
         <v>22</v>
       </c>
       <c r="J35" t="n">
-        <v>8.68</v>
+        <v>10.66</v>
       </c>
       <c r="K35" t="n">
-        <v>128.59</v>
+        <v>158</v>
       </c>
       <c r="L35" t="n">
-        <v>128.88</v>
+        <v>158.36</v>
       </c>
     </row>
     <row r="36">
@@ -1564,13 +1564,13 @@
         <v>22</v>
       </c>
       <c r="J36" t="n">
-        <v>67.64</v>
+        <v>84.27</v>
       </c>
       <c r="K36" t="n">
-        <v>-105.8</v>
+        <v>-131.81</v>
       </c>
       <c r="L36" t="n">
-        <v>125.57</v>
+        <v>156.45</v>
       </c>
     </row>
     <row r="37">
@@ -1606,13 +1606,13 @@
         <v>25</v>
       </c>
       <c r="J37" t="n">
-        <v>-77.09</v>
+        <v>-99.39</v>
       </c>
       <c r="K37" t="n">
-        <v>58.87</v>
+        <v>75.89</v>
       </c>
       <c r="L37" t="n">
-        <v>97</v>
+        <v>125.05</v>
       </c>
     </row>
     <row r="38">
@@ -1648,13 +1648,13 @@
         <v>20</v>
       </c>
       <c r="J38" t="n">
-        <v>144.27</v>
+        <v>190.75</v>
       </c>
       <c r="K38" t="n">
-        <v>65.69</v>
+        <v>86.84999999999999</v>
       </c>
       <c r="L38" t="n">
-        <v>158.53</v>
+        <v>209.59</v>
       </c>
     </row>
     <row r="39">
@@ -1690,13 +1690,13 @@
         <v>23</v>
       </c>
       <c r="J39" t="n">
-        <v>-0.72</v>
+        <v>-0.89</v>
       </c>
       <c r="K39" t="n">
-        <v>200.74</v>
+        <v>248.15</v>
       </c>
       <c r="L39" t="n">
-        <v>200.74</v>
+        <v>248.15</v>
       </c>
     </row>
     <row r="40">
@@ -1732,13 +1732,13 @@
         <v>23</v>
       </c>
       <c r="J40" t="n">
-        <v>51.55</v>
+        <v>64.34999999999999</v>
       </c>
       <c r="K40" t="n">
-        <v>-201.03</v>
+        <v>-250.95</v>
       </c>
       <c r="L40" t="n">
-        <v>207.54</v>
+        <v>259.06</v>
       </c>
     </row>
     <row r="41">
@@ -1774,13 +1774,13 @@
         <v>21</v>
       </c>
       <c r="J41" t="n">
-        <v>-202.33</v>
+        <v>-286.01</v>
       </c>
       <c r="K41" t="n">
-        <v>-30.99</v>
+        <v>-43.8</v>
       </c>
       <c r="L41" t="n">
-        <v>204.69</v>
+        <v>289.35</v>
       </c>
     </row>
     <row r="42">
@@ -1816,13 +1816,13 @@
         <v>21</v>
       </c>
       <c r="J42" t="n">
-        <v>-229.12</v>
+        <v>-328.08</v>
       </c>
       <c r="K42" t="n">
-        <v>61.33</v>
+        <v>87.81999999999999</v>
       </c>
       <c r="L42" t="n">
-        <v>237.19</v>
+        <v>339.63</v>
       </c>
     </row>
     <row r="43">
@@ -1858,13 +1858,13 @@
         <v>24</v>
       </c>
       <c r="J43" t="n">
-        <v>-228.61</v>
+        <v>-304.01</v>
       </c>
       <c r="K43" t="n">
-        <v>-33.85</v>
+        <v>-45.01</v>
       </c>
       <c r="L43" t="n">
-        <v>231.1</v>
+        <v>307.32</v>
       </c>
     </row>
     <row r="44">
@@ -1900,13 +1900,13 @@
         <v>25</v>
       </c>
       <c r="J44" t="n">
-        <v>-63.87</v>
+        <v>-71.90000000000001</v>
       </c>
       <c r="K44" t="n">
-        <v>-45.12</v>
+        <v>-50.8</v>
       </c>
       <c r="L44" t="n">
-        <v>78.2</v>
+        <v>88.03</v>
       </c>
     </row>
     <row r="45">
@@ -1942,13 +1942,13 @@
         <v>22</v>
       </c>
       <c r="J45" t="n">
-        <v>-31.27</v>
+        <v>-39.66</v>
       </c>
       <c r="K45" t="n">
-        <v>43.31</v>
+        <v>54.94</v>
       </c>
       <c r="L45" t="n">
-        <v>53.42</v>
+        <v>67.76000000000001</v>
       </c>
     </row>
     <row r="46">
@@ -1984,13 +1984,13 @@
         <v>25</v>
       </c>
       <c r="J46" t="n">
-        <v>38.57</v>
+        <v>47.04</v>
       </c>
       <c r="K46" t="n">
-        <v>38.57</v>
+        <v>47.05</v>
       </c>
       <c r="L46" t="n">
-        <v>54.54</v>
+        <v>66.54000000000001</v>
       </c>
     </row>
     <row r="47">
@@ -2026,13 +2026,13 @@
         <v>19</v>
       </c>
       <c r="J47" t="n">
-        <v>-108.77</v>
+        <v>-123.64</v>
       </c>
       <c r="K47" t="n">
-        <v>-1.74</v>
+        <v>-1.98</v>
       </c>
       <c r="L47" t="n">
-        <v>108.79</v>
+        <v>123.65</v>
       </c>
     </row>
     <row r="48">
@@ -2068,13 +2068,13 @@
         <v>25</v>
       </c>
       <c r="J48" t="n">
-        <v>-73.28</v>
+        <v>-88.14</v>
       </c>
       <c r="K48" t="n">
-        <v>21.79</v>
+        <v>26.21</v>
       </c>
       <c r="L48" t="n">
-        <v>76.45</v>
+        <v>91.95</v>
       </c>
     </row>
     <row r="49">
@@ -2110,13 +2110,13 @@
         <v>23</v>
       </c>
       <c r="J49" t="n">
-        <v>-11.92</v>
+        <v>-13.2</v>
       </c>
       <c r="K49" t="n">
-        <v>107.86</v>
+        <v>119.48</v>
       </c>
       <c r="L49" t="n">
-        <v>108.51</v>
+        <v>120.21</v>
       </c>
     </row>
     <row r="50">
@@ -2152,13 +2152,13 @@
         <v>25</v>
       </c>
       <c r="J50" t="n">
-        <v>-148.86</v>
+        <v>-169.45</v>
       </c>
       <c r="K50" t="n">
-        <v>-102.67</v>
+        <v>-116.86</v>
       </c>
       <c r="L50" t="n">
-        <v>180.83</v>
+        <v>205.84</v>
       </c>
     </row>
     <row r="51">
@@ -2194,13 +2194,13 @@
         <v>19</v>
       </c>
       <c r="J51" t="n">
-        <v>2.69</v>
+        <v>3.38</v>
       </c>
       <c r="K51" t="n">
-        <v>-130.9</v>
+        <v>-164.31</v>
       </c>
       <c r="L51" t="n">
-        <v>130.93</v>
+        <v>164.34</v>
       </c>
     </row>
     <row r="52">
@@ -2236,13 +2236,13 @@
         <v>22</v>
       </c>
       <c r="J52" t="n">
-        <v>-88.09999999999999</v>
+        <v>-110.66</v>
       </c>
       <c r="K52" t="n">
-        <v>116.42</v>
+        <v>146.22</v>
       </c>
       <c r="L52" t="n">
-        <v>146</v>
+        <v>183.37</v>
       </c>
     </row>
     <row r="53">
@@ -2278,13 +2278,13 @@
         <v>21</v>
       </c>
       <c r="J53" t="n">
-        <v>192.82</v>
+        <v>234.44</v>
       </c>
       <c r="K53" t="n">
-        <v>-122.76</v>
+        <v>-149.27</v>
       </c>
       <c r="L53" t="n">
-        <v>228.58</v>
+        <v>277.93</v>
       </c>
     </row>
     <row r="54">
@@ -2320,13 +2320,13 @@
         <v>23</v>
       </c>
       <c r="J54" t="n">
-        <v>-128.53</v>
+        <v>-163.74</v>
       </c>
       <c r="K54" t="n">
-        <v>114.47</v>
+        <v>145.83</v>
       </c>
       <c r="L54" t="n">
-        <v>172.11</v>
+        <v>219.27</v>
       </c>
     </row>
     <row r="55">
@@ -2362,13 +2362,13 @@
         <v>23</v>
       </c>
       <c r="J55" t="n">
-        <v>-51.94</v>
+        <v>-65.40000000000001</v>
       </c>
       <c r="K55" t="n">
-        <v>-175.63</v>
+        <v>-221.17</v>
       </c>
       <c r="L55" t="n">
-        <v>183.15</v>
+        <v>230.64</v>
       </c>
     </row>
     <row r="56">
@@ -2404,13 +2404,13 @@
         <v>22</v>
       </c>
       <c r="J56" t="n">
-        <v>-208.22</v>
+        <v>-284.28</v>
       </c>
       <c r="K56" t="n">
-        <v>68.25</v>
+        <v>93.18000000000001</v>
       </c>
       <c r="L56" t="n">
-        <v>219.12</v>
+        <v>299.16</v>
       </c>
     </row>
     <row r="57">
@@ -2446,13 +2446,13 @@
         <v>22</v>
       </c>
       <c r="J57" t="n">
-        <v>-13.07</v>
+        <v>-19.07</v>
       </c>
       <c r="K57" t="n">
-        <v>-280.44</v>
+        <v>-409.28</v>
       </c>
       <c r="L57" t="n">
-        <v>280.75</v>
+        <v>409.73</v>
       </c>
     </row>
     <row r="58">
@@ -2488,13 +2488,13 @@
         <v>19</v>
       </c>
       <c r="J58" t="n">
-        <v>-235.99</v>
+        <v>-311.28</v>
       </c>
       <c r="K58" t="n">
-        <v>-249.04</v>
+        <v>-328.49</v>
       </c>
       <c r="L58" t="n">
-        <v>343.09</v>
+        <v>452.55</v>
       </c>
     </row>
     <row r="59">
@@ -2530,13 +2530,13 @@
         <v>22</v>
       </c>
       <c r="J59" t="n">
-        <v>80.61</v>
+        <v>94.04000000000001</v>
       </c>
       <c r="K59" t="n">
-        <v>-2.8</v>
+        <v>-3.27</v>
       </c>
       <c r="L59" t="n">
-        <v>80.66</v>
+        <v>94.09999999999999</v>
       </c>
     </row>
     <row r="60">
@@ -2572,13 +2572,13 @@
         <v>20</v>
       </c>
       <c r="J60" t="n">
-        <v>73.88</v>
+        <v>81.51000000000001</v>
       </c>
       <c r="K60" t="n">
-        <v>65.95999999999999</v>
+        <v>72.78</v>
       </c>
       <c r="L60" t="n">
-        <v>99.04000000000001</v>
+        <v>109.28</v>
       </c>
     </row>
     <row r="61">
@@ -2614,13 +2614,13 @@
         <v>24</v>
       </c>
       <c r="J61" t="n">
-        <v>-46.33</v>
+        <v>-57.96</v>
       </c>
       <c r="K61" t="n">
-        <v>-28.25</v>
+        <v>-35.35</v>
       </c>
       <c r="L61" t="n">
-        <v>54.27</v>
+        <v>67.89</v>
       </c>
     </row>
     <row r="62">
@@ -2656,13 +2656,13 @@
         <v>22</v>
       </c>
       <c r="J62" t="n">
-        <v>-83.16</v>
+        <v>-95.27</v>
       </c>
       <c r="K62" t="n">
-        <v>-48.85</v>
+        <v>-55.97</v>
       </c>
       <c r="L62" t="n">
-        <v>96.45</v>
+        <v>110.49</v>
       </c>
     </row>
     <row r="63">
@@ -2698,13 +2698,13 @@
         <v>23</v>
       </c>
       <c r="J63" t="n">
-        <v>-73.56999999999999</v>
+        <v>-90.22</v>
       </c>
       <c r="K63" t="n">
-        <v>-24.52</v>
+        <v>-30.07</v>
       </c>
       <c r="L63" t="n">
-        <v>77.55</v>
+        <v>95.09999999999999</v>
       </c>
     </row>
     <row r="64">
@@ -2740,13 +2740,13 @@
         <v>19</v>
       </c>
       <c r="J64" t="n">
-        <v>-24.87</v>
+        <v>-29.3</v>
       </c>
       <c r="K64" t="n">
-        <v>-94.48999999999999</v>
+        <v>-111.3</v>
       </c>
       <c r="L64" t="n">
-        <v>97.70999999999999</v>
+        <v>115.1</v>
       </c>
     </row>
     <row r="65">
@@ -2782,13 +2782,13 @@
         <v>20</v>
       </c>
       <c r="J65" t="n">
-        <v>148.1</v>
+        <v>174.95</v>
       </c>
       <c r="K65" t="n">
-        <v>70.94</v>
+        <v>83.8</v>
       </c>
       <c r="L65" t="n">
-        <v>164.22</v>
+        <v>193.98</v>
       </c>
     </row>
     <row r="66">
@@ -2824,13 +2824,13 @@
         <v>19</v>
       </c>
       <c r="J66" t="n">
-        <v>-3.65</v>
+        <v>-4.85</v>
       </c>
       <c r="K66" t="n">
-        <v>-119.68</v>
+        <v>-159.02</v>
       </c>
       <c r="L66" t="n">
-        <v>119.74</v>
+        <v>159.1</v>
       </c>
     </row>
     <row r="67">
@@ -2866,13 +2866,13 @@
         <v>19</v>
       </c>
       <c r="J67" t="n">
-        <v>247.1</v>
+        <v>269.04</v>
       </c>
       <c r="K67" t="n">
-        <v>-179.34</v>
+        <v>-195.26</v>
       </c>
       <c r="L67" t="n">
-        <v>305.32</v>
+        <v>332.43</v>
       </c>
     </row>
     <row r="68">
@@ -2908,13 +2908,13 @@
         <v>22</v>
       </c>
       <c r="J68" t="n">
-        <v>33.9</v>
+        <v>45.27</v>
       </c>
       <c r="K68" t="n">
-        <v>150.98</v>
+        <v>201.64</v>
       </c>
       <c r="L68" t="n">
-        <v>154.74</v>
+        <v>206.66</v>
       </c>
     </row>
     <row r="69">
@@ -2950,13 +2950,13 @@
         <v>23</v>
       </c>
       <c r="J69" t="n">
-        <v>41.51</v>
+        <v>53.12</v>
       </c>
       <c r="K69" t="n">
-        <v>-237.09</v>
+        <v>-303.46</v>
       </c>
       <c r="L69" t="n">
-        <v>240.7</v>
+        <v>308.07</v>
       </c>
     </row>
     <row r="70">
@@ -2992,13 +2992,13 @@
         <v>23</v>
       </c>
       <c r="J70" t="n">
-        <v>34.62</v>
+        <v>44.01</v>
       </c>
       <c r="K70" t="n">
-        <v>-169.22</v>
+        <v>-215.12</v>
       </c>
       <c r="L70" t="n">
-        <v>172.73</v>
+        <v>219.58</v>
       </c>
     </row>
     <row r="71">
@@ -3034,13 +3034,13 @@
         <v>21</v>
       </c>
       <c r="J71" t="n">
-        <v>-99.3</v>
+        <v>-139.8</v>
       </c>
       <c r="K71" t="n">
-        <v>-190.53</v>
+        <v>-268.25</v>
       </c>
       <c r="L71" t="n">
-        <v>214.86</v>
+        <v>302.5</v>
       </c>
     </row>
     <row r="72">
@@ -3076,13 +3076,13 @@
         <v>23</v>
       </c>
       <c r="J72" t="n">
-        <v>152.24</v>
+        <v>197.33</v>
       </c>
       <c r="K72" t="n">
-        <v>311.88</v>
+        <v>404.24</v>
       </c>
       <c r="L72" t="n">
-        <v>347.05</v>
+        <v>449.83</v>
       </c>
     </row>
     <row r="73">
@@ -3118,13 +3118,13 @@
         <v>20</v>
       </c>
       <c r="J73" t="n">
-        <v>-209.21</v>
+        <v>-302.23</v>
       </c>
       <c r="K73" t="n">
-        <v>-12.64</v>
+        <v>-18.26</v>
       </c>
       <c r="L73" t="n">
-        <v>209.59</v>
+        <v>302.78</v>
       </c>
     </row>
     <row r="74">
@@ -3160,13 +3160,13 @@
         <v>21</v>
       </c>
       <c r="J74" t="n">
-        <v>55.19</v>
+        <v>69.25</v>
       </c>
       <c r="K74" t="n">
-        <v>-20.81</v>
+        <v>-26.11</v>
       </c>
       <c r="L74" t="n">
-        <v>58.99</v>
+        <v>74.01000000000001</v>
       </c>
     </row>
     <row r="75">
@@ -3202,13 +3202,13 @@
         <v>20</v>
       </c>
       <c r="J75" t="n">
-        <v>-31.81</v>
+        <v>-33.99</v>
       </c>
       <c r="K75" t="n">
-        <v>108.69</v>
+        <v>116.11</v>
       </c>
       <c r="L75" t="n">
-        <v>113.25</v>
+        <v>120.98</v>
       </c>
     </row>
     <row r="76">
@@ -3244,13 +3244,13 @@
         <v>22</v>
       </c>
       <c r="J76" t="n">
-        <v>-40.15</v>
+        <v>-43.66</v>
       </c>
       <c r="K76" t="n">
-        <v>92.26000000000001</v>
+        <v>100.32</v>
       </c>
       <c r="L76" t="n">
-        <v>100.62</v>
+        <v>109.41</v>
       </c>
     </row>
     <row r="77">
@@ -3286,13 +3286,13 @@
         <v>24</v>
       </c>
       <c r="J77" t="n">
-        <v>-115.84</v>
+        <v>-122.68</v>
       </c>
       <c r="K77" t="n">
-        <v>-70.34</v>
+        <v>-74.5</v>
       </c>
       <c r="L77" t="n">
-        <v>135.53</v>
+        <v>143.53</v>
       </c>
     </row>
     <row r="78">
@@ -3328,13 +3328,13 @@
         <v>24</v>
       </c>
       <c r="J78" t="n">
-        <v>50.95</v>
+        <v>55.76</v>
       </c>
       <c r="K78" t="n">
-        <v>-113.8</v>
+        <v>-124.56</v>
       </c>
       <c r="L78" t="n">
-        <v>124.69</v>
+        <v>136.47</v>
       </c>
     </row>
     <row r="79">
@@ -3370,13 +3370,13 @@
         <v>24</v>
       </c>
       <c r="J79" t="n">
-        <v>114.12</v>
+        <v>124.78</v>
       </c>
       <c r="K79" t="n">
-        <v>-49.49</v>
+        <v>-54.11</v>
       </c>
       <c r="L79" t="n">
-        <v>124.39</v>
+        <v>136.01</v>
       </c>
     </row>
     <row r="80">
@@ -3412,13 +3412,13 @@
         <v>25</v>
       </c>
       <c r="J80" t="n">
-        <v>84.06999999999999</v>
+        <v>109.89</v>
       </c>
       <c r="K80" t="n">
-        <v>51.32</v>
+        <v>67.08</v>
       </c>
       <c r="L80" t="n">
-        <v>98.5</v>
+        <v>128.74</v>
       </c>
     </row>
     <row r="81">
@@ -3454,13 +3454,13 @@
         <v>23</v>
       </c>
       <c r="J81" t="n">
-        <v>78.48</v>
+        <v>93.31999999999999</v>
       </c>
       <c r="K81" t="n">
-        <v>148.47</v>
+        <v>176.56</v>
       </c>
       <c r="L81" t="n">
-        <v>167.93</v>
+        <v>199.71</v>
       </c>
     </row>
     <row r="82">
@@ -3496,13 +3496,13 @@
         <v>20</v>
       </c>
       <c r="J82" t="n">
-        <v>19.89</v>
+        <v>25.06</v>
       </c>
       <c r="K82" t="n">
-        <v>131.95</v>
+        <v>166.26</v>
       </c>
       <c r="L82" t="n">
-        <v>133.44</v>
+        <v>168.13</v>
       </c>
     </row>
     <row r="83">
@@ -3538,13 +3538,13 @@
         <v>21</v>
       </c>
       <c r="J83" t="n">
-        <v>66.40000000000001</v>
+        <v>89.8</v>
       </c>
       <c r="K83" t="n">
-        <v>-154.36</v>
+        <v>-208.73</v>
       </c>
       <c r="L83" t="n">
-        <v>168.03</v>
+        <v>227.22</v>
       </c>
     </row>
     <row r="84">
@@ -3580,13 +3580,13 @@
         <v>19</v>
       </c>
       <c r="J84" t="n">
-        <v>166.27</v>
+        <v>236.03</v>
       </c>
       <c r="K84" t="n">
-        <v>60.83</v>
+        <v>86.34999999999999</v>
       </c>
       <c r="L84" t="n">
-        <v>177.04</v>
+        <v>251.32</v>
       </c>
     </row>
     <row r="85">
@@ -3622,13 +3622,13 @@
         <v>19</v>
       </c>
       <c r="J85" t="n">
-        <v>155.74</v>
+        <v>208.81</v>
       </c>
       <c r="K85" t="n">
-        <v>145.72</v>
+        <v>195.38</v>
       </c>
       <c r="L85" t="n">
-        <v>213.28</v>
+        <v>285.97</v>
       </c>
     </row>
     <row r="86">
@@ -3664,13 +3664,13 @@
         <v>20</v>
       </c>
       <c r="J86" t="n">
-        <v>264.29</v>
+        <v>371.15</v>
       </c>
       <c r="K86" t="n">
-        <v>-156.02</v>
+        <v>-219.11</v>
       </c>
       <c r="L86" t="n">
-        <v>306.91</v>
+        <v>431</v>
       </c>
     </row>
     <row r="87">
@@ -3706,13 +3706,13 @@
         <v>25</v>
       </c>
       <c r="J87" t="n">
-        <v>5.65</v>
+        <v>8.369999999999999</v>
       </c>
       <c r="K87" t="n">
-        <v>79.61</v>
+        <v>117.93</v>
       </c>
       <c r="L87" t="n">
-        <v>79.81</v>
+        <v>118.23</v>
       </c>
     </row>
     <row r="88">
@@ -3748,13 +3748,13 @@
         <v>25</v>
       </c>
       <c r="J88" t="n">
-        <v>-192.95</v>
+        <v>-265.44</v>
       </c>
       <c r="K88" t="n">
-        <v>-100.48</v>
+        <v>-138.23</v>
       </c>
       <c r="L88" t="n">
-        <v>217.54</v>
+        <v>299.28</v>
       </c>
     </row>
   </sheetData>

--- a/output/2024-10-08.xlsx
+++ b/output/2024-10-08.xlsx
@@ -640,13 +640,13 @@
         <v>23</v>
       </c>
       <c r="J14" t="n">
-        <v>66.51000000000001</v>
+        <v>74.52</v>
       </c>
       <c r="K14" t="n">
-        <v>-35.75</v>
+        <v>-40.05</v>
       </c>
       <c r="L14" t="n">
-        <v>75.51000000000001</v>
+        <v>84.59999999999999</v>
       </c>
     </row>
     <row r="15">
@@ -682,13 +682,13 @@
         <v>23</v>
       </c>
       <c r="J15" t="n">
-        <v>-46.49</v>
+        <v>-57.33</v>
       </c>
       <c r="K15" t="n">
-        <v>63.3</v>
+        <v>78.06</v>
       </c>
       <c r="L15" t="n">
-        <v>78.53</v>
+        <v>96.84999999999999</v>
       </c>
     </row>
     <row r="16">
@@ -724,13 +724,13 @@
         <v>20</v>
       </c>
       <c r="J16" t="n">
-        <v>-42.02</v>
+        <v>-43.12</v>
       </c>
       <c r="K16" t="n">
-        <v>99.15000000000001</v>
+        <v>101.76</v>
       </c>
       <c r="L16" t="n">
-        <v>107.69</v>
+        <v>110.52</v>
       </c>
     </row>
     <row r="17">
@@ -766,13 +766,13 @@
         <v>25</v>
       </c>
       <c r="J17" t="n">
-        <v>-66.06</v>
+        <v>-67.98999999999999</v>
       </c>
       <c r="K17" t="n">
-        <v>66.28</v>
+        <v>68.22</v>
       </c>
       <c r="L17" t="n">
-        <v>93.58</v>
+        <v>96.31999999999999</v>
       </c>
     </row>
     <row r="18">
@@ -808,13 +808,13 @@
         <v>23</v>
       </c>
       <c r="J18" t="n">
-        <v>-58.22</v>
+        <v>-62.68</v>
       </c>
       <c r="K18" t="n">
-        <v>-73.08</v>
+        <v>-78.66</v>
       </c>
       <c r="L18" t="n">
-        <v>93.44</v>
+        <v>100.58</v>
       </c>
     </row>
     <row r="19">
@@ -850,13 +850,13 @@
         <v>19</v>
       </c>
       <c r="J19" t="n">
-        <v>113.03</v>
+        <v>132.48</v>
       </c>
       <c r="K19" t="n">
-        <v>11.63</v>
+        <v>13.63</v>
       </c>
       <c r="L19" t="n">
-        <v>113.63</v>
+        <v>133.17</v>
       </c>
     </row>
     <row r="20">
@@ -1270,13 +1270,13 @@
         <v>24</v>
       </c>
       <c r="J29" t="n">
-        <v>28.69</v>
+        <v>30.71</v>
       </c>
       <c r="K29" t="n">
-        <v>-85.53</v>
+        <v>-91.56999999999999</v>
       </c>
       <c r="L29" t="n">
-        <v>90.22</v>
+        <v>96.59</v>
       </c>
     </row>
     <row r="30">
@@ -1312,13 +1312,13 @@
         <v>20</v>
       </c>
       <c r="J30" t="n">
-        <v>-8.35</v>
+        <v>-10.03</v>
       </c>
       <c r="K30" t="n">
-        <v>95.88</v>
+        <v>115.14</v>
       </c>
       <c r="L30" t="n">
-        <v>96.25</v>
+        <v>115.58</v>
       </c>
     </row>
     <row r="31">
@@ -1354,13 +1354,13 @@
         <v>24</v>
       </c>
       <c r="J31" t="n">
-        <v>24.45</v>
+        <v>27.67</v>
       </c>
       <c r="K31" t="n">
-        <v>-64.52</v>
+        <v>-73.03</v>
       </c>
       <c r="L31" t="n">
-        <v>69</v>
+        <v>78.09</v>
       </c>
     </row>
     <row r="32">
@@ -1396,13 +1396,13 @@
         <v>20</v>
       </c>
       <c r="J32" t="n">
-        <v>-134.85</v>
+        <v>-147.33</v>
       </c>
       <c r="K32" t="n">
-        <v>20.32</v>
+        <v>22.2</v>
       </c>
       <c r="L32" t="n">
-        <v>136.38</v>
+        <v>149</v>
       </c>
     </row>
     <row r="33">
@@ -1438,13 +1438,13 @@
         <v>20</v>
       </c>
       <c r="J33" t="n">
-        <v>49.33</v>
+        <v>60.38</v>
       </c>
       <c r="K33" t="n">
-        <v>-133.2</v>
+        <v>-163.02</v>
       </c>
       <c r="L33" t="n">
-        <v>142.04</v>
+        <v>173.85</v>
       </c>
     </row>
     <row r="34">
@@ -1480,13 +1480,13 @@
         <v>19</v>
       </c>
       <c r="J34" t="n">
-        <v>-63.47</v>
+        <v>-73.23999999999999</v>
       </c>
       <c r="K34" t="n">
-        <v>-68.26000000000001</v>
+        <v>-78.78</v>
       </c>
       <c r="L34" t="n">
-        <v>93.20999999999999</v>
+        <v>107.57</v>
       </c>
     </row>
     <row r="35">
@@ -1900,13 +1900,13 @@
         <v>25</v>
       </c>
       <c r="J44" t="n">
-        <v>-71.90000000000001</v>
+        <v>-85.63</v>
       </c>
       <c r="K44" t="n">
-        <v>-50.8</v>
+        <v>-60.5</v>
       </c>
       <c r="L44" t="n">
-        <v>88.03</v>
+        <v>104.85</v>
       </c>
     </row>
     <row r="45">
@@ -1942,13 +1942,13 @@
         <v>22</v>
       </c>
       <c r="J45" t="n">
-        <v>-39.66</v>
+        <v>-44.18</v>
       </c>
       <c r="K45" t="n">
-        <v>54.94</v>
+        <v>61.19</v>
       </c>
       <c r="L45" t="n">
-        <v>67.76000000000001</v>
+        <v>75.47</v>
       </c>
     </row>
     <row r="46">
@@ -1984,13 +1984,13 @@
         <v>25</v>
       </c>
       <c r="J46" t="n">
-        <v>47.04</v>
+        <v>50.76</v>
       </c>
       <c r="K46" t="n">
-        <v>47.05</v>
+        <v>50.77</v>
       </c>
       <c r="L46" t="n">
-        <v>66.54000000000001</v>
+        <v>71.79000000000001</v>
       </c>
     </row>
     <row r="47">
@@ -2026,13 +2026,13 @@
         <v>19</v>
       </c>
       <c r="J47" t="n">
-        <v>-123.64</v>
+        <v>-136.09</v>
       </c>
       <c r="K47" t="n">
-        <v>-1.98</v>
+        <v>-2.18</v>
       </c>
       <c r="L47" t="n">
-        <v>123.65</v>
+        <v>136.11</v>
       </c>
     </row>
     <row r="48">
@@ -2068,13 +2068,13 @@
         <v>25</v>
       </c>
       <c r="J48" t="n">
-        <v>-88.14</v>
+        <v>-104.75</v>
       </c>
       <c r="K48" t="n">
-        <v>26.21</v>
+        <v>31.15</v>
       </c>
       <c r="L48" t="n">
-        <v>91.95</v>
+        <v>109.28</v>
       </c>
     </row>
     <row r="49">
@@ -2110,13 +2110,13 @@
         <v>23</v>
       </c>
       <c r="J49" t="n">
-        <v>-13.2</v>
+        <v>-14.36</v>
       </c>
       <c r="K49" t="n">
-        <v>119.48</v>
+        <v>129.95</v>
       </c>
       <c r="L49" t="n">
-        <v>120.21</v>
+        <v>130.74</v>
       </c>
     </row>
     <row r="50">
@@ -2530,13 +2530,13 @@
         <v>22</v>
       </c>
       <c r="J59" t="n">
-        <v>94.04000000000001</v>
+        <v>146.62</v>
       </c>
       <c r="K59" t="n">
-        <v>-3.27</v>
+        <v>-5.1</v>
       </c>
       <c r="L59" t="n">
-        <v>94.09999999999999</v>
+        <v>146.71</v>
       </c>
     </row>
     <row r="60">
@@ -2572,13 +2572,13 @@
         <v>20</v>
       </c>
       <c r="J60" t="n">
-        <v>81.51000000000001</v>
+        <v>99.70999999999999</v>
       </c>
       <c r="K60" t="n">
-        <v>72.78</v>
+        <v>89.02</v>
       </c>
       <c r="L60" t="n">
-        <v>109.28</v>
+        <v>133.67</v>
       </c>
     </row>
     <row r="61">
@@ -2614,13 +2614,13 @@
         <v>24</v>
       </c>
       <c r="J61" t="n">
-        <v>-57.96</v>
+        <v>-70.04000000000001</v>
       </c>
       <c r="K61" t="n">
-        <v>-35.35</v>
+        <v>-42.71</v>
       </c>
       <c r="L61" t="n">
-        <v>67.89</v>
+        <v>82.03</v>
       </c>
     </row>
     <row r="62">
@@ -2656,13 +2656,13 @@
         <v>22</v>
       </c>
       <c r="J62" t="n">
-        <v>-95.27</v>
+        <v>-104.71</v>
       </c>
       <c r="K62" t="n">
-        <v>-55.97</v>
+        <v>-61.51</v>
       </c>
       <c r="L62" t="n">
-        <v>110.49</v>
+        <v>121.44</v>
       </c>
     </row>
     <row r="63">
@@ -2698,13 +2698,13 @@
         <v>23</v>
       </c>
       <c r="J63" t="n">
-        <v>-90.22</v>
+        <v>-109.91</v>
       </c>
       <c r="K63" t="n">
-        <v>-30.07</v>
+        <v>-36.64</v>
       </c>
       <c r="L63" t="n">
-        <v>95.09999999999999</v>
+        <v>115.85</v>
       </c>
     </row>
     <row r="64">
@@ -2740,13 +2740,13 @@
         <v>19</v>
       </c>
       <c r="J64" t="n">
-        <v>-29.3</v>
+        <v>-34.45</v>
       </c>
       <c r="K64" t="n">
-        <v>-111.3</v>
+        <v>-130.86</v>
       </c>
       <c r="L64" t="n">
-        <v>115.1</v>
+        <v>135.31</v>
       </c>
     </row>
     <row r="65">
@@ -3160,13 +3160,13 @@
         <v>21</v>
       </c>
       <c r="J74" t="n">
-        <v>69.25</v>
+        <v>84.01000000000001</v>
       </c>
       <c r="K74" t="n">
-        <v>-26.11</v>
+        <v>-31.68</v>
       </c>
       <c r="L74" t="n">
-        <v>74.01000000000001</v>
+        <v>89.79000000000001</v>
       </c>
     </row>
     <row r="75">
@@ -3202,13 +3202,13 @@
         <v>20</v>
       </c>
       <c r="J75" t="n">
-        <v>-33.99</v>
+        <v>-40.73</v>
       </c>
       <c r="K75" t="n">
-        <v>116.11</v>
+        <v>139.15</v>
       </c>
       <c r="L75" t="n">
-        <v>120.98</v>
+        <v>144.99</v>
       </c>
     </row>
     <row r="76">
@@ -3244,13 +3244,13 @@
         <v>22</v>
       </c>
       <c r="J76" t="n">
-        <v>-43.66</v>
+        <v>-52</v>
       </c>
       <c r="K76" t="n">
-        <v>100.32</v>
+        <v>119.49</v>
       </c>
       <c r="L76" t="n">
-        <v>109.41</v>
+        <v>130.31</v>
       </c>
     </row>
     <row r="77">
@@ -3286,13 +3286,13 @@
         <v>24</v>
       </c>
       <c r="J77" t="n">
-        <v>-122.68</v>
+        <v>-133.84</v>
       </c>
       <c r="K77" t="n">
-        <v>-74.5</v>
+        <v>-81.27</v>
       </c>
       <c r="L77" t="n">
-        <v>143.53</v>
+        <v>156.58</v>
       </c>
     </row>
     <row r="78">
@@ -3328,13 +3328,13 @@
         <v>24</v>
       </c>
       <c r="J78" t="n">
-        <v>55.76</v>
+        <v>68.14</v>
       </c>
       <c r="K78" t="n">
-        <v>-124.56</v>
+        <v>-152.22</v>
       </c>
       <c r="L78" t="n">
-        <v>136.47</v>
+        <v>166.77</v>
       </c>
     </row>
     <row r="79">
@@ -3370,13 +3370,13 @@
         <v>24</v>
       </c>
       <c r="J79" t="n">
-        <v>124.78</v>
+        <v>158.24</v>
       </c>
       <c r="K79" t="n">
-        <v>-54.11</v>
+        <v>-68.62</v>
       </c>
       <c r="L79" t="n">
-        <v>136.01</v>
+        <v>172.48</v>
       </c>
     </row>
     <row r="80">
